--- a/data/50001451 - ZITRON COLOMBIA.xlsx
+++ b/data/50001451 - ZITRON COLOMBIA.xlsx
@@ -1963,13 +1963,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46077.65350881944</v>
+        <v>46077.82017548611</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55602336806</v>
+        <v>46092.72269003472</v>
       </c>
       <c r="D4" s="5">
-        <v>46097.369704571756</v>
+        <v>46097.53637123843</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2012,13 +2012,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46077.653509247684</v>
+        <v>46077.820175914356</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55599392361</v>
+        <v>46092.722660590276</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.556023425925</v>
+        <v>46092.72269009259</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2075,13 +2075,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46077.65350954861</v>
+        <v>46077.820176215275</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55599454861</v>
+        <v>46092.72266121527</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55602371528</v>
+        <v>46092.72269038194</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2138,13 +2138,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46077.65350987269</v>
+        <v>46077.82017653935</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55599501157</v>
+        <v>46092.72266167824</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.556023819445</v>
+        <v>46092.722690486116</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -2201,13 +2201,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46077.65351016204</v>
+        <v>46077.8201768287</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.555995532406</v>
+        <v>46092.72266219907</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.603775358795</v>
+        <v>46100.77044202546</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -2264,13 +2264,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46077.65351048611</v>
+        <v>46077.82017715278</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55599620371</v>
+        <v>46092.72266287037</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.55602438658</v>
+        <v>46092.72269105324</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -2327,13 +2327,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46077.65351078704</v>
+        <v>46077.8201774537</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.67309768518</v>
+        <v>46114.839764351855</v>
       </c>
       <c r="D10" s="5">
-        <v>46125.39536578704</v>
+        <v>46125.5620324537</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -2378,13 +2378,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46077.65351107639</v>
+        <v>46077.82017774305</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.37212284722</v>
+        <v>46097.538789513885</v>
       </c>
       <c r="D11" s="8">
-        <v>46107.469534895834</v>
+        <v>46107.636201562505</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -2443,13 +2443,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46077.653511365745</v>
+        <v>46077.82017803241</v>
       </c>
       <c r="C12" s="5">
-        <v>46113.3996452662</v>
+        <v>46113.56631193287</v>
       </c>
       <c r="D12" s="5">
-        <v>46113.3996571875</v>
+        <v>46113.56632385417</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2508,13 +2508,13 @@
         <v>55</v>
       </c>
       <c r="B13" s="8">
-        <v>46107.49398770834</v>
+        <v>46107.660654374995</v>
       </c>
       <c r="C13" s="8">
-        <v>46109.5651262037</v>
+        <v>46109.73179287037</v>
       </c>
       <c r="D13" s="8">
-        <v>46109.5673341088</v>
+        <v>46109.73400077547</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>56</v>
@@ -2563,13 +2563,13 @@
         <v>59</v>
       </c>
       <c r="B14" s="5">
-        <v>46107.49412581019</v>
+        <v>46107.66079247685</v>
       </c>
       <c r="C14" s="5">
-        <v>46109.56514158565</v>
+        <v>46109.73180825231</v>
       </c>
       <c r="D14" s="5">
-        <v>46109.565142962965</v>
+        <v>46109.73180962963</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>60</v>
@@ -2618,13 +2618,13 @@
         <v>62</v>
       </c>
       <c r="B15" s="8">
-        <v>46107.49416398148</v>
+        <v>46107.66083064815</v>
       </c>
       <c r="C15" s="8">
-        <v>46109.56515916667</v>
+        <v>46109.73182583333</v>
       </c>
       <c r="D15" s="8">
-        <v>46109.56516092592</v>
+        <v>46109.73182759259</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>63</v>
@@ -2673,13 +2673,13 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46107.494209826385</v>
+        <v>46107.66087649306</v>
       </c>
       <c r="C16" s="5">
-        <v>46113.39960600695</v>
+        <v>46113.56627267361</v>
       </c>
       <c r="D16" s="5">
-        <v>46113.399607245374</v>
+        <v>46113.56627391204</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2728,13 +2728,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="8">
-        <v>46107.49425076389</v>
+        <v>46107.660917430556</v>
       </c>
       <c r="C17" s="8">
-        <v>46113.39963071759</v>
+        <v>46113.566297384255</v>
       </c>
       <c r="D17" s="8">
-        <v>46113.39963194444</v>
+        <v>46113.56629861111</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>69</v>
@@ -2783,13 +2783,13 @@
         <v>71</v>
       </c>
       <c r="B18" s="5">
-        <v>46077.653511655095</v>
+        <v>46077.82017832176</v>
       </c>
       <c r="C18" s="5">
-        <v>46097.36960097222</v>
+        <v>46097.53626763889</v>
       </c>
       <c r="D18" s="5">
-        <v>46125.39533824074</v>
+        <v>46125.562004907406</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>72</v>
@@ -2832,13 +2832,13 @@
         <v>74</v>
       </c>
       <c r="B19" s="8">
-        <v>46077.65350872686</v>
+        <v>46077.82017539351</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.36843689815</v>
+        <v>46097.53510356482</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.3684552662</v>
+        <v>46097.53512193287</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>75</v>
@@ -2897,13 +2897,13 @@
         <v>77</v>
       </c>
       <c r="B20" s="5">
-        <v>46077.65350956019</v>
+        <v>46077.82017622685</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.36919636574</v>
+        <v>46097.535863032404</v>
       </c>
       <c r="D20" s="5">
-        <v>46100.60651576389</v>
+        <v>46100.77318243055</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>78</v>
@@ -2962,13 +2962,13 @@
         <v>80</v>
       </c>
       <c r="B21" s="8">
-        <v>46077.65350987269</v>
+        <v>46077.82017653935</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.36955335648</v>
+        <v>46097.53622002315</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.36956980324</v>
+        <v>46097.53623646991</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>81</v>
@@ -3027,13 +3027,13 @@
         <v>83</v>
       </c>
       <c r="B22" s="5">
-        <v>46077.65351017361</v>
+        <v>46077.82017684028</v>
       </c>
       <c r="C22" s="5">
-        <v>46097.369580439816</v>
+        <v>46097.53624710648</v>
       </c>
       <c r="D22" s="5">
-        <v>46097.369601597224</v>
+        <v>46097.53626826389</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>84</v>
@@ -3092,13 +3092,13 @@
         <v>86</v>
       </c>
       <c r="B23" s="8">
-        <v>46077.65351047454</v>
+        <v>46077.8201771412</v>
       </c>
       <c r="C23" s="8">
-        <v>46104.461916493055</v>
+        <v>46104.62858315972</v>
       </c>
       <c r="D23" s="8">
-        <v>46112.63144489583</v>
+        <v>46112.7981115625</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>87</v>
@@ -3141,13 +3141,13 @@
         <v>89</v>
       </c>
       <c r="B24" s="5">
-        <v>46077.653511111115</v>
+        <v>46077.82017777778</v>
       </c>
       <c r="C24" s="5">
-        <v>46097.368501053235</v>
+        <v>46097.53516771991</v>
       </c>
       <c r="D24" s="5">
-        <v>46097.36852065972</v>
+        <v>46097.535187326386</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>90</v>
@@ -3206,13 +3206,13 @@
         <v>91</v>
       </c>
       <c r="B25" s="8">
-        <v>46077.65351077546</v>
+        <v>46077.82017744213</v>
       </c>
       <c r="C25" s="8">
-        <v>46097.36854178241</v>
+        <v>46097.53520844907</v>
       </c>
       <c r="D25" s="8">
-        <v>46125.39528435185</v>
+        <v>46125.56195101852</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>92</v>
@@ -3271,13 +3271,13 @@
         <v>94</v>
       </c>
       <c r="B26" s="5">
-        <v>46077.65351142361</v>
+        <v>46077.820178090275</v>
       </c>
       <c r="C26" s="5">
-        <v>46097.37217054398</v>
+        <v>46097.53883721065</v>
       </c>
       <c r="D26" s="5">
-        <v>46112.512462824074</v>
+        <v>46112.679129490745</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>95</v>
@@ -3336,13 +3336,13 @@
         <v>97</v>
       </c>
       <c r="B27" s="8">
-        <v>46077.65351171297</v>
+        <v>46077.820178379625</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.36923239584</v>
+        <v>46097.535899062495</v>
       </c>
       <c r="D27" s="8">
-        <v>46100.60341217593</v>
+        <v>46100.770078842594</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>98</v>
@@ -3401,13 +3401,13 @@
         <v>100</v>
       </c>
       <c r="B28" s="5">
-        <v>46077.65350892361</v>
+        <v>46077.82017559028</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.369854131946</v>
+        <v>46097.53652079861</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.36987444444</v>
+        <v>46097.53654111111</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>101</v>
@@ -3466,13 +3466,13 @@
         <v>104</v>
       </c>
       <c r="B29" s="8">
-        <v>46078.49200716435</v>
+        <v>46078.658673831014</v>
       </c>
       <c r="C29" s="8">
-        <v>46104.46189391204</v>
+        <v>46104.628560578705</v>
       </c>
       <c r="D29" s="8">
-        <v>46104.461917106484</v>
+        <v>46104.62858377315</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>105</v>
@@ -3531,13 +3531,13 @@
         <v>107</v>
       </c>
       <c r="B30" s="5">
-        <v>46078.49209234954</v>
+        <v>46078.65875901621</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.370087766205</v>
+        <v>46097.53675443287</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.37010788194</v>
+        <v>46097.536774548615</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>108</v>
@@ -3596,13 +3596,13 @@
         <v>110</v>
       </c>
       <c r="B31" s="8">
-        <v>46077.65350929398</v>
+        <v>46077.820175960645</v>
       </c>
       <c r="C31" s="8">
-        <v>46112.63125395833</v>
+        <v>46112.797920625</v>
       </c>
       <c r="D31" s="8">
-        <v>46112.63136230324</v>
+        <v>46112.798028969904</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>111</v>
@@ -3645,13 +3645,13 @@
         <v>113</v>
       </c>
       <c r="B32" s="5">
-        <v>46077.65350956019</v>
+        <v>46077.82017622685</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.36866423611</v>
+        <v>46097.53533090278</v>
       </c>
       <c r="D32" s="5">
-        <v>46097.36868027778</v>
+        <v>46097.535346944445</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>114</v>
@@ -3710,13 +3710,13 @@
         <v>118</v>
       </c>
       <c r="B33" s="8">
-        <v>46077.65350983797</v>
+        <v>46077.820176504625</v>
       </c>
       <c r="C33" s="8">
-        <v>46097.36860832176</v>
+        <v>46097.535274988426</v>
       </c>
       <c r="D33" s="8">
-        <v>46097.36860973379</v>
+        <v>46097.535276400464</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>119</v>
@@ -3771,13 +3771,13 @@
         <v>123</v>
       </c>
       <c r="B34" s="5">
-        <v>46077.65351012732</v>
+        <v>46077.82017679398</v>
       </c>
       <c r="C34" s="5">
-        <v>46097.368646250005</v>
+        <v>46097.53531291666</v>
       </c>
       <c r="D34" s="5">
-        <v>46097.368648483796</v>
+        <v>46097.53531515047</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>124</v>
@@ -3832,13 +3832,13 @@
         <v>126</v>
       </c>
       <c r="B35" s="8">
-        <v>46077.65351039352</v>
+        <v>46077.82017706019</v>
       </c>
       <c r="C35" s="8">
-        <v>46097.37301059028</v>
+        <v>46097.539677256944</v>
       </c>
       <c r="D35" s="8">
-        <v>46097.3730234838</v>
+        <v>46097.539690150465</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>127</v>
@@ -3897,13 +3897,13 @@
         <v>129</v>
       </c>
       <c r="B36" s="5">
-        <v>46077.65351063658</v>
+        <v>46077.82017730324</v>
       </c>
       <c r="C36" s="5">
-        <v>46097.372233125</v>
+        <v>46097.53889979167</v>
       </c>
       <c r="D36" s="5">
-        <v>46097.372234525465</v>
+        <v>46097.53890119213</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>130</v>
@@ -3958,13 +3958,13 @@
         <v>132</v>
       </c>
       <c r="B37" s="8">
-        <v>46077.65351089121</v>
+        <v>46077.82017755787</v>
       </c>
       <c r="C37" s="8">
-        <v>46097.37299694444</v>
+        <v>46097.53966361111</v>
       </c>
       <c r="D37" s="8">
-        <v>46097.37299827546</v>
+        <v>46097.53966494213</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>133</v>
@@ -4019,13 +4019,13 @@
         <v>135</v>
       </c>
       <c r="B38" s="5">
-        <v>46077.653511145836</v>
+        <v>46077.8201778125</v>
       </c>
       <c r="C38" s="5">
-        <v>46097.36934012732</v>
+        <v>46097.53600679398</v>
       </c>
       <c r="D38" s="5">
-        <v>46097.36935715278</v>
+        <v>46097.53602381944</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>136</v>
@@ -4084,13 +4084,13 @@
         <v>138</v>
       </c>
       <c r="B39" s="8">
-        <v>46077.65351138889</v>
+        <v>46077.820178055554</v>
       </c>
       <c r="C39" s="8">
-        <v>46097.36928626157</v>
+        <v>46097.53595292824</v>
       </c>
       <c r="D39" s="8">
-        <v>46097.369287395835</v>
+        <v>46097.5359540625</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>139</v>
@@ -4145,13 +4145,13 @@
         <v>141</v>
       </c>
       <c r="B40" s="5">
-        <v>46077.653508877316</v>
+        <v>46077.82017554398</v>
       </c>
       <c r="C40" s="5">
-        <v>46097.369326643515</v>
+        <v>46097.535993310186</v>
       </c>
       <c r="D40" s="5">
-        <v>46097.369328078705</v>
+        <v>46097.53599474537</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>142</v>
@@ -4206,13 +4206,13 @@
         <v>144</v>
       </c>
       <c r="B41" s="8">
-        <v>46077.65350934028</v>
+        <v>46077.82017600695</v>
       </c>
       <c r="C41" s="8">
-        <v>46097.36878138889</v>
+        <v>46097.535448055554</v>
       </c>
       <c r="D41" s="8">
-        <v>46097.368794050926</v>
+        <v>46097.5354607176</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>145</v>
@@ -4271,13 +4271,13 @@
         <v>147</v>
       </c>
       <c r="B42" s="5">
-        <v>46077.65350965278</v>
+        <v>46077.820176319445</v>
       </c>
       <c r="C42" s="5">
-        <v>46097.368692662036</v>
+        <v>46097.5353593287</v>
       </c>
       <c r="D42" s="5">
-        <v>46182.52677819444</v>
+        <v>46182.693444861114</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>148</v>
@@ -4332,13 +4332,13 @@
         <v>151</v>
       </c>
       <c r="B43" s="8">
-        <v>46077.65350996528</v>
+        <v>46077.82017663194</v>
       </c>
       <c r="C43" s="8">
-        <v>46097.368739247686</v>
+        <v>46097.53540591435</v>
       </c>
       <c r="D43" s="8">
-        <v>46097.368740833335</v>
+        <v>46097.5354075</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>152</v>
@@ -4393,13 +4393,13 @@
         <v>154</v>
       </c>
       <c r="B44" s="5">
-        <v>46077.6535102662</v>
+        <v>46077.82017693287</v>
       </c>
       <c r="C44" s="5">
-        <v>46097.3687653588</v>
+        <v>46097.53543202546</v>
       </c>
       <c r="D44" s="5">
-        <v>46097.36876675926</v>
+        <v>46097.535433425925</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>155</v>
@@ -4454,13 +4454,13 @@
         <v>157</v>
       </c>
       <c r="B45" s="8">
-        <v>46077.65351056713</v>
+        <v>46077.82017723379</v>
       </c>
       <c r="C45" s="8">
-        <v>46097.370020138886</v>
+        <v>46097.53668680556</v>
       </c>
       <c r="D45" s="8">
-        <v>46097.3700330787</v>
+        <v>46097.53669974537</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>158</v>
@@ -4519,13 +4519,13 @@
         <v>162</v>
       </c>
       <c r="B46" s="5">
-        <v>46077.653510902775</v>
+        <v>46077.82017756945</v>
       </c>
       <c r="C46" s="5">
-        <v>46097.36994253472</v>
+        <v>46097.53660920139</v>
       </c>
       <c r="D46" s="5">
-        <v>46097.369944108796</v>
+        <v>46097.53661077547</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>163</v>
@@ -4580,13 +4580,13 @@
         <v>165</v>
       </c>
       <c r="B47" s="8">
-        <v>46077.65351120371</v>
+        <v>46077.820177870366</v>
       </c>
       <c r="C47" s="8">
-        <v>46097.37000571759</v>
+        <v>46097.53667238426</v>
       </c>
       <c r="D47" s="8">
-        <v>46097.37000703704</v>
+        <v>46097.536673703704</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>166</v>
@@ -4641,13 +4641,13 @@
         <v>167</v>
       </c>
       <c r="B48" s="5">
-        <v>46078.488932141205</v>
+        <v>46078.65559880787</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.67368665509</v>
+        <v>46107.840353321764</v>
       </c>
       <c r="D48" s="5">
-        <v>46107.67375971065</v>
+        <v>46107.84042637731</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>168</v>
@@ -4706,13 +4706,13 @@
         <v>170</v>
       </c>
       <c r="B49" s="8">
-        <v>46078.48899142361</v>
+        <v>46078.655658090276</v>
       </c>
       <c r="C49" s="8">
-        <v>46107.673577118054</v>
+        <v>46107.840243784725</v>
       </c>
       <c r="D49" s="8">
-        <v>46107.673578773145</v>
+        <v>46107.84024543982</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>171</v>
@@ -4767,13 +4767,13 @@
         <v>173</v>
       </c>
       <c r="B50" s="5">
-        <v>46078.489103368054</v>
+        <v>46078.65577003472</v>
       </c>
       <c r="C50" s="5">
-        <v>46107.67367146991</v>
+        <v>46107.84033813658</v>
       </c>
       <c r="D50" s="5">
-        <v>46107.673672951394</v>
+        <v>46107.84033961805</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>174</v>
@@ -4828,13 +4828,13 @@
         <v>176</v>
       </c>
       <c r="B51" s="8">
-        <v>46078.48757837963</v>
+        <v>46078.654245046295</v>
       </c>
       <c r="C51" s="8">
-        <v>46105.616744212966</v>
+        <v>46105.78341087963</v>
       </c>
       <c r="D51" s="8">
-        <v>46105.61675715278</v>
+        <v>46105.78342381945</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>177</v>
@@ -4893,13 +4893,13 @@
         <v>181</v>
       </c>
       <c r="B52" s="5">
-        <v>46078.487632696764</v>
+        <v>46078.65429936342</v>
       </c>
       <c r="C52" s="5">
-        <v>46097.37018913194</v>
+        <v>46097.53685579861</v>
       </c>
       <c r="D52" s="5">
-        <v>46111.48887483796</v>
+        <v>46111.65554150463</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>182</v>
@@ -4954,13 +4954,13 @@
         <v>184</v>
       </c>
       <c r="B53" s="8">
-        <v>46078.488023275466</v>
+        <v>46078.65468994213</v>
       </c>
       <c r="C53" s="8">
-        <v>46105.61672585648</v>
+        <v>46105.78339252315</v>
       </c>
       <c r="D53" s="8">
-        <v>46105.616727395834</v>
+        <v>46105.7833940625</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>185</v>
@@ -5015,13 +5015,13 @@
         <v>188</v>
       </c>
       <c r="B54" s="5">
-        <v>46104.46379498843</v>
+        <v>46104.63046165509</v>
       </c>
       <c r="C54" s="5">
-        <v>46105.58714668981</v>
+        <v>46105.75381335648</v>
       </c>
       <c r="D54" s="5">
-        <v>46107.51235769676</v>
+        <v>46107.67902436343</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>189</v>
@@ -5070,13 +5070,13 @@
         <v>190</v>
       </c>
       <c r="B55" s="8">
-        <v>46104.46460832176</v>
+        <v>46104.631274988424</v>
       </c>
       <c r="C55" s="8">
-        <v>46104.48089810185</v>
+        <v>46104.647564768515</v>
       </c>
       <c r="D55" s="8">
-        <v>46107.512552361106</v>
+        <v>46107.67921902778</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>191</v>
@@ -5125,13 +5125,13 @@
         <v>192</v>
       </c>
       <c r="B56" s="5">
-        <v>46104.465005011574</v>
+        <v>46104.631671678246</v>
       </c>
       <c r="C56" s="5">
-        <v>46104.480031886575</v>
+        <v>46104.646698553246</v>
       </c>
       <c r="D56" s="5">
-        <v>46107.512663877314</v>
+        <v>46107.67933054398</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>193</v>
@@ -5180,13 +5180,13 @@
         <v>194</v>
       </c>
       <c r="B57" s="8">
-        <v>46104.46529033565</v>
+        <v>46104.63195700232</v>
       </c>
       <c r="C57" s="8">
-        <v>46104.47969530092</v>
+        <v>46104.64636196759</v>
       </c>
       <c r="D57" s="8">
-        <v>46107.51277224537</v>
+        <v>46107.67943891203</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>195</v>
@@ -5235,13 +5235,13 @@
         <v>196</v>
       </c>
       <c r="B58" s="5">
-        <v>46104.46541815972</v>
+        <v>46104.632084826386</v>
       </c>
       <c r="C58" s="5">
-        <v>46104.47900508102</v>
+        <v>46104.64567174768</v>
       </c>
       <c r="D58" s="5">
-        <v>46107.51318376158</v>
+        <v>46107.67985042824</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>197</v>
@@ -5290,13 +5290,13 @@
         <v>198</v>
       </c>
       <c r="B59" s="8">
-        <v>46104.46560704861</v>
+        <v>46104.63227371528</v>
       </c>
       <c r="C59" s="8">
-        <v>46104.478267708335</v>
+        <v>46104.644934375</v>
       </c>
       <c r="D59" s="8">
-        <v>46107.512891921295</v>
+        <v>46107.67955858796</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>199</v>
@@ -5345,13 +5345,13 @@
         <v>200</v>
       </c>
       <c r="B60" s="5">
-        <v>46077.65351149306</v>
+        <v>46077.82017815972</v>
       </c>
       <c r="C60" s="5">
-        <v>46114.60105153936</v>
+        <v>46114.767718206014</v>
       </c>
       <c r="D60" s="5">
-        <v>46114.682059224535</v>
+        <v>46114.84872589121</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>201</v>
@@ -5396,13 +5396,13 @@
         <v>203</v>
       </c>
       <c r="B61" s="8">
-        <v>46077.65351179398</v>
+        <v>46077.82017846065</v>
       </c>
       <c r="C61" s="8">
-        <v>46097.37042160879</v>
+        <v>46097.537088275465</v>
       </c>
       <c r="D61" s="8">
-        <v>46097.370440046296</v>
+        <v>46097.53710671296</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>204</v>
@@ -5461,13 +5461,13 @@
         <v>208</v>
       </c>
       <c r="B62" s="5">
-        <v>46077.65350959491</v>
+        <v>46077.82017626158</v>
       </c>
       <c r="C62" s="5">
-        <v>46097.3704739699</v>
+        <v>46097.537140636574</v>
       </c>
       <c r="D62" s="5">
-        <v>46097.37049597222</v>
+        <v>46097.53716263889</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>209</v>
@@ -5526,13 +5526,13 @@
         <v>212</v>
       </c>
       <c r="B63" s="8">
-        <v>46090.71305146991</v>
+        <v>46090.87971813657</v>
       </c>
       <c r="C63" s="8">
-        <v>46097.370544652775</v>
+        <v>46097.537211319446</v>
       </c>
       <c r="D63" s="8">
-        <v>46114.48416702547</v>
+        <v>46114.650833692125</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>213</v>
@@ -5589,13 +5589,13 @@
         <v>215</v>
       </c>
       <c r="B64" s="5">
-        <v>46090.71317484954</v>
+        <v>46090.8798415162</v>
       </c>
       <c r="C64" s="5">
-        <v>46114.601034293984</v>
+        <v>46114.76770096065</v>
       </c>
       <c r="D64" s="5">
-        <v>46119.61215399306</v>
+        <v>46119.77882065972</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>216</v>
@@ -5654,13 +5654,13 @@
         <v>220</v>
       </c>
       <c r="B65" s="8">
-        <v>46107.43952543981</v>
+        <v>46107.60619210648</v>
       </c>
       <c r="C65" s="8">
-        <v>46114.62188774305</v>
+        <v>46114.78855440972</v>
       </c>
       <c r="D65" s="8">
-        <v>46114.621889201386</v>
+        <v>46114.78855586806</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>221</v>
@@ -5707,13 +5707,13 @@
         <v>223</v>
       </c>
       <c r="B66" s="5">
-        <v>46107.439735775464</v>
+        <v>46107.60640244213</v>
       </c>
       <c r="C66" s="5">
-        <v>46114.62191454861</v>
+        <v>46114.78858121528</v>
       </c>
       <c r="D66" s="5">
-        <v>46114.62191614583</v>
+        <v>46114.7885828125</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>224</v>
@@ -5760,13 +5760,13 @@
         <v>225</v>
       </c>
       <c r="B67" s="8">
-        <v>46107.43976915509</v>
+        <v>46107.606435821755</v>
       </c>
       <c r="C67" s="8">
-        <v>46108.49240393519</v>
+        <v>46108.65907060185</v>
       </c>
       <c r="D67" s="8">
-        <v>46114.68165832176</v>
+        <v>46114.84832498843</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>226</v>
@@ -5813,13 +5813,13 @@
         <v>228</v>
       </c>
       <c r="B68" s="5">
-        <v>46107.439817199076</v>
+        <v>46107.60648386574</v>
       </c>
       <c r="C68" s="5">
-        <v>46108.49242011574</v>
+        <v>46108.65908678241</v>
       </c>
       <c r="D68" s="5">
-        <v>46114.6818049537</v>
+        <v>46114.84847162037</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>229</v>
@@ -5866,13 +5866,13 @@
         <v>230</v>
       </c>
       <c r="B69" s="8">
-        <v>46078.48723896991</v>
+        <v>46078.65390563657</v>
       </c>
       <c r="C69" s="8">
-        <v>46105.68957541666</v>
+        <v>46105.85624208333</v>
       </c>
       <c r="D69" s="8">
-        <v>46107.52070784722</v>
+        <v>46107.68737451389</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>231</v>
@@ -5919,13 +5919,13 @@
         <v>234</v>
       </c>
       <c r="B70" s="5">
-        <v>46078.53589244213</v>
+        <v>46078.702559108795</v>
       </c>
       <c r="C70" s="5">
-        <v>46105.68955804398</v>
+        <v>46105.856224710646</v>
       </c>
       <c r="D70" s="5">
-        <v>46107.67383010416</v>
+        <v>46107.840496770834</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>232</v>
@@ -5984,13 +5984,13 @@
         <v>239</v>
       </c>
       <c r="B71" s="8">
-        <v>46077.65351230324</v>
+        <v>46077.82017896991</v>
       </c>
       <c r="C71" s="8">
-        <v>46107.67721232639</v>
+        <v>46107.84387899305</v>
       </c>
       <c r="D71" s="8">
-        <v>46107.67722675926</v>
+        <v>46107.843893425925</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>240</v>
@@ -6037,13 +6037,13 @@
         <v>242</v>
       </c>
       <c r="B72" s="5">
-        <v>46077.65351263889</v>
+        <v>46077.820179305556</v>
       </c>
       <c r="C72" s="5">
-        <v>46107.67567266204</v>
+        <v>46107.84233932871</v>
       </c>
       <c r="D72" s="5">
-        <v>46107.67568759259</v>
+        <v>46107.842354259265</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>243</v>
@@ -6102,13 +6102,13 @@
         <v>247</v>
       </c>
       <c r="B73" s="8">
-        <v>46077.65351076389</v>
+        <v>46077.820177430556</v>
       </c>
       <c r="C73" s="8">
-        <v>46107.67719534722</v>
+        <v>46107.84386201389</v>
       </c>
       <c r="D73" s="8">
-        <v>46107.67721335648</v>
+        <v>46107.84388002315</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>57</v>
@@ -6167,13 +6167,13 @@
         <v>249</v>
       </c>
       <c r="B74" s="5">
-        <v>46077.65351128472</v>
+        <v>46077.82017795139</v>
       </c>
       <c r="C74" s="5">
-        <v>46107.67525778935</v>
+        <v>46107.84192445602</v>
       </c>
       <c r="D74" s="5">
-        <v>46107.67527457176</v>
+        <v>46107.841941238425</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>250</v>
@@ -6232,13 +6232,13 @@
         <v>252</v>
       </c>
       <c r="B75" s="8">
-        <v>46077.65351174769</v>
+        <v>46077.82017841435</v>
       </c>
       <c r="C75" s="8">
-        <v>46107.67515953704</v>
+        <v>46107.8418262037</v>
       </c>
       <c r="D75" s="8">
-        <v>46107.675177708334</v>
+        <v>46107.841844375</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>253</v>
@@ -6297,13 +6297,13 @@
         <v>254</v>
       </c>
       <c r="B76" s="5">
-        <v>46078.49225604167</v>
+        <v>46078.65892270833</v>
       </c>
       <c r="C76" s="5">
-        <v>46107.676195196764</v>
+        <v>46107.84286186342</v>
       </c>
       <c r="D76" s="5">
-        <v>46107.67621280093</v>
+        <v>46107.84287946759</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>255</v>
@@ -6362,13 +6362,13 @@
         <v>256</v>
       </c>
       <c r="B77" s="8">
-        <v>46078.49233570602</v>
+        <v>46078.65900237269</v>
       </c>
       <c r="C77" s="8">
-        <v>46107.675708993054</v>
+        <v>46107.84237565972</v>
       </c>
       <c r="D77" s="8">
-        <v>46107.67572636574</v>
+        <v>46107.842393032406</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>257</v>
@@ -6427,13 +6427,13 @@
         <v>258</v>
       </c>
       <c r="B78" s="5">
-        <v>46077.65351240741</v>
+        <v>46077.82017907407</v>
       </c>
       <c r="C78" s="5">
-        <v>46118.6844856713</v>
+        <v>46118.851152337964</v>
       </c>
       <c r="D78" s="5">
-        <v>46125.39512971065</v>
+        <v>46125.56179637731</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>259</v>
@@ -6478,13 +6478,13 @@
         <v>261</v>
       </c>
       <c r="B79" s="8">
-        <v>46077.65351276621</v>
+        <v>46077.82017943287</v>
       </c>
       <c r="C79" s="8">
-        <v>46113.39128444444</v>
+        <v>46113.557951111114</v>
       </c>
       <c r="D79" s="8">
-        <v>46114.68664321759</v>
+        <v>46114.85330988426</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>262</v>
@@ -6543,13 +6543,13 @@
         <v>264</v>
       </c>
       <c r="B80" s="5">
-        <v>46107.429962152775</v>
+        <v>46107.59662881945</v>
       </c>
       <c r="C80" s="5">
-        <v>46113.39093767361</v>
+        <v>46113.557604340276</v>
       </c>
       <c r="D80" s="5">
-        <v>46114.689403067125</v>
+        <v>46114.856069733796</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>222</v>
@@ -6598,13 +6598,13 @@
         <v>266</v>
       </c>
       <c r="B81" s="8">
-        <v>46107.431094583335</v>
+        <v>46107.59776125</v>
       </c>
       <c r="C81" s="8">
-        <v>46113.39095212963</v>
+        <v>46113.5576187963</v>
       </c>
       <c r="D81" s="8">
-        <v>46114.68945225695</v>
+        <v>46114.856118923606</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>222</v>
@@ -6653,13 +6653,13 @@
         <v>267</v>
       </c>
       <c r="B82" s="5">
-        <v>46107.43050732639</v>
+        <v>46107.597173993054</v>
       </c>
       <c r="C82" s="5">
-        <v>46107.67206599537</v>
+        <v>46107.838732662036</v>
       </c>
       <c r="D82" s="5">
-        <v>46107.672067673615</v>
+        <v>46107.83873434028</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>226</v>
@@ -6708,13 +6708,13 @@
         <v>269</v>
       </c>
       <c r="B83" s="8">
-        <v>46107.43079521991</v>
+        <v>46107.59746188657</v>
       </c>
       <c r="C83" s="8">
-        <v>46107.67207206019</v>
+        <v>46107.83873872685</v>
       </c>
       <c r="D83" s="8">
-        <v>46107.672073842594</v>
+        <v>46107.83874050926</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>229</v>
@@ -6763,13 +6763,13 @@
         <v>271</v>
       </c>
       <c r="B84" s="5">
-        <v>46077.653513136574</v>
+        <v>46077.82017980324</v>
       </c>
       <c r="C84" s="5">
-        <v>46113.39102497685</v>
+        <v>46113.557691643524</v>
       </c>
       <c r="D84" s="5">
-        <v>46125.395162615736</v>
+        <v>46125.56182928241</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>272</v>
@@ -6828,13 +6828,13 @@
         <v>275</v>
       </c>
       <c r="B85" s="8">
-        <v>46107.433116099535</v>
+        <v>46107.59978276621</v>
       </c>
       <c r="C85" s="8">
-        <v>46113.39158454861</v>
+        <v>46113.558251215276</v>
       </c>
       <c r="D85" s="8">
-        <v>46114.68904462963</v>
+        <v>46114.855711296295</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>222</v>
@@ -6883,13 +6883,13 @@
         <v>278</v>
       </c>
       <c r="B86" s="5">
-        <v>46107.433155763894</v>
+        <v>46107.59982243055</v>
       </c>
       <c r="C86" s="5">
-        <v>46113.3915975</v>
+        <v>46113.55826416667</v>
       </c>
       <c r="D86" s="5">
-        <v>46114.68909915509</v>
+        <v>46114.85576582176</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>222</v>
@@ -6938,13 +6938,13 @@
         <v>279</v>
       </c>
       <c r="B87" s="8">
-        <v>46107.43319819444</v>
+        <v>46107.59986486111</v>
       </c>
       <c r="C87" s="8">
-        <v>46107.68172623843</v>
+        <v>46107.84839290509</v>
       </c>
       <c r="D87" s="8">
-        <v>46107.68172790509</v>
+        <v>46107.84839457176</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>226</v>
@@ -6993,13 +6993,13 @@
         <v>282</v>
       </c>
       <c r="B88" s="5">
-        <v>46107.43324458333</v>
+        <v>46107.59991125</v>
       </c>
       <c r="C88" s="5">
-        <v>46107.68171991898</v>
+        <v>46107.84838658565</v>
       </c>
       <c r="D88" s="5">
-        <v>46107.68172150463</v>
+        <v>46107.8483881713</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>229</v>
@@ -7048,13 +7048,13 @@
         <v>285</v>
       </c>
       <c r="B89" s="8">
-        <v>46077.65351359954</v>
+        <v>46077.82018026621</v>
       </c>
       <c r="C89" s="8">
-        <v>46113.39107770834</v>
+        <v>46113.557744375</v>
       </c>
       <c r="D89" s="8">
-        <v>46125.395179432875</v>
+        <v>46125.56184609953</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>286</v>
@@ -7113,13 +7113,13 @@
         <v>288</v>
       </c>
       <c r="B90" s="5">
-        <v>46107.433287962966</v>
+        <v>46107.59995462963</v>
       </c>
       <c r="C90" s="5">
-        <v>46113.391681747686</v>
+        <v>46113.55834841436</v>
       </c>
       <c r="D90" s="5">
-        <v>46114.68927886574</v>
+        <v>46114.85594553241</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>289</v>
@@ -7168,13 +7168,13 @@
         <v>292</v>
       </c>
       <c r="B91" s="8">
-        <v>46107.433360069444</v>
+        <v>46107.60002673611</v>
       </c>
       <c r="C91" s="8">
-        <v>46113.39169880787</v>
+        <v>46113.55836547454</v>
       </c>
       <c r="D91" s="8">
-        <v>46114.689099490744</v>
+        <v>46114.85576615741</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>289</v>
@@ -7223,13 +7223,13 @@
         <v>294</v>
       </c>
       <c r="B92" s="5">
-        <v>46107.433403159725</v>
+        <v>46107.60006982639</v>
       </c>
       <c r="C92" s="5">
-        <v>46107.68177224537</v>
+        <v>46107.84843891204</v>
       </c>
       <c r="D92" s="5">
-        <v>46107.68177365741</v>
+        <v>46107.84844032407</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>226</v>
@@ -7278,13 +7278,13 @@
         <v>297</v>
       </c>
       <c r="B93" s="8">
-        <v>46107.43343826389</v>
+        <v>46107.600104930556</v>
       </c>
       <c r="C93" s="8">
-        <v>46107.68176678241</v>
+        <v>46107.84843344908</v>
       </c>
       <c r="D93" s="8">
-        <v>46107.681768587965</v>
+        <v>46107.84843525463</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>229</v>
@@ -7333,13 +7333,13 @@
         <v>300</v>
       </c>
       <c r="B94" s="5">
-        <v>46077.65351396991</v>
+        <v>46077.82018063657</v>
       </c>
       <c r="C94" s="5">
-        <v>46113.39114666666</v>
+        <v>46113.55781333333</v>
       </c>
       <c r="D94" s="5">
-        <v>46125.39520136574</v>
+        <v>46125.56186803241</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>301</v>
@@ -7398,13 +7398,13 @@
         <v>302</v>
       </c>
       <c r="B95" s="8">
-        <v>46107.434553125</v>
+        <v>46107.60121979167</v>
       </c>
       <c r="C95" s="8">
-        <v>46113.391739212966</v>
+        <v>46113.55840587963</v>
       </c>
       <c r="D95" s="8">
-        <v>46114.68386609954</v>
+        <v>46114.8505327662</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>222</v>
@@ -7453,13 +7453,13 @@
         <v>305</v>
       </c>
       <c r="B96" s="5">
-        <v>46107.43462958334</v>
+        <v>46107.601296249995</v>
       </c>
       <c r="C96" s="5">
-        <v>46113.3917533912</v>
+        <v>46113.558420057874</v>
       </c>
       <c r="D96" s="5">
-        <v>46114.68410795139</v>
+        <v>46114.850774618055</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>222</v>
@@ -7508,13 +7508,13 @@
         <v>307</v>
       </c>
       <c r="B97" s="8">
-        <v>46107.43467732639</v>
+        <v>46107.601343993054</v>
       </c>
       <c r="C97" s="8">
-        <v>46107.68184967592</v>
+        <v>46107.848516342594</v>
       </c>
       <c r="D97" s="8">
-        <v>46107.681851284724</v>
+        <v>46107.84851795139</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>226</v>
@@ -7563,13 +7563,13 @@
         <v>310</v>
       </c>
       <c r="B98" s="5">
-        <v>46107.434719675926</v>
+        <v>46107.60138634259</v>
       </c>
       <c r="C98" s="5">
-        <v>46107.68184467593</v>
+        <v>46107.84851134259</v>
       </c>
       <c r="D98" s="5">
-        <v>46107.68184670139</v>
+        <v>46107.84851336805</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>229</v>
@@ -7618,13 +7618,13 @@
         <v>313</v>
       </c>
       <c r="B99" s="8">
-        <v>46078.492548043985</v>
+        <v>46078.65921471065</v>
       </c>
       <c r="C99" s="8">
-        <v>46114.47800960648</v>
+        <v>46114.64467627315</v>
       </c>
       <c r="D99" s="8">
-        <v>46114.484171331016</v>
+        <v>46114.65083799769</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>314</v>
@@ -7683,13 +7683,13 @@
         <v>316</v>
       </c>
       <c r="B100" s="5">
-        <v>46107.43478660879</v>
+        <v>46107.60145327546</v>
       </c>
       <c r="C100" s="5">
-        <v>46114.47798848379</v>
+        <v>46114.64465515046</v>
       </c>
       <c r="D100" s="5">
-        <v>46114.683211145835</v>
+        <v>46114.8498778125</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>222</v>
@@ -7738,13 +7738,13 @@
         <v>318</v>
       </c>
       <c r="B101" s="8">
-        <v>46107.43485856481</v>
+        <v>46107.60152523148</v>
       </c>
       <c r="C101" s="8">
-        <v>46114.47799614583</v>
+        <v>46114.6446628125</v>
       </c>
       <c r="D101" s="8">
-        <v>46114.683343171295</v>
+        <v>46114.85000983796</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>222</v>
@@ -7793,13 +7793,13 @@
         <v>320</v>
       </c>
       <c r="B102" s="5">
-        <v>46107.43489554398</v>
+        <v>46107.60156221065</v>
       </c>
       <c r="C102" s="5">
-        <v>46107.68189892361</v>
+        <v>46107.84856559028</v>
       </c>
       <c r="D102" s="5">
-        <v>46107.68190063657</v>
+        <v>46107.84856730324</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>226</v>
@@ -7848,13 +7848,13 @@
         <v>322</v>
       </c>
       <c r="B103" s="8">
-        <v>46107.43494063657</v>
+        <v>46107.60160730324</v>
       </c>
       <c r="C103" s="8">
-        <v>46107.68189209491</v>
+        <v>46107.84855876157</v>
       </c>
       <c r="D103" s="8">
-        <v>46107.681893726854</v>
+        <v>46107.84856039352</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>229</v>
@@ -7903,13 +7903,13 @@
         <v>324</v>
       </c>
       <c r="B104" s="5">
-        <v>46077.653514363425</v>
+        <v>46077.820181030096</v>
       </c>
       <c r="C104" s="5">
-        <v>46114.47811685185</v>
+        <v>46114.64478351852</v>
       </c>
       <c r="D104" s="5">
-        <v>46125.395225775464</v>
+        <v>46125.56189244213</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>325</v>
@@ -7968,13 +7968,13 @@
         <v>328</v>
       </c>
       <c r="B105" s="8">
-        <v>46107.435016828706</v>
+        <v>46107.60168349537</v>
       </c>
       <c r="C105" s="8">
-        <v>46114.4780957176</v>
+        <v>46114.644762384254</v>
       </c>
       <c r="D105" s="8">
-        <v>46114.68904494213</v>
+        <v>46114.8557116088</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>222</v>
@@ -8021,13 +8021,13 @@
         <v>330</v>
       </c>
       <c r="B106" s="5">
-        <v>46107.43508928241</v>
+        <v>46107.60175594907</v>
       </c>
       <c r="C106" s="5">
-        <v>46114.47810065972</v>
+        <v>46114.64476732639</v>
       </c>
       <c r="D106" s="5">
-        <v>46114.68909969907</v>
+        <v>46114.85576636574</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>222</v>
@@ -8074,13 +8074,13 @@
         <v>331</v>
       </c>
       <c r="B107" s="8">
-        <v>46107.43512337963</v>
+        <v>46107.6017900463</v>
       </c>
       <c r="C107" s="8">
-        <v>46107.6819471412</v>
+        <v>46107.84861380787</v>
       </c>
       <c r="D107" s="8">
-        <v>46114.680651574075</v>
+        <v>46114.84731824074</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>226</v>
@@ -8129,13 +8129,13 @@
         <v>333</v>
       </c>
       <c r="B108" s="5">
-        <v>46107.43515822917</v>
+        <v>46107.60182489583</v>
       </c>
       <c r="C108" s="5">
-        <v>46107.68194172454</v>
+        <v>46107.8486083912</v>
       </c>
       <c r="D108" s="5">
-        <v>46114.68076538194</v>
+        <v>46114.84743204861</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>229</v>
@@ -8184,13 +8184,13 @@
         <v>335</v>
       </c>
       <c r="B109" s="8">
-        <v>46077.653514756945</v>
+        <v>46077.82018142361</v>
       </c>
       <c r="C109" s="8">
-        <v>46118.68446939815</v>
+        <v>46118.85113606481</v>
       </c>
       <c r="D109" s="8">
-        <v>46118.694731550924</v>
+        <v>46118.86139821759</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>336</v>
@@ -8249,13 +8249,13 @@
         <v>337</v>
       </c>
       <c r="B110" s="5">
-        <v>46107.43520423611</v>
+        <v>46107.60187090278</v>
       </c>
       <c r="C110" s="5">
-        <v>46114.685311967594</v>
+        <v>46114.85197863426</v>
       </c>
       <c r="D110" s="5">
-        <v>46114.68531369213</v>
+        <v>46114.8519803588</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>222</v>
@@ -8302,13 +8302,13 @@
         <v>339</v>
       </c>
       <c r="B111" s="8">
-        <v>46107.4352709838</v>
+        <v>46107.60193765046</v>
       </c>
       <c r="C111" s="8">
-        <v>46118.6843984838</v>
+        <v>46118.85106515046</v>
       </c>
       <c r="D111" s="8">
-        <v>46118.69489804398</v>
+        <v>46118.86156471065</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>222</v>
@@ -8355,13 +8355,13 @@
         <v>340</v>
       </c>
       <c r="B112" s="5">
-        <v>46107.43531439815</v>
+        <v>46107.601981064814</v>
       </c>
       <c r="C112" s="5">
-        <v>46108.49721596065</v>
+        <v>46108.66388262731</v>
       </c>
       <c r="D112" s="5">
-        <v>46114.68252231482</v>
+        <v>46114.84918898148</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>226</v>
@@ -8408,13 +8408,13 @@
         <v>342</v>
       </c>
       <c r="B113" s="8">
-        <v>46107.43534848379</v>
+        <v>46107.60201515046</v>
       </c>
       <c r="C113" s="8">
-        <v>46108.49722452546</v>
+        <v>46108.66389119213</v>
       </c>
       <c r="D113" s="8">
-        <v>46114.68260300926</v>
+        <v>46114.84926967593</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>229</v>
@@ -8463,13 +8463,13 @@
         <v>344</v>
       </c>
       <c r="B114" s="5">
-        <v>46077.65350886574</v>
+        <v>46077.82017553241</v>
       </c>
       <c r="C114" s="5">
-        <v>46125.39424491898</v>
+        <v>46125.56091158565</v>
       </c>
       <c r="D114" s="5">
-        <v>46125.39504523148</v>
+        <v>46125.561711898146</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>345</v>
@@ -8512,13 +8512,13 @@
         <v>347</v>
       </c>
       <c r="B115" s="8">
-        <v>46077.65350920139</v>
+        <v>46077.82017586805</v>
       </c>
       <c r="C115" s="8">
-        <v>46121.67337837963</v>
+        <v>46121.840045046294</v>
       </c>
       <c r="D115" s="8">
-        <v>46121.67339505787</v>
+        <v>46121.840061724535</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>348</v>
@@ -8577,13 +8577,13 @@
         <v>352</v>
       </c>
       <c r="B116" s="5">
-        <v>46107.435515474535</v>
+        <v>46107.6021821412</v>
       </c>
       <c r="C116" s="5">
-        <v>46121.67334778935</v>
+        <v>46121.840014456015</v>
       </c>
       <c r="D116" s="5">
-        <v>46121.673349930556</v>
+        <v>46121.84001659723</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>222</v>
@@ -8630,13 +8630,13 @@
         <v>354</v>
       </c>
       <c r="B117" s="8">
-        <v>46107.43555876157</v>
+        <v>46107.60222542824</v>
       </c>
       <c r="C117" s="8">
-        <v>46121.67335912037</v>
+        <v>46121.84002578704</v>
       </c>
       <c r="D117" s="8">
-        <v>46121.673360706016</v>
+        <v>46121.84002737269</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>222</v>
@@ -8683,13 +8683,13 @@
         <v>355</v>
       </c>
       <c r="B118" s="5">
-        <v>46107.43558870371</v>
+        <v>46107.602255370366</v>
       </c>
       <c r="C118" s="5">
-        <v>46108.49733738426</v>
+        <v>46108.66400405092</v>
       </c>
       <c r="D118" s="5">
-        <v>46114.69284753472</v>
+        <v>46114.85951420139</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>226</v>
@@ -8738,13 +8738,13 @@
         <v>357</v>
       </c>
       <c r="B119" s="8">
-        <v>46107.43562164352</v>
+        <v>46107.60228831018</v>
       </c>
       <c r="C119" s="8">
-        <v>46108.49736246528</v>
+        <v>46108.66402913195</v>
       </c>
       <c r="D119" s="8">
-        <v>46114.69290731481</v>
+        <v>46114.85957398148</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>229</v>
@@ -8791,13 +8791,13 @@
         <v>359</v>
       </c>
       <c r="B120" s="5">
-        <v>46107.46985704861</v>
+        <v>46107.63652371528</v>
       </c>
       <c r="C120" s="5">
-        <v>46109.56785152778</v>
+        <v>46109.73451819444</v>
       </c>
       <c r="D120" s="5">
-        <v>46109.56785303241</v>
+        <v>46109.73451969908</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>56</v>
@@ -8844,13 +8844,13 @@
         <v>361</v>
       </c>
       <c r="B121" s="8">
-        <v>46107.469900763885</v>
+        <v>46107.636567430556</v>
       </c>
       <c r="C121" s="8">
-        <v>46109.56543170139</v>
+        <v>46109.732098368055</v>
       </c>
       <c r="D121" s="8">
-        <v>46109.56543320602</v>
+        <v>46109.73209987269</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>60</v>
@@ -8897,13 +8897,13 @@
         <v>363</v>
       </c>
       <c r="B122" s="5">
-        <v>46107.46993355324</v>
+        <v>46107.63660021991</v>
       </c>
       <c r="C122" s="5">
-        <v>46109.56547548611</v>
+        <v>46109.732142152774</v>
       </c>
       <c r="D122" s="5">
-        <v>46109.56547681713</v>
+        <v>46109.732143483794</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>63</v>
@@ -8950,13 +8950,13 @@
         <v>365</v>
       </c>
       <c r="B123" s="8">
-        <v>46107.46997388889</v>
+        <v>46107.63664055556</v>
       </c>
       <c r="C123" s="8">
-        <v>46113.39993212963</v>
+        <v>46113.5665987963</v>
       </c>
       <c r="D123" s="8">
-        <v>46113.399933622684</v>
+        <v>46113.566600289356</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>66</v>
@@ -9003,13 +9003,13 @@
         <v>367</v>
       </c>
       <c r="B124" s="5">
-        <v>46107.470011550926</v>
+        <v>46107.63667821759</v>
       </c>
       <c r="C124" s="5">
-        <v>46113.39994310185</v>
+        <v>46113.56660976852</v>
       </c>
       <c r="D124" s="5">
-        <v>46113.39994459491</v>
+        <v>46113.56661126157</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>69</v>
@@ -9056,13 +9056,13 @@
         <v>369</v>
       </c>
       <c r="B125" s="8">
-        <v>46077.653509490745</v>
+        <v>46077.82017615741</v>
       </c>
       <c r="C125" s="8">
-        <v>46122.4457921875</v>
+        <v>46122.61245885417</v>
       </c>
       <c r="D125" s="8">
-        <v>46126.00348665509</v>
+        <v>46126.17015332176</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>370</v>
@@ -9121,13 +9121,13 @@
         <v>372</v>
       </c>
       <c r="B126" s="5">
-        <v>46107.435665509256</v>
+        <v>46107.60233217593</v>
       </c>
       <c r="C126" s="5">
-        <v>46122.44576736111</v>
+        <v>46122.612434027775</v>
       </c>
       <c r="D126" s="5">
-        <v>46122.44576905093</v>
+        <v>46122.612435717594</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>222</v>
@@ -9176,13 +9176,13 @@
         <v>374</v>
       </c>
       <c r="B127" s="8">
-        <v>46107.43573319445</v>
+        <v>46107.60239986111</v>
       </c>
       <c r="C127" s="8">
-        <v>46122.445778657406</v>
+        <v>46122.61244532408</v>
       </c>
       <c r="D127" s="8">
-        <v>46122.44578006944</v>
+        <v>46122.61244673611</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>222</v>
@@ -9231,13 +9231,13 @@
         <v>375</v>
       </c>
       <c r="B128" s="5">
-        <v>46107.43576706019</v>
+        <v>46107.60243372685</v>
       </c>
       <c r="C128" s="5">
-        <v>46108.49749129629</v>
+        <v>46108.664157962965</v>
       </c>
       <c r="D128" s="5">
-        <v>46114.69284715278</v>
+        <v>46114.85951381944</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>226</v>
@@ -9286,13 +9286,13 @@
         <v>377</v>
       </c>
       <c r="B129" s="8">
-        <v>46107.435805138884</v>
+        <v>46107.602471805556</v>
       </c>
       <c r="C129" s="8">
-        <v>46108.4974994213</v>
+        <v>46108.66416608796</v>
       </c>
       <c r="D129" s="8">
-        <v>46114.69290652778</v>
+        <v>46114.859573194444</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>229</v>
@@ -9341,13 +9341,13 @@
         <v>379</v>
       </c>
       <c r="B130" s="5">
-        <v>46107.47200091435</v>
+        <v>46107.63866758102</v>
       </c>
       <c r="C130" s="5">
-        <v>46109.567952638885</v>
+        <v>46109.73461930556</v>
       </c>
       <c r="D130" s="5">
-        <v>46109.56795405093</v>
+        <v>46109.734620717594</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>56</v>
@@ -9396,13 +9396,13 @@
         <v>381</v>
       </c>
       <c r="B131" s="8">
-        <v>46107.47204607639</v>
+        <v>46107.63871274306</v>
       </c>
       <c r="C131" s="8">
-        <v>46109.56796303241</v>
+        <v>46109.73462969907</v>
       </c>
       <c r="D131" s="8">
-        <v>46109.567964525464</v>
+        <v>46109.73463119213</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>60</v>
@@ -9451,13 +9451,13 @@
         <v>383</v>
       </c>
       <c r="B132" s="5">
-        <v>46107.47208232639</v>
+        <v>46107.63874899306</v>
       </c>
       <c r="C132" s="5">
-        <v>46109.567997465274</v>
+        <v>46109.734664131945</v>
       </c>
       <c r="D132" s="5">
-        <v>46109.56799877315</v>
+        <v>46109.73466543981</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>63</v>
@@ -9506,13 +9506,13 @@
         <v>385</v>
       </c>
       <c r="B133" s="8">
-        <v>46107.47212644676</v>
+        <v>46107.63879311342</v>
       </c>
       <c r="C133" s="8">
-        <v>46113.40002371528</v>
+        <v>46113.566690381944</v>
       </c>
       <c r="D133" s="8">
-        <v>46113.40002502315</v>
+        <v>46113.56669168982</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>66</v>
@@ -9561,13 +9561,13 @@
         <v>387</v>
       </c>
       <c r="B134" s="5">
-        <v>46107.472158449076</v>
+        <v>46107.63882511574</v>
       </c>
       <c r="C134" s="5">
-        <v>46113.40003310185</v>
+        <v>46113.56669976852</v>
       </c>
       <c r="D134" s="5">
-        <v>46113.40003446759</v>
+        <v>46113.56670113426</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>69</v>
@@ -9616,13 +9616,13 @@
         <v>389</v>
       </c>
       <c r="B135" s="8">
-        <v>46077.653509780095</v>
+        <v>46077.82017644676</v>
       </c>
       <c r="C135" s="8">
-        <v>46125.39418625</v>
+        <v>46125.560852916664</v>
       </c>
       <c r="D135" s="8">
-        <v>46127.018723113426</v>
+        <v>46127.18538978009</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>390</v>
@@ -9681,13 +9681,13 @@
         <v>393</v>
       </c>
       <c r="B136" s="5">
-        <v>46107.43598591435</v>
+        <v>46107.602652581016</v>
       </c>
       <c r="C136" s="5">
-        <v>46125.394441805554</v>
+        <v>46125.56110847222</v>
       </c>
       <c r="D136" s="5">
-        <v>46125.39444354166</v>
+        <v>46125.561110208335</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>222</v>
@@ -9734,13 +9734,13 @@
         <v>395</v>
       </c>
       <c r="B137" s="8">
-        <v>46107.436006585645</v>
+        <v>46107.60267325232</v>
       </c>
       <c r="C137" s="8">
-        <v>46125.39445302083</v>
+        <v>46125.561119687496</v>
       </c>
       <c r="D137" s="8">
-        <v>46125.394454548616</v>
+        <v>46125.56112121527</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>222</v>
@@ -9787,13 +9787,13 @@
         <v>396</v>
       </c>
       <c r="B138" s="5">
-        <v>46107.436163171296</v>
+        <v>46107.60282983797</v>
       </c>
       <c r="C138" s="5">
-        <v>46109.56209954861</v>
+        <v>46109.72876621528</v>
       </c>
       <c r="D138" s="5">
-        <v>46114.69138053241</v>
+        <v>46114.85804719907</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>226</v>
@@ -9840,13 +9840,13 @@
         <v>398</v>
       </c>
       <c r="B139" s="8">
-        <v>46107.4362052662</v>
+        <v>46107.602871932875</v>
       </c>
       <c r="C139" s="8">
-        <v>46109.56211155093</v>
+        <v>46109.72877821759</v>
       </c>
       <c r="D139" s="8">
-        <v>46114.69138138889</v>
+        <v>46114.858048055554</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>229</v>
@@ -9893,13 +9893,13 @@
         <v>400</v>
       </c>
       <c r="B140" s="5">
-        <v>46107.43795597222</v>
+        <v>46107.604622638886</v>
       </c>
       <c r="C140" s="5">
-        <v>46109.56809878472</v>
+        <v>46109.73476545139</v>
       </c>
       <c r="D140" s="5">
-        <v>46109.56810045139</v>
+        <v>46109.734767118054</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>56</v>
@@ -9946,13 +9946,13 @@
         <v>402</v>
       </c>
       <c r="B141" s="8">
-        <v>46107.43799892361</v>
+        <v>46107.604665590276</v>
       </c>
       <c r="C141" s="8">
-        <v>46109.568112395835</v>
+        <v>46109.7347790625</v>
       </c>
       <c r="D141" s="8">
-        <v>46109.56811394676</v>
+        <v>46109.73478061343</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>60</v>
@@ -9999,13 +9999,13 @@
         <v>404</v>
       </c>
       <c r="B142" s="5">
-        <v>46107.438038148146</v>
+        <v>46107.60470481482</v>
       </c>
       <c r="C142" s="5">
-        <v>46109.56814829861</v>
+        <v>46109.73481496528</v>
       </c>
       <c r="D142" s="5">
-        <v>46109.56814986111</v>
+        <v>46109.73481652778</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>63</v>
@@ -10052,13 +10052,13 @@
         <v>406</v>
       </c>
       <c r="B143" s="8">
-        <v>46107.438075405094</v>
+        <v>46107.60474207176</v>
       </c>
       <c r="C143" s="8">
-        <v>46113.400086435184</v>
+        <v>46113.566753101855</v>
       </c>
       <c r="D143" s="8">
-        <v>46113.40008774305</v>
+        <v>46113.56675440972</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>66</v>
@@ -10105,13 +10105,13 @@
         <v>408</v>
       </c>
       <c r="B144" s="5">
-        <v>46107.43810650463</v>
+        <v>46107.6047731713</v>
       </c>
       <c r="C144" s="5">
-        <v>46113.400100659725</v>
+        <v>46113.56676732639</v>
       </c>
       <c r="D144" s="5">
-        <v>46113.40010255787</v>
+        <v>46113.56676922453</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>69</v>
@@ -10158,13 +10158,13 @@
         <v>410</v>
       </c>
       <c r="B145" s="8">
-        <v>46077.65351005787</v>
+        <v>46077.820176724534</v>
       </c>
       <c r="C145" s="8">
-        <v>46125.39422983796</v>
+        <v>46125.56089650463</v>
       </c>
       <c r="D145" s="8">
-        <v>46128.030638738426</v>
+        <v>46128.19730540509</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>411</v>
@@ -10223,13 +10223,13 @@
         <v>414</v>
       </c>
       <c r="B146" s="5">
-        <v>46107.438723113424</v>
+        <v>46107.60538978009</v>
       </c>
       <c r="C146" s="5">
-        <v>46125.39450851852</v>
+        <v>46125.56117518518</v>
       </c>
       <c r="D146" s="5">
-        <v>46125.394510011574</v>
+        <v>46125.56117667824</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>222</v>
@@ -10276,13 +10276,13 @@
         <v>415</v>
       </c>
       <c r="B147" s="8">
-        <v>46107.43882452547</v>
+        <v>46107.60549119213</v>
       </c>
       <c r="C147" s="8">
-        <v>46125.39451719908</v>
+        <v>46125.56118386574</v>
       </c>
       <c r="D147" s="8">
-        <v>46125.39451866898</v>
+        <v>46125.56118533565</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>222</v>
@@ -10329,13 +10329,13 @@
         <v>416</v>
       </c>
       <c r="B148" s="5">
-        <v>46107.43886091435</v>
+        <v>46107.60552758102</v>
       </c>
       <c r="C148" s="5">
-        <v>46109.56822582176</v>
+        <v>46109.73489248843</v>
       </c>
       <c r="D148" s="5">
-        <v>46114.69214179398</v>
+        <v>46114.858808460645</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>226</v>
@@ -10382,13 +10382,13 @@
         <v>417</v>
       </c>
       <c r="B149" s="8">
-        <v>46107.43889311343</v>
+        <v>46107.60555978009</v>
       </c>
       <c r="C149" s="8">
-        <v>46109.5682419213</v>
+        <v>46109.73490858796</v>
       </c>
       <c r="D149" s="8">
-        <v>46114.69204347223</v>
+        <v>46114.858710138884</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>229</v>
@@ -10435,13 +10435,13 @@
         <v>418</v>
       </c>
       <c r="B150" s="5">
-        <v>46107.439016122684</v>
+        <v>46107.60568278935</v>
       </c>
       <c r="C150" s="5">
-        <v>46109.56874033565</v>
+        <v>46109.735407002314</v>
       </c>
       <c r="D150" s="5">
-        <v>46109.56874215278</v>
+        <v>46109.73540881944</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>419</v>
@@ -10488,13 +10488,13 @@
         <v>420</v>
       </c>
       <c r="B151" s="8">
-        <v>46107.43907828703</v>
+        <v>46107.605744953704</v>
       </c>
       <c r="C151" s="8">
-        <v>46109.56880127315</v>
+        <v>46109.73546793981</v>
       </c>
       <c r="D151" s="8">
-        <v>46109.56880287037</v>
+        <v>46109.73546953704</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>60</v>
@@ -10541,13 +10541,13 @@
         <v>421</v>
       </c>
       <c r="B152" s="5">
-        <v>46107.43916361111</v>
+        <v>46107.60583027778</v>
       </c>
       <c r="C152" s="5">
-        <v>46109.56885171296</v>
+        <v>46109.73551837963</v>
       </c>
       <c r="D152" s="5">
-        <v>46109.56885335648</v>
+        <v>46109.73552002315</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>63</v>
@@ -10594,13 +10594,13 @@
         <v>422</v>
       </c>
       <c r="B153" s="8">
-        <v>46107.43920138889</v>
+        <v>46107.60586805556</v>
       </c>
       <c r="C153" s="8">
-        <v>46113.4001645949</v>
+        <v>46113.566831261574</v>
       </c>
       <c r="D153" s="8">
-        <v>46113.40016614583</v>
+        <v>46113.5668328125</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>66</v>
@@ -10647,13 +10647,13 @@
         <v>423</v>
       </c>
       <c r="B154" s="5">
-        <v>46107.43923920139</v>
+        <v>46107.605905868055</v>
       </c>
       <c r="C154" s="5">
-        <v>46113.40017584491</v>
+        <v>46113.56684251157</v>
       </c>
       <c r="D154" s="5">
-        <v>46113.40017732639</v>
+        <v>46113.56684399306</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>69</v>
@@ -10700,11 +10700,11 @@
         <v>424</v>
       </c>
       <c r="B155" s="8">
-        <v>46077.65351034723</v>
+        <v>46077.820177013884</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46114.48416508102</v>
+        <v>46114.650831747684</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>425</v>
@@ -10747,11 +10747,11 @@
         <v>427</v>
       </c>
       <c r="B156" s="5">
-        <v>46077.65351063658</v>
+        <v>46077.82017730324</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46137.02136050926</v>
+        <v>46137.18802717593</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>428</v>
@@ -10810,11 +10810,11 @@
         <v>432</v>
       </c>
       <c r="B157" s="8">
-        <v>46077.653510902775</v>
+        <v>46077.82017756945</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46137.02136047454</v>
+        <v>46137.18802714121</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>433</v>
@@ -10873,11 +10873,11 @@
         <v>435</v>
       </c>
       <c r="B158" s="5">
-        <v>46090.71338690972</v>
+        <v>46090.88005357639</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46114.48434215278</v>
+        <v>46114.65100881945</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>436</v>
@@ -10920,11 +10920,11 @@
         <v>438</v>
       </c>
       <c r="B159" s="8">
-        <v>46090.713713668985</v>
+        <v>46090.88038033565</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46137.02136048611</v>
+        <v>46137.18802715278</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>439</v>
@@ -10983,11 +10983,11 @@
         <v>440</v>
       </c>
       <c r="B160" s="5">
-        <v>46090.71395774306</v>
+        <v>46090.88062440972</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46137.02136047454</v>
+        <v>46137.18802714121</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>441</v>

--- a/data/50001451 - ZITRON COLOMBIA.xlsx
+++ b/data/50001451 - ZITRON COLOMBIA.xlsx
@@ -1963,13 +1963,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46077.82017548611</v>
+        <v>46077.65350881944</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.72269003472</v>
+        <v>46092.55602336806</v>
       </c>
       <c r="D4" s="5">
-        <v>46097.53637123843</v>
+        <v>46097.369704571756</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2012,13 +2012,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46077.820175914356</v>
+        <v>46077.653509247684</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.722660590276</v>
+        <v>46092.55599392361</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.72269009259</v>
+        <v>46092.556023425925</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2075,13 +2075,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46077.820176215275</v>
+        <v>46077.65350954861</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.72266121527</v>
+        <v>46092.55599454861</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.72269038194</v>
+        <v>46092.55602371528</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2138,13 +2138,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46077.82017653935</v>
+        <v>46077.65350987269</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.72266167824</v>
+        <v>46092.55599501157</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.722690486116</v>
+        <v>46092.556023819445</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -2201,13 +2201,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46077.8201768287</v>
+        <v>46077.65351016204</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.72266219907</v>
+        <v>46092.555995532406</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.77044202546</v>
+        <v>46100.603775358795</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -2264,13 +2264,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46077.82017715278</v>
+        <v>46077.65351048611</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.72266287037</v>
+        <v>46092.55599620371</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.72269105324</v>
+        <v>46092.55602438658</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -2327,13 +2327,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46077.8201774537</v>
+        <v>46077.65351078704</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.839764351855</v>
+        <v>46114.67309768518</v>
       </c>
       <c r="D10" s="5">
-        <v>46125.5620324537</v>
+        <v>46125.39536578704</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -2378,13 +2378,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46077.82017774305</v>
+        <v>46077.65351107639</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.538789513885</v>
+        <v>46097.37212284722</v>
       </c>
       <c r="D11" s="8">
-        <v>46107.636201562505</v>
+        <v>46107.469534895834</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -2443,13 +2443,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46077.82017803241</v>
+        <v>46077.653511365745</v>
       </c>
       <c r="C12" s="5">
-        <v>46113.56631193287</v>
+        <v>46113.3996452662</v>
       </c>
       <c r="D12" s="5">
-        <v>46113.56632385417</v>
+        <v>46113.3996571875</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2508,13 +2508,13 @@
         <v>55</v>
       </c>
       <c r="B13" s="8">
-        <v>46107.660654374995</v>
+        <v>46107.49398770834</v>
       </c>
       <c r="C13" s="8">
-        <v>46109.73179287037</v>
+        <v>46109.5651262037</v>
       </c>
       <c r="D13" s="8">
-        <v>46109.73400077547</v>
+        <v>46109.5673341088</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>56</v>
@@ -2563,13 +2563,13 @@
         <v>59</v>
       </c>
       <c r="B14" s="5">
-        <v>46107.66079247685</v>
+        <v>46107.49412581019</v>
       </c>
       <c r="C14" s="5">
-        <v>46109.73180825231</v>
+        <v>46109.56514158565</v>
       </c>
       <c r="D14" s="5">
-        <v>46109.73180962963</v>
+        <v>46109.565142962965</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>60</v>
@@ -2618,13 +2618,13 @@
         <v>62</v>
       </c>
       <c r="B15" s="8">
-        <v>46107.66083064815</v>
+        <v>46107.49416398148</v>
       </c>
       <c r="C15" s="8">
-        <v>46109.73182583333</v>
+        <v>46109.56515916667</v>
       </c>
       <c r="D15" s="8">
-        <v>46109.73182759259</v>
+        <v>46109.56516092592</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>63</v>
@@ -2673,13 +2673,13 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46107.66087649306</v>
+        <v>46107.494209826385</v>
       </c>
       <c r="C16" s="5">
-        <v>46113.56627267361</v>
+        <v>46113.39960600695</v>
       </c>
       <c r="D16" s="5">
-        <v>46113.56627391204</v>
+        <v>46113.399607245374</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2728,13 +2728,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="8">
-        <v>46107.660917430556</v>
+        <v>46107.49425076389</v>
       </c>
       <c r="C17" s="8">
-        <v>46113.566297384255</v>
+        <v>46113.39963071759</v>
       </c>
       <c r="D17" s="8">
-        <v>46113.56629861111</v>
+        <v>46113.39963194444</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>69</v>
@@ -2783,13 +2783,13 @@
         <v>71</v>
       </c>
       <c r="B18" s="5">
-        <v>46077.82017832176</v>
+        <v>46077.653511655095</v>
       </c>
       <c r="C18" s="5">
-        <v>46097.53626763889</v>
+        <v>46097.36960097222</v>
       </c>
       <c r="D18" s="5">
-        <v>46125.562004907406</v>
+        <v>46125.39533824074</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>72</v>
@@ -2832,13 +2832,13 @@
         <v>74</v>
       </c>
       <c r="B19" s="8">
-        <v>46077.82017539351</v>
+        <v>46077.65350872686</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.53510356482</v>
+        <v>46097.36843689815</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.53512193287</v>
+        <v>46097.3684552662</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>75</v>
@@ -2897,13 +2897,13 @@
         <v>77</v>
       </c>
       <c r="B20" s="5">
-        <v>46077.82017622685</v>
+        <v>46077.65350956019</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.535863032404</v>
+        <v>46097.36919636574</v>
       </c>
       <c r="D20" s="5">
-        <v>46100.77318243055</v>
+        <v>46100.60651576389</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>78</v>
@@ -2962,13 +2962,13 @@
         <v>80</v>
       </c>
       <c r="B21" s="8">
-        <v>46077.82017653935</v>
+        <v>46077.65350987269</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.53622002315</v>
+        <v>46097.36955335648</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.53623646991</v>
+        <v>46097.36956980324</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>81</v>
@@ -3027,13 +3027,13 @@
         <v>83</v>
       </c>
       <c r="B22" s="5">
-        <v>46077.82017684028</v>
+        <v>46077.65351017361</v>
       </c>
       <c r="C22" s="5">
-        <v>46097.53624710648</v>
+        <v>46097.369580439816</v>
       </c>
       <c r="D22" s="5">
-        <v>46097.53626826389</v>
+        <v>46097.369601597224</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>84</v>
@@ -3092,13 +3092,13 @@
         <v>86</v>
       </c>
       <c r="B23" s="8">
-        <v>46077.8201771412</v>
+        <v>46077.65351047454</v>
       </c>
       <c r="C23" s="8">
-        <v>46104.62858315972</v>
+        <v>46104.461916493055</v>
       </c>
       <c r="D23" s="8">
-        <v>46112.7981115625</v>
+        <v>46112.63144489583</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>87</v>
@@ -3141,13 +3141,13 @@
         <v>89</v>
       </c>
       <c r="B24" s="5">
-        <v>46077.82017777778</v>
+        <v>46077.653511111115</v>
       </c>
       <c r="C24" s="5">
-        <v>46097.53516771991</v>
+        <v>46097.368501053235</v>
       </c>
       <c r="D24" s="5">
-        <v>46097.535187326386</v>
+        <v>46097.36852065972</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>90</v>
@@ -3206,13 +3206,13 @@
         <v>91</v>
       </c>
       <c r="B25" s="8">
-        <v>46077.82017744213</v>
+        <v>46077.65351077546</v>
       </c>
       <c r="C25" s="8">
-        <v>46097.53520844907</v>
+        <v>46097.36854178241</v>
       </c>
       <c r="D25" s="8">
-        <v>46125.56195101852</v>
+        <v>46125.39528435185</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>92</v>
@@ -3271,13 +3271,13 @@
         <v>94</v>
       </c>
       <c r="B26" s="5">
-        <v>46077.820178090275</v>
+        <v>46077.65351142361</v>
       </c>
       <c r="C26" s="5">
-        <v>46097.53883721065</v>
+        <v>46097.37217054398</v>
       </c>
       <c r="D26" s="5">
-        <v>46112.679129490745</v>
+        <v>46112.512462824074</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>95</v>
@@ -3336,13 +3336,13 @@
         <v>97</v>
       </c>
       <c r="B27" s="8">
-        <v>46077.820178379625</v>
+        <v>46077.65351171297</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.535899062495</v>
+        <v>46097.36923239584</v>
       </c>
       <c r="D27" s="8">
-        <v>46100.770078842594</v>
+        <v>46100.60341217593</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>98</v>
@@ -3401,13 +3401,13 @@
         <v>100</v>
       </c>
       <c r="B28" s="5">
-        <v>46077.82017559028</v>
+        <v>46077.65350892361</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.53652079861</v>
+        <v>46097.369854131946</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.53654111111</v>
+        <v>46097.36987444444</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>101</v>
@@ -3466,13 +3466,13 @@
         <v>104</v>
       </c>
       <c r="B29" s="8">
-        <v>46078.658673831014</v>
+        <v>46078.49200716435</v>
       </c>
       <c r="C29" s="8">
-        <v>46104.628560578705</v>
+        <v>46104.46189391204</v>
       </c>
       <c r="D29" s="8">
-        <v>46104.62858377315</v>
+        <v>46104.461917106484</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>105</v>
@@ -3531,13 +3531,13 @@
         <v>107</v>
       </c>
       <c r="B30" s="5">
-        <v>46078.65875901621</v>
+        <v>46078.49209234954</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.53675443287</v>
+        <v>46097.370087766205</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.536774548615</v>
+        <v>46097.37010788194</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>108</v>
@@ -3596,13 +3596,13 @@
         <v>110</v>
       </c>
       <c r="B31" s="8">
-        <v>46077.820175960645</v>
+        <v>46077.65350929398</v>
       </c>
       <c r="C31" s="8">
-        <v>46112.797920625</v>
+        <v>46112.63125395833</v>
       </c>
       <c r="D31" s="8">
-        <v>46112.798028969904</v>
+        <v>46112.63136230324</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>111</v>
@@ -3645,13 +3645,13 @@
         <v>113</v>
       </c>
       <c r="B32" s="5">
-        <v>46077.82017622685</v>
+        <v>46077.65350956019</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.53533090278</v>
+        <v>46097.36866423611</v>
       </c>
       <c r="D32" s="5">
-        <v>46097.535346944445</v>
+        <v>46097.36868027778</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>114</v>
@@ -3710,13 +3710,13 @@
         <v>118</v>
       </c>
       <c r="B33" s="8">
-        <v>46077.820176504625</v>
+        <v>46077.65350983797</v>
       </c>
       <c r="C33" s="8">
-        <v>46097.535274988426</v>
+        <v>46097.36860832176</v>
       </c>
       <c r="D33" s="8">
-        <v>46097.535276400464</v>
+        <v>46097.36860973379</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>119</v>
@@ -3771,13 +3771,13 @@
         <v>123</v>
       </c>
       <c r="B34" s="5">
-        <v>46077.82017679398</v>
+        <v>46077.65351012732</v>
       </c>
       <c r="C34" s="5">
-        <v>46097.53531291666</v>
+        <v>46097.368646250005</v>
       </c>
       <c r="D34" s="5">
-        <v>46097.53531515047</v>
+        <v>46097.368648483796</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>124</v>
@@ -3832,13 +3832,13 @@
         <v>126</v>
       </c>
       <c r="B35" s="8">
-        <v>46077.82017706019</v>
+        <v>46077.65351039352</v>
       </c>
       <c r="C35" s="8">
-        <v>46097.539677256944</v>
+        <v>46097.37301059028</v>
       </c>
       <c r="D35" s="8">
-        <v>46097.539690150465</v>
+        <v>46097.3730234838</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>127</v>
@@ -3897,13 +3897,13 @@
         <v>129</v>
       </c>
       <c r="B36" s="5">
-        <v>46077.82017730324</v>
+        <v>46077.65351063658</v>
       </c>
       <c r="C36" s="5">
-        <v>46097.53889979167</v>
+        <v>46097.372233125</v>
       </c>
       <c r="D36" s="5">
-        <v>46097.53890119213</v>
+        <v>46097.372234525465</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>130</v>
@@ -3958,13 +3958,13 @@
         <v>132</v>
       </c>
       <c r="B37" s="8">
-        <v>46077.82017755787</v>
+        <v>46077.65351089121</v>
       </c>
       <c r="C37" s="8">
-        <v>46097.53966361111</v>
+        <v>46097.37299694444</v>
       </c>
       <c r="D37" s="8">
-        <v>46097.53966494213</v>
+        <v>46097.37299827546</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>133</v>
@@ -4019,13 +4019,13 @@
         <v>135</v>
       </c>
       <c r="B38" s="5">
-        <v>46077.8201778125</v>
+        <v>46077.653511145836</v>
       </c>
       <c r="C38" s="5">
-        <v>46097.53600679398</v>
+        <v>46097.36934012732</v>
       </c>
       <c r="D38" s="5">
-        <v>46097.53602381944</v>
+        <v>46097.36935715278</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>136</v>
@@ -4084,13 +4084,13 @@
         <v>138</v>
       </c>
       <c r="B39" s="8">
-        <v>46077.820178055554</v>
+        <v>46077.65351138889</v>
       </c>
       <c r="C39" s="8">
-        <v>46097.53595292824</v>
+        <v>46097.36928626157</v>
       </c>
       <c r="D39" s="8">
-        <v>46097.5359540625</v>
+        <v>46097.369287395835</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>139</v>
@@ -4145,13 +4145,13 @@
         <v>141</v>
       </c>
       <c r="B40" s="5">
-        <v>46077.82017554398</v>
+        <v>46077.653508877316</v>
       </c>
       <c r="C40" s="5">
-        <v>46097.535993310186</v>
+        <v>46097.369326643515</v>
       </c>
       <c r="D40" s="5">
-        <v>46097.53599474537</v>
+        <v>46097.369328078705</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>142</v>
@@ -4206,13 +4206,13 @@
         <v>144</v>
       </c>
       <c r="B41" s="8">
-        <v>46077.82017600695</v>
+        <v>46077.65350934028</v>
       </c>
       <c r="C41" s="8">
-        <v>46097.535448055554</v>
+        <v>46097.36878138889</v>
       </c>
       <c r="D41" s="8">
-        <v>46097.5354607176</v>
+        <v>46097.368794050926</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>145</v>
@@ -4271,13 +4271,13 @@
         <v>147</v>
       </c>
       <c r="B42" s="5">
-        <v>46077.820176319445</v>
+        <v>46077.65350965278</v>
       </c>
       <c r="C42" s="5">
-        <v>46097.5353593287</v>
+        <v>46097.368692662036</v>
       </c>
       <c r="D42" s="5">
-        <v>46182.693444861114</v>
+        <v>46182.52677819444</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>148</v>
@@ -4332,13 +4332,13 @@
         <v>151</v>
       </c>
       <c r="B43" s="8">
-        <v>46077.82017663194</v>
+        <v>46077.65350996528</v>
       </c>
       <c r="C43" s="8">
-        <v>46097.53540591435</v>
+        <v>46097.368739247686</v>
       </c>
       <c r="D43" s="8">
-        <v>46097.5354075</v>
+        <v>46097.368740833335</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>152</v>
@@ -4393,13 +4393,13 @@
         <v>154</v>
       </c>
       <c r="B44" s="5">
-        <v>46077.82017693287</v>
+        <v>46077.6535102662</v>
       </c>
       <c r="C44" s="5">
-        <v>46097.53543202546</v>
+        <v>46097.3687653588</v>
       </c>
       <c r="D44" s="5">
-        <v>46097.535433425925</v>
+        <v>46097.36876675926</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>155</v>
@@ -4454,13 +4454,13 @@
         <v>157</v>
       </c>
       <c r="B45" s="8">
-        <v>46077.82017723379</v>
+        <v>46077.65351056713</v>
       </c>
       <c r="C45" s="8">
-        <v>46097.53668680556</v>
+        <v>46097.370020138886</v>
       </c>
       <c r="D45" s="8">
-        <v>46097.53669974537</v>
+        <v>46097.3700330787</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>158</v>
@@ -4519,13 +4519,13 @@
         <v>162</v>
       </c>
       <c r="B46" s="5">
-        <v>46077.82017756945</v>
+        <v>46077.653510902775</v>
       </c>
       <c r="C46" s="5">
-        <v>46097.53660920139</v>
+        <v>46097.36994253472</v>
       </c>
       <c r="D46" s="5">
-        <v>46097.53661077547</v>
+        <v>46097.369944108796</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>163</v>
@@ -4580,13 +4580,13 @@
         <v>165</v>
       </c>
       <c r="B47" s="8">
-        <v>46077.820177870366</v>
+        <v>46077.65351120371</v>
       </c>
       <c r="C47" s="8">
-        <v>46097.53667238426</v>
+        <v>46097.37000571759</v>
       </c>
       <c r="D47" s="8">
-        <v>46097.536673703704</v>
+        <v>46097.37000703704</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>166</v>
@@ -4641,13 +4641,13 @@
         <v>167</v>
       </c>
       <c r="B48" s="5">
-        <v>46078.65559880787</v>
+        <v>46078.488932141205</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.840353321764</v>
+        <v>46107.67368665509</v>
       </c>
       <c r="D48" s="5">
-        <v>46107.84042637731</v>
+        <v>46107.67375971065</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>168</v>
@@ -4706,13 +4706,13 @@
         <v>170</v>
       </c>
       <c r="B49" s="8">
-        <v>46078.655658090276</v>
+        <v>46078.48899142361</v>
       </c>
       <c r="C49" s="8">
-        <v>46107.840243784725</v>
+        <v>46107.673577118054</v>
       </c>
       <c r="D49" s="8">
-        <v>46107.84024543982</v>
+        <v>46107.673578773145</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>171</v>
@@ -4767,13 +4767,13 @@
         <v>173</v>
       </c>
       <c r="B50" s="5">
-        <v>46078.65577003472</v>
+        <v>46078.489103368054</v>
       </c>
       <c r="C50" s="5">
-        <v>46107.84033813658</v>
+        <v>46107.67367146991</v>
       </c>
       <c r="D50" s="5">
-        <v>46107.84033961805</v>
+        <v>46107.673672951394</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>174</v>
@@ -4828,13 +4828,13 @@
         <v>176</v>
       </c>
       <c r="B51" s="8">
-        <v>46078.654245046295</v>
+        <v>46078.48757837963</v>
       </c>
       <c r="C51" s="8">
-        <v>46105.78341087963</v>
+        <v>46105.616744212966</v>
       </c>
       <c r="D51" s="8">
-        <v>46105.78342381945</v>
+        <v>46105.61675715278</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>177</v>
@@ -4893,13 +4893,13 @@
         <v>181</v>
       </c>
       <c r="B52" s="5">
-        <v>46078.65429936342</v>
+        <v>46078.487632696764</v>
       </c>
       <c r="C52" s="5">
-        <v>46097.53685579861</v>
+        <v>46097.37018913194</v>
       </c>
       <c r="D52" s="5">
-        <v>46111.65554150463</v>
+        <v>46111.48887483796</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>182</v>
@@ -4954,13 +4954,13 @@
         <v>184</v>
       </c>
       <c r="B53" s="8">
-        <v>46078.65468994213</v>
+        <v>46078.488023275466</v>
       </c>
       <c r="C53" s="8">
-        <v>46105.78339252315</v>
+        <v>46105.61672585648</v>
       </c>
       <c r="D53" s="8">
-        <v>46105.7833940625</v>
+        <v>46105.616727395834</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>185</v>
@@ -5015,13 +5015,13 @@
         <v>188</v>
       </c>
       <c r="B54" s="5">
-        <v>46104.63046165509</v>
+        <v>46104.46379498843</v>
       </c>
       <c r="C54" s="5">
-        <v>46105.75381335648</v>
+        <v>46105.58714668981</v>
       </c>
       <c r="D54" s="5">
-        <v>46107.67902436343</v>
+        <v>46107.51235769676</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>189</v>
@@ -5070,13 +5070,13 @@
         <v>190</v>
       </c>
       <c r="B55" s="8">
-        <v>46104.631274988424</v>
+        <v>46104.46460832176</v>
       </c>
       <c r="C55" s="8">
-        <v>46104.647564768515</v>
+        <v>46104.48089810185</v>
       </c>
       <c r="D55" s="8">
-        <v>46107.67921902778</v>
+        <v>46107.512552361106</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>191</v>
@@ -5125,13 +5125,13 @@
         <v>192</v>
       </c>
       <c r="B56" s="5">
-        <v>46104.631671678246</v>
+        <v>46104.465005011574</v>
       </c>
       <c r="C56" s="5">
-        <v>46104.646698553246</v>
+        <v>46104.480031886575</v>
       </c>
       <c r="D56" s="5">
-        <v>46107.67933054398</v>
+        <v>46107.512663877314</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>193</v>
@@ -5180,13 +5180,13 @@
         <v>194</v>
       </c>
       <c r="B57" s="8">
-        <v>46104.63195700232</v>
+        <v>46104.46529033565</v>
       </c>
       <c r="C57" s="8">
-        <v>46104.64636196759</v>
+        <v>46104.47969530092</v>
       </c>
       <c r="D57" s="8">
-        <v>46107.67943891203</v>
+        <v>46107.51277224537</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>195</v>
@@ -5235,13 +5235,13 @@
         <v>196</v>
       </c>
       <c r="B58" s="5">
-        <v>46104.632084826386</v>
+        <v>46104.46541815972</v>
       </c>
       <c r="C58" s="5">
-        <v>46104.64567174768</v>
+        <v>46104.47900508102</v>
       </c>
       <c r="D58" s="5">
-        <v>46107.67985042824</v>
+        <v>46107.51318376158</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>197</v>
@@ -5290,13 +5290,13 @@
         <v>198</v>
       </c>
       <c r="B59" s="8">
-        <v>46104.63227371528</v>
+        <v>46104.46560704861</v>
       </c>
       <c r="C59" s="8">
-        <v>46104.644934375</v>
+        <v>46104.478267708335</v>
       </c>
       <c r="D59" s="8">
-        <v>46107.67955858796</v>
+        <v>46107.512891921295</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>199</v>
@@ -5345,13 +5345,13 @@
         <v>200</v>
       </c>
       <c r="B60" s="5">
-        <v>46077.82017815972</v>
+        <v>46077.65351149306</v>
       </c>
       <c r="C60" s="5">
-        <v>46114.767718206014</v>
+        <v>46114.60105153936</v>
       </c>
       <c r="D60" s="5">
-        <v>46114.84872589121</v>
+        <v>46114.682059224535</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>201</v>
@@ -5396,13 +5396,13 @@
         <v>203</v>
       </c>
       <c r="B61" s="8">
-        <v>46077.82017846065</v>
+        <v>46077.65351179398</v>
       </c>
       <c r="C61" s="8">
-        <v>46097.537088275465</v>
+        <v>46097.37042160879</v>
       </c>
       <c r="D61" s="8">
-        <v>46097.53710671296</v>
+        <v>46097.370440046296</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>204</v>
@@ -5461,13 +5461,13 @@
         <v>208</v>
       </c>
       <c r="B62" s="5">
-        <v>46077.82017626158</v>
+        <v>46077.65350959491</v>
       </c>
       <c r="C62" s="5">
-        <v>46097.537140636574</v>
+        <v>46097.3704739699</v>
       </c>
       <c r="D62" s="5">
-        <v>46097.53716263889</v>
+        <v>46097.37049597222</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>209</v>
@@ -5526,13 +5526,13 @@
         <v>212</v>
       </c>
       <c r="B63" s="8">
-        <v>46090.87971813657</v>
+        <v>46090.71305146991</v>
       </c>
       <c r="C63" s="8">
-        <v>46097.537211319446</v>
+        <v>46097.370544652775</v>
       </c>
       <c r="D63" s="8">
-        <v>46114.650833692125</v>
+        <v>46114.48416702547</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>213</v>
@@ -5589,13 +5589,13 @@
         <v>215</v>
       </c>
       <c r="B64" s="5">
-        <v>46090.8798415162</v>
+        <v>46090.71317484954</v>
       </c>
       <c r="C64" s="5">
-        <v>46114.76770096065</v>
+        <v>46114.601034293984</v>
       </c>
       <c r="D64" s="5">
-        <v>46119.77882065972</v>
+        <v>46119.61215399306</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>216</v>
@@ -5654,13 +5654,13 @@
         <v>220</v>
       </c>
       <c r="B65" s="8">
-        <v>46107.60619210648</v>
+        <v>46107.43952543981</v>
       </c>
       <c r="C65" s="8">
-        <v>46114.78855440972</v>
+        <v>46114.62188774305</v>
       </c>
       <c r="D65" s="8">
-        <v>46114.78855586806</v>
+        <v>46114.621889201386</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>221</v>
@@ -5707,13 +5707,13 @@
         <v>223</v>
       </c>
       <c r="B66" s="5">
-        <v>46107.60640244213</v>
+        <v>46107.439735775464</v>
       </c>
       <c r="C66" s="5">
-        <v>46114.78858121528</v>
+        <v>46114.62191454861</v>
       </c>
       <c r="D66" s="5">
-        <v>46114.7885828125</v>
+        <v>46114.62191614583</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>224</v>
@@ -5760,13 +5760,13 @@
         <v>225</v>
       </c>
       <c r="B67" s="8">
-        <v>46107.606435821755</v>
+        <v>46107.43976915509</v>
       </c>
       <c r="C67" s="8">
-        <v>46108.65907060185</v>
+        <v>46108.49240393519</v>
       </c>
       <c r="D67" s="8">
-        <v>46114.84832498843</v>
+        <v>46114.68165832176</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>226</v>
@@ -5813,13 +5813,13 @@
         <v>228</v>
       </c>
       <c r="B68" s="5">
-        <v>46107.60648386574</v>
+        <v>46107.439817199076</v>
       </c>
       <c r="C68" s="5">
-        <v>46108.65908678241</v>
+        <v>46108.49242011574</v>
       </c>
       <c r="D68" s="5">
-        <v>46114.84847162037</v>
+        <v>46114.6818049537</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>229</v>
@@ -5866,13 +5866,13 @@
         <v>230</v>
       </c>
       <c r="B69" s="8">
-        <v>46078.65390563657</v>
+        <v>46078.48723896991</v>
       </c>
       <c r="C69" s="8">
-        <v>46105.85624208333</v>
+        <v>46105.68957541666</v>
       </c>
       <c r="D69" s="8">
-        <v>46107.68737451389</v>
+        <v>46107.52070784722</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>231</v>
@@ -5919,13 +5919,13 @@
         <v>234</v>
       </c>
       <c r="B70" s="5">
-        <v>46078.702559108795</v>
+        <v>46078.53589244213</v>
       </c>
       <c r="C70" s="5">
-        <v>46105.856224710646</v>
+        <v>46105.68955804398</v>
       </c>
       <c r="D70" s="5">
-        <v>46107.840496770834</v>
+        <v>46107.67383010416</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>232</v>
@@ -5984,13 +5984,13 @@
         <v>239</v>
       </c>
       <c r="B71" s="8">
-        <v>46077.82017896991</v>
+        <v>46077.65351230324</v>
       </c>
       <c r="C71" s="8">
-        <v>46107.84387899305</v>
+        <v>46107.67721232639</v>
       </c>
       <c r="D71" s="8">
-        <v>46107.843893425925</v>
+        <v>46107.67722675926</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>240</v>
@@ -6037,13 +6037,13 @@
         <v>242</v>
       </c>
       <c r="B72" s="5">
-        <v>46077.820179305556</v>
+        <v>46077.65351263889</v>
       </c>
       <c r="C72" s="5">
-        <v>46107.84233932871</v>
+        <v>46107.67567266204</v>
       </c>
       <c r="D72" s="5">
-        <v>46107.842354259265</v>
+        <v>46107.67568759259</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>243</v>
@@ -6102,13 +6102,13 @@
         <v>247</v>
       </c>
       <c r="B73" s="8">
-        <v>46077.820177430556</v>
+        <v>46077.65351076389</v>
       </c>
       <c r="C73" s="8">
-        <v>46107.84386201389</v>
+        <v>46107.67719534722</v>
       </c>
       <c r="D73" s="8">
-        <v>46107.84388002315</v>
+        <v>46107.67721335648</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>57</v>
@@ -6167,13 +6167,13 @@
         <v>249</v>
       </c>
       <c r="B74" s="5">
-        <v>46077.82017795139</v>
+        <v>46077.65351128472</v>
       </c>
       <c r="C74" s="5">
-        <v>46107.84192445602</v>
+        <v>46107.67525778935</v>
       </c>
       <c r="D74" s="5">
-        <v>46107.841941238425</v>
+        <v>46107.67527457176</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>250</v>
@@ -6232,13 +6232,13 @@
         <v>252</v>
       </c>
       <c r="B75" s="8">
-        <v>46077.82017841435</v>
+        <v>46077.65351174769</v>
       </c>
       <c r="C75" s="8">
-        <v>46107.8418262037</v>
+        <v>46107.67515953704</v>
       </c>
       <c r="D75" s="8">
-        <v>46107.841844375</v>
+        <v>46107.675177708334</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>253</v>
@@ -6297,13 +6297,13 @@
         <v>254</v>
       </c>
       <c r="B76" s="5">
-        <v>46078.65892270833</v>
+        <v>46078.49225604167</v>
       </c>
       <c r="C76" s="5">
-        <v>46107.84286186342</v>
+        <v>46107.676195196764</v>
       </c>
       <c r="D76" s="5">
-        <v>46107.84287946759</v>
+        <v>46107.67621280093</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>255</v>
@@ -6362,13 +6362,13 @@
         <v>256</v>
       </c>
       <c r="B77" s="8">
-        <v>46078.65900237269</v>
+        <v>46078.49233570602</v>
       </c>
       <c r="C77" s="8">
-        <v>46107.84237565972</v>
+        <v>46107.675708993054</v>
       </c>
       <c r="D77" s="8">
-        <v>46107.842393032406</v>
+        <v>46107.67572636574</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>257</v>
@@ -6427,13 +6427,13 @@
         <v>258</v>
       </c>
       <c r="B78" s="5">
-        <v>46077.82017907407</v>
+        <v>46077.65351240741</v>
       </c>
       <c r="C78" s="5">
-        <v>46118.851152337964</v>
+        <v>46118.6844856713</v>
       </c>
       <c r="D78" s="5">
-        <v>46125.56179637731</v>
+        <v>46125.39512971065</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>259</v>
@@ -6478,13 +6478,13 @@
         <v>261</v>
       </c>
       <c r="B79" s="8">
-        <v>46077.82017943287</v>
+        <v>46077.65351276621</v>
       </c>
       <c r="C79" s="8">
-        <v>46113.557951111114</v>
+        <v>46113.39128444444</v>
       </c>
       <c r="D79" s="8">
-        <v>46114.85330988426</v>
+        <v>46114.68664321759</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>262</v>
@@ -6543,13 +6543,13 @@
         <v>264</v>
       </c>
       <c r="B80" s="5">
-        <v>46107.59662881945</v>
+        <v>46107.429962152775</v>
       </c>
       <c r="C80" s="5">
-        <v>46113.557604340276</v>
+        <v>46113.39093767361</v>
       </c>
       <c r="D80" s="5">
-        <v>46114.856069733796</v>
+        <v>46114.689403067125</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>222</v>
@@ -6598,13 +6598,13 @@
         <v>266</v>
       </c>
       <c r="B81" s="8">
-        <v>46107.59776125</v>
+        <v>46107.431094583335</v>
       </c>
       <c r="C81" s="8">
-        <v>46113.5576187963</v>
+        <v>46113.39095212963</v>
       </c>
       <c r="D81" s="8">
-        <v>46114.856118923606</v>
+        <v>46114.68945225695</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>222</v>
@@ -6653,13 +6653,13 @@
         <v>267</v>
       </c>
       <c r="B82" s="5">
-        <v>46107.597173993054</v>
+        <v>46107.43050732639</v>
       </c>
       <c r="C82" s="5">
-        <v>46107.838732662036</v>
+        <v>46107.67206599537</v>
       </c>
       <c r="D82" s="5">
-        <v>46107.83873434028</v>
+        <v>46107.672067673615</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>226</v>
@@ -6708,13 +6708,13 @@
         <v>269</v>
       </c>
       <c r="B83" s="8">
-        <v>46107.59746188657</v>
+        <v>46107.43079521991</v>
       </c>
       <c r="C83" s="8">
-        <v>46107.83873872685</v>
+        <v>46107.67207206019</v>
       </c>
       <c r="D83" s="8">
-        <v>46107.83874050926</v>
+        <v>46107.672073842594</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>229</v>
@@ -6763,13 +6763,13 @@
         <v>271</v>
       </c>
       <c r="B84" s="5">
-        <v>46077.82017980324</v>
+        <v>46077.653513136574</v>
       </c>
       <c r="C84" s="5">
-        <v>46113.557691643524</v>
+        <v>46113.39102497685</v>
       </c>
       <c r="D84" s="5">
-        <v>46125.56182928241</v>
+        <v>46125.395162615736</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>272</v>
@@ -6828,13 +6828,13 @@
         <v>275</v>
       </c>
       <c r="B85" s="8">
-        <v>46107.59978276621</v>
+        <v>46107.433116099535</v>
       </c>
       <c r="C85" s="8">
-        <v>46113.558251215276</v>
+        <v>46113.39158454861</v>
       </c>
       <c r="D85" s="8">
-        <v>46114.855711296295</v>
+        <v>46114.68904462963</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>222</v>
@@ -6883,13 +6883,13 @@
         <v>278</v>
       </c>
       <c r="B86" s="5">
-        <v>46107.59982243055</v>
+        <v>46107.433155763894</v>
       </c>
       <c r="C86" s="5">
-        <v>46113.55826416667</v>
+        <v>46113.3915975</v>
       </c>
       <c r="D86" s="5">
-        <v>46114.85576582176</v>
+        <v>46114.68909915509</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>222</v>
@@ -6938,13 +6938,13 @@
         <v>279</v>
       </c>
       <c r="B87" s="8">
-        <v>46107.59986486111</v>
+        <v>46107.43319819444</v>
       </c>
       <c r="C87" s="8">
-        <v>46107.84839290509</v>
+        <v>46107.68172623843</v>
       </c>
       <c r="D87" s="8">
-        <v>46107.84839457176</v>
+        <v>46107.68172790509</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>226</v>
@@ -6993,13 +6993,13 @@
         <v>282</v>
       </c>
       <c r="B88" s="5">
-        <v>46107.59991125</v>
+        <v>46107.43324458333</v>
       </c>
       <c r="C88" s="5">
-        <v>46107.84838658565</v>
+        <v>46107.68171991898</v>
       </c>
       <c r="D88" s="5">
-        <v>46107.8483881713</v>
+        <v>46107.68172150463</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>229</v>
@@ -7048,13 +7048,13 @@
         <v>285</v>
       </c>
       <c r="B89" s="8">
-        <v>46077.82018026621</v>
+        <v>46077.65351359954</v>
       </c>
       <c r="C89" s="8">
-        <v>46113.557744375</v>
+        <v>46113.39107770834</v>
       </c>
       <c r="D89" s="8">
-        <v>46125.56184609953</v>
+        <v>46125.395179432875</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>286</v>
@@ -7113,13 +7113,13 @@
         <v>288</v>
       </c>
       <c r="B90" s="5">
-        <v>46107.59995462963</v>
+        <v>46107.433287962966</v>
       </c>
       <c r="C90" s="5">
-        <v>46113.55834841436</v>
+        <v>46113.391681747686</v>
       </c>
       <c r="D90" s="5">
-        <v>46114.85594553241</v>
+        <v>46114.68927886574</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>289</v>
@@ -7168,13 +7168,13 @@
         <v>292</v>
       </c>
       <c r="B91" s="8">
-        <v>46107.60002673611</v>
+        <v>46107.433360069444</v>
       </c>
       <c r="C91" s="8">
-        <v>46113.55836547454</v>
+        <v>46113.39169880787</v>
       </c>
       <c r="D91" s="8">
-        <v>46114.85576615741</v>
+        <v>46114.689099490744</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>289</v>
@@ -7223,13 +7223,13 @@
         <v>294</v>
       </c>
       <c r="B92" s="5">
-        <v>46107.60006982639</v>
+        <v>46107.433403159725</v>
       </c>
       <c r="C92" s="5">
-        <v>46107.84843891204</v>
+        <v>46107.68177224537</v>
       </c>
       <c r="D92" s="5">
-        <v>46107.84844032407</v>
+        <v>46107.68177365741</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>226</v>
@@ -7278,13 +7278,13 @@
         <v>297</v>
       </c>
       <c r="B93" s="8">
-        <v>46107.600104930556</v>
+        <v>46107.43343826389</v>
       </c>
       <c r="C93" s="8">
-        <v>46107.84843344908</v>
+        <v>46107.68176678241</v>
       </c>
       <c r="D93" s="8">
-        <v>46107.84843525463</v>
+        <v>46107.681768587965</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>229</v>
@@ -7333,13 +7333,13 @@
         <v>300</v>
       </c>
       <c r="B94" s="5">
-        <v>46077.82018063657</v>
+        <v>46077.65351396991</v>
       </c>
       <c r="C94" s="5">
-        <v>46113.55781333333</v>
+        <v>46113.39114666666</v>
       </c>
       <c r="D94" s="5">
-        <v>46125.56186803241</v>
+        <v>46125.39520136574</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>301</v>
@@ -7398,13 +7398,13 @@
         <v>302</v>
       </c>
       <c r="B95" s="8">
-        <v>46107.60121979167</v>
+        <v>46107.434553125</v>
       </c>
       <c r="C95" s="8">
-        <v>46113.55840587963</v>
+        <v>46113.391739212966</v>
       </c>
       <c r="D95" s="8">
-        <v>46114.8505327662</v>
+        <v>46114.68386609954</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>222</v>
@@ -7453,13 +7453,13 @@
         <v>305</v>
       </c>
       <c r="B96" s="5">
-        <v>46107.601296249995</v>
+        <v>46107.43462958334</v>
       </c>
       <c r="C96" s="5">
-        <v>46113.558420057874</v>
+        <v>46113.3917533912</v>
       </c>
       <c r="D96" s="5">
-        <v>46114.850774618055</v>
+        <v>46114.68410795139</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>222</v>
@@ -7508,13 +7508,13 @@
         <v>307</v>
       </c>
       <c r="B97" s="8">
-        <v>46107.601343993054</v>
+        <v>46107.43467732639</v>
       </c>
       <c r="C97" s="8">
-        <v>46107.848516342594</v>
+        <v>46107.68184967592</v>
       </c>
       <c r="D97" s="8">
-        <v>46107.84851795139</v>
+        <v>46107.681851284724</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>226</v>
@@ -7563,13 +7563,13 @@
         <v>310</v>
       </c>
       <c r="B98" s="5">
-        <v>46107.60138634259</v>
+        <v>46107.434719675926</v>
       </c>
       <c r="C98" s="5">
-        <v>46107.84851134259</v>
+        <v>46107.68184467593</v>
       </c>
       <c r="D98" s="5">
-        <v>46107.84851336805</v>
+        <v>46107.68184670139</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>229</v>
@@ -7618,13 +7618,13 @@
         <v>313</v>
       </c>
       <c r="B99" s="8">
-        <v>46078.65921471065</v>
+        <v>46078.492548043985</v>
       </c>
       <c r="C99" s="8">
-        <v>46114.64467627315</v>
+        <v>46114.47800960648</v>
       </c>
       <c r="D99" s="8">
-        <v>46114.65083799769</v>
+        <v>46114.484171331016</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>314</v>
@@ -7683,13 +7683,13 @@
         <v>316</v>
       </c>
       <c r="B100" s="5">
-        <v>46107.60145327546</v>
+        <v>46107.43478660879</v>
       </c>
       <c r="C100" s="5">
-        <v>46114.64465515046</v>
+        <v>46114.47798848379</v>
       </c>
       <c r="D100" s="5">
-        <v>46114.8498778125</v>
+        <v>46114.683211145835</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>222</v>
@@ -7738,13 +7738,13 @@
         <v>318</v>
       </c>
       <c r="B101" s="8">
-        <v>46107.60152523148</v>
+        <v>46107.43485856481</v>
       </c>
       <c r="C101" s="8">
-        <v>46114.6446628125</v>
+        <v>46114.47799614583</v>
       </c>
       <c r="D101" s="8">
-        <v>46114.85000983796</v>
+        <v>46114.683343171295</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>222</v>
@@ -7793,13 +7793,13 @@
         <v>320</v>
       </c>
       <c r="B102" s="5">
-        <v>46107.60156221065</v>
+        <v>46107.43489554398</v>
       </c>
       <c r="C102" s="5">
-        <v>46107.84856559028</v>
+        <v>46107.68189892361</v>
       </c>
       <c r="D102" s="5">
-        <v>46107.84856730324</v>
+        <v>46107.68190063657</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>226</v>
@@ -7848,13 +7848,13 @@
         <v>322</v>
       </c>
       <c r="B103" s="8">
-        <v>46107.60160730324</v>
+        <v>46107.43494063657</v>
       </c>
       <c r="C103" s="8">
-        <v>46107.84855876157</v>
+        <v>46107.68189209491</v>
       </c>
       <c r="D103" s="8">
-        <v>46107.84856039352</v>
+        <v>46107.681893726854</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>229</v>
@@ -7903,13 +7903,13 @@
         <v>324</v>
       </c>
       <c r="B104" s="5">
-        <v>46077.820181030096</v>
+        <v>46077.653514363425</v>
       </c>
       <c r="C104" s="5">
-        <v>46114.64478351852</v>
+        <v>46114.47811685185</v>
       </c>
       <c r="D104" s="5">
-        <v>46125.56189244213</v>
+        <v>46125.395225775464</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>325</v>
@@ -7968,13 +7968,13 @@
         <v>328</v>
       </c>
       <c r="B105" s="8">
-        <v>46107.60168349537</v>
+        <v>46107.435016828706</v>
       </c>
       <c r="C105" s="8">
-        <v>46114.644762384254</v>
+        <v>46114.4780957176</v>
       </c>
       <c r="D105" s="8">
-        <v>46114.8557116088</v>
+        <v>46114.68904494213</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>222</v>
@@ -8021,13 +8021,13 @@
         <v>330</v>
       </c>
       <c r="B106" s="5">
-        <v>46107.60175594907</v>
+        <v>46107.43508928241</v>
       </c>
       <c r="C106" s="5">
-        <v>46114.64476732639</v>
+        <v>46114.47810065972</v>
       </c>
       <c r="D106" s="5">
-        <v>46114.85576636574</v>
+        <v>46114.68909969907</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>222</v>
@@ -8074,13 +8074,13 @@
         <v>331</v>
       </c>
       <c r="B107" s="8">
-        <v>46107.6017900463</v>
+        <v>46107.43512337963</v>
       </c>
       <c r="C107" s="8">
-        <v>46107.84861380787</v>
+        <v>46107.6819471412</v>
       </c>
       <c r="D107" s="8">
-        <v>46114.84731824074</v>
+        <v>46114.680651574075</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>226</v>
@@ -8129,13 +8129,13 @@
         <v>333</v>
       </c>
       <c r="B108" s="5">
-        <v>46107.60182489583</v>
+        <v>46107.43515822917</v>
       </c>
       <c r="C108" s="5">
-        <v>46107.8486083912</v>
+        <v>46107.68194172454</v>
       </c>
       <c r="D108" s="5">
-        <v>46114.84743204861</v>
+        <v>46114.68076538194</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>229</v>
@@ -8184,13 +8184,13 @@
         <v>335</v>
       </c>
       <c r="B109" s="8">
-        <v>46077.82018142361</v>
+        <v>46077.653514756945</v>
       </c>
       <c r="C109" s="8">
-        <v>46118.85113606481</v>
+        <v>46118.68446939815</v>
       </c>
       <c r="D109" s="8">
-        <v>46118.86139821759</v>
+        <v>46118.694731550924</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>336</v>
@@ -8249,13 +8249,13 @@
         <v>337</v>
       </c>
       <c r="B110" s="5">
-        <v>46107.60187090278</v>
+        <v>46107.43520423611</v>
       </c>
       <c r="C110" s="5">
-        <v>46114.85197863426</v>
+        <v>46114.685311967594</v>
       </c>
       <c r="D110" s="5">
-        <v>46114.8519803588</v>
+        <v>46114.68531369213</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>222</v>
@@ -8302,13 +8302,13 @@
         <v>339</v>
       </c>
       <c r="B111" s="8">
-        <v>46107.60193765046</v>
+        <v>46107.4352709838</v>
       </c>
       <c r="C111" s="8">
-        <v>46118.85106515046</v>
+        <v>46118.6843984838</v>
       </c>
       <c r="D111" s="8">
-        <v>46118.86156471065</v>
+        <v>46118.69489804398</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>222</v>
@@ -8355,13 +8355,13 @@
         <v>340</v>
       </c>
       <c r="B112" s="5">
-        <v>46107.601981064814</v>
+        <v>46107.43531439815</v>
       </c>
       <c r="C112" s="5">
-        <v>46108.66388262731</v>
+        <v>46108.49721596065</v>
       </c>
       <c r="D112" s="5">
-        <v>46114.84918898148</v>
+        <v>46114.68252231482</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>226</v>
@@ -8408,13 +8408,13 @@
         <v>342</v>
       </c>
       <c r="B113" s="8">
-        <v>46107.60201515046</v>
+        <v>46107.43534848379</v>
       </c>
       <c r="C113" s="8">
-        <v>46108.66389119213</v>
+        <v>46108.49722452546</v>
       </c>
       <c r="D113" s="8">
-        <v>46114.84926967593</v>
+        <v>46114.68260300926</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>229</v>
@@ -8463,13 +8463,13 @@
         <v>344</v>
       </c>
       <c r="B114" s="5">
-        <v>46077.82017553241</v>
+        <v>46077.65350886574</v>
       </c>
       <c r="C114" s="5">
-        <v>46125.56091158565</v>
+        <v>46125.39424491898</v>
       </c>
       <c r="D114" s="5">
-        <v>46125.561711898146</v>
+        <v>46125.39504523148</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>345</v>
@@ -8512,13 +8512,13 @@
         <v>347</v>
       </c>
       <c r="B115" s="8">
-        <v>46077.82017586805</v>
+        <v>46077.65350920139</v>
       </c>
       <c r="C115" s="8">
-        <v>46121.840045046294</v>
+        <v>46121.67337837963</v>
       </c>
       <c r="D115" s="8">
-        <v>46121.840061724535</v>
+        <v>46121.67339505787</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>348</v>
@@ -8577,13 +8577,13 @@
         <v>352</v>
       </c>
       <c r="B116" s="5">
-        <v>46107.6021821412</v>
+        <v>46107.435515474535</v>
       </c>
       <c r="C116" s="5">
-        <v>46121.840014456015</v>
+        <v>46121.67334778935</v>
       </c>
       <c r="D116" s="5">
-        <v>46121.84001659723</v>
+        <v>46121.673349930556</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>222</v>
@@ -8630,13 +8630,13 @@
         <v>354</v>
       </c>
       <c r="B117" s="8">
-        <v>46107.60222542824</v>
+        <v>46107.43555876157</v>
       </c>
       <c r="C117" s="8">
-        <v>46121.84002578704</v>
+        <v>46121.67335912037</v>
       </c>
       <c r="D117" s="8">
-        <v>46121.84002737269</v>
+        <v>46121.673360706016</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>222</v>
@@ -8683,13 +8683,13 @@
         <v>355</v>
       </c>
       <c r="B118" s="5">
-        <v>46107.602255370366</v>
+        <v>46107.43558870371</v>
       </c>
       <c r="C118" s="5">
-        <v>46108.66400405092</v>
+        <v>46108.49733738426</v>
       </c>
       <c r="D118" s="5">
-        <v>46114.85951420139</v>
+        <v>46114.69284753472</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>226</v>
@@ -8738,13 +8738,13 @@
         <v>357</v>
       </c>
       <c r="B119" s="8">
-        <v>46107.60228831018</v>
+        <v>46107.43562164352</v>
       </c>
       <c r="C119" s="8">
-        <v>46108.66402913195</v>
+        <v>46108.49736246528</v>
       </c>
       <c r="D119" s="8">
-        <v>46114.85957398148</v>
+        <v>46114.69290731481</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>229</v>
@@ -8791,13 +8791,13 @@
         <v>359</v>
       </c>
       <c r="B120" s="5">
-        <v>46107.63652371528</v>
+        <v>46107.46985704861</v>
       </c>
       <c r="C120" s="5">
-        <v>46109.73451819444</v>
+        <v>46109.56785152778</v>
       </c>
       <c r="D120" s="5">
-        <v>46109.73451969908</v>
+        <v>46109.56785303241</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>56</v>
@@ -8844,13 +8844,13 @@
         <v>361</v>
       </c>
       <c r="B121" s="8">
-        <v>46107.636567430556</v>
+        <v>46107.469900763885</v>
       </c>
       <c r="C121" s="8">
-        <v>46109.732098368055</v>
+        <v>46109.56543170139</v>
       </c>
       <c r="D121" s="8">
-        <v>46109.73209987269</v>
+        <v>46109.56543320602</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>60</v>
@@ -8897,13 +8897,13 @@
         <v>363</v>
       </c>
       <c r="B122" s="5">
-        <v>46107.63660021991</v>
+        <v>46107.46993355324</v>
       </c>
       <c r="C122" s="5">
-        <v>46109.732142152774</v>
+        <v>46109.56547548611</v>
       </c>
       <c r="D122" s="5">
-        <v>46109.732143483794</v>
+        <v>46109.56547681713</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>63</v>
@@ -8950,13 +8950,13 @@
         <v>365</v>
       </c>
       <c r="B123" s="8">
-        <v>46107.63664055556</v>
+        <v>46107.46997388889</v>
       </c>
       <c r="C123" s="8">
-        <v>46113.5665987963</v>
+        <v>46113.39993212963</v>
       </c>
       <c r="D123" s="8">
-        <v>46113.566600289356</v>
+        <v>46113.399933622684</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>66</v>
@@ -9003,13 +9003,13 @@
         <v>367</v>
       </c>
       <c r="B124" s="5">
-        <v>46107.63667821759</v>
+        <v>46107.470011550926</v>
       </c>
       <c r="C124" s="5">
-        <v>46113.56660976852</v>
+        <v>46113.39994310185</v>
       </c>
       <c r="D124" s="5">
-        <v>46113.56661126157</v>
+        <v>46113.39994459491</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>69</v>
@@ -9056,13 +9056,13 @@
         <v>369</v>
       </c>
       <c r="B125" s="8">
-        <v>46077.82017615741</v>
+        <v>46077.653509490745</v>
       </c>
       <c r="C125" s="8">
-        <v>46122.61245885417</v>
+        <v>46122.4457921875</v>
       </c>
       <c r="D125" s="8">
-        <v>46126.17015332176</v>
+        <v>46126.00348665509</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>370</v>
@@ -9121,13 +9121,13 @@
         <v>372</v>
       </c>
       <c r="B126" s="5">
-        <v>46107.60233217593</v>
+        <v>46107.435665509256</v>
       </c>
       <c r="C126" s="5">
-        <v>46122.612434027775</v>
+        <v>46122.44576736111</v>
       </c>
       <c r="D126" s="5">
-        <v>46122.612435717594</v>
+        <v>46122.44576905093</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>222</v>
@@ -9176,13 +9176,13 @@
         <v>374</v>
       </c>
       <c r="B127" s="8">
-        <v>46107.60239986111</v>
+        <v>46107.43573319445</v>
       </c>
       <c r="C127" s="8">
-        <v>46122.61244532408</v>
+        <v>46122.445778657406</v>
       </c>
       <c r="D127" s="8">
-        <v>46122.61244673611</v>
+        <v>46122.44578006944</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>222</v>
@@ -9231,13 +9231,13 @@
         <v>375</v>
       </c>
       <c r="B128" s="5">
-        <v>46107.60243372685</v>
+        <v>46107.43576706019</v>
       </c>
       <c r="C128" s="5">
-        <v>46108.664157962965</v>
+        <v>46108.49749129629</v>
       </c>
       <c r="D128" s="5">
-        <v>46114.85951381944</v>
+        <v>46114.69284715278</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>226</v>
@@ -9286,13 +9286,13 @@
         <v>377</v>
       </c>
       <c r="B129" s="8">
-        <v>46107.602471805556</v>
+        <v>46107.435805138884</v>
       </c>
       <c r="C129" s="8">
-        <v>46108.66416608796</v>
+        <v>46108.4974994213</v>
       </c>
       <c r="D129" s="8">
-        <v>46114.859573194444</v>
+        <v>46114.69290652778</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>229</v>
@@ -9341,13 +9341,13 @@
         <v>379</v>
       </c>
       <c r="B130" s="5">
-        <v>46107.63866758102</v>
+        <v>46107.47200091435</v>
       </c>
       <c r="C130" s="5">
-        <v>46109.73461930556</v>
+        <v>46109.567952638885</v>
       </c>
       <c r="D130" s="5">
-        <v>46109.734620717594</v>
+        <v>46109.56795405093</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>56</v>
@@ -9396,13 +9396,13 @@
         <v>381</v>
       </c>
       <c r="B131" s="8">
-        <v>46107.63871274306</v>
+        <v>46107.47204607639</v>
       </c>
       <c r="C131" s="8">
-        <v>46109.73462969907</v>
+        <v>46109.56796303241</v>
       </c>
       <c r="D131" s="8">
-        <v>46109.73463119213</v>
+        <v>46109.567964525464</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>60</v>
@@ -9451,13 +9451,13 @@
         <v>383</v>
       </c>
       <c r="B132" s="5">
-        <v>46107.63874899306</v>
+        <v>46107.47208232639</v>
       </c>
       <c r="C132" s="5">
-        <v>46109.734664131945</v>
+        <v>46109.567997465274</v>
       </c>
       <c r="D132" s="5">
-        <v>46109.73466543981</v>
+        <v>46109.56799877315</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>63</v>
@@ -9506,13 +9506,13 @@
         <v>385</v>
       </c>
       <c r="B133" s="8">
-        <v>46107.63879311342</v>
+        <v>46107.47212644676</v>
       </c>
       <c r="C133" s="8">
-        <v>46113.566690381944</v>
+        <v>46113.40002371528</v>
       </c>
       <c r="D133" s="8">
-        <v>46113.56669168982</v>
+        <v>46113.40002502315</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>66</v>
@@ -9561,13 +9561,13 @@
         <v>387</v>
       </c>
       <c r="B134" s="5">
-        <v>46107.63882511574</v>
+        <v>46107.472158449076</v>
       </c>
       <c r="C134" s="5">
-        <v>46113.56669976852</v>
+        <v>46113.40003310185</v>
       </c>
       <c r="D134" s="5">
-        <v>46113.56670113426</v>
+        <v>46113.40003446759</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>69</v>
@@ -9616,13 +9616,13 @@
         <v>389</v>
       </c>
       <c r="B135" s="8">
-        <v>46077.82017644676</v>
+        <v>46077.653509780095</v>
       </c>
       <c r="C135" s="8">
-        <v>46125.560852916664</v>
+        <v>46125.39418625</v>
       </c>
       <c r="D135" s="8">
-        <v>46127.18538978009</v>
+        <v>46127.018723113426</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>390</v>
@@ -9681,13 +9681,13 @@
         <v>393</v>
       </c>
       <c r="B136" s="5">
-        <v>46107.602652581016</v>
+        <v>46107.43598591435</v>
       </c>
       <c r="C136" s="5">
-        <v>46125.56110847222</v>
+        <v>46125.394441805554</v>
       </c>
       <c r="D136" s="5">
-        <v>46125.561110208335</v>
+        <v>46125.39444354166</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>222</v>
@@ -9734,13 +9734,13 @@
         <v>395</v>
       </c>
       <c r="B137" s="8">
-        <v>46107.60267325232</v>
+        <v>46107.436006585645</v>
       </c>
       <c r="C137" s="8">
-        <v>46125.561119687496</v>
+        <v>46125.39445302083</v>
       </c>
       <c r="D137" s="8">
-        <v>46125.56112121527</v>
+        <v>46125.394454548616</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>222</v>
@@ -9787,13 +9787,13 @@
         <v>396</v>
       </c>
       <c r="B138" s="5">
-        <v>46107.60282983797</v>
+        <v>46107.436163171296</v>
       </c>
       <c r="C138" s="5">
-        <v>46109.72876621528</v>
+        <v>46109.56209954861</v>
       </c>
       <c r="D138" s="5">
-        <v>46114.85804719907</v>
+        <v>46114.69138053241</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>226</v>
@@ -9840,13 +9840,13 @@
         <v>398</v>
       </c>
       <c r="B139" s="8">
-        <v>46107.602871932875</v>
+        <v>46107.4362052662</v>
       </c>
       <c r="C139" s="8">
-        <v>46109.72877821759</v>
+        <v>46109.56211155093</v>
       </c>
       <c r="D139" s="8">
-        <v>46114.858048055554</v>
+        <v>46114.69138138889</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>229</v>
@@ -9893,13 +9893,13 @@
         <v>400</v>
       </c>
       <c r="B140" s="5">
-        <v>46107.604622638886</v>
+        <v>46107.43795597222</v>
       </c>
       <c r="C140" s="5">
-        <v>46109.73476545139</v>
+        <v>46109.56809878472</v>
       </c>
       <c r="D140" s="5">
-        <v>46109.734767118054</v>
+        <v>46109.56810045139</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>56</v>
@@ -9946,13 +9946,13 @@
         <v>402</v>
       </c>
       <c r="B141" s="8">
-        <v>46107.604665590276</v>
+        <v>46107.43799892361</v>
       </c>
       <c r="C141" s="8">
-        <v>46109.7347790625</v>
+        <v>46109.568112395835</v>
       </c>
       <c r="D141" s="8">
-        <v>46109.73478061343</v>
+        <v>46109.56811394676</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>60</v>
@@ -9999,13 +9999,13 @@
         <v>404</v>
       </c>
       <c r="B142" s="5">
-        <v>46107.60470481482</v>
+        <v>46107.438038148146</v>
       </c>
       <c r="C142" s="5">
-        <v>46109.73481496528</v>
+        <v>46109.56814829861</v>
       </c>
       <c r="D142" s="5">
-        <v>46109.73481652778</v>
+        <v>46109.56814986111</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>63</v>
@@ -10052,13 +10052,13 @@
         <v>406</v>
       </c>
       <c r="B143" s="8">
-        <v>46107.60474207176</v>
+        <v>46107.438075405094</v>
       </c>
       <c r="C143" s="8">
-        <v>46113.566753101855</v>
+        <v>46113.400086435184</v>
       </c>
       <c r="D143" s="8">
-        <v>46113.56675440972</v>
+        <v>46113.40008774305</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>66</v>
@@ -10105,13 +10105,13 @@
         <v>408</v>
       </c>
       <c r="B144" s="5">
-        <v>46107.6047731713</v>
+        <v>46107.43810650463</v>
       </c>
       <c r="C144" s="5">
-        <v>46113.56676732639</v>
+        <v>46113.400100659725</v>
       </c>
       <c r="D144" s="5">
-        <v>46113.56676922453</v>
+        <v>46113.40010255787</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>69</v>
@@ -10158,13 +10158,13 @@
         <v>410</v>
       </c>
       <c r="B145" s="8">
-        <v>46077.820176724534</v>
+        <v>46077.65351005787</v>
       </c>
       <c r="C145" s="8">
-        <v>46125.56089650463</v>
+        <v>46125.39422983796</v>
       </c>
       <c r="D145" s="8">
-        <v>46128.19730540509</v>
+        <v>46128.030638738426</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>411</v>
@@ -10223,13 +10223,13 @@
         <v>414</v>
       </c>
       <c r="B146" s="5">
-        <v>46107.60538978009</v>
+        <v>46107.438723113424</v>
       </c>
       <c r="C146" s="5">
-        <v>46125.56117518518</v>
+        <v>46125.39450851852</v>
       </c>
       <c r="D146" s="5">
-        <v>46125.56117667824</v>
+        <v>46125.394510011574</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>222</v>
@@ -10276,13 +10276,13 @@
         <v>415</v>
       </c>
       <c r="B147" s="8">
-        <v>46107.60549119213</v>
+        <v>46107.43882452547</v>
       </c>
       <c r="C147" s="8">
-        <v>46125.56118386574</v>
+        <v>46125.39451719908</v>
       </c>
       <c r="D147" s="8">
-        <v>46125.56118533565</v>
+        <v>46125.39451866898</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>222</v>
@@ -10329,13 +10329,13 @@
         <v>416</v>
       </c>
       <c r="B148" s="5">
-        <v>46107.60552758102</v>
+        <v>46107.43886091435</v>
       </c>
       <c r="C148" s="5">
-        <v>46109.73489248843</v>
+        <v>46109.56822582176</v>
       </c>
       <c r="D148" s="5">
-        <v>46114.858808460645</v>
+        <v>46114.69214179398</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>226</v>
@@ -10382,13 +10382,13 @@
         <v>417</v>
       </c>
       <c r="B149" s="8">
-        <v>46107.60555978009</v>
+        <v>46107.43889311343</v>
       </c>
       <c r="C149" s="8">
-        <v>46109.73490858796</v>
+        <v>46109.5682419213</v>
       </c>
       <c r="D149" s="8">
-        <v>46114.858710138884</v>
+        <v>46114.69204347223</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>229</v>
@@ -10435,13 +10435,13 @@
         <v>418</v>
       </c>
       <c r="B150" s="5">
-        <v>46107.60568278935</v>
+        <v>46107.439016122684</v>
       </c>
       <c r="C150" s="5">
-        <v>46109.735407002314</v>
+        <v>46109.56874033565</v>
       </c>
       <c r="D150" s="5">
-        <v>46109.73540881944</v>
+        <v>46109.56874215278</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>419</v>
@@ -10488,13 +10488,13 @@
         <v>420</v>
       </c>
       <c r="B151" s="8">
-        <v>46107.605744953704</v>
+        <v>46107.43907828703</v>
       </c>
       <c r="C151" s="8">
-        <v>46109.73546793981</v>
+        <v>46109.56880127315</v>
       </c>
       <c r="D151" s="8">
-        <v>46109.73546953704</v>
+        <v>46109.56880287037</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>60</v>
@@ -10541,13 +10541,13 @@
         <v>421</v>
       </c>
       <c r="B152" s="5">
-        <v>46107.60583027778</v>
+        <v>46107.43916361111</v>
       </c>
       <c r="C152" s="5">
-        <v>46109.73551837963</v>
+        <v>46109.56885171296</v>
       </c>
       <c r="D152" s="5">
-        <v>46109.73552002315</v>
+        <v>46109.56885335648</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>63</v>
@@ -10594,13 +10594,13 @@
         <v>422</v>
       </c>
       <c r="B153" s="8">
-        <v>46107.60586805556</v>
+        <v>46107.43920138889</v>
       </c>
       <c r="C153" s="8">
-        <v>46113.566831261574</v>
+        <v>46113.4001645949</v>
       </c>
       <c r="D153" s="8">
-        <v>46113.5668328125</v>
+        <v>46113.40016614583</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>66</v>
@@ -10647,13 +10647,13 @@
         <v>423</v>
       </c>
       <c r="B154" s="5">
-        <v>46107.605905868055</v>
+        <v>46107.43923920139</v>
       </c>
       <c r="C154" s="5">
-        <v>46113.56684251157</v>
+        <v>46113.40017584491</v>
       </c>
       <c r="D154" s="5">
-        <v>46113.56684399306</v>
+        <v>46113.40017732639</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>69</v>
@@ -10700,11 +10700,11 @@
         <v>424</v>
       </c>
       <c r="B155" s="8">
-        <v>46077.820177013884</v>
+        <v>46077.65351034723</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46114.650831747684</v>
+        <v>46114.48416508102</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>425</v>
@@ -10747,11 +10747,11 @@
         <v>427</v>
       </c>
       <c r="B156" s="5">
-        <v>46077.82017730324</v>
+        <v>46077.65351063658</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46137.18802717593</v>
+        <v>46137.02136050926</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>428</v>
@@ -10810,11 +10810,11 @@
         <v>432</v>
       </c>
       <c r="B157" s="8">
-        <v>46077.82017756945</v>
+        <v>46077.653510902775</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46137.18802714121</v>
+        <v>46137.02136047454</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>433</v>
@@ -10873,11 +10873,11 @@
         <v>435</v>
       </c>
       <c r="B158" s="5">
-        <v>46090.88005357639</v>
+        <v>46090.71338690972</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46114.65100881945</v>
+        <v>46114.48434215278</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>436</v>
@@ -10920,11 +10920,11 @@
         <v>438</v>
       </c>
       <c r="B159" s="8">
-        <v>46090.88038033565</v>
+        <v>46090.713713668985</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46137.18802715278</v>
+        <v>46137.02136048611</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>439</v>
@@ -10983,11 +10983,11 @@
         <v>440</v>
       </c>
       <c r="B160" s="5">
-        <v>46090.88062440972</v>
+        <v>46090.71395774306</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46137.18802714121</v>
+        <v>46137.02136047454</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>441</v>

--- a/data/50001451 - ZITRON COLOMBIA.xlsx
+++ b/data/50001451 - ZITRON COLOMBIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="444">
   <si>
     <t>50001451 - ZITRON COLOMBIA</t>
   </si>
@@ -628,31 +628,37 @@
     <t>Planos preliminar</t>
   </si>
   <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Planos Definitivos</t>
+  </si>
+  <si>
+    <t>1213425602906617</t>
+  </si>
+  <si>
+    <t>Planos Definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Check Planos</t>
+  </si>
+  <si>
+    <t>1213576320894715</t>
+  </si>
+  <si>
+    <t>Check Planos</t>
+  </si>
+  <si>
     <t>Hernan Roberto Gutierrez Barrientos</t>
   </si>
   <si>
     <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Planos Definitivos</t>
-  </si>
-  <si>
-    <t>1213425602906617</t>
-  </si>
-  <si>
-    <t>Planos Definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Check Planos</t>
-  </si>
-  <si>
-    <t>1213576320894715</t>
-  </si>
-  <si>
-    <t>Check Planos</t>
   </si>
   <si>
     <t>Fabricación completa proveedor externo,Revision Fabricacion Externa ,Ingenieria y diseño:,OT 4094 - ZVN 1-25-630/6,OT 4094 - ZVN 1-25-630/6,OT 4095 - ZVN 1-20-220/6,OT 4096 - ZVN 1-20-200/6,OT  4094 - ZVN 1-25-630/6,OT  4094 - ZVN 1-25-630/6,OT 4095 - ZVN 1-20-220/6,OT 4096 - ZVN 1-20-200/6,OT 4094 - ZVN 1-25-630/6,OT 4094 - ZVN 1-25-630/6,OT 4095 - ZVN 1-20-220/6,OT 4096 - ZVN 1-20-200/6,OT 4094 - ZVN 1-25-630/6,OT 4094 - ZVN 1-25-630/6,OT 4095 - ZVN 1-20-220/6,OT 4096 - ZVN 1-20-200/6,Check Pruebas FAT</t>
@@ -1963,13 +1969,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46077.65350881944</v>
+        <v>46077.82017548611</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55602336806</v>
+        <v>46092.72269003472</v>
       </c>
       <c r="D4" s="5">
-        <v>46097.369704571756</v>
+        <v>46097.53637123843</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2012,13 +2018,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46077.653509247684</v>
+        <v>46077.820175914356</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55599392361</v>
+        <v>46092.722660590276</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.556023425925</v>
+        <v>46092.72269009259</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2075,13 +2081,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46077.65350954861</v>
+        <v>46077.820176215275</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55599454861</v>
+        <v>46092.72266121527</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55602371528</v>
+        <v>46092.72269038194</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2138,13 +2144,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46077.65350987269</v>
+        <v>46077.82017653935</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55599501157</v>
+        <v>46092.72266167824</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.556023819445</v>
+        <v>46092.722690486116</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -2201,13 +2207,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46077.65351016204</v>
+        <v>46077.8201768287</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.555995532406</v>
+        <v>46092.72266219907</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.603775358795</v>
+        <v>46100.77044202546</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -2264,13 +2270,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46077.65351048611</v>
+        <v>46077.82017715278</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55599620371</v>
+        <v>46092.72266287037</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.55602438658</v>
+        <v>46092.72269105324</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -2327,13 +2333,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46077.65351078704</v>
+        <v>46077.8201774537</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.67309768518</v>
+        <v>46114.839764351855</v>
       </c>
       <c r="D10" s="5">
-        <v>46125.39536578704</v>
+        <v>46125.5620324537</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -2378,13 +2384,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46077.65351107639</v>
+        <v>46077.82017774305</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.37212284722</v>
+        <v>46097.538789513885</v>
       </c>
       <c r="D11" s="8">
-        <v>46107.469534895834</v>
+        <v>46107.636201562505</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -2443,13 +2449,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46077.653511365745</v>
+        <v>46077.82017803241</v>
       </c>
       <c r="C12" s="5">
-        <v>46113.3996452662</v>
+        <v>46113.56631193287</v>
       </c>
       <c r="D12" s="5">
-        <v>46113.3996571875</v>
+        <v>46113.56632385417</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2508,13 +2514,13 @@
         <v>55</v>
       </c>
       <c r="B13" s="8">
-        <v>46107.49398770834</v>
+        <v>46107.660654374995</v>
       </c>
       <c r="C13" s="8">
-        <v>46109.5651262037</v>
+        <v>46109.73179287037</v>
       </c>
       <c r="D13" s="8">
-        <v>46109.5673341088</v>
+        <v>46109.73400077547</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>56</v>
@@ -2563,13 +2569,13 @@
         <v>59</v>
       </c>
       <c r="B14" s="5">
-        <v>46107.49412581019</v>
+        <v>46107.66079247685</v>
       </c>
       <c r="C14" s="5">
-        <v>46109.56514158565</v>
+        <v>46109.73180825231</v>
       </c>
       <c r="D14" s="5">
-        <v>46109.565142962965</v>
+        <v>46109.73180962963</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>60</v>
@@ -2618,13 +2624,13 @@
         <v>62</v>
       </c>
       <c r="B15" s="8">
-        <v>46107.49416398148</v>
+        <v>46107.66083064815</v>
       </c>
       <c r="C15" s="8">
-        <v>46109.56515916667</v>
+        <v>46109.73182583333</v>
       </c>
       <c r="D15" s="8">
-        <v>46109.56516092592</v>
+        <v>46109.73182759259</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>63</v>
@@ -2673,13 +2679,13 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46107.494209826385</v>
+        <v>46107.66087649306</v>
       </c>
       <c r="C16" s="5">
-        <v>46113.39960600695</v>
+        <v>46113.56627267361</v>
       </c>
       <c r="D16" s="5">
-        <v>46113.399607245374</v>
+        <v>46113.56627391204</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2728,13 +2734,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="8">
-        <v>46107.49425076389</v>
+        <v>46107.660917430556</v>
       </c>
       <c r="C17" s="8">
-        <v>46113.39963071759</v>
+        <v>46113.566297384255</v>
       </c>
       <c r="D17" s="8">
-        <v>46113.39963194444</v>
+        <v>46113.56629861111</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>69</v>
@@ -2783,13 +2789,13 @@
         <v>71</v>
       </c>
       <c r="B18" s="5">
-        <v>46077.653511655095</v>
+        <v>46077.82017832176</v>
       </c>
       <c r="C18" s="5">
-        <v>46097.36960097222</v>
+        <v>46097.53626763889</v>
       </c>
       <c r="D18" s="5">
-        <v>46125.39533824074</v>
+        <v>46125.562004907406</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>72</v>
@@ -2832,13 +2838,13 @@
         <v>74</v>
       </c>
       <c r="B19" s="8">
-        <v>46077.65350872686</v>
+        <v>46077.82017539351</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.36843689815</v>
+        <v>46097.53510356482</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.3684552662</v>
+        <v>46097.53512193287</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>75</v>
@@ -2897,13 +2903,13 @@
         <v>77</v>
       </c>
       <c r="B20" s="5">
-        <v>46077.65350956019</v>
+        <v>46077.82017622685</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.36919636574</v>
+        <v>46097.535863032404</v>
       </c>
       <c r="D20" s="5">
-        <v>46100.60651576389</v>
+        <v>46100.77318243055</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>78</v>
@@ -2962,13 +2968,13 @@
         <v>80</v>
       </c>
       <c r="B21" s="8">
-        <v>46077.65350987269</v>
+        <v>46077.82017653935</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.36955335648</v>
+        <v>46097.53622002315</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.36956980324</v>
+        <v>46097.53623646991</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>81</v>
@@ -3027,13 +3033,13 @@
         <v>83</v>
       </c>
       <c r="B22" s="5">
-        <v>46077.65351017361</v>
+        <v>46077.82017684028</v>
       </c>
       <c r="C22" s="5">
-        <v>46097.369580439816</v>
+        <v>46097.53624710648</v>
       </c>
       <c r="D22" s="5">
-        <v>46097.369601597224</v>
+        <v>46097.53626826389</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>84</v>
@@ -3092,13 +3098,13 @@
         <v>86</v>
       </c>
       <c r="B23" s="8">
-        <v>46077.65351047454</v>
+        <v>46077.8201771412</v>
       </c>
       <c r="C23" s="8">
-        <v>46104.461916493055</v>
+        <v>46104.62858315972</v>
       </c>
       <c r="D23" s="8">
-        <v>46112.63144489583</v>
+        <v>46112.7981115625</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>87</v>
@@ -3141,13 +3147,13 @@
         <v>89</v>
       </c>
       <c r="B24" s="5">
-        <v>46077.653511111115</v>
+        <v>46077.82017777778</v>
       </c>
       <c r="C24" s="5">
-        <v>46097.368501053235</v>
+        <v>46097.53516771991</v>
       </c>
       <c r="D24" s="5">
-        <v>46097.36852065972</v>
+        <v>46097.535187326386</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>90</v>
@@ -3206,13 +3212,13 @@
         <v>91</v>
       </c>
       <c r="B25" s="8">
-        <v>46077.65351077546</v>
+        <v>46077.82017744213</v>
       </c>
       <c r="C25" s="8">
-        <v>46097.36854178241</v>
+        <v>46097.53520844907</v>
       </c>
       <c r="D25" s="8">
-        <v>46125.39528435185</v>
+        <v>46125.56195101852</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>92</v>
@@ -3271,13 +3277,13 @@
         <v>94</v>
       </c>
       <c r="B26" s="5">
-        <v>46077.65351142361</v>
+        <v>46077.820178090275</v>
       </c>
       <c r="C26" s="5">
-        <v>46097.37217054398</v>
+        <v>46097.53883721065</v>
       </c>
       <c r="D26" s="5">
-        <v>46112.512462824074</v>
+        <v>46112.679129490745</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>95</v>
@@ -3336,13 +3342,13 @@
         <v>97</v>
       </c>
       <c r="B27" s="8">
-        <v>46077.65351171297</v>
+        <v>46077.820178379625</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.36923239584</v>
+        <v>46097.535899062495</v>
       </c>
       <c r="D27" s="8">
-        <v>46100.60341217593</v>
+        <v>46100.770078842594</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>98</v>
@@ -3401,13 +3407,13 @@
         <v>100</v>
       </c>
       <c r="B28" s="5">
-        <v>46077.65350892361</v>
+        <v>46077.82017559028</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.369854131946</v>
+        <v>46097.53652079861</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.36987444444</v>
+        <v>46097.53654111111</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>101</v>
@@ -3466,13 +3472,13 @@
         <v>104</v>
       </c>
       <c r="B29" s="8">
-        <v>46078.49200716435</v>
+        <v>46078.658673831014</v>
       </c>
       <c r="C29" s="8">
-        <v>46104.46189391204</v>
+        <v>46104.628560578705</v>
       </c>
       <c r="D29" s="8">
-        <v>46104.461917106484</v>
+        <v>46104.62858377315</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>105</v>
@@ -3531,13 +3537,13 @@
         <v>107</v>
       </c>
       <c r="B30" s="5">
-        <v>46078.49209234954</v>
+        <v>46078.65875901621</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.370087766205</v>
+        <v>46097.53675443287</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.37010788194</v>
+        <v>46097.536774548615</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>108</v>
@@ -3596,13 +3602,13 @@
         <v>110</v>
       </c>
       <c r="B31" s="8">
-        <v>46077.65350929398</v>
+        <v>46077.820175960645</v>
       </c>
       <c r="C31" s="8">
-        <v>46112.63125395833</v>
+        <v>46112.797920625</v>
       </c>
       <c r="D31" s="8">
-        <v>46112.63136230324</v>
+        <v>46112.798028969904</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>111</v>
@@ -3645,13 +3651,13 @@
         <v>113</v>
       </c>
       <c r="B32" s="5">
-        <v>46077.65350956019</v>
+        <v>46077.82017622685</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.36866423611</v>
+        <v>46097.53533090278</v>
       </c>
       <c r="D32" s="5">
-        <v>46097.36868027778</v>
+        <v>46097.535346944445</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>114</v>
@@ -3710,13 +3716,13 @@
         <v>118</v>
       </c>
       <c r="B33" s="8">
-        <v>46077.65350983797</v>
+        <v>46077.820176504625</v>
       </c>
       <c r="C33" s="8">
-        <v>46097.36860832176</v>
+        <v>46097.535274988426</v>
       </c>
       <c r="D33" s="8">
-        <v>46097.36860973379</v>
+        <v>46097.535276400464</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>119</v>
@@ -3771,13 +3777,13 @@
         <v>123</v>
       </c>
       <c r="B34" s="5">
-        <v>46077.65351012732</v>
+        <v>46077.82017679398</v>
       </c>
       <c r="C34" s="5">
-        <v>46097.368646250005</v>
+        <v>46097.53531291666</v>
       </c>
       <c r="D34" s="5">
-        <v>46097.368648483796</v>
+        <v>46097.53531515047</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>124</v>
@@ -3832,13 +3838,13 @@
         <v>126</v>
       </c>
       <c r="B35" s="8">
-        <v>46077.65351039352</v>
+        <v>46077.82017706019</v>
       </c>
       <c r="C35" s="8">
-        <v>46097.37301059028</v>
+        <v>46097.539677256944</v>
       </c>
       <c r="D35" s="8">
-        <v>46097.3730234838</v>
+        <v>46097.539690150465</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>127</v>
@@ -3897,13 +3903,13 @@
         <v>129</v>
       </c>
       <c r="B36" s="5">
-        <v>46077.65351063658</v>
+        <v>46077.82017730324</v>
       </c>
       <c r="C36" s="5">
-        <v>46097.372233125</v>
+        <v>46097.53889979167</v>
       </c>
       <c r="D36" s="5">
-        <v>46097.372234525465</v>
+        <v>46097.53890119213</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>130</v>
@@ -3958,13 +3964,13 @@
         <v>132</v>
       </c>
       <c r="B37" s="8">
-        <v>46077.65351089121</v>
+        <v>46077.82017755787</v>
       </c>
       <c r="C37" s="8">
-        <v>46097.37299694444</v>
+        <v>46097.53966361111</v>
       </c>
       <c r="D37" s="8">
-        <v>46097.37299827546</v>
+        <v>46097.53966494213</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>133</v>
@@ -4019,13 +4025,13 @@
         <v>135</v>
       </c>
       <c r="B38" s="5">
-        <v>46077.653511145836</v>
+        <v>46077.8201778125</v>
       </c>
       <c r="C38" s="5">
-        <v>46097.36934012732</v>
+        <v>46097.53600679398</v>
       </c>
       <c r="D38" s="5">
-        <v>46097.36935715278</v>
+        <v>46097.53602381944</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>136</v>
@@ -4084,13 +4090,13 @@
         <v>138</v>
       </c>
       <c r="B39" s="8">
-        <v>46077.65351138889</v>
+        <v>46077.820178055554</v>
       </c>
       <c r="C39" s="8">
-        <v>46097.36928626157</v>
+        <v>46097.53595292824</v>
       </c>
       <c r="D39" s="8">
-        <v>46097.369287395835</v>
+        <v>46097.5359540625</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>139</v>
@@ -4145,13 +4151,13 @@
         <v>141</v>
       </c>
       <c r="B40" s="5">
-        <v>46077.653508877316</v>
+        <v>46077.82017554398</v>
       </c>
       <c r="C40" s="5">
-        <v>46097.369326643515</v>
+        <v>46097.535993310186</v>
       </c>
       <c r="D40" s="5">
-        <v>46097.369328078705</v>
+        <v>46097.53599474537</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>142</v>
@@ -4206,13 +4212,13 @@
         <v>144</v>
       </c>
       <c r="B41" s="8">
-        <v>46077.65350934028</v>
+        <v>46077.82017600695</v>
       </c>
       <c r="C41" s="8">
-        <v>46097.36878138889</v>
+        <v>46097.535448055554</v>
       </c>
       <c r="D41" s="8">
-        <v>46097.368794050926</v>
+        <v>46097.5354607176</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>145</v>
@@ -4271,13 +4277,13 @@
         <v>147</v>
       </c>
       <c r="B42" s="5">
-        <v>46077.65350965278</v>
+        <v>46077.820176319445</v>
       </c>
       <c r="C42" s="5">
-        <v>46097.368692662036</v>
+        <v>46097.5353593287</v>
       </c>
       <c r="D42" s="5">
-        <v>46182.52677819444</v>
+        <v>46182.693444861114</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>148</v>
@@ -4332,13 +4338,13 @@
         <v>151</v>
       </c>
       <c r="B43" s="8">
-        <v>46077.65350996528</v>
+        <v>46077.82017663194</v>
       </c>
       <c r="C43" s="8">
-        <v>46097.368739247686</v>
+        <v>46097.53540591435</v>
       </c>
       <c r="D43" s="8">
-        <v>46097.368740833335</v>
+        <v>46097.5354075</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>152</v>
@@ -4393,13 +4399,13 @@
         <v>154</v>
       </c>
       <c r="B44" s="5">
-        <v>46077.6535102662</v>
+        <v>46077.82017693287</v>
       </c>
       <c r="C44" s="5">
-        <v>46097.3687653588</v>
+        <v>46097.53543202546</v>
       </c>
       <c r="D44" s="5">
-        <v>46097.36876675926</v>
+        <v>46097.535433425925</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>155</v>
@@ -4454,13 +4460,13 @@
         <v>157</v>
       </c>
       <c r="B45" s="8">
-        <v>46077.65351056713</v>
+        <v>46077.82017723379</v>
       </c>
       <c r="C45" s="8">
-        <v>46097.370020138886</v>
+        <v>46097.53668680556</v>
       </c>
       <c r="D45" s="8">
-        <v>46097.3700330787</v>
+        <v>46097.53669974537</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>158</v>
@@ -4519,13 +4525,13 @@
         <v>162</v>
       </c>
       <c r="B46" s="5">
-        <v>46077.653510902775</v>
+        <v>46077.82017756945</v>
       </c>
       <c r="C46" s="5">
-        <v>46097.36994253472</v>
+        <v>46097.53660920139</v>
       </c>
       <c r="D46" s="5">
-        <v>46097.369944108796</v>
+        <v>46097.53661077547</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>163</v>
@@ -4580,13 +4586,13 @@
         <v>165</v>
       </c>
       <c r="B47" s="8">
-        <v>46077.65351120371</v>
+        <v>46077.820177870366</v>
       </c>
       <c r="C47" s="8">
-        <v>46097.37000571759</v>
+        <v>46097.53667238426</v>
       </c>
       <c r="D47" s="8">
-        <v>46097.37000703704</v>
+        <v>46097.536673703704</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>166</v>
@@ -4641,13 +4647,13 @@
         <v>167</v>
       </c>
       <c r="B48" s="5">
-        <v>46078.488932141205</v>
+        <v>46078.65559880787</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.67368665509</v>
+        <v>46107.840353321764</v>
       </c>
       <c r="D48" s="5">
-        <v>46107.67375971065</v>
+        <v>46107.84042637731</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>168</v>
@@ -4706,13 +4712,13 @@
         <v>170</v>
       </c>
       <c r="B49" s="8">
-        <v>46078.48899142361</v>
+        <v>46078.655658090276</v>
       </c>
       <c r="C49" s="8">
-        <v>46107.673577118054</v>
+        <v>46107.840243784725</v>
       </c>
       <c r="D49" s="8">
-        <v>46107.673578773145</v>
+        <v>46107.84024543982</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>171</v>
@@ -4767,13 +4773,13 @@
         <v>173</v>
       </c>
       <c r="B50" s="5">
-        <v>46078.489103368054</v>
+        <v>46078.65577003472</v>
       </c>
       <c r="C50" s="5">
-        <v>46107.67367146991</v>
+        <v>46107.84033813658</v>
       </c>
       <c r="D50" s="5">
-        <v>46107.673672951394</v>
+        <v>46107.84033961805</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>174</v>
@@ -4828,13 +4834,13 @@
         <v>176</v>
       </c>
       <c r="B51" s="8">
-        <v>46078.48757837963</v>
+        <v>46078.654245046295</v>
       </c>
       <c r="C51" s="8">
-        <v>46105.616744212966</v>
+        <v>46105.78341087963</v>
       </c>
       <c r="D51" s="8">
-        <v>46105.61675715278</v>
+        <v>46105.78342381945</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>177</v>
@@ -4893,13 +4899,13 @@
         <v>181</v>
       </c>
       <c r="B52" s="5">
-        <v>46078.487632696764</v>
+        <v>46078.65429936342</v>
       </c>
       <c r="C52" s="5">
-        <v>46097.37018913194</v>
+        <v>46097.53685579861</v>
       </c>
       <c r="D52" s="5">
-        <v>46111.48887483796</v>
+        <v>46111.65554150463</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>182</v>
@@ -4954,13 +4960,13 @@
         <v>184</v>
       </c>
       <c r="B53" s="8">
-        <v>46078.488023275466</v>
+        <v>46078.65468994213</v>
       </c>
       <c r="C53" s="8">
-        <v>46105.61672585648</v>
+        <v>46105.78339252315</v>
       </c>
       <c r="D53" s="8">
-        <v>46105.616727395834</v>
+        <v>46105.7833940625</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>185</v>
@@ -5015,13 +5021,13 @@
         <v>188</v>
       </c>
       <c r="B54" s="5">
-        <v>46104.46379498843</v>
+        <v>46104.63046165509</v>
       </c>
       <c r="C54" s="5">
-        <v>46105.58714668981</v>
+        <v>46105.75381335648</v>
       </c>
       <c r="D54" s="5">
-        <v>46107.51235769676</v>
+        <v>46107.67902436343</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>189</v>
@@ -5070,13 +5076,13 @@
         <v>190</v>
       </c>
       <c r="B55" s="8">
-        <v>46104.46460832176</v>
+        <v>46104.631274988424</v>
       </c>
       <c r="C55" s="8">
-        <v>46104.48089810185</v>
+        <v>46104.647564768515</v>
       </c>
       <c r="D55" s="8">
-        <v>46107.512552361106</v>
+        <v>46107.67921902778</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>191</v>
@@ -5125,13 +5131,13 @@
         <v>192</v>
       </c>
       <c r="B56" s="5">
-        <v>46104.465005011574</v>
+        <v>46104.631671678246</v>
       </c>
       <c r="C56" s="5">
-        <v>46104.480031886575</v>
+        <v>46104.646698553246</v>
       </c>
       <c r="D56" s="5">
-        <v>46107.512663877314</v>
+        <v>46107.67933054398</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>193</v>
@@ -5180,13 +5186,13 @@
         <v>194</v>
       </c>
       <c r="B57" s="8">
-        <v>46104.46529033565</v>
+        <v>46104.63195700232</v>
       </c>
       <c r="C57" s="8">
-        <v>46104.47969530092</v>
+        <v>46104.64636196759</v>
       </c>
       <c r="D57" s="8">
-        <v>46107.51277224537</v>
+        <v>46107.67943891203</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>195</v>
@@ -5235,13 +5241,13 @@
         <v>196</v>
       </c>
       <c r="B58" s="5">
-        <v>46104.46541815972</v>
+        <v>46104.632084826386</v>
       </c>
       <c r="C58" s="5">
-        <v>46104.47900508102</v>
+        <v>46104.64567174768</v>
       </c>
       <c r="D58" s="5">
-        <v>46107.51318376158</v>
+        <v>46107.67985042824</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>197</v>
@@ -5290,13 +5296,13 @@
         <v>198</v>
       </c>
       <c r="B59" s="8">
-        <v>46104.46560704861</v>
+        <v>46104.63227371528</v>
       </c>
       <c r="C59" s="8">
-        <v>46104.478267708335</v>
+        <v>46104.644934375</v>
       </c>
       <c r="D59" s="8">
-        <v>46107.512891921295</v>
+        <v>46107.67955858796</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>199</v>
@@ -5345,13 +5351,13 @@
         <v>200</v>
       </c>
       <c r="B60" s="5">
-        <v>46077.65351149306</v>
+        <v>46077.82017815972</v>
       </c>
       <c r="C60" s="5">
-        <v>46114.60105153936</v>
+        <v>46114.767718206014</v>
       </c>
       <c r="D60" s="5">
-        <v>46114.682059224535</v>
+        <v>46114.84872589121</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>201</v>
@@ -5396,13 +5402,13 @@
         <v>203</v>
       </c>
       <c r="B61" s="8">
-        <v>46077.65351179398</v>
+        <v>46077.82017846065</v>
       </c>
       <c r="C61" s="8">
-        <v>46097.37042160879</v>
+        <v>46097.537088275465</v>
       </c>
       <c r="D61" s="8">
-        <v>46097.370440046296</v>
+        <v>46197.707138425925</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>204</v>
@@ -5461,13 +5467,13 @@
         <v>208</v>
       </c>
       <c r="B62" s="5">
-        <v>46077.65350959491</v>
+        <v>46077.82017626158</v>
       </c>
       <c r="C62" s="5">
-        <v>46097.3704739699</v>
+        <v>46097.537140636574</v>
       </c>
       <c r="D62" s="5">
-        <v>46097.37049597222</v>
+        <v>46197.707159328704</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>209</v>
@@ -5526,13 +5532,13 @@
         <v>212</v>
       </c>
       <c r="B63" s="8">
-        <v>46090.71305146991</v>
+        <v>46090.87971813657</v>
       </c>
       <c r="C63" s="8">
-        <v>46097.370544652775</v>
+        <v>46097.537211319446</v>
       </c>
       <c r="D63" s="8">
-        <v>46114.48416702547</v>
+        <v>46114.650833692125</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>213</v>
@@ -5541,10 +5547,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="8">
@@ -5566,7 +5572,7 @@
         <v>209</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q63" s="8">
         <v>45967</v>
@@ -5586,28 +5592,28 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B64" s="5">
-        <v>46090.71317484954</v>
+        <v>46090.8798415162</v>
       </c>
       <c r="C64" s="5">
-        <v>46114.601034293984</v>
+        <v>46114.76770096065</v>
       </c>
       <c r="D64" s="5">
-        <v>46119.61215399306</v>
+        <v>46119.77882065972</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I64" s="5">
         <v>46092</v>
@@ -5628,7 +5634,7 @@
         <v>201</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>201</v>
@@ -5651,28 +5657,28 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B65" s="8">
+        <v>46107.60619210648</v>
+      </c>
+      <c r="C65" s="8">
+        <v>46114.78855440972</v>
+      </c>
+      <c r="D65" s="8">
+        <v>46114.78855586806</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>220</v>
-      </c>
-      <c r="B65" s="8">
-        <v>46107.43952543981</v>
-      </c>
-      <c r="C65" s="8">
-        <v>46114.62188774305</v>
-      </c>
-      <c r="D65" s="8">
-        <v>46114.621889201386</v>
-      </c>
-      <c r="E65" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>218</v>
       </c>
       <c r="I65" s="9"/>
       <c r="J65" s="8">
@@ -5688,13 +5694,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5704,28 +5710,28 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B66" s="5">
-        <v>46107.439735775464</v>
+        <v>46107.60640244213</v>
       </c>
       <c r="C66" s="5">
-        <v>46114.62191454861</v>
+        <v>46114.78858121528</v>
       </c>
       <c r="D66" s="5">
-        <v>46114.62191614583</v>
+        <v>46114.7885828125</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5741,13 +5747,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5757,28 +5763,28 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B67" s="8">
-        <v>46107.43976915509</v>
+        <v>46107.606435821755</v>
       </c>
       <c r="C67" s="8">
-        <v>46108.49240393519</v>
+        <v>46108.65907060185</v>
       </c>
       <c r="D67" s="8">
-        <v>46114.68165832176</v>
+        <v>46114.84832498843</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="8">
@@ -5788,19 +5794,19 @@
         <v>26</v>
       </c>
       <c r="L67" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -5810,28 +5816,28 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B68" s="5">
-        <v>46107.439817199076</v>
+        <v>46107.60648386574</v>
       </c>
       <c r="C68" s="5">
-        <v>46108.49242011574</v>
+        <v>46108.65908678241</v>
       </c>
       <c r="D68" s="5">
-        <v>46114.6818049537</v>
+        <v>46114.84847162037</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5847,13 +5853,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5863,19 +5869,19 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B69" s="8">
-        <v>46078.48723896991</v>
+        <v>46078.65390563657</v>
       </c>
       <c r="C69" s="8">
-        <v>46105.68957541666</v>
+        <v>46105.85624208333</v>
       </c>
       <c r="D69" s="8">
-        <v>46107.52070784722</v>
+        <v>46107.68737451389</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5899,10 +5905,10 @@
         <v>26</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5916,28 +5922,28 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B70" s="5">
+        <v>46078.702559108795</v>
+      </c>
+      <c r="C70" s="5">
+        <v>46105.856224710646</v>
+      </c>
+      <c r="D70" s="5">
+        <v>46107.840496770834</v>
+      </c>
+      <c r="E70" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="B70" s="5">
-        <v>46078.53589244213</v>
-      </c>
-      <c r="C70" s="5">
-        <v>46105.68955804398</v>
-      </c>
-      <c r="D70" s="5">
-        <v>46107.67383010416</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>232</v>
-      </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I70" s="5">
         <v>46057</v>
@@ -5955,13 +5961,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q70" s="5">
         <v>46057</v>
@@ -5981,19 +5987,19 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B71" s="8">
-        <v>46077.65351230324</v>
+        <v>46077.82017896991</v>
       </c>
       <c r="C71" s="8">
-        <v>46107.67721232639</v>
+        <v>46107.84387899305</v>
       </c>
       <c r="D71" s="8">
-        <v>46107.67722675926</v>
+        <v>46107.843893425925</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -6017,7 +6023,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6034,28 +6040,28 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B72" s="5">
-        <v>46077.65351263889</v>
+        <v>46077.820179305556</v>
       </c>
       <c r="C72" s="5">
-        <v>46107.67567266204</v>
+        <v>46107.84233932871</v>
       </c>
       <c r="D72" s="5">
-        <v>46107.67568759259</v>
+        <v>46107.842354259265</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I72" s="5">
         <v>45971</v>
@@ -6073,13 +6079,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>142</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q72" s="5">
         <v>45971</v>
@@ -6099,16 +6105,16 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B73" s="8">
-        <v>46077.65351076389</v>
+        <v>46077.820177430556</v>
       </c>
       <c r="C73" s="8">
-        <v>46107.67719534722</v>
+        <v>46107.84386201389</v>
       </c>
       <c r="D73" s="8">
-        <v>46107.67721335648</v>
+        <v>46107.84388002315</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>57</v>
@@ -6117,10 +6123,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I73" s="8">
         <v>46027</v>
@@ -6138,13 +6144,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O73" s="9" t="s">
         <v>133</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q73" s="8">
         <v>46027</v>
@@ -6164,28 +6170,28 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B74" s="5">
-        <v>46077.65351128472</v>
+        <v>46077.82017795139</v>
       </c>
       <c r="C74" s="5">
-        <v>46107.67525778935</v>
+        <v>46107.84192445602</v>
       </c>
       <c r="D74" s="5">
-        <v>46107.67527457176</v>
+        <v>46107.841941238425</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I74" s="5">
         <v>46041</v>
@@ -6203,13 +6209,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>124</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q74" s="5">
         <v>46041</v>
@@ -6229,28 +6235,28 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B75" s="8">
-        <v>46077.65351174769</v>
+        <v>46077.82017841435</v>
       </c>
       <c r="C75" s="8">
-        <v>46107.67515953704</v>
+        <v>46107.8418262037</v>
       </c>
       <c r="D75" s="8">
-        <v>46107.675177708334</v>
+        <v>46107.841844375</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I75" s="8">
         <v>46056</v>
@@ -6268,13 +6274,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O75" s="9" t="s">
         <v>152</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q75" s="8">
         <v>46056</v>
@@ -6294,28 +6300,28 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B76" s="5">
-        <v>46078.49225604167</v>
+        <v>46078.65892270833</v>
       </c>
       <c r="C76" s="5">
-        <v>46107.676195196764</v>
+        <v>46107.84286186342</v>
       </c>
       <c r="D76" s="5">
-        <v>46107.67621280093</v>
+        <v>46107.84287946759</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I76" s="5">
         <v>46057</v>
@@ -6333,13 +6339,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>185</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q76" s="5">
         <v>46034</v>
@@ -6359,28 +6365,28 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B77" s="8">
-        <v>46078.49233570602</v>
+        <v>46078.65900237269</v>
       </c>
       <c r="C77" s="8">
-        <v>46107.675708993054</v>
+        <v>46107.84237565972</v>
       </c>
       <c r="D77" s="8">
-        <v>46107.67572636574</v>
+        <v>46107.842393032406</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I77" s="8">
         <v>46034</v>
@@ -6398,13 +6404,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O77" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q77" s="8">
         <v>46034</v>
@@ -6424,19 +6430,19 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B78" s="5">
-        <v>46077.65351240741</v>
+        <v>46077.82017907407</v>
       </c>
       <c r="C78" s="5">
-        <v>46118.6844856713</v>
+        <v>46118.851152337964</v>
       </c>
       <c r="D78" s="5">
-        <v>46125.39512971065</v>
+        <v>46125.56179637731</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6460,7 +6466,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6475,19 +6481,19 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B79" s="8">
-        <v>46077.65351276621</v>
+        <v>46077.82017943287</v>
       </c>
       <c r="C79" s="8">
-        <v>46113.39128444444</v>
+        <v>46113.557951111114</v>
       </c>
       <c r="D79" s="8">
-        <v>46114.68664321759</v>
+        <v>46114.85330988426</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6514,13 +6520,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q79" s="8">
         <v>46059</v>
@@ -6540,19 +6546,19 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B80" s="5">
-        <v>46107.429962152775</v>
+        <v>46107.59662881945</v>
       </c>
       <c r="C80" s="5">
-        <v>46113.39093767361</v>
+        <v>46113.557604340276</v>
       </c>
       <c r="D80" s="5">
-        <v>46114.689403067125</v>
+        <v>46114.856069733796</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6579,13 +6585,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6595,19 +6601,19 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B81" s="8">
-        <v>46107.431094583335</v>
+        <v>46107.59776125</v>
       </c>
       <c r="C81" s="8">
-        <v>46113.39095212963</v>
+        <v>46113.5576187963</v>
       </c>
       <c r="D81" s="8">
-        <v>46114.68945225695</v>
+        <v>46114.856118923606</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6634,13 +6640,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6650,19 +6656,19 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B82" s="5">
-        <v>46107.43050732639</v>
+        <v>46107.597173993054</v>
       </c>
       <c r="C82" s="5">
-        <v>46107.67206599537</v>
+        <v>46107.838732662036</v>
       </c>
       <c r="D82" s="5">
-        <v>46107.672067673615</v>
+        <v>46107.83873434028</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6689,13 +6695,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6705,19 +6711,19 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B83" s="8">
-        <v>46107.43079521991</v>
+        <v>46107.59746188657</v>
       </c>
       <c r="C83" s="8">
-        <v>46107.67207206019</v>
+        <v>46107.83873872685</v>
       </c>
       <c r="D83" s="8">
-        <v>46107.672073842594</v>
+        <v>46107.83874050926</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6744,13 +6750,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6760,19 +6766,19 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B84" s="5">
-        <v>46077.653513136574</v>
+        <v>46077.82017980324</v>
       </c>
       <c r="C84" s="5">
-        <v>46113.39102497685</v>
+        <v>46113.557691643524</v>
       </c>
       <c r="D84" s="5">
-        <v>46125.395162615736</v>
+        <v>46125.56182928241</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6799,13 +6805,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q84" s="5">
         <v>46079</v>
@@ -6825,19 +6831,19 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B85" s="8">
-        <v>46107.433116099535</v>
+        <v>46107.59978276621</v>
       </c>
       <c r="C85" s="8">
-        <v>46113.39158454861</v>
+        <v>46113.558251215276</v>
       </c>
       <c r="D85" s="8">
-        <v>46114.68904462963</v>
+        <v>46114.855711296295</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6864,13 +6870,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6880,19 +6886,19 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B86" s="5">
-        <v>46107.433155763894</v>
+        <v>46107.59982243055</v>
       </c>
       <c r="C86" s="5">
-        <v>46113.3915975</v>
+        <v>46113.55826416667</v>
       </c>
       <c r="D86" s="5">
-        <v>46114.68909915509</v>
+        <v>46114.85576582176</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6919,13 +6925,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6935,19 +6941,19 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B87" s="8">
-        <v>46107.43319819444</v>
+        <v>46107.59986486111</v>
       </c>
       <c r="C87" s="8">
-        <v>46107.68172623843</v>
+        <v>46107.84839290509</v>
       </c>
       <c r="D87" s="8">
-        <v>46107.68172790509</v>
+        <v>46107.84839457176</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
@@ -6974,13 +6980,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -6990,19 +6996,19 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B88" s="5">
-        <v>46107.43324458333</v>
+        <v>46107.59991125</v>
       </c>
       <c r="C88" s="5">
-        <v>46107.68171991898</v>
+        <v>46107.84838658565</v>
       </c>
       <c r="D88" s="5">
-        <v>46107.68172150463</v>
+        <v>46107.8483881713</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -7029,13 +7035,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7045,19 +7051,19 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B89" s="8">
-        <v>46077.65351359954</v>
+        <v>46077.82018026621</v>
       </c>
       <c r="C89" s="8">
-        <v>46113.39107770834</v>
+        <v>46113.557744375</v>
       </c>
       <c r="D89" s="8">
-        <v>46125.395179432875</v>
+        <v>46125.56184609953</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -7084,13 +7090,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q89" s="8">
         <v>46083</v>
@@ -7110,19 +7116,19 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B90" s="5">
-        <v>46107.433287962966</v>
+        <v>46107.59995462963</v>
       </c>
       <c r="C90" s="5">
-        <v>46113.391681747686</v>
+        <v>46113.55834841436</v>
       </c>
       <c r="D90" s="5">
-        <v>46114.68927886574</v>
+        <v>46114.85594553241</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7149,13 +7155,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7165,19 +7171,19 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B91" s="8">
-        <v>46107.433360069444</v>
+        <v>46107.60002673611</v>
       </c>
       <c r="C91" s="8">
-        <v>46113.39169880787</v>
+        <v>46113.55836547454</v>
       </c>
       <c r="D91" s="8">
-        <v>46114.689099490744</v>
+        <v>46114.85576615741</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -7204,13 +7210,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O91" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="P91" s="9" t="s">
         <v>293</v>
-      </c>
-      <c r="P91" s="9" t="s">
-        <v>291</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -7220,19 +7226,19 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B92" s="5">
-        <v>46107.433403159725</v>
+        <v>46107.60006982639</v>
       </c>
       <c r="C92" s="5">
-        <v>46107.68177224537</v>
+        <v>46107.84843891204</v>
       </c>
       <c r="D92" s="5">
-        <v>46107.68177365741</v>
+        <v>46107.84844032407</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7259,13 +7265,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7275,19 +7281,19 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B93" s="8">
-        <v>46107.43343826389</v>
+        <v>46107.600104930556</v>
       </c>
       <c r="C93" s="8">
-        <v>46107.68176678241</v>
+        <v>46107.84843344908</v>
       </c>
       <c r="D93" s="8">
-        <v>46107.681768587965</v>
+        <v>46107.84843525463</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7314,13 +7320,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7330,19 +7336,19 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B94" s="5">
-        <v>46077.65351396991</v>
+        <v>46077.82018063657</v>
       </c>
       <c r="C94" s="5">
-        <v>46113.39114666666</v>
+        <v>46113.55781333333</v>
       </c>
       <c r="D94" s="5">
-        <v>46125.39520136574</v>
+        <v>46125.56186803241</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7369,13 +7375,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q94" s="5">
         <v>46085</v>
@@ -7395,19 +7401,19 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B95" s="8">
-        <v>46107.434553125</v>
+        <v>46107.60121979167</v>
       </c>
       <c r="C95" s="8">
-        <v>46113.391739212966</v>
+        <v>46113.55840587963</v>
       </c>
       <c r="D95" s="8">
-        <v>46114.68386609954</v>
+        <v>46114.8505327662</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7434,13 +7440,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7450,19 +7456,19 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B96" s="5">
-        <v>46107.43462958334</v>
+        <v>46107.601296249995</v>
       </c>
       <c r="C96" s="5">
-        <v>46113.3917533912</v>
+        <v>46113.558420057874</v>
       </c>
       <c r="D96" s="5">
-        <v>46114.68410795139</v>
+        <v>46114.850774618055</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7489,13 +7495,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O96" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="P96" s="6" t="s">
         <v>306</v>
-      </c>
-      <c r="P96" s="6" t="s">
-        <v>304</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7505,19 +7511,19 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B97" s="8">
-        <v>46107.43467732639</v>
+        <v>46107.601343993054</v>
       </c>
       <c r="C97" s="8">
-        <v>46107.68184967592</v>
+        <v>46107.848516342594</v>
       </c>
       <c r="D97" s="8">
-        <v>46107.681851284724</v>
+        <v>46107.84851795139</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7544,13 +7550,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7560,19 +7566,19 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B98" s="5">
-        <v>46107.434719675926</v>
+        <v>46107.60138634259</v>
       </c>
       <c r="C98" s="5">
-        <v>46107.68184467593</v>
+        <v>46107.84851134259</v>
       </c>
       <c r="D98" s="5">
-        <v>46107.68184670139</v>
+        <v>46107.84851336805</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7599,13 +7605,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7615,19 +7621,19 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B99" s="8">
-        <v>46078.492548043985</v>
+        <v>46078.65921471065</v>
       </c>
       <c r="C99" s="8">
-        <v>46114.47800960648</v>
+        <v>46114.64467627315</v>
       </c>
       <c r="D99" s="8">
-        <v>46114.484171331016</v>
+        <v>46114.65083799769</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7654,13 +7660,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q99" s="8">
         <v>46087</v>
@@ -7680,19 +7686,19 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B100" s="5">
-        <v>46107.43478660879</v>
+        <v>46107.60145327546</v>
       </c>
       <c r="C100" s="5">
-        <v>46114.47798848379</v>
+        <v>46114.64465515046</v>
       </c>
       <c r="D100" s="5">
-        <v>46114.683211145835</v>
+        <v>46114.8498778125</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7719,13 +7725,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7735,19 +7741,19 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B101" s="8">
-        <v>46107.43485856481</v>
+        <v>46107.60152523148</v>
       </c>
       <c r="C101" s="8">
-        <v>46114.47799614583</v>
+        <v>46114.6446628125</v>
       </c>
       <c r="D101" s="8">
-        <v>46114.683343171295</v>
+        <v>46114.85000983796</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7774,13 +7780,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7790,19 +7796,19 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B102" s="5">
-        <v>46107.43489554398</v>
+        <v>46107.60156221065</v>
       </c>
       <c r="C102" s="5">
-        <v>46107.68189892361</v>
+        <v>46107.84856559028</v>
       </c>
       <c r="D102" s="5">
-        <v>46107.68190063657</v>
+        <v>46107.84856730324</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7829,13 +7835,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7845,19 +7851,19 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B103" s="8">
-        <v>46107.43494063657</v>
+        <v>46107.60160730324</v>
       </c>
       <c r="C103" s="8">
-        <v>46107.68189209491</v>
+        <v>46107.84855876157</v>
       </c>
       <c r="D103" s="8">
-        <v>46107.681893726854</v>
+        <v>46107.84856039352</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7884,13 +7890,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7900,19 +7906,19 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B104" s="5">
-        <v>46077.653514363425</v>
+        <v>46077.820181030096</v>
       </c>
       <c r="C104" s="5">
-        <v>46114.47811685185</v>
+        <v>46114.64478351852</v>
       </c>
       <c r="D104" s="5">
-        <v>46125.395225775464</v>
+        <v>46125.56189244213</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7939,13 +7945,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q104" s="5">
         <v>46091</v>
@@ -7965,19 +7971,19 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B105" s="8">
-        <v>46107.435016828706</v>
+        <v>46107.60168349537</v>
       </c>
       <c r="C105" s="8">
-        <v>46114.4780957176</v>
+        <v>46114.644762384254</v>
       </c>
       <c r="D105" s="8">
-        <v>46114.68904494213</v>
+        <v>46114.8557116088</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -8002,13 +8008,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8018,19 +8024,19 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B106" s="5">
-        <v>46107.43508928241</v>
+        <v>46107.60175594907</v>
       </c>
       <c r="C106" s="5">
-        <v>46114.47810065972</v>
+        <v>46114.64476732639</v>
       </c>
       <c r="D106" s="5">
-        <v>46114.68909969907</v>
+        <v>46114.85576636574</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8055,13 +8061,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8071,19 +8077,19 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B107" s="8">
-        <v>46107.43512337963</v>
+        <v>46107.6017900463</v>
       </c>
       <c r="C107" s="8">
-        <v>46107.6819471412</v>
+        <v>46107.84861380787</v>
       </c>
       <c r="D107" s="8">
-        <v>46114.680651574075</v>
+        <v>46114.84731824074</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -8110,13 +8116,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8126,19 +8132,19 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B108" s="5">
-        <v>46107.43515822917</v>
+        <v>46107.60182489583</v>
       </c>
       <c r="C108" s="5">
-        <v>46107.68194172454</v>
+        <v>46107.8486083912</v>
       </c>
       <c r="D108" s="5">
-        <v>46114.68076538194</v>
+        <v>46114.84743204861</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8165,13 +8171,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8181,19 +8187,19 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B109" s="8">
-        <v>46077.653514756945</v>
+        <v>46077.82018142361</v>
       </c>
       <c r="C109" s="8">
-        <v>46118.68446939815</v>
+        <v>46118.85113606481</v>
       </c>
       <c r="D109" s="8">
-        <v>46118.694731550924</v>
+        <v>46118.86139821759</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8220,13 +8226,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q109" s="8">
         <v>46119</v>
@@ -8246,19 +8252,19 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B110" s="5">
-        <v>46107.43520423611</v>
+        <v>46107.60187090278</v>
       </c>
       <c r="C110" s="5">
-        <v>46114.685311967594</v>
+        <v>46114.85197863426</v>
       </c>
       <c r="D110" s="5">
-        <v>46114.68531369213</v>
+        <v>46114.8519803588</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8283,13 +8289,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8299,19 +8305,19 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B111" s="8">
-        <v>46107.4352709838</v>
+        <v>46107.60193765046</v>
       </c>
       <c r="C111" s="8">
-        <v>46118.6843984838</v>
+        <v>46118.85106515046</v>
       </c>
       <c r="D111" s="8">
-        <v>46118.69489804398</v>
+        <v>46118.86156471065</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8336,13 +8342,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8352,19 +8358,19 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B112" s="5">
-        <v>46107.43531439815</v>
+        <v>46107.601981064814</v>
       </c>
       <c r="C112" s="5">
-        <v>46108.49721596065</v>
+        <v>46108.66388262731</v>
       </c>
       <c r="D112" s="5">
-        <v>46114.68252231482</v>
+        <v>46114.84918898148</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8389,13 +8395,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8405,19 +8411,19 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B113" s="8">
-        <v>46107.43534848379</v>
+        <v>46107.60201515046</v>
       </c>
       <c r="C113" s="8">
-        <v>46108.49722452546</v>
+        <v>46108.66389119213</v>
       </c>
       <c r="D113" s="8">
-        <v>46114.68260300926</v>
+        <v>46114.84926967593</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8444,13 +8450,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8460,19 +8466,19 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B114" s="5">
-        <v>46077.65350886574</v>
+        <v>46077.82017553241</v>
       </c>
       <c r="C114" s="5">
-        <v>46125.39424491898</v>
+        <v>46125.56091158565</v>
       </c>
       <c r="D114" s="5">
-        <v>46125.39504523148</v>
+        <v>46125.561711898146</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>25</v>
@@ -8496,7 +8502,7 @@
         <v>26</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8509,28 +8515,28 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B115" s="8">
-        <v>46077.65350920139</v>
+        <v>46077.82017586805</v>
       </c>
       <c r="C115" s="8">
-        <v>46121.67337837963</v>
+        <v>46121.840045046294</v>
       </c>
       <c r="D115" s="8">
-        <v>46121.67339505787</v>
+        <v>46121.840061724535</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I115" s="8">
         <v>46094</v>
@@ -8548,13 +8554,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q115" s="8">
         <v>46097</v>
@@ -8574,28 +8580,28 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="B116" s="5">
+        <v>46107.6021821412</v>
+      </c>
+      <c r="C116" s="5">
+        <v>46121.840014456015</v>
+      </c>
+      <c r="D116" s="5">
+        <v>46121.84001659723</v>
+      </c>
+      <c r="E116" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G116" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="H116" s="6" t="s">
         <v>352</v>
-      </c>
-      <c r="B116" s="5">
-        <v>46107.435515474535</v>
-      </c>
-      <c r="C116" s="5">
-        <v>46121.67334778935</v>
-      </c>
-      <c r="D116" s="5">
-        <v>46121.673349930556</v>
-      </c>
-      <c r="E116" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="F116" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G116" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>350</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8611,13 +8617,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8627,28 +8633,28 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B117" s="8">
-        <v>46107.43555876157</v>
+        <v>46107.60222542824</v>
       </c>
       <c r="C117" s="8">
-        <v>46121.67335912037</v>
+        <v>46121.84002578704</v>
       </c>
       <c r="D117" s="8">
-        <v>46121.673360706016</v>
+        <v>46121.84002737269</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8664,13 +8670,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8680,28 +8686,28 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B118" s="5">
-        <v>46107.43558870371</v>
+        <v>46107.602255370366</v>
       </c>
       <c r="C118" s="5">
-        <v>46108.49733738426</v>
+        <v>46108.66400405092</v>
       </c>
       <c r="D118" s="5">
-        <v>46114.69284753472</v>
+        <v>46114.85951420139</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I118" s="5">
         <v>46094</v>
@@ -8719,13 +8725,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8735,28 +8741,28 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B119" s="8">
-        <v>46107.43562164352</v>
+        <v>46107.60228831018</v>
       </c>
       <c r="C119" s="8">
-        <v>46108.49736246528</v>
+        <v>46108.66402913195</v>
       </c>
       <c r="D119" s="8">
-        <v>46114.69290731481</v>
+        <v>46114.85957398148</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I119" s="9"/>
       <c r="J119" s="8">
@@ -8772,13 +8778,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8788,16 +8794,16 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B120" s="5">
-        <v>46107.46985704861</v>
+        <v>46107.63652371528</v>
       </c>
       <c r="C120" s="5">
-        <v>46109.56785152778</v>
+        <v>46109.73451819444</v>
       </c>
       <c r="D120" s="5">
-        <v>46109.56785303241</v>
+        <v>46109.73451969908</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>56</v>
@@ -8806,10 +8812,10 @@
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8825,13 +8831,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8841,16 +8847,16 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B121" s="8">
-        <v>46107.469900763885</v>
+        <v>46107.636567430556</v>
       </c>
       <c r="C121" s="8">
-        <v>46109.56543170139</v>
+        <v>46109.732098368055</v>
       </c>
       <c r="D121" s="8">
-        <v>46109.56543320602</v>
+        <v>46109.73209987269</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>60</v>
@@ -8859,10 +8865,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
@@ -8878,13 +8884,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="O121" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8894,16 +8900,16 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B122" s="5">
-        <v>46107.46993355324</v>
+        <v>46107.63660021991</v>
       </c>
       <c r="C122" s="5">
-        <v>46109.56547548611</v>
+        <v>46109.732142152774</v>
       </c>
       <c r="D122" s="5">
-        <v>46109.56547681713</v>
+        <v>46109.732143483794</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>63</v>
@@ -8912,10 +8918,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
@@ -8931,13 +8937,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8947,16 +8953,16 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B123" s="8">
-        <v>46107.46997388889</v>
+        <v>46107.63664055556</v>
       </c>
       <c r="C123" s="8">
-        <v>46113.39993212963</v>
+        <v>46113.5665987963</v>
       </c>
       <c r="D123" s="8">
-        <v>46113.399933622684</v>
+        <v>46113.566600289356</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>66</v>
@@ -8965,10 +8971,10 @@
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I123" s="9"/>
       <c r="J123" s="8">
@@ -8984,13 +8990,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="O123" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -9000,16 +9006,16 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B124" s="5">
-        <v>46107.470011550926</v>
+        <v>46107.63667821759</v>
       </c>
       <c r="C124" s="5">
-        <v>46113.39994310185</v>
+        <v>46113.56660976852</v>
       </c>
       <c r="D124" s="5">
-        <v>46113.39994459491</v>
+        <v>46113.56661126157</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>69</v>
@@ -9018,10 +9024,10 @@
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I124" s="6"/>
       <c r="J124" s="5">
@@ -9037,13 +9043,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9053,19 +9059,19 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B125" s="8">
-        <v>46077.653509490745</v>
+        <v>46077.82017615741</v>
       </c>
       <c r="C125" s="8">
-        <v>46122.4457921875</v>
+        <v>46122.61245885417</v>
       </c>
       <c r="D125" s="8">
-        <v>46126.00348665509</v>
+        <v>46126.17015332176</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9092,13 +9098,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q125" s="8">
         <v>46097</v>
@@ -9118,19 +9124,19 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B126" s="5">
-        <v>46107.435665509256</v>
+        <v>46107.60233217593</v>
       </c>
       <c r="C126" s="5">
-        <v>46122.44576736111</v>
+        <v>46122.612434027775</v>
       </c>
       <c r="D126" s="5">
-        <v>46122.44576905093</v>
+        <v>46122.612435717594</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9157,13 +9163,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9173,19 +9179,19 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B127" s="8">
-        <v>46107.43573319445</v>
+        <v>46107.60239986111</v>
       </c>
       <c r="C127" s="8">
-        <v>46122.445778657406</v>
+        <v>46122.61244532408</v>
       </c>
       <c r="D127" s="8">
-        <v>46122.44578006944</v>
+        <v>46122.61244673611</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -9212,13 +9218,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9228,19 +9234,19 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B128" s="5">
-        <v>46107.43576706019</v>
+        <v>46107.60243372685</v>
       </c>
       <c r="C128" s="5">
-        <v>46108.49749129629</v>
+        <v>46108.664157962965</v>
       </c>
       <c r="D128" s="5">
-        <v>46114.69284715278</v>
+        <v>46114.85951381944</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9267,13 +9273,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9283,19 +9289,19 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B129" s="8">
-        <v>46107.435805138884</v>
+        <v>46107.602471805556</v>
       </c>
       <c r="C129" s="8">
-        <v>46108.4974994213</v>
+        <v>46108.66416608796</v>
       </c>
       <c r="D129" s="8">
-        <v>46114.69290652778</v>
+        <v>46114.859573194444</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -9322,13 +9328,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9338,16 +9344,16 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B130" s="5">
-        <v>46107.47200091435</v>
+        <v>46107.63866758102</v>
       </c>
       <c r="C130" s="5">
-        <v>46109.567952638885</v>
+        <v>46109.73461930556</v>
       </c>
       <c r="D130" s="5">
-        <v>46109.56795405093</v>
+        <v>46109.734620717594</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>56</v>
@@ -9377,13 +9383,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9393,16 +9399,16 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B131" s="8">
-        <v>46107.47204607639</v>
+        <v>46107.63871274306</v>
       </c>
       <c r="C131" s="8">
-        <v>46109.56796303241</v>
+        <v>46109.73462969907</v>
       </c>
       <c r="D131" s="8">
-        <v>46109.567964525464</v>
+        <v>46109.73463119213</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>60</v>
@@ -9432,13 +9438,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O131" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9448,16 +9454,16 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B132" s="5">
-        <v>46107.47208232639</v>
+        <v>46107.63874899306</v>
       </c>
       <c r="C132" s="5">
-        <v>46109.567997465274</v>
+        <v>46109.734664131945</v>
       </c>
       <c r="D132" s="5">
-        <v>46109.56799877315</v>
+        <v>46109.73466543981</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>63</v>
@@ -9487,13 +9493,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9503,16 +9509,16 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B133" s="8">
-        <v>46107.47212644676</v>
+        <v>46107.63879311342</v>
       </c>
       <c r="C133" s="8">
-        <v>46113.40002371528</v>
+        <v>46113.566690381944</v>
       </c>
       <c r="D133" s="8">
-        <v>46113.40002502315</v>
+        <v>46113.56669168982</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>66</v>
@@ -9542,13 +9548,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O133" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9558,16 +9564,16 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B134" s="5">
-        <v>46107.472158449076</v>
+        <v>46107.63882511574</v>
       </c>
       <c r="C134" s="5">
-        <v>46113.40003310185</v>
+        <v>46113.56669976852</v>
       </c>
       <c r="D134" s="5">
-        <v>46113.40003446759</v>
+        <v>46113.56670113426</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>69</v>
@@ -9597,13 +9603,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9613,28 +9619,28 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B135" s="8">
-        <v>46077.653509780095</v>
+        <v>46077.82017644676</v>
       </c>
       <c r="C135" s="8">
-        <v>46125.39418625</v>
+        <v>46125.560852916664</v>
       </c>
       <c r="D135" s="8">
-        <v>46127.018723113426</v>
+        <v>46127.18538978009</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I135" s="8">
         <v>46100</v>
@@ -9652,13 +9658,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q135" s="8">
         <v>46100</v>
@@ -9678,28 +9684,28 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="B136" s="5">
+        <v>46107.602652581016</v>
+      </c>
+      <c r="C136" s="5">
+        <v>46125.56110847222</v>
+      </c>
+      <c r="D136" s="5">
+        <v>46125.561110208335</v>
+      </c>
+      <c r="E136" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="F136" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G136" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="B136" s="5">
-        <v>46107.43598591435</v>
-      </c>
-      <c r="C136" s="5">
-        <v>46125.394441805554</v>
-      </c>
-      <c r="D136" s="5">
-        <v>46125.39444354166</v>
-      </c>
-      <c r="E136" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="F136" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G136" s="6" t="s">
-        <v>391</v>
-      </c>
       <c r="H136" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9715,13 +9721,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9731,28 +9737,28 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B137" s="8">
-        <v>46107.436006585645</v>
+        <v>46107.60267325232</v>
       </c>
       <c r="C137" s="8">
-        <v>46125.39445302083</v>
+        <v>46125.561119687496</v>
       </c>
       <c r="D137" s="8">
-        <v>46125.394454548616</v>
+        <v>46125.56112121527</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I137" s="9"/>
       <c r="J137" s="8">
@@ -9768,13 +9774,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9784,28 +9790,28 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B138" s="5">
-        <v>46107.436163171296</v>
+        <v>46107.60282983797</v>
       </c>
       <c r="C138" s="5">
-        <v>46109.56209954861</v>
+        <v>46109.72876621528</v>
       </c>
       <c r="D138" s="5">
-        <v>46114.69138053241</v>
+        <v>46114.85804719907</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9821,13 +9827,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9837,28 +9843,28 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B139" s="8">
-        <v>46107.4362052662</v>
+        <v>46107.602871932875</v>
       </c>
       <c r="C139" s="8">
-        <v>46109.56211155093</v>
+        <v>46109.72877821759</v>
       </c>
       <c r="D139" s="8">
-        <v>46114.69138138889</v>
+        <v>46114.858048055554</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I139" s="9"/>
       <c r="J139" s="8">
@@ -9874,13 +9880,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9890,16 +9896,16 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B140" s="5">
-        <v>46107.43795597222</v>
+        <v>46107.604622638886</v>
       </c>
       <c r="C140" s="5">
-        <v>46109.56809878472</v>
+        <v>46109.73476545139</v>
       </c>
       <c r="D140" s="5">
-        <v>46109.56810045139</v>
+        <v>46109.734767118054</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>56</v>
@@ -9908,10 +9914,10 @@
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I140" s="6"/>
       <c r="J140" s="5">
@@ -9927,13 +9933,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="O140" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9943,16 +9949,16 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B141" s="8">
-        <v>46107.43799892361</v>
+        <v>46107.604665590276</v>
       </c>
       <c r="C141" s="8">
-        <v>46109.568112395835</v>
+        <v>46109.7347790625</v>
       </c>
       <c r="D141" s="8">
-        <v>46109.56811394676</v>
+        <v>46109.73478061343</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>60</v>
@@ -9961,10 +9967,10 @@
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="8">
@@ -9980,13 +9986,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="O141" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -9996,16 +10002,16 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B142" s="5">
-        <v>46107.438038148146</v>
+        <v>46107.60470481482</v>
       </c>
       <c r="C142" s="5">
-        <v>46109.56814829861</v>
+        <v>46109.73481496528</v>
       </c>
       <c r="D142" s="5">
-        <v>46109.56814986111</v>
+        <v>46109.73481652778</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>63</v>
@@ -10014,10 +10020,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I142" s="6"/>
       <c r="J142" s="5">
@@ -10033,13 +10039,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10049,16 +10055,16 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B143" s="8">
-        <v>46107.438075405094</v>
+        <v>46107.60474207176</v>
       </c>
       <c r="C143" s="8">
-        <v>46113.400086435184</v>
+        <v>46113.566753101855</v>
       </c>
       <c r="D143" s="8">
-        <v>46113.40008774305</v>
+        <v>46113.56675440972</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>66</v>
@@ -10067,10 +10073,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I143" s="9"/>
       <c r="J143" s="8">
@@ -10086,13 +10092,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="O143" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10102,16 +10108,16 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B144" s="5">
-        <v>46107.43810650463</v>
+        <v>46107.6047731713</v>
       </c>
       <c r="C144" s="5">
-        <v>46113.400100659725</v>
+        <v>46113.56676732639</v>
       </c>
       <c r="D144" s="5">
-        <v>46113.40010255787</v>
+        <v>46113.56676922453</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>69</v>
@@ -10120,10 +10126,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I144" s="6"/>
       <c r="J144" s="5">
@@ -10139,13 +10145,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10155,28 +10161,28 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B145" s="8">
-        <v>46077.65351005787</v>
+        <v>46077.820176724534</v>
       </c>
       <c r="C145" s="8">
-        <v>46125.39422983796</v>
+        <v>46125.56089650463</v>
       </c>
       <c r="D145" s="8">
-        <v>46128.030638738426</v>
+        <v>46128.19730540509</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I145" s="8">
         <v>46101</v>
@@ -10194,13 +10200,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="Q145" s="8">
         <v>46101</v>
@@ -10220,28 +10226,28 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B146" s="5">
-        <v>46107.438723113424</v>
+        <v>46107.60538978009</v>
       </c>
       <c r="C146" s="5">
-        <v>46125.39450851852</v>
+        <v>46125.56117518518</v>
       </c>
       <c r="D146" s="5">
-        <v>46125.394510011574</v>
+        <v>46125.56117667824</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10257,13 +10263,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10273,28 +10279,28 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B147" s="8">
-        <v>46107.43882452547</v>
+        <v>46107.60549119213</v>
       </c>
       <c r="C147" s="8">
-        <v>46125.39451719908</v>
+        <v>46125.56118386574</v>
       </c>
       <c r="D147" s="8">
-        <v>46125.39451866898</v>
+        <v>46125.56118533565</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I147" s="9"/>
       <c r="J147" s="8">
@@ -10310,13 +10316,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
@@ -10326,28 +10332,28 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B148" s="5">
-        <v>46107.43886091435</v>
+        <v>46107.60552758102</v>
       </c>
       <c r="C148" s="5">
-        <v>46109.56822582176</v>
+        <v>46109.73489248843</v>
       </c>
       <c r="D148" s="5">
-        <v>46114.69214179398</v>
+        <v>46114.858808460645</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">
@@ -10363,13 +10369,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10379,28 +10385,28 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B149" s="8">
-        <v>46107.43889311343</v>
+        <v>46107.60555978009</v>
       </c>
       <c r="C149" s="8">
-        <v>46109.5682419213</v>
+        <v>46109.73490858796</v>
       </c>
       <c r="D149" s="8">
-        <v>46114.69204347223</v>
+        <v>46114.858710138884</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I149" s="9"/>
       <c r="J149" s="8">
@@ -10416,13 +10422,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10432,28 +10438,28 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B150" s="5">
-        <v>46107.439016122684</v>
+        <v>46107.60568278935</v>
       </c>
       <c r="C150" s="5">
-        <v>46109.56874033565</v>
+        <v>46109.735407002314</v>
       </c>
       <c r="D150" s="5">
-        <v>46109.56874215278</v>
+        <v>46109.73540881944</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I150" s="6"/>
       <c r="J150" s="5">
@@ -10469,13 +10475,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O150" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10485,16 +10491,16 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B151" s="8">
-        <v>46107.43907828703</v>
+        <v>46107.605744953704</v>
       </c>
       <c r="C151" s="8">
-        <v>46109.56880127315</v>
+        <v>46109.73546793981</v>
       </c>
       <c r="D151" s="8">
-        <v>46109.56880287037</v>
+        <v>46109.73546953704</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>60</v>
@@ -10503,10 +10509,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I151" s="9"/>
       <c r="J151" s="8">
@@ -10522,13 +10528,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O151" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10538,16 +10544,16 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B152" s="5">
-        <v>46107.43916361111</v>
+        <v>46107.60583027778</v>
       </c>
       <c r="C152" s="5">
-        <v>46109.56885171296</v>
+        <v>46109.73551837963</v>
       </c>
       <c r="D152" s="5">
-        <v>46109.56885335648</v>
+        <v>46109.73552002315</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>63</v>
@@ -10556,10 +10562,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I152" s="6"/>
       <c r="J152" s="5">
@@ -10575,13 +10581,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O152" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10591,16 +10597,16 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B153" s="8">
-        <v>46107.43920138889</v>
+        <v>46107.60586805556</v>
       </c>
       <c r="C153" s="8">
-        <v>46113.4001645949</v>
+        <v>46113.566831261574</v>
       </c>
       <c r="D153" s="8">
-        <v>46113.40016614583</v>
+        <v>46113.5668328125</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>66</v>
@@ -10609,10 +10615,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H153" s="9" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I153" s="9"/>
       <c r="J153" s="8">
@@ -10628,13 +10634,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O153" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P153" s="9" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
@@ -10644,16 +10650,16 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B154" s="5">
-        <v>46107.43923920139</v>
+        <v>46107.605905868055</v>
       </c>
       <c r="C154" s="5">
-        <v>46113.40017584491</v>
+        <v>46113.56684251157</v>
       </c>
       <c r="D154" s="5">
-        <v>46113.40017732639</v>
+        <v>46113.56684399306</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>69</v>
@@ -10662,10 +10668,10 @@
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I154" s="6"/>
       <c r="J154" s="5">
@@ -10681,13 +10687,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O154" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10697,17 +10703,17 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B155" s="8">
-        <v>46077.65351034723</v>
+        <v>46077.820177013884</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46114.48416508102</v>
+        <v>46114.650831747684</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>25</v>
@@ -10731,7 +10737,7 @@
         <v>26</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="P155" s="9" t="s">
         <v>26</v>
@@ -10744,26 +10750,26 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B156" s="5">
-        <v>46077.65351063658</v>
+        <v>46077.82017730324</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46137.02136050926</v>
+        <v>46137.18802717593</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="I156" s="5">
         <v>46128</v>
@@ -10781,13 +10787,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Q156" s="5">
         <v>46128</v>
@@ -10802,31 +10808,31 @@
         <v>31</v>
       </c>
       <c r="U156" s="12" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B157" s="8">
-        <v>46077.653510902775</v>
+        <v>46077.82017756945</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46137.02136047454</v>
+        <v>46137.18802714121</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H157" s="9" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="I157" s="8">
         <v>46128</v>
@@ -10844,13 +10850,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="P157" s="9" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Q157" s="8">
         <v>46128</v>
@@ -10865,22 +10871,22 @@
         <v>31</v>
       </c>
       <c r="U157" s="12" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B158" s="5">
-        <v>46090.71338690972</v>
+        <v>46090.88005357639</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46114.48434215278</v>
+        <v>46114.65100881945</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>25</v>
@@ -10904,7 +10910,7 @@
         <v>26</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>26</v>
@@ -10917,17 +10923,17 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B159" s="8">
-        <v>46090.713713668985</v>
+        <v>46090.88038033565</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46137.02136048611</v>
+        <v>46137.18802715278</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
@@ -10954,13 +10960,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="P159" s="9" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="Q159" s="8">
         <v>46128</v>
@@ -10975,22 +10981,22 @@
         <v>31</v>
       </c>
       <c r="U159" s="12" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B160" s="5">
-        <v>46090.71395774306</v>
+        <v>46090.88062440972</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46137.02136047454</v>
+        <v>46137.18802714121</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -11017,13 +11023,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="Q160" s="5">
         <v>46128</v>
@@ -11038,7 +11044,7 @@
         <v>31</v>
       </c>
       <c r="U160" s="12" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001451 - ZITRON COLOMBIA.xlsx
+++ b/data/50001451 - ZITRON COLOMBIA.xlsx
@@ -1969,13 +1969,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46077.82017548611</v>
+        <v>46077.65350881944</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.72269003472</v>
+        <v>46092.55602336806</v>
       </c>
       <c r="D4" s="5">
-        <v>46097.53637123843</v>
+        <v>46097.369704571756</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2018,13 +2018,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46077.820175914356</v>
+        <v>46077.653509247684</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.722660590276</v>
+        <v>46092.55599392361</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.72269009259</v>
+        <v>46092.556023425925</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2081,13 +2081,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46077.820176215275</v>
+        <v>46077.65350954861</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.72266121527</v>
+        <v>46092.55599454861</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.72269038194</v>
+        <v>46092.55602371528</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2144,13 +2144,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46077.82017653935</v>
+        <v>46077.65350987269</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.72266167824</v>
+        <v>46092.55599501157</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.722690486116</v>
+        <v>46092.556023819445</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -2207,13 +2207,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46077.8201768287</v>
+        <v>46077.65351016204</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.72266219907</v>
+        <v>46092.555995532406</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.77044202546</v>
+        <v>46100.603775358795</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -2270,13 +2270,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46077.82017715278</v>
+        <v>46077.65351048611</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.72266287037</v>
+        <v>46092.55599620371</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.72269105324</v>
+        <v>46092.55602438658</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -2333,13 +2333,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46077.8201774537</v>
+        <v>46077.65351078704</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.839764351855</v>
+        <v>46114.67309768518</v>
       </c>
       <c r="D10" s="5">
-        <v>46125.5620324537</v>
+        <v>46125.39536578704</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -2384,13 +2384,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46077.82017774305</v>
+        <v>46077.65351107639</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.538789513885</v>
+        <v>46097.37212284722</v>
       </c>
       <c r="D11" s="8">
-        <v>46107.636201562505</v>
+        <v>46107.469534895834</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -2449,13 +2449,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46077.82017803241</v>
+        <v>46077.653511365745</v>
       </c>
       <c r="C12" s="5">
-        <v>46113.56631193287</v>
+        <v>46113.3996452662</v>
       </c>
       <c r="D12" s="5">
-        <v>46113.56632385417</v>
+        <v>46113.3996571875</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2514,13 +2514,13 @@
         <v>55</v>
       </c>
       <c r="B13" s="8">
-        <v>46107.660654374995</v>
+        <v>46107.49398770834</v>
       </c>
       <c r="C13" s="8">
-        <v>46109.73179287037</v>
+        <v>46109.5651262037</v>
       </c>
       <c r="D13" s="8">
-        <v>46109.73400077547</v>
+        <v>46109.5673341088</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>56</v>
@@ -2569,13 +2569,13 @@
         <v>59</v>
       </c>
       <c r="B14" s="5">
-        <v>46107.66079247685</v>
+        <v>46107.49412581019</v>
       </c>
       <c r="C14" s="5">
-        <v>46109.73180825231</v>
+        <v>46109.56514158565</v>
       </c>
       <c r="D14" s="5">
-        <v>46109.73180962963</v>
+        <v>46109.565142962965</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>60</v>
@@ -2624,13 +2624,13 @@
         <v>62</v>
       </c>
       <c r="B15" s="8">
-        <v>46107.66083064815</v>
+        <v>46107.49416398148</v>
       </c>
       <c r="C15" s="8">
-        <v>46109.73182583333</v>
+        <v>46109.56515916667</v>
       </c>
       <c r="D15" s="8">
-        <v>46109.73182759259</v>
+        <v>46109.56516092592</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>63</v>
@@ -2679,13 +2679,13 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46107.66087649306</v>
+        <v>46107.494209826385</v>
       </c>
       <c r="C16" s="5">
-        <v>46113.56627267361</v>
+        <v>46113.39960600695</v>
       </c>
       <c r="D16" s="5">
-        <v>46113.56627391204</v>
+        <v>46113.399607245374</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2734,13 +2734,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="8">
-        <v>46107.660917430556</v>
+        <v>46107.49425076389</v>
       </c>
       <c r="C17" s="8">
-        <v>46113.566297384255</v>
+        <v>46113.39963071759</v>
       </c>
       <c r="D17" s="8">
-        <v>46113.56629861111</v>
+        <v>46113.39963194444</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>69</v>
@@ -2789,13 +2789,13 @@
         <v>71</v>
       </c>
       <c r="B18" s="5">
-        <v>46077.82017832176</v>
+        <v>46077.653511655095</v>
       </c>
       <c r="C18" s="5">
-        <v>46097.53626763889</v>
+        <v>46097.36960097222</v>
       </c>
       <c r="D18" s="5">
-        <v>46125.562004907406</v>
+        <v>46125.39533824074</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>72</v>
@@ -2838,13 +2838,13 @@
         <v>74</v>
       </c>
       <c r="B19" s="8">
-        <v>46077.82017539351</v>
+        <v>46077.65350872686</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.53510356482</v>
+        <v>46097.36843689815</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.53512193287</v>
+        <v>46097.3684552662</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>75</v>
@@ -2903,13 +2903,13 @@
         <v>77</v>
       </c>
       <c r="B20" s="5">
-        <v>46077.82017622685</v>
+        <v>46077.65350956019</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.535863032404</v>
+        <v>46097.36919636574</v>
       </c>
       <c r="D20" s="5">
-        <v>46100.77318243055</v>
+        <v>46100.60651576389</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>78</v>
@@ -2968,13 +2968,13 @@
         <v>80</v>
       </c>
       <c r="B21" s="8">
-        <v>46077.82017653935</v>
+        <v>46077.65350987269</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.53622002315</v>
+        <v>46097.36955335648</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.53623646991</v>
+        <v>46097.36956980324</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>81</v>
@@ -3033,13 +3033,13 @@
         <v>83</v>
       </c>
       <c r="B22" s="5">
-        <v>46077.82017684028</v>
+        <v>46077.65351017361</v>
       </c>
       <c r="C22" s="5">
-        <v>46097.53624710648</v>
+        <v>46097.369580439816</v>
       </c>
       <c r="D22" s="5">
-        <v>46097.53626826389</v>
+        <v>46097.369601597224</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>84</v>
@@ -3098,13 +3098,13 @@
         <v>86</v>
       </c>
       <c r="B23" s="8">
-        <v>46077.8201771412</v>
+        <v>46077.65351047454</v>
       </c>
       <c r="C23" s="8">
-        <v>46104.62858315972</v>
+        <v>46104.461916493055</v>
       </c>
       <c r="D23" s="8">
-        <v>46112.7981115625</v>
+        <v>46112.63144489583</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>87</v>
@@ -3147,13 +3147,13 @@
         <v>89</v>
       </c>
       <c r="B24" s="5">
-        <v>46077.82017777778</v>
+        <v>46077.653511111115</v>
       </c>
       <c r="C24" s="5">
-        <v>46097.53516771991</v>
+        <v>46097.368501053235</v>
       </c>
       <c r="D24" s="5">
-        <v>46097.535187326386</v>
+        <v>46097.36852065972</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>90</v>
@@ -3212,13 +3212,13 @@
         <v>91</v>
       </c>
       <c r="B25" s="8">
-        <v>46077.82017744213</v>
+        <v>46077.65351077546</v>
       </c>
       <c r="C25" s="8">
-        <v>46097.53520844907</v>
+        <v>46097.36854178241</v>
       </c>
       <c r="D25" s="8">
-        <v>46125.56195101852</v>
+        <v>46125.39528435185</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>92</v>
@@ -3277,13 +3277,13 @@
         <v>94</v>
       </c>
       <c r="B26" s="5">
-        <v>46077.820178090275</v>
+        <v>46077.65351142361</v>
       </c>
       <c r="C26" s="5">
-        <v>46097.53883721065</v>
+        <v>46097.37217054398</v>
       </c>
       <c r="D26" s="5">
-        <v>46112.679129490745</v>
+        <v>46112.512462824074</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>95</v>
@@ -3342,13 +3342,13 @@
         <v>97</v>
       </c>
       <c r="B27" s="8">
-        <v>46077.820178379625</v>
+        <v>46077.65351171297</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.535899062495</v>
+        <v>46097.36923239584</v>
       </c>
       <c r="D27" s="8">
-        <v>46100.770078842594</v>
+        <v>46100.60341217593</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>98</v>
@@ -3407,13 +3407,13 @@
         <v>100</v>
       </c>
       <c r="B28" s="5">
-        <v>46077.82017559028</v>
+        <v>46077.65350892361</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.53652079861</v>
+        <v>46097.369854131946</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.53654111111</v>
+        <v>46097.36987444444</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>101</v>
@@ -3472,13 +3472,13 @@
         <v>104</v>
       </c>
       <c r="B29" s="8">
-        <v>46078.658673831014</v>
+        <v>46078.49200716435</v>
       </c>
       <c r="C29" s="8">
-        <v>46104.628560578705</v>
+        <v>46104.46189391204</v>
       </c>
       <c r="D29" s="8">
-        <v>46104.62858377315</v>
+        <v>46104.461917106484</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>105</v>
@@ -3537,13 +3537,13 @@
         <v>107</v>
       </c>
       <c r="B30" s="5">
-        <v>46078.65875901621</v>
+        <v>46078.49209234954</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.53675443287</v>
+        <v>46097.370087766205</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.536774548615</v>
+        <v>46097.37010788194</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>108</v>
@@ -3602,13 +3602,13 @@
         <v>110</v>
       </c>
       <c r="B31" s="8">
-        <v>46077.820175960645</v>
+        <v>46077.65350929398</v>
       </c>
       <c r="C31" s="8">
-        <v>46112.797920625</v>
+        <v>46112.63125395833</v>
       </c>
       <c r="D31" s="8">
-        <v>46112.798028969904</v>
+        <v>46112.63136230324</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>111</v>
@@ -3651,13 +3651,13 @@
         <v>113</v>
       </c>
       <c r="B32" s="5">
-        <v>46077.82017622685</v>
+        <v>46077.65350956019</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.53533090278</v>
+        <v>46097.36866423611</v>
       </c>
       <c r="D32" s="5">
-        <v>46097.535346944445</v>
+        <v>46097.36868027778</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>114</v>
@@ -3716,13 +3716,13 @@
         <v>118</v>
       </c>
       <c r="B33" s="8">
-        <v>46077.820176504625</v>
+        <v>46077.65350983797</v>
       </c>
       <c r="C33" s="8">
-        <v>46097.535274988426</v>
+        <v>46097.36860832176</v>
       </c>
       <c r="D33" s="8">
-        <v>46097.535276400464</v>
+        <v>46097.36860973379</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>119</v>
@@ -3777,13 +3777,13 @@
         <v>123</v>
       </c>
       <c r="B34" s="5">
-        <v>46077.82017679398</v>
+        <v>46077.65351012732</v>
       </c>
       <c r="C34" s="5">
-        <v>46097.53531291666</v>
+        <v>46097.368646250005</v>
       </c>
       <c r="D34" s="5">
-        <v>46097.53531515047</v>
+        <v>46097.368648483796</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>124</v>
@@ -3838,13 +3838,13 @@
         <v>126</v>
       </c>
       <c r="B35" s="8">
-        <v>46077.82017706019</v>
+        <v>46077.65351039352</v>
       </c>
       <c r="C35" s="8">
-        <v>46097.539677256944</v>
+        <v>46097.37301059028</v>
       </c>
       <c r="D35" s="8">
-        <v>46097.539690150465</v>
+        <v>46097.3730234838</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>127</v>
@@ -3903,13 +3903,13 @@
         <v>129</v>
       </c>
       <c r="B36" s="5">
-        <v>46077.82017730324</v>
+        <v>46077.65351063658</v>
       </c>
       <c r="C36" s="5">
-        <v>46097.53889979167</v>
+        <v>46097.372233125</v>
       </c>
       <c r="D36" s="5">
-        <v>46097.53890119213</v>
+        <v>46097.372234525465</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>130</v>
@@ -3964,13 +3964,13 @@
         <v>132</v>
       </c>
       <c r="B37" s="8">
-        <v>46077.82017755787</v>
+        <v>46077.65351089121</v>
       </c>
       <c r="C37" s="8">
-        <v>46097.53966361111</v>
+        <v>46097.37299694444</v>
       </c>
       <c r="D37" s="8">
-        <v>46097.53966494213</v>
+        <v>46097.37299827546</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>133</v>
@@ -4025,13 +4025,13 @@
         <v>135</v>
       </c>
       <c r="B38" s="5">
-        <v>46077.8201778125</v>
+        <v>46077.653511145836</v>
       </c>
       <c r="C38" s="5">
-        <v>46097.53600679398</v>
+        <v>46097.36934012732</v>
       </c>
       <c r="D38" s="5">
-        <v>46097.53602381944</v>
+        <v>46097.36935715278</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>136</v>
@@ -4090,13 +4090,13 @@
         <v>138</v>
       </c>
       <c r="B39" s="8">
-        <v>46077.820178055554</v>
+        <v>46077.65351138889</v>
       </c>
       <c r="C39" s="8">
-        <v>46097.53595292824</v>
+        <v>46097.36928626157</v>
       </c>
       <c r="D39" s="8">
-        <v>46097.5359540625</v>
+        <v>46097.369287395835</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>139</v>
@@ -4151,13 +4151,13 @@
         <v>141</v>
       </c>
       <c r="B40" s="5">
-        <v>46077.82017554398</v>
+        <v>46077.653508877316</v>
       </c>
       <c r="C40" s="5">
-        <v>46097.535993310186</v>
+        <v>46097.369326643515</v>
       </c>
       <c r="D40" s="5">
-        <v>46097.53599474537</v>
+        <v>46097.369328078705</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>142</v>
@@ -4212,13 +4212,13 @@
         <v>144</v>
       </c>
       <c r="B41" s="8">
-        <v>46077.82017600695</v>
+        <v>46077.65350934028</v>
       </c>
       <c r="C41" s="8">
-        <v>46097.535448055554</v>
+        <v>46097.36878138889</v>
       </c>
       <c r="D41" s="8">
-        <v>46097.5354607176</v>
+        <v>46097.368794050926</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>145</v>
@@ -4277,13 +4277,13 @@
         <v>147</v>
       </c>
       <c r="B42" s="5">
-        <v>46077.820176319445</v>
+        <v>46077.65350965278</v>
       </c>
       <c r="C42" s="5">
-        <v>46097.5353593287</v>
+        <v>46097.368692662036</v>
       </c>
       <c r="D42" s="5">
-        <v>46182.693444861114</v>
+        <v>46182.52677819444</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>148</v>
@@ -4338,13 +4338,13 @@
         <v>151</v>
       </c>
       <c r="B43" s="8">
-        <v>46077.82017663194</v>
+        <v>46077.65350996528</v>
       </c>
       <c r="C43" s="8">
-        <v>46097.53540591435</v>
+        <v>46097.368739247686</v>
       </c>
       <c r="D43" s="8">
-        <v>46097.5354075</v>
+        <v>46097.368740833335</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>152</v>
@@ -4399,13 +4399,13 @@
         <v>154</v>
       </c>
       <c r="B44" s="5">
-        <v>46077.82017693287</v>
+        <v>46077.6535102662</v>
       </c>
       <c r="C44" s="5">
-        <v>46097.53543202546</v>
+        <v>46097.3687653588</v>
       </c>
       <c r="D44" s="5">
-        <v>46097.535433425925</v>
+        <v>46097.36876675926</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>155</v>
@@ -4460,13 +4460,13 @@
         <v>157</v>
       </c>
       <c r="B45" s="8">
-        <v>46077.82017723379</v>
+        <v>46077.65351056713</v>
       </c>
       <c r="C45" s="8">
-        <v>46097.53668680556</v>
+        <v>46097.370020138886</v>
       </c>
       <c r="D45" s="8">
-        <v>46097.53669974537</v>
+        <v>46097.3700330787</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>158</v>
@@ -4525,13 +4525,13 @@
         <v>162</v>
       </c>
       <c r="B46" s="5">
-        <v>46077.82017756945</v>
+        <v>46077.653510902775</v>
       </c>
       <c r="C46" s="5">
-        <v>46097.53660920139</v>
+        <v>46097.36994253472</v>
       </c>
       <c r="D46" s="5">
-        <v>46097.53661077547</v>
+        <v>46097.369944108796</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>163</v>
@@ -4586,13 +4586,13 @@
         <v>165</v>
       </c>
       <c r="B47" s="8">
-        <v>46077.820177870366</v>
+        <v>46077.65351120371</v>
       </c>
       <c r="C47" s="8">
-        <v>46097.53667238426</v>
+        <v>46097.37000571759</v>
       </c>
       <c r="D47" s="8">
-        <v>46097.536673703704</v>
+        <v>46097.37000703704</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>166</v>
@@ -4647,13 +4647,13 @@
         <v>167</v>
       </c>
       <c r="B48" s="5">
-        <v>46078.65559880787</v>
+        <v>46078.488932141205</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.840353321764</v>
+        <v>46107.67368665509</v>
       </c>
       <c r="D48" s="5">
-        <v>46107.84042637731</v>
+        <v>46107.67375971065</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>168</v>
@@ -4712,13 +4712,13 @@
         <v>170</v>
       </c>
       <c r="B49" s="8">
-        <v>46078.655658090276</v>
+        <v>46078.48899142361</v>
       </c>
       <c r="C49" s="8">
-        <v>46107.840243784725</v>
+        <v>46107.673577118054</v>
       </c>
       <c r="D49" s="8">
-        <v>46107.84024543982</v>
+        <v>46107.673578773145</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>171</v>
@@ -4773,13 +4773,13 @@
         <v>173</v>
       </c>
       <c r="B50" s="5">
-        <v>46078.65577003472</v>
+        <v>46078.489103368054</v>
       </c>
       <c r="C50" s="5">
-        <v>46107.84033813658</v>
+        <v>46107.67367146991</v>
       </c>
       <c r="D50" s="5">
-        <v>46107.84033961805</v>
+        <v>46107.673672951394</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>174</v>
@@ -4834,13 +4834,13 @@
         <v>176</v>
       </c>
       <c r="B51" s="8">
-        <v>46078.654245046295</v>
+        <v>46078.48757837963</v>
       </c>
       <c r="C51" s="8">
-        <v>46105.78341087963</v>
+        <v>46105.616744212966</v>
       </c>
       <c r="D51" s="8">
-        <v>46105.78342381945</v>
+        <v>46105.61675715278</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>177</v>
@@ -4899,13 +4899,13 @@
         <v>181</v>
       </c>
       <c r="B52" s="5">
-        <v>46078.65429936342</v>
+        <v>46078.487632696764</v>
       </c>
       <c r="C52" s="5">
-        <v>46097.53685579861</v>
+        <v>46097.37018913194</v>
       </c>
       <c r="D52" s="5">
-        <v>46111.65554150463</v>
+        <v>46111.48887483796</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>182</v>
@@ -4960,13 +4960,13 @@
         <v>184</v>
       </c>
       <c r="B53" s="8">
-        <v>46078.65468994213</v>
+        <v>46078.488023275466</v>
       </c>
       <c r="C53" s="8">
-        <v>46105.78339252315</v>
+        <v>46105.61672585648</v>
       </c>
       <c r="D53" s="8">
-        <v>46105.7833940625</v>
+        <v>46105.616727395834</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>185</v>
@@ -5021,13 +5021,13 @@
         <v>188</v>
       </c>
       <c r="B54" s="5">
-        <v>46104.63046165509</v>
+        <v>46104.46379498843</v>
       </c>
       <c r="C54" s="5">
-        <v>46105.75381335648</v>
+        <v>46105.58714668981</v>
       </c>
       <c r="D54" s="5">
-        <v>46107.67902436343</v>
+        <v>46107.51235769676</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>189</v>
@@ -5076,13 +5076,13 @@
         <v>190</v>
       </c>
       <c r="B55" s="8">
-        <v>46104.631274988424</v>
+        <v>46104.46460832176</v>
       </c>
       <c r="C55" s="8">
-        <v>46104.647564768515</v>
+        <v>46104.48089810185</v>
       </c>
       <c r="D55" s="8">
-        <v>46107.67921902778</v>
+        <v>46107.512552361106</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>191</v>
@@ -5131,13 +5131,13 @@
         <v>192</v>
       </c>
       <c r="B56" s="5">
-        <v>46104.631671678246</v>
+        <v>46104.465005011574</v>
       </c>
       <c r="C56" s="5">
-        <v>46104.646698553246</v>
+        <v>46104.480031886575</v>
       </c>
       <c r="D56" s="5">
-        <v>46107.67933054398</v>
+        <v>46107.512663877314</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>193</v>
@@ -5186,13 +5186,13 @@
         <v>194</v>
       </c>
       <c r="B57" s="8">
-        <v>46104.63195700232</v>
+        <v>46104.46529033565</v>
       </c>
       <c r="C57" s="8">
-        <v>46104.64636196759</v>
+        <v>46104.47969530092</v>
       </c>
       <c r="D57" s="8">
-        <v>46107.67943891203</v>
+        <v>46107.51277224537</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>195</v>
@@ -5241,13 +5241,13 @@
         <v>196</v>
       </c>
       <c r="B58" s="5">
-        <v>46104.632084826386</v>
+        <v>46104.46541815972</v>
       </c>
       <c r="C58" s="5">
-        <v>46104.64567174768</v>
+        <v>46104.47900508102</v>
       </c>
       <c r="D58" s="5">
-        <v>46107.67985042824</v>
+        <v>46107.51318376158</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>197</v>
@@ -5296,13 +5296,13 @@
         <v>198</v>
       </c>
       <c r="B59" s="8">
-        <v>46104.63227371528</v>
+        <v>46104.46560704861</v>
       </c>
       <c r="C59" s="8">
-        <v>46104.644934375</v>
+        <v>46104.478267708335</v>
       </c>
       <c r="D59" s="8">
-        <v>46107.67955858796</v>
+        <v>46107.512891921295</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>199</v>
@@ -5351,13 +5351,13 @@
         <v>200</v>
       </c>
       <c r="B60" s="5">
-        <v>46077.82017815972</v>
+        <v>46077.65351149306</v>
       </c>
       <c r="C60" s="5">
-        <v>46114.767718206014</v>
+        <v>46114.60105153936</v>
       </c>
       <c r="D60" s="5">
-        <v>46114.84872589121</v>
+        <v>46114.682059224535</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>201</v>
@@ -5402,13 +5402,13 @@
         <v>203</v>
       </c>
       <c r="B61" s="8">
-        <v>46077.82017846065</v>
+        <v>46077.65351179398</v>
       </c>
       <c r="C61" s="8">
-        <v>46097.537088275465</v>
+        <v>46097.37042160879</v>
       </c>
       <c r="D61" s="8">
-        <v>46197.707138425925</v>
+        <v>46197.54047175926</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>204</v>
@@ -5467,13 +5467,13 @@
         <v>208</v>
       </c>
       <c r="B62" s="5">
-        <v>46077.82017626158</v>
+        <v>46077.65350959491</v>
       </c>
       <c r="C62" s="5">
-        <v>46097.537140636574</v>
+        <v>46097.3704739699</v>
       </c>
       <c r="D62" s="5">
-        <v>46197.707159328704</v>
+        <v>46197.54049266204</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>209</v>
@@ -5532,13 +5532,13 @@
         <v>212</v>
       </c>
       <c r="B63" s="8">
-        <v>46090.87971813657</v>
+        <v>46090.71305146991</v>
       </c>
       <c r="C63" s="8">
-        <v>46097.537211319446</v>
+        <v>46097.370544652775</v>
       </c>
       <c r="D63" s="8">
-        <v>46114.650833692125</v>
+        <v>46114.48416702547</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>213</v>
@@ -5595,13 +5595,13 @@
         <v>217</v>
       </c>
       <c r="B64" s="5">
-        <v>46090.8798415162</v>
+        <v>46090.71317484954</v>
       </c>
       <c r="C64" s="5">
-        <v>46114.76770096065</v>
+        <v>46114.601034293984</v>
       </c>
       <c r="D64" s="5">
-        <v>46119.77882065972</v>
+        <v>46119.61215399306</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>218</v>
@@ -5660,13 +5660,13 @@
         <v>222</v>
       </c>
       <c r="B65" s="8">
-        <v>46107.60619210648</v>
+        <v>46107.43952543981</v>
       </c>
       <c r="C65" s="8">
-        <v>46114.78855440972</v>
+        <v>46114.62188774305</v>
       </c>
       <c r="D65" s="8">
-        <v>46114.78855586806</v>
+        <v>46114.621889201386</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>223</v>
@@ -5713,13 +5713,13 @@
         <v>225</v>
       </c>
       <c r="B66" s="5">
-        <v>46107.60640244213</v>
+        <v>46107.439735775464</v>
       </c>
       <c r="C66" s="5">
-        <v>46114.78858121528</v>
+        <v>46114.62191454861</v>
       </c>
       <c r="D66" s="5">
-        <v>46114.7885828125</v>
+        <v>46114.62191614583</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>226</v>
@@ -5766,13 +5766,13 @@
         <v>227</v>
       </c>
       <c r="B67" s="8">
-        <v>46107.606435821755</v>
+        <v>46107.43976915509</v>
       </c>
       <c r="C67" s="8">
-        <v>46108.65907060185</v>
+        <v>46108.49240393519</v>
       </c>
       <c r="D67" s="8">
-        <v>46114.84832498843</v>
+        <v>46114.68165832176</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>228</v>
@@ -5819,13 +5819,13 @@
         <v>230</v>
       </c>
       <c r="B68" s="5">
-        <v>46107.60648386574</v>
+        <v>46107.439817199076</v>
       </c>
       <c r="C68" s="5">
-        <v>46108.65908678241</v>
+        <v>46108.49242011574</v>
       </c>
       <c r="D68" s="5">
-        <v>46114.84847162037</v>
+        <v>46114.6818049537</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>231</v>
@@ -5872,13 +5872,13 @@
         <v>232</v>
       </c>
       <c r="B69" s="8">
-        <v>46078.65390563657</v>
+        <v>46078.48723896991</v>
       </c>
       <c r="C69" s="8">
-        <v>46105.85624208333</v>
+        <v>46105.68957541666</v>
       </c>
       <c r="D69" s="8">
-        <v>46107.68737451389</v>
+        <v>46107.52070784722</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>233</v>
@@ -5925,13 +5925,13 @@
         <v>236</v>
       </c>
       <c r="B70" s="5">
-        <v>46078.702559108795</v>
+        <v>46078.53589244213</v>
       </c>
       <c r="C70" s="5">
-        <v>46105.856224710646</v>
+        <v>46105.68955804398</v>
       </c>
       <c r="D70" s="5">
-        <v>46107.840496770834</v>
+        <v>46107.67383010416</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>234</v>
@@ -5990,13 +5990,13 @@
         <v>241</v>
       </c>
       <c r="B71" s="8">
-        <v>46077.82017896991</v>
+        <v>46077.65351230324</v>
       </c>
       <c r="C71" s="8">
-        <v>46107.84387899305</v>
+        <v>46107.67721232639</v>
       </c>
       <c r="D71" s="8">
-        <v>46107.843893425925</v>
+        <v>46107.67722675926</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>242</v>
@@ -6043,13 +6043,13 @@
         <v>244</v>
       </c>
       <c r="B72" s="5">
-        <v>46077.820179305556</v>
+        <v>46077.65351263889</v>
       </c>
       <c r="C72" s="5">
-        <v>46107.84233932871</v>
+        <v>46107.67567266204</v>
       </c>
       <c r="D72" s="5">
-        <v>46107.842354259265</v>
+        <v>46107.67568759259</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>245</v>
@@ -6108,13 +6108,13 @@
         <v>249</v>
       </c>
       <c r="B73" s="8">
-        <v>46077.820177430556</v>
+        <v>46077.65351076389</v>
       </c>
       <c r="C73" s="8">
-        <v>46107.84386201389</v>
+        <v>46107.67719534722</v>
       </c>
       <c r="D73" s="8">
-        <v>46107.84388002315</v>
+        <v>46107.67721335648</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>57</v>
@@ -6173,13 +6173,13 @@
         <v>251</v>
       </c>
       <c r="B74" s="5">
-        <v>46077.82017795139</v>
+        <v>46077.65351128472</v>
       </c>
       <c r="C74" s="5">
-        <v>46107.84192445602</v>
+        <v>46107.67525778935</v>
       </c>
       <c r="D74" s="5">
-        <v>46107.841941238425</v>
+        <v>46107.67527457176</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>252</v>
@@ -6238,13 +6238,13 @@
         <v>254</v>
       </c>
       <c r="B75" s="8">
-        <v>46077.82017841435</v>
+        <v>46077.65351174769</v>
       </c>
       <c r="C75" s="8">
-        <v>46107.8418262037</v>
+        <v>46107.67515953704</v>
       </c>
       <c r="D75" s="8">
-        <v>46107.841844375</v>
+        <v>46107.675177708334</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>255</v>
@@ -6303,13 +6303,13 @@
         <v>256</v>
       </c>
       <c r="B76" s="5">
-        <v>46078.65892270833</v>
+        <v>46078.49225604167</v>
       </c>
       <c r="C76" s="5">
-        <v>46107.84286186342</v>
+        <v>46107.676195196764</v>
       </c>
       <c r="D76" s="5">
-        <v>46107.84287946759</v>
+        <v>46107.67621280093</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>257</v>
@@ -6368,13 +6368,13 @@
         <v>258</v>
       </c>
       <c r="B77" s="8">
-        <v>46078.65900237269</v>
+        <v>46078.49233570602</v>
       </c>
       <c r="C77" s="8">
-        <v>46107.84237565972</v>
+        <v>46107.675708993054</v>
       </c>
       <c r="D77" s="8">
-        <v>46107.842393032406</v>
+        <v>46107.67572636574</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>259</v>
@@ -6433,13 +6433,13 @@
         <v>260</v>
       </c>
       <c r="B78" s="5">
-        <v>46077.82017907407</v>
+        <v>46077.65351240741</v>
       </c>
       <c r="C78" s="5">
-        <v>46118.851152337964</v>
+        <v>46118.6844856713</v>
       </c>
       <c r="D78" s="5">
-        <v>46125.56179637731</v>
+        <v>46125.39512971065</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>261</v>
@@ -6484,13 +6484,13 @@
         <v>263</v>
       </c>
       <c r="B79" s="8">
-        <v>46077.82017943287</v>
+        <v>46077.65351276621</v>
       </c>
       <c r="C79" s="8">
-        <v>46113.557951111114</v>
+        <v>46113.39128444444</v>
       </c>
       <c r="D79" s="8">
-        <v>46114.85330988426</v>
+        <v>46114.68664321759</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>264</v>
@@ -6549,13 +6549,13 @@
         <v>266</v>
       </c>
       <c r="B80" s="5">
-        <v>46107.59662881945</v>
+        <v>46107.429962152775</v>
       </c>
       <c r="C80" s="5">
-        <v>46113.557604340276</v>
+        <v>46113.39093767361</v>
       </c>
       <c r="D80" s="5">
-        <v>46114.856069733796</v>
+        <v>46114.689403067125</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>224</v>
@@ -6604,13 +6604,13 @@
         <v>268</v>
       </c>
       <c r="B81" s="8">
-        <v>46107.59776125</v>
+        <v>46107.431094583335</v>
       </c>
       <c r="C81" s="8">
-        <v>46113.5576187963</v>
+        <v>46113.39095212963</v>
       </c>
       <c r="D81" s="8">
-        <v>46114.856118923606</v>
+        <v>46114.68945225695</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>224</v>
@@ -6659,13 +6659,13 @@
         <v>269</v>
       </c>
       <c r="B82" s="5">
-        <v>46107.597173993054</v>
+        <v>46107.43050732639</v>
       </c>
       <c r="C82" s="5">
-        <v>46107.838732662036</v>
+        <v>46107.67206599537</v>
       </c>
       <c r="D82" s="5">
-        <v>46107.83873434028</v>
+        <v>46107.672067673615</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>228</v>
@@ -6714,13 +6714,13 @@
         <v>271</v>
       </c>
       <c r="B83" s="8">
-        <v>46107.59746188657</v>
+        <v>46107.43079521991</v>
       </c>
       <c r="C83" s="8">
-        <v>46107.83873872685</v>
+        <v>46107.67207206019</v>
       </c>
       <c r="D83" s="8">
-        <v>46107.83874050926</v>
+        <v>46107.672073842594</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>231</v>
@@ -6769,13 +6769,13 @@
         <v>273</v>
       </c>
       <c r="B84" s="5">
-        <v>46077.82017980324</v>
+        <v>46077.653513136574</v>
       </c>
       <c r="C84" s="5">
-        <v>46113.557691643524</v>
+        <v>46113.39102497685</v>
       </c>
       <c r="D84" s="5">
-        <v>46125.56182928241</v>
+        <v>46125.395162615736</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>274</v>
@@ -6834,13 +6834,13 @@
         <v>277</v>
       </c>
       <c r="B85" s="8">
-        <v>46107.59978276621</v>
+        <v>46107.433116099535</v>
       </c>
       <c r="C85" s="8">
-        <v>46113.558251215276</v>
+        <v>46113.39158454861</v>
       </c>
       <c r="D85" s="8">
-        <v>46114.855711296295</v>
+        <v>46114.68904462963</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>224</v>
@@ -6889,13 +6889,13 @@
         <v>280</v>
       </c>
       <c r="B86" s="5">
-        <v>46107.59982243055</v>
+        <v>46107.433155763894</v>
       </c>
       <c r="C86" s="5">
-        <v>46113.55826416667</v>
+        <v>46113.3915975</v>
       </c>
       <c r="D86" s="5">
-        <v>46114.85576582176</v>
+        <v>46114.68909915509</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>224</v>
@@ -6944,13 +6944,13 @@
         <v>281</v>
       </c>
       <c r="B87" s="8">
-        <v>46107.59986486111</v>
+        <v>46107.43319819444</v>
       </c>
       <c r="C87" s="8">
-        <v>46107.84839290509</v>
+        <v>46107.68172623843</v>
       </c>
       <c r="D87" s="8">
-        <v>46107.84839457176</v>
+        <v>46107.68172790509</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>228</v>
@@ -6999,13 +6999,13 @@
         <v>284</v>
       </c>
       <c r="B88" s="5">
-        <v>46107.59991125</v>
+        <v>46107.43324458333</v>
       </c>
       <c r="C88" s="5">
-        <v>46107.84838658565</v>
+        <v>46107.68171991898</v>
       </c>
       <c r="D88" s="5">
-        <v>46107.8483881713</v>
+        <v>46107.68172150463</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>231</v>
@@ -7054,13 +7054,13 @@
         <v>287</v>
       </c>
       <c r="B89" s="8">
-        <v>46077.82018026621</v>
+        <v>46077.65351359954</v>
       </c>
       <c r="C89" s="8">
-        <v>46113.557744375</v>
+        <v>46113.39107770834</v>
       </c>
       <c r="D89" s="8">
-        <v>46125.56184609953</v>
+        <v>46125.395179432875</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>288</v>
@@ -7119,13 +7119,13 @@
         <v>290</v>
       </c>
       <c r="B90" s="5">
-        <v>46107.59995462963</v>
+        <v>46107.433287962966</v>
       </c>
       <c r="C90" s="5">
-        <v>46113.55834841436</v>
+        <v>46113.391681747686</v>
       </c>
       <c r="D90" s="5">
-        <v>46114.85594553241</v>
+        <v>46114.68927886574</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>291</v>
@@ -7174,13 +7174,13 @@
         <v>294</v>
       </c>
       <c r="B91" s="8">
-        <v>46107.60002673611</v>
+        <v>46107.433360069444</v>
       </c>
       <c r="C91" s="8">
-        <v>46113.55836547454</v>
+        <v>46113.39169880787</v>
       </c>
       <c r="D91" s="8">
-        <v>46114.85576615741</v>
+        <v>46114.689099490744</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>291</v>
@@ -7229,13 +7229,13 @@
         <v>296</v>
       </c>
       <c r="B92" s="5">
-        <v>46107.60006982639</v>
+        <v>46107.433403159725</v>
       </c>
       <c r="C92" s="5">
-        <v>46107.84843891204</v>
+        <v>46107.68177224537</v>
       </c>
       <c r="D92" s="5">
-        <v>46107.84844032407</v>
+        <v>46107.68177365741</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>228</v>
@@ -7284,13 +7284,13 @@
         <v>299</v>
       </c>
       <c r="B93" s="8">
-        <v>46107.600104930556</v>
+        <v>46107.43343826389</v>
       </c>
       <c r="C93" s="8">
-        <v>46107.84843344908</v>
+        <v>46107.68176678241</v>
       </c>
       <c r="D93" s="8">
-        <v>46107.84843525463</v>
+        <v>46107.681768587965</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>231</v>
@@ -7339,13 +7339,13 @@
         <v>302</v>
       </c>
       <c r="B94" s="5">
-        <v>46077.82018063657</v>
+        <v>46077.65351396991</v>
       </c>
       <c r="C94" s="5">
-        <v>46113.55781333333</v>
+        <v>46113.39114666666</v>
       </c>
       <c r="D94" s="5">
-        <v>46125.56186803241</v>
+        <v>46125.39520136574</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>303</v>
@@ -7404,13 +7404,13 @@
         <v>304</v>
       </c>
       <c r="B95" s="8">
-        <v>46107.60121979167</v>
+        <v>46107.434553125</v>
       </c>
       <c r="C95" s="8">
-        <v>46113.55840587963</v>
+        <v>46113.391739212966</v>
       </c>
       <c r="D95" s="8">
-        <v>46114.8505327662</v>
+        <v>46114.68386609954</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>224</v>
@@ -7459,13 +7459,13 @@
         <v>307</v>
       </c>
       <c r="B96" s="5">
-        <v>46107.601296249995</v>
+        <v>46107.43462958334</v>
       </c>
       <c r="C96" s="5">
-        <v>46113.558420057874</v>
+        <v>46113.3917533912</v>
       </c>
       <c r="D96" s="5">
-        <v>46114.850774618055</v>
+        <v>46114.68410795139</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>224</v>
@@ -7514,13 +7514,13 @@
         <v>309</v>
       </c>
       <c r="B97" s="8">
-        <v>46107.601343993054</v>
+        <v>46107.43467732639</v>
       </c>
       <c r="C97" s="8">
-        <v>46107.848516342594</v>
+        <v>46107.68184967592</v>
       </c>
       <c r="D97" s="8">
-        <v>46107.84851795139</v>
+        <v>46107.681851284724</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>228</v>
@@ -7569,13 +7569,13 @@
         <v>312</v>
       </c>
       <c r="B98" s="5">
-        <v>46107.60138634259</v>
+        <v>46107.434719675926</v>
       </c>
       <c r="C98" s="5">
-        <v>46107.84851134259</v>
+        <v>46107.68184467593</v>
       </c>
       <c r="D98" s="5">
-        <v>46107.84851336805</v>
+        <v>46107.68184670139</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>231</v>
@@ -7624,13 +7624,13 @@
         <v>315</v>
       </c>
       <c r="B99" s="8">
-        <v>46078.65921471065</v>
+        <v>46078.492548043985</v>
       </c>
       <c r="C99" s="8">
-        <v>46114.64467627315</v>
+        <v>46114.47800960648</v>
       </c>
       <c r="D99" s="8">
-        <v>46114.65083799769</v>
+        <v>46114.484171331016</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>316</v>
@@ -7689,13 +7689,13 @@
         <v>318</v>
       </c>
       <c r="B100" s="5">
-        <v>46107.60145327546</v>
+        <v>46107.43478660879</v>
       </c>
       <c r="C100" s="5">
-        <v>46114.64465515046</v>
+        <v>46114.47798848379</v>
       </c>
       <c r="D100" s="5">
-        <v>46114.8498778125</v>
+        <v>46114.683211145835</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>224</v>
@@ -7744,13 +7744,13 @@
         <v>320</v>
       </c>
       <c r="B101" s="8">
-        <v>46107.60152523148</v>
+        <v>46107.43485856481</v>
       </c>
       <c r="C101" s="8">
-        <v>46114.6446628125</v>
+        <v>46114.47799614583</v>
       </c>
       <c r="D101" s="8">
-        <v>46114.85000983796</v>
+        <v>46114.683343171295</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>224</v>
@@ -7799,13 +7799,13 @@
         <v>322</v>
       </c>
       <c r="B102" s="5">
-        <v>46107.60156221065</v>
+        <v>46107.43489554398</v>
       </c>
       <c r="C102" s="5">
-        <v>46107.84856559028</v>
+        <v>46107.68189892361</v>
       </c>
       <c r="D102" s="5">
-        <v>46107.84856730324</v>
+        <v>46107.68190063657</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>228</v>
@@ -7854,13 +7854,13 @@
         <v>324</v>
       </c>
       <c r="B103" s="8">
-        <v>46107.60160730324</v>
+        <v>46107.43494063657</v>
       </c>
       <c r="C103" s="8">
-        <v>46107.84855876157</v>
+        <v>46107.68189209491</v>
       </c>
       <c r="D103" s="8">
-        <v>46107.84856039352</v>
+        <v>46107.681893726854</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>231</v>
@@ -7909,13 +7909,13 @@
         <v>326</v>
       </c>
       <c r="B104" s="5">
-        <v>46077.820181030096</v>
+        <v>46077.653514363425</v>
       </c>
       <c r="C104" s="5">
-        <v>46114.64478351852</v>
+        <v>46114.47811685185</v>
       </c>
       <c r="D104" s="5">
-        <v>46125.56189244213</v>
+        <v>46125.395225775464</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>327</v>
@@ -7974,13 +7974,13 @@
         <v>330</v>
       </c>
       <c r="B105" s="8">
-        <v>46107.60168349537</v>
+        <v>46107.435016828706</v>
       </c>
       <c r="C105" s="8">
-        <v>46114.644762384254</v>
+        <v>46114.4780957176</v>
       </c>
       <c r="D105" s="8">
-        <v>46114.8557116088</v>
+        <v>46114.68904494213</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>224</v>
@@ -8027,13 +8027,13 @@
         <v>332</v>
       </c>
       <c r="B106" s="5">
-        <v>46107.60175594907</v>
+        <v>46107.43508928241</v>
       </c>
       <c r="C106" s="5">
-        <v>46114.64476732639</v>
+        <v>46114.47810065972</v>
       </c>
       <c r="D106" s="5">
-        <v>46114.85576636574</v>
+        <v>46114.68909969907</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>224</v>
@@ -8080,13 +8080,13 @@
         <v>333</v>
       </c>
       <c r="B107" s="8">
-        <v>46107.6017900463</v>
+        <v>46107.43512337963</v>
       </c>
       <c r="C107" s="8">
-        <v>46107.84861380787</v>
+        <v>46107.6819471412</v>
       </c>
       <c r="D107" s="8">
-        <v>46114.84731824074</v>
+        <v>46114.680651574075</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>228</v>
@@ -8135,13 +8135,13 @@
         <v>335</v>
       </c>
       <c r="B108" s="5">
-        <v>46107.60182489583</v>
+        <v>46107.43515822917</v>
       </c>
       <c r="C108" s="5">
-        <v>46107.8486083912</v>
+        <v>46107.68194172454</v>
       </c>
       <c r="D108" s="5">
-        <v>46114.84743204861</v>
+        <v>46114.68076538194</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>231</v>
@@ -8190,13 +8190,13 @@
         <v>337</v>
       </c>
       <c r="B109" s="8">
-        <v>46077.82018142361</v>
+        <v>46077.653514756945</v>
       </c>
       <c r="C109" s="8">
-        <v>46118.85113606481</v>
+        <v>46118.68446939815</v>
       </c>
       <c r="D109" s="8">
-        <v>46118.86139821759</v>
+        <v>46118.694731550924</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>338</v>
@@ -8255,13 +8255,13 @@
         <v>339</v>
       </c>
       <c r="B110" s="5">
-        <v>46107.60187090278</v>
+        <v>46107.43520423611</v>
       </c>
       <c r="C110" s="5">
-        <v>46114.85197863426</v>
+        <v>46114.685311967594</v>
       </c>
       <c r="D110" s="5">
-        <v>46114.8519803588</v>
+        <v>46114.68531369213</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>224</v>
@@ -8308,13 +8308,13 @@
         <v>341</v>
       </c>
       <c r="B111" s="8">
-        <v>46107.60193765046</v>
+        <v>46107.4352709838</v>
       </c>
       <c r="C111" s="8">
-        <v>46118.85106515046</v>
+        <v>46118.6843984838</v>
       </c>
       <c r="D111" s="8">
-        <v>46118.86156471065</v>
+        <v>46118.69489804398</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>224</v>
@@ -8361,13 +8361,13 @@
         <v>342</v>
       </c>
       <c r="B112" s="5">
-        <v>46107.601981064814</v>
+        <v>46107.43531439815</v>
       </c>
       <c r="C112" s="5">
-        <v>46108.66388262731</v>
+        <v>46108.49721596065</v>
       </c>
       <c r="D112" s="5">
-        <v>46114.84918898148</v>
+        <v>46114.68252231482</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>228</v>
@@ -8414,13 +8414,13 @@
         <v>344</v>
       </c>
       <c r="B113" s="8">
-        <v>46107.60201515046</v>
+        <v>46107.43534848379</v>
       </c>
       <c r="C113" s="8">
-        <v>46108.66389119213</v>
+        <v>46108.49722452546</v>
       </c>
       <c r="D113" s="8">
-        <v>46114.84926967593</v>
+        <v>46114.68260300926</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>231</v>
@@ -8469,13 +8469,13 @@
         <v>346</v>
       </c>
       <c r="B114" s="5">
-        <v>46077.82017553241</v>
+        <v>46077.65350886574</v>
       </c>
       <c r="C114" s="5">
-        <v>46125.56091158565</v>
+        <v>46125.39424491898</v>
       </c>
       <c r="D114" s="5">
-        <v>46125.561711898146</v>
+        <v>46125.39504523148</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>347</v>
@@ -8518,13 +8518,13 @@
         <v>349</v>
       </c>
       <c r="B115" s="8">
-        <v>46077.82017586805</v>
+        <v>46077.65350920139</v>
       </c>
       <c r="C115" s="8">
-        <v>46121.840045046294</v>
+        <v>46121.67337837963</v>
       </c>
       <c r="D115" s="8">
-        <v>46121.840061724535</v>
+        <v>46121.67339505787</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>350</v>
@@ -8583,13 +8583,13 @@
         <v>354</v>
       </c>
       <c r="B116" s="5">
-        <v>46107.6021821412</v>
+        <v>46107.435515474535</v>
       </c>
       <c r="C116" s="5">
-        <v>46121.840014456015</v>
+        <v>46121.67334778935</v>
       </c>
       <c r="D116" s="5">
-        <v>46121.84001659723</v>
+        <v>46121.673349930556</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>224</v>
@@ -8636,13 +8636,13 @@
         <v>356</v>
       </c>
       <c r="B117" s="8">
-        <v>46107.60222542824</v>
+        <v>46107.43555876157</v>
       </c>
       <c r="C117" s="8">
-        <v>46121.84002578704</v>
+        <v>46121.67335912037</v>
       </c>
       <c r="D117" s="8">
-        <v>46121.84002737269</v>
+        <v>46121.673360706016</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>224</v>
@@ -8689,13 +8689,13 @@
         <v>357</v>
       </c>
       <c r="B118" s="5">
-        <v>46107.602255370366</v>
+        <v>46107.43558870371</v>
       </c>
       <c r="C118" s="5">
-        <v>46108.66400405092</v>
+        <v>46108.49733738426</v>
       </c>
       <c r="D118" s="5">
-        <v>46114.85951420139</v>
+        <v>46114.69284753472</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>228</v>
@@ -8744,13 +8744,13 @@
         <v>359</v>
       </c>
       <c r="B119" s="8">
-        <v>46107.60228831018</v>
+        <v>46107.43562164352</v>
       </c>
       <c r="C119" s="8">
-        <v>46108.66402913195</v>
+        <v>46108.49736246528</v>
       </c>
       <c r="D119" s="8">
-        <v>46114.85957398148</v>
+        <v>46114.69290731481</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>231</v>
@@ -8797,13 +8797,13 @@
         <v>361</v>
       </c>
       <c r="B120" s="5">
-        <v>46107.63652371528</v>
+        <v>46107.46985704861</v>
       </c>
       <c r="C120" s="5">
-        <v>46109.73451819444</v>
+        <v>46109.56785152778</v>
       </c>
       <c r="D120" s="5">
-        <v>46109.73451969908</v>
+        <v>46109.56785303241</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>56</v>
@@ -8850,13 +8850,13 @@
         <v>363</v>
       </c>
       <c r="B121" s="8">
-        <v>46107.636567430556</v>
+        <v>46107.469900763885</v>
       </c>
       <c r="C121" s="8">
-        <v>46109.732098368055</v>
+        <v>46109.56543170139</v>
       </c>
       <c r="D121" s="8">
-        <v>46109.73209987269</v>
+        <v>46109.56543320602</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>60</v>
@@ -8903,13 +8903,13 @@
         <v>365</v>
       </c>
       <c r="B122" s="5">
-        <v>46107.63660021991</v>
+        <v>46107.46993355324</v>
       </c>
       <c r="C122" s="5">
-        <v>46109.732142152774</v>
+        <v>46109.56547548611</v>
       </c>
       <c r="D122" s="5">
-        <v>46109.732143483794</v>
+        <v>46109.56547681713</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>63</v>
@@ -8956,13 +8956,13 @@
         <v>367</v>
       </c>
       <c r="B123" s="8">
-        <v>46107.63664055556</v>
+        <v>46107.46997388889</v>
       </c>
       <c r="C123" s="8">
-        <v>46113.5665987963</v>
+        <v>46113.39993212963</v>
       </c>
       <c r="D123" s="8">
-        <v>46113.566600289356</v>
+        <v>46113.399933622684</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>66</v>
@@ -9009,13 +9009,13 @@
         <v>369</v>
       </c>
       <c r="B124" s="5">
-        <v>46107.63667821759</v>
+        <v>46107.470011550926</v>
       </c>
       <c r="C124" s="5">
-        <v>46113.56660976852</v>
+        <v>46113.39994310185</v>
       </c>
       <c r="D124" s="5">
-        <v>46113.56661126157</v>
+        <v>46113.39994459491</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>69</v>
@@ -9062,13 +9062,13 @@
         <v>371</v>
       </c>
       <c r="B125" s="8">
-        <v>46077.82017615741</v>
+        <v>46077.653509490745</v>
       </c>
       <c r="C125" s="8">
-        <v>46122.61245885417</v>
+        <v>46122.4457921875</v>
       </c>
       <c r="D125" s="8">
-        <v>46126.17015332176</v>
+        <v>46126.00348665509</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>372</v>
@@ -9127,13 +9127,13 @@
         <v>374</v>
       </c>
       <c r="B126" s="5">
-        <v>46107.60233217593</v>
+        <v>46107.435665509256</v>
       </c>
       <c r="C126" s="5">
-        <v>46122.612434027775</v>
+        <v>46122.44576736111</v>
       </c>
       <c r="D126" s="5">
-        <v>46122.612435717594</v>
+        <v>46122.44576905093</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>224</v>
@@ -9182,13 +9182,13 @@
         <v>376</v>
       </c>
       <c r="B127" s="8">
-        <v>46107.60239986111</v>
+        <v>46107.43573319445</v>
       </c>
       <c r="C127" s="8">
-        <v>46122.61244532408</v>
+        <v>46122.445778657406</v>
       </c>
       <c r="D127" s="8">
-        <v>46122.61244673611</v>
+        <v>46122.44578006944</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>224</v>
@@ -9237,13 +9237,13 @@
         <v>377</v>
       </c>
       <c r="B128" s="5">
-        <v>46107.60243372685</v>
+        <v>46107.43576706019</v>
       </c>
       <c r="C128" s="5">
-        <v>46108.664157962965</v>
+        <v>46108.49749129629</v>
       </c>
       <c r="D128" s="5">
-        <v>46114.85951381944</v>
+        <v>46114.69284715278</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>228</v>
@@ -9292,13 +9292,13 @@
         <v>379</v>
       </c>
       <c r="B129" s="8">
-        <v>46107.602471805556</v>
+        <v>46107.435805138884</v>
       </c>
       <c r="C129" s="8">
-        <v>46108.66416608796</v>
+        <v>46108.4974994213</v>
       </c>
       <c r="D129" s="8">
-        <v>46114.859573194444</v>
+        <v>46114.69290652778</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>231</v>
@@ -9347,13 +9347,13 @@
         <v>381</v>
       </c>
       <c r="B130" s="5">
-        <v>46107.63866758102</v>
+        <v>46107.47200091435</v>
       </c>
       <c r="C130" s="5">
-        <v>46109.73461930556</v>
+        <v>46109.567952638885</v>
       </c>
       <c r="D130" s="5">
-        <v>46109.734620717594</v>
+        <v>46109.56795405093</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>56</v>
@@ -9402,13 +9402,13 @@
         <v>383</v>
       </c>
       <c r="B131" s="8">
-        <v>46107.63871274306</v>
+        <v>46107.47204607639</v>
       </c>
       <c r="C131" s="8">
-        <v>46109.73462969907</v>
+        <v>46109.56796303241</v>
       </c>
       <c r="D131" s="8">
-        <v>46109.73463119213</v>
+        <v>46109.567964525464</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>60</v>
@@ -9457,13 +9457,13 @@
         <v>385</v>
       </c>
       <c r="B132" s="5">
-        <v>46107.63874899306</v>
+        <v>46107.47208232639</v>
       </c>
       <c r="C132" s="5">
-        <v>46109.734664131945</v>
+        <v>46109.567997465274</v>
       </c>
       <c r="D132" s="5">
-        <v>46109.73466543981</v>
+        <v>46109.56799877315</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>63</v>
@@ -9512,13 +9512,13 @@
         <v>387</v>
       </c>
       <c r="B133" s="8">
-        <v>46107.63879311342</v>
+        <v>46107.47212644676</v>
       </c>
       <c r="C133" s="8">
-        <v>46113.566690381944</v>
+        <v>46113.40002371528</v>
       </c>
       <c r="D133" s="8">
-        <v>46113.56669168982</v>
+        <v>46113.40002502315</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>66</v>
@@ -9567,13 +9567,13 @@
         <v>389</v>
       </c>
       <c r="B134" s="5">
-        <v>46107.63882511574</v>
+        <v>46107.472158449076</v>
       </c>
       <c r="C134" s="5">
-        <v>46113.56669976852</v>
+        <v>46113.40003310185</v>
       </c>
       <c r="D134" s="5">
-        <v>46113.56670113426</v>
+        <v>46113.40003446759</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>69</v>
@@ -9622,13 +9622,13 @@
         <v>391</v>
       </c>
       <c r="B135" s="8">
-        <v>46077.82017644676</v>
+        <v>46077.653509780095</v>
       </c>
       <c r="C135" s="8">
-        <v>46125.560852916664</v>
+        <v>46125.39418625</v>
       </c>
       <c r="D135" s="8">
-        <v>46127.18538978009</v>
+        <v>46127.018723113426</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>392</v>
@@ -9687,13 +9687,13 @@
         <v>395</v>
       </c>
       <c r="B136" s="5">
-        <v>46107.602652581016</v>
+        <v>46107.43598591435</v>
       </c>
       <c r="C136" s="5">
-        <v>46125.56110847222</v>
+        <v>46125.394441805554</v>
       </c>
       <c r="D136" s="5">
-        <v>46125.561110208335</v>
+        <v>46125.39444354166</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>224</v>
@@ -9740,13 +9740,13 @@
         <v>397</v>
       </c>
       <c r="B137" s="8">
-        <v>46107.60267325232</v>
+        <v>46107.436006585645</v>
       </c>
       <c r="C137" s="8">
-        <v>46125.561119687496</v>
+        <v>46125.39445302083</v>
       </c>
       <c r="D137" s="8">
-        <v>46125.56112121527</v>
+        <v>46125.394454548616</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>224</v>
@@ -9793,13 +9793,13 @@
         <v>398</v>
       </c>
       <c r="B138" s="5">
-        <v>46107.60282983797</v>
+        <v>46107.436163171296</v>
       </c>
       <c r="C138" s="5">
-        <v>46109.72876621528</v>
+        <v>46109.56209954861</v>
       </c>
       <c r="D138" s="5">
-        <v>46114.85804719907</v>
+        <v>46114.69138053241</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>228</v>
@@ -9846,13 +9846,13 @@
         <v>400</v>
       </c>
       <c r="B139" s="8">
-        <v>46107.602871932875</v>
+        <v>46107.4362052662</v>
       </c>
       <c r="C139" s="8">
-        <v>46109.72877821759</v>
+        <v>46109.56211155093</v>
       </c>
       <c r="D139" s="8">
-        <v>46114.858048055554</v>
+        <v>46114.69138138889</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>231</v>
@@ -9899,13 +9899,13 @@
         <v>402</v>
       </c>
       <c r="B140" s="5">
-        <v>46107.604622638886</v>
+        <v>46107.43795597222</v>
       </c>
       <c r="C140" s="5">
-        <v>46109.73476545139</v>
+        <v>46109.56809878472</v>
       </c>
       <c r="D140" s="5">
-        <v>46109.734767118054</v>
+        <v>46109.56810045139</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>56</v>
@@ -9952,13 +9952,13 @@
         <v>404</v>
       </c>
       <c r="B141" s="8">
-        <v>46107.604665590276</v>
+        <v>46107.43799892361</v>
       </c>
       <c r="C141" s="8">
-        <v>46109.7347790625</v>
+        <v>46109.568112395835</v>
       </c>
       <c r="D141" s="8">
-        <v>46109.73478061343</v>
+        <v>46109.56811394676</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>60</v>
@@ -10005,13 +10005,13 @@
         <v>406</v>
       </c>
       <c r="B142" s="5">
-        <v>46107.60470481482</v>
+        <v>46107.438038148146</v>
       </c>
       <c r="C142" s="5">
-        <v>46109.73481496528</v>
+        <v>46109.56814829861</v>
       </c>
       <c r="D142" s="5">
-        <v>46109.73481652778</v>
+        <v>46109.56814986111</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>63</v>
@@ -10058,13 +10058,13 @@
         <v>408</v>
       </c>
       <c r="B143" s="8">
-        <v>46107.60474207176</v>
+        <v>46107.438075405094</v>
       </c>
       <c r="C143" s="8">
-        <v>46113.566753101855</v>
+        <v>46113.400086435184</v>
       </c>
       <c r="D143" s="8">
-        <v>46113.56675440972</v>
+        <v>46113.40008774305</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>66</v>
@@ -10111,13 +10111,13 @@
         <v>410</v>
       </c>
       <c r="B144" s="5">
-        <v>46107.6047731713</v>
+        <v>46107.43810650463</v>
       </c>
       <c r="C144" s="5">
-        <v>46113.56676732639</v>
+        <v>46113.400100659725</v>
       </c>
       <c r="D144" s="5">
-        <v>46113.56676922453</v>
+        <v>46113.40010255787</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>69</v>
@@ -10164,13 +10164,13 @@
         <v>412</v>
       </c>
       <c r="B145" s="8">
-        <v>46077.820176724534</v>
+        <v>46077.65351005787</v>
       </c>
       <c r="C145" s="8">
-        <v>46125.56089650463</v>
+        <v>46125.39422983796</v>
       </c>
       <c r="D145" s="8">
-        <v>46128.19730540509</v>
+        <v>46128.030638738426</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>413</v>
@@ -10229,13 +10229,13 @@
         <v>416</v>
       </c>
       <c r="B146" s="5">
-        <v>46107.60538978009</v>
+        <v>46107.438723113424</v>
       </c>
       <c r="C146" s="5">
-        <v>46125.56117518518</v>
+        <v>46125.39450851852</v>
       </c>
       <c r="D146" s="5">
-        <v>46125.56117667824</v>
+        <v>46125.394510011574</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>224</v>
@@ -10282,13 +10282,13 @@
         <v>417</v>
       </c>
       <c r="B147" s="8">
-        <v>46107.60549119213</v>
+        <v>46107.43882452547</v>
       </c>
       <c r="C147" s="8">
-        <v>46125.56118386574</v>
+        <v>46125.39451719908</v>
       </c>
       <c r="D147" s="8">
-        <v>46125.56118533565</v>
+        <v>46125.39451866898</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>224</v>
@@ -10335,13 +10335,13 @@
         <v>418</v>
       </c>
       <c r="B148" s="5">
-        <v>46107.60552758102</v>
+        <v>46107.43886091435</v>
       </c>
       <c r="C148" s="5">
-        <v>46109.73489248843</v>
+        <v>46109.56822582176</v>
       </c>
       <c r="D148" s="5">
-        <v>46114.858808460645</v>
+        <v>46114.69214179398</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>228</v>
@@ -10388,13 +10388,13 @@
         <v>419</v>
       </c>
       <c r="B149" s="8">
-        <v>46107.60555978009</v>
+        <v>46107.43889311343</v>
       </c>
       <c r="C149" s="8">
-        <v>46109.73490858796</v>
+        <v>46109.5682419213</v>
       </c>
       <c r="D149" s="8">
-        <v>46114.858710138884</v>
+        <v>46114.69204347223</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>231</v>
@@ -10441,13 +10441,13 @@
         <v>420</v>
       </c>
       <c r="B150" s="5">
-        <v>46107.60568278935</v>
+        <v>46107.439016122684</v>
       </c>
       <c r="C150" s="5">
-        <v>46109.735407002314</v>
+        <v>46109.56874033565</v>
       </c>
       <c r="D150" s="5">
-        <v>46109.73540881944</v>
+        <v>46109.56874215278</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>421</v>
@@ -10494,13 +10494,13 @@
         <v>422</v>
       </c>
       <c r="B151" s="8">
-        <v>46107.605744953704</v>
+        <v>46107.43907828703</v>
       </c>
       <c r="C151" s="8">
-        <v>46109.73546793981</v>
+        <v>46109.56880127315</v>
       </c>
       <c r="D151" s="8">
-        <v>46109.73546953704</v>
+        <v>46109.56880287037</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>60</v>
@@ -10547,13 +10547,13 @@
         <v>423</v>
       </c>
       <c r="B152" s="5">
-        <v>46107.60583027778</v>
+        <v>46107.43916361111</v>
       </c>
       <c r="C152" s="5">
-        <v>46109.73551837963</v>
+        <v>46109.56885171296</v>
       </c>
       <c r="D152" s="5">
-        <v>46109.73552002315</v>
+        <v>46109.56885335648</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>63</v>
@@ -10600,13 +10600,13 @@
         <v>424</v>
       </c>
       <c r="B153" s="8">
-        <v>46107.60586805556</v>
+        <v>46107.43920138889</v>
       </c>
       <c r="C153" s="8">
-        <v>46113.566831261574</v>
+        <v>46113.4001645949</v>
       </c>
       <c r="D153" s="8">
-        <v>46113.5668328125</v>
+        <v>46113.40016614583</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>66</v>
@@ -10653,13 +10653,13 @@
         <v>425</v>
       </c>
       <c r="B154" s="5">
-        <v>46107.605905868055</v>
+        <v>46107.43923920139</v>
       </c>
       <c r="C154" s="5">
-        <v>46113.56684251157</v>
+        <v>46113.40017584491</v>
       </c>
       <c r="D154" s="5">
-        <v>46113.56684399306</v>
+        <v>46113.40017732639</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>69</v>
@@ -10706,11 +10706,11 @@
         <v>426</v>
       </c>
       <c r="B155" s="8">
-        <v>46077.820177013884</v>
+        <v>46077.65351034723</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46114.650831747684</v>
+        <v>46114.48416508102</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>427</v>
@@ -10753,11 +10753,11 @@
         <v>429</v>
       </c>
       <c r="B156" s="5">
-        <v>46077.82017730324</v>
+        <v>46077.65351063658</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46137.18802717593</v>
+        <v>46137.02136050926</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>430</v>
@@ -10816,11 +10816,11 @@
         <v>434</v>
       </c>
       <c r="B157" s="8">
-        <v>46077.82017756945</v>
+        <v>46077.653510902775</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46137.18802714121</v>
+        <v>46137.02136047454</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>435</v>
@@ -10879,11 +10879,11 @@
         <v>437</v>
       </c>
       <c r="B158" s="5">
-        <v>46090.88005357639</v>
+        <v>46090.71338690972</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46114.65100881945</v>
+        <v>46114.48434215278</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>438</v>
@@ -10926,11 +10926,11 @@
         <v>440</v>
       </c>
       <c r="B159" s="8">
-        <v>46090.88038033565</v>
+        <v>46090.713713668985</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46137.18802715278</v>
+        <v>46137.02136048611</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>441</v>
@@ -10989,11 +10989,11 @@
         <v>442</v>
       </c>
       <c r="B160" s="5">
-        <v>46090.88062440972</v>
+        <v>46090.71395774306</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46137.18802714121</v>
+        <v>46137.02136047454</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>443</v>

--- a/data/50001451 - ZITRON COLOMBIA.xlsx
+++ b/data/50001451 - ZITRON COLOMBIA.xlsx
@@ -1969,13 +1969,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46077.65350881944</v>
+        <v>46077.82017548611</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55602336806</v>
+        <v>46092.72269003472</v>
       </c>
       <c r="D4" s="5">
-        <v>46097.369704571756</v>
+        <v>46097.53637123843</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2018,13 +2018,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46077.653509247684</v>
+        <v>46077.820175914356</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55599392361</v>
+        <v>46092.722660590276</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.556023425925</v>
+        <v>46092.72269009259</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2081,13 +2081,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46077.65350954861</v>
+        <v>46077.820176215275</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55599454861</v>
+        <v>46092.72266121527</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55602371528</v>
+        <v>46092.72269038194</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2144,13 +2144,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46077.65350987269</v>
+        <v>46077.82017653935</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55599501157</v>
+        <v>46092.72266167824</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.556023819445</v>
+        <v>46092.722690486116</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -2207,13 +2207,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46077.65351016204</v>
+        <v>46077.8201768287</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.555995532406</v>
+        <v>46092.72266219907</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.603775358795</v>
+        <v>46100.77044202546</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -2270,13 +2270,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46077.65351048611</v>
+        <v>46077.82017715278</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55599620371</v>
+        <v>46092.72266287037</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.55602438658</v>
+        <v>46092.72269105324</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -2333,13 +2333,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46077.65351078704</v>
+        <v>46077.8201774537</v>
       </c>
       <c r="C10" s="5">
-        <v>46114.67309768518</v>
+        <v>46114.839764351855</v>
       </c>
       <c r="D10" s="5">
-        <v>46125.39536578704</v>
+        <v>46125.5620324537</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -2384,13 +2384,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46077.65351107639</v>
+        <v>46077.82017774305</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.37212284722</v>
+        <v>46097.538789513885</v>
       </c>
       <c r="D11" s="8">
-        <v>46107.469534895834</v>
+        <v>46107.636201562505</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -2449,13 +2449,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46077.653511365745</v>
+        <v>46077.82017803241</v>
       </c>
       <c r="C12" s="5">
-        <v>46113.3996452662</v>
+        <v>46113.56631193287</v>
       </c>
       <c r="D12" s="5">
-        <v>46113.3996571875</v>
+        <v>46113.56632385417</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2514,13 +2514,13 @@
         <v>55</v>
       </c>
       <c r="B13" s="8">
-        <v>46107.49398770834</v>
+        <v>46107.660654374995</v>
       </c>
       <c r="C13" s="8">
-        <v>46109.5651262037</v>
+        <v>46109.73179287037</v>
       </c>
       <c r="D13" s="8">
-        <v>46109.5673341088</v>
+        <v>46109.73400077547</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>56</v>
@@ -2569,13 +2569,13 @@
         <v>59</v>
       </c>
       <c r="B14" s="5">
-        <v>46107.49412581019</v>
+        <v>46107.66079247685</v>
       </c>
       <c r="C14" s="5">
-        <v>46109.56514158565</v>
+        <v>46109.73180825231</v>
       </c>
       <c r="D14" s="5">
-        <v>46109.565142962965</v>
+        <v>46109.73180962963</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>60</v>
@@ -2624,13 +2624,13 @@
         <v>62</v>
       </c>
       <c r="B15" s="8">
-        <v>46107.49416398148</v>
+        <v>46107.66083064815</v>
       </c>
       <c r="C15" s="8">
-        <v>46109.56515916667</v>
+        <v>46109.73182583333</v>
       </c>
       <c r="D15" s="8">
-        <v>46109.56516092592</v>
+        <v>46109.73182759259</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>63</v>
@@ -2679,13 +2679,13 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46107.494209826385</v>
+        <v>46107.66087649306</v>
       </c>
       <c r="C16" s="5">
-        <v>46113.39960600695</v>
+        <v>46113.56627267361</v>
       </c>
       <c r="D16" s="5">
-        <v>46113.399607245374</v>
+        <v>46113.56627391204</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2734,13 +2734,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="8">
-        <v>46107.49425076389</v>
+        <v>46107.660917430556</v>
       </c>
       <c r="C17" s="8">
-        <v>46113.39963071759</v>
+        <v>46113.566297384255</v>
       </c>
       <c r="D17" s="8">
-        <v>46113.39963194444</v>
+        <v>46113.56629861111</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>69</v>
@@ -2789,13 +2789,13 @@
         <v>71</v>
       </c>
       <c r="B18" s="5">
-        <v>46077.653511655095</v>
+        <v>46077.82017832176</v>
       </c>
       <c r="C18" s="5">
-        <v>46097.36960097222</v>
+        <v>46097.53626763889</v>
       </c>
       <c r="D18" s="5">
-        <v>46125.39533824074</v>
+        <v>46125.562004907406</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>72</v>
@@ -2838,13 +2838,13 @@
         <v>74</v>
       </c>
       <c r="B19" s="8">
-        <v>46077.65350872686</v>
+        <v>46077.82017539351</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.36843689815</v>
+        <v>46097.53510356482</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.3684552662</v>
+        <v>46097.53512193287</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>75</v>
@@ -2903,13 +2903,13 @@
         <v>77</v>
       </c>
       <c r="B20" s="5">
-        <v>46077.65350956019</v>
+        <v>46077.82017622685</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.36919636574</v>
+        <v>46097.535863032404</v>
       </c>
       <c r="D20" s="5">
-        <v>46100.60651576389</v>
+        <v>46100.77318243055</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>78</v>
@@ -2968,13 +2968,13 @@
         <v>80</v>
       </c>
       <c r="B21" s="8">
-        <v>46077.65350987269</v>
+        <v>46077.82017653935</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.36955335648</v>
+        <v>46097.53622002315</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.36956980324</v>
+        <v>46097.53623646991</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>81</v>
@@ -3033,13 +3033,13 @@
         <v>83</v>
       </c>
       <c r="B22" s="5">
-        <v>46077.65351017361</v>
+        <v>46077.82017684028</v>
       </c>
       <c r="C22" s="5">
-        <v>46097.369580439816</v>
+        <v>46097.53624710648</v>
       </c>
       <c r="D22" s="5">
-        <v>46097.369601597224</v>
+        <v>46097.53626826389</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>84</v>
@@ -3098,13 +3098,13 @@
         <v>86</v>
       </c>
       <c r="B23" s="8">
-        <v>46077.65351047454</v>
+        <v>46077.8201771412</v>
       </c>
       <c r="C23" s="8">
-        <v>46104.461916493055</v>
+        <v>46104.62858315972</v>
       </c>
       <c r="D23" s="8">
-        <v>46112.63144489583</v>
+        <v>46112.7981115625</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>87</v>
@@ -3147,13 +3147,13 @@
         <v>89</v>
       </c>
       <c r="B24" s="5">
-        <v>46077.653511111115</v>
+        <v>46077.82017777778</v>
       </c>
       <c r="C24" s="5">
-        <v>46097.368501053235</v>
+        <v>46097.53516771991</v>
       </c>
       <c r="D24" s="5">
-        <v>46097.36852065972</v>
+        <v>46097.535187326386</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>90</v>
@@ -3212,13 +3212,13 @@
         <v>91</v>
       </c>
       <c r="B25" s="8">
-        <v>46077.65351077546</v>
+        <v>46077.82017744213</v>
       </c>
       <c r="C25" s="8">
-        <v>46097.36854178241</v>
+        <v>46097.53520844907</v>
       </c>
       <c r="D25" s="8">
-        <v>46125.39528435185</v>
+        <v>46125.56195101852</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>92</v>
@@ -3277,13 +3277,13 @@
         <v>94</v>
       </c>
       <c r="B26" s="5">
-        <v>46077.65351142361</v>
+        <v>46077.820178090275</v>
       </c>
       <c r="C26" s="5">
-        <v>46097.37217054398</v>
+        <v>46097.53883721065</v>
       </c>
       <c r="D26" s="5">
-        <v>46112.512462824074</v>
+        <v>46112.679129490745</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>95</v>
@@ -3342,13 +3342,13 @@
         <v>97</v>
       </c>
       <c r="B27" s="8">
-        <v>46077.65351171297</v>
+        <v>46077.820178379625</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.36923239584</v>
+        <v>46097.535899062495</v>
       </c>
       <c r="D27" s="8">
-        <v>46100.60341217593</v>
+        <v>46100.770078842594</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>98</v>
@@ -3407,13 +3407,13 @@
         <v>100</v>
       </c>
       <c r="B28" s="5">
-        <v>46077.65350892361</v>
+        <v>46077.82017559028</v>
       </c>
       <c r="C28" s="5">
-        <v>46097.369854131946</v>
+        <v>46097.53652079861</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.36987444444</v>
+        <v>46097.53654111111</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>101</v>
@@ -3472,13 +3472,13 @@
         <v>104</v>
       </c>
       <c r="B29" s="8">
-        <v>46078.49200716435</v>
+        <v>46078.658673831014</v>
       </c>
       <c r="C29" s="8">
-        <v>46104.46189391204</v>
+        <v>46104.628560578705</v>
       </c>
       <c r="D29" s="8">
-        <v>46104.461917106484</v>
+        <v>46104.62858377315</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>105</v>
@@ -3537,13 +3537,13 @@
         <v>107</v>
       </c>
       <c r="B30" s="5">
-        <v>46078.49209234954</v>
+        <v>46078.65875901621</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.370087766205</v>
+        <v>46097.53675443287</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.37010788194</v>
+        <v>46097.536774548615</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>108</v>
@@ -3602,13 +3602,13 @@
         <v>110</v>
       </c>
       <c r="B31" s="8">
-        <v>46077.65350929398</v>
+        <v>46077.820175960645</v>
       </c>
       <c r="C31" s="8">
-        <v>46112.63125395833</v>
+        <v>46112.797920625</v>
       </c>
       <c r="D31" s="8">
-        <v>46112.63136230324</v>
+        <v>46112.798028969904</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>111</v>
@@ -3651,13 +3651,13 @@
         <v>113</v>
       </c>
       <c r="B32" s="5">
-        <v>46077.65350956019</v>
+        <v>46077.82017622685</v>
       </c>
       <c r="C32" s="5">
-        <v>46097.36866423611</v>
+        <v>46097.53533090278</v>
       </c>
       <c r="D32" s="5">
-        <v>46097.36868027778</v>
+        <v>46097.535346944445</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>114</v>
@@ -3716,13 +3716,13 @@
         <v>118</v>
       </c>
       <c r="B33" s="8">
-        <v>46077.65350983797</v>
+        <v>46077.820176504625</v>
       </c>
       <c r="C33" s="8">
-        <v>46097.36860832176</v>
+        <v>46097.535274988426</v>
       </c>
       <c r="D33" s="8">
-        <v>46097.36860973379</v>
+        <v>46097.535276400464</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>119</v>
@@ -3777,13 +3777,13 @@
         <v>123</v>
       </c>
       <c r="B34" s="5">
-        <v>46077.65351012732</v>
+        <v>46077.82017679398</v>
       </c>
       <c r="C34" s="5">
-        <v>46097.368646250005</v>
+        <v>46097.53531291666</v>
       </c>
       <c r="D34" s="5">
-        <v>46097.368648483796</v>
+        <v>46097.53531515047</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>124</v>
@@ -3838,13 +3838,13 @@
         <v>126</v>
       </c>
       <c r="B35" s="8">
-        <v>46077.65351039352</v>
+        <v>46077.82017706019</v>
       </c>
       <c r="C35" s="8">
-        <v>46097.37301059028</v>
+        <v>46097.539677256944</v>
       </c>
       <c r="D35" s="8">
-        <v>46097.3730234838</v>
+        <v>46097.539690150465</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>127</v>
@@ -3903,13 +3903,13 @@
         <v>129</v>
       </c>
       <c r="B36" s="5">
-        <v>46077.65351063658</v>
+        <v>46077.82017730324</v>
       </c>
       <c r="C36" s="5">
-        <v>46097.372233125</v>
+        <v>46097.53889979167</v>
       </c>
       <c r="D36" s="5">
-        <v>46097.372234525465</v>
+        <v>46097.53890119213</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>130</v>
@@ -3964,13 +3964,13 @@
         <v>132</v>
       </c>
       <c r="B37" s="8">
-        <v>46077.65351089121</v>
+        <v>46077.82017755787</v>
       </c>
       <c r="C37" s="8">
-        <v>46097.37299694444</v>
+        <v>46097.53966361111</v>
       </c>
       <c r="D37" s="8">
-        <v>46097.37299827546</v>
+        <v>46097.53966494213</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>133</v>
@@ -4025,13 +4025,13 @@
         <v>135</v>
       </c>
       <c r="B38" s="5">
-        <v>46077.653511145836</v>
+        <v>46077.8201778125</v>
       </c>
       <c r="C38" s="5">
-        <v>46097.36934012732</v>
+        <v>46097.53600679398</v>
       </c>
       <c r="D38" s="5">
-        <v>46097.36935715278</v>
+        <v>46097.53602381944</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>136</v>
@@ -4090,13 +4090,13 @@
         <v>138</v>
       </c>
       <c r="B39" s="8">
-        <v>46077.65351138889</v>
+        <v>46077.820178055554</v>
       </c>
       <c r="C39" s="8">
-        <v>46097.36928626157</v>
+        <v>46097.53595292824</v>
       </c>
       <c r="D39" s="8">
-        <v>46097.369287395835</v>
+        <v>46097.5359540625</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>139</v>
@@ -4151,13 +4151,13 @@
         <v>141</v>
       </c>
       <c r="B40" s="5">
-        <v>46077.653508877316</v>
+        <v>46077.82017554398</v>
       </c>
       <c r="C40" s="5">
-        <v>46097.369326643515</v>
+        <v>46097.535993310186</v>
       </c>
       <c r="D40" s="5">
-        <v>46097.369328078705</v>
+        <v>46097.53599474537</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>142</v>
@@ -4212,13 +4212,13 @@
         <v>144</v>
       </c>
       <c r="B41" s="8">
-        <v>46077.65350934028</v>
+        <v>46077.82017600695</v>
       </c>
       <c r="C41" s="8">
-        <v>46097.36878138889</v>
+        <v>46097.535448055554</v>
       </c>
       <c r="D41" s="8">
-        <v>46097.368794050926</v>
+        <v>46097.5354607176</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>145</v>
@@ -4277,13 +4277,13 @@
         <v>147</v>
       </c>
       <c r="B42" s="5">
-        <v>46077.65350965278</v>
+        <v>46077.820176319445</v>
       </c>
       <c r="C42" s="5">
-        <v>46097.368692662036</v>
+        <v>46097.5353593287</v>
       </c>
       <c r="D42" s="5">
-        <v>46182.52677819444</v>
+        <v>46182.693444861114</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>148</v>
@@ -4338,13 +4338,13 @@
         <v>151</v>
       </c>
       <c r="B43" s="8">
-        <v>46077.65350996528</v>
+        <v>46077.82017663194</v>
       </c>
       <c r="C43" s="8">
-        <v>46097.368739247686</v>
+        <v>46097.53540591435</v>
       </c>
       <c r="D43" s="8">
-        <v>46097.368740833335</v>
+        <v>46097.5354075</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>152</v>
@@ -4399,13 +4399,13 @@
         <v>154</v>
       </c>
       <c r="B44" s="5">
-        <v>46077.6535102662</v>
+        <v>46077.82017693287</v>
       </c>
       <c r="C44" s="5">
-        <v>46097.3687653588</v>
+        <v>46097.53543202546</v>
       </c>
       <c r="D44" s="5">
-        <v>46097.36876675926</v>
+        <v>46097.535433425925</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>155</v>
@@ -4460,13 +4460,13 @@
         <v>157</v>
       </c>
       <c r="B45" s="8">
-        <v>46077.65351056713</v>
+        <v>46077.82017723379</v>
       </c>
       <c r="C45" s="8">
-        <v>46097.370020138886</v>
+        <v>46097.53668680556</v>
       </c>
       <c r="D45" s="8">
-        <v>46097.3700330787</v>
+        <v>46097.53669974537</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>158</v>
@@ -4525,13 +4525,13 @@
         <v>162</v>
       </c>
       <c r="B46" s="5">
-        <v>46077.653510902775</v>
+        <v>46077.82017756945</v>
       </c>
       <c r="C46" s="5">
-        <v>46097.36994253472</v>
+        <v>46097.53660920139</v>
       </c>
       <c r="D46" s="5">
-        <v>46097.369944108796</v>
+        <v>46097.53661077547</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>163</v>
@@ -4586,13 +4586,13 @@
         <v>165</v>
       </c>
       <c r="B47" s="8">
-        <v>46077.65351120371</v>
+        <v>46077.820177870366</v>
       </c>
       <c r="C47" s="8">
-        <v>46097.37000571759</v>
+        <v>46097.53667238426</v>
       </c>
       <c r="D47" s="8">
-        <v>46097.37000703704</v>
+        <v>46097.536673703704</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>166</v>
@@ -4647,13 +4647,13 @@
         <v>167</v>
       </c>
       <c r="B48" s="5">
-        <v>46078.488932141205</v>
+        <v>46078.65559880787</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.67368665509</v>
+        <v>46107.840353321764</v>
       </c>
       <c r="D48" s="5">
-        <v>46107.67375971065</v>
+        <v>46107.84042637731</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>168</v>
@@ -4712,13 +4712,13 @@
         <v>170</v>
       </c>
       <c r="B49" s="8">
-        <v>46078.48899142361</v>
+        <v>46078.655658090276</v>
       </c>
       <c r="C49" s="8">
-        <v>46107.673577118054</v>
+        <v>46107.840243784725</v>
       </c>
       <c r="D49" s="8">
-        <v>46107.673578773145</v>
+        <v>46107.84024543982</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>171</v>
@@ -4773,13 +4773,13 @@
         <v>173</v>
       </c>
       <c r="B50" s="5">
-        <v>46078.489103368054</v>
+        <v>46078.65577003472</v>
       </c>
       <c r="C50" s="5">
-        <v>46107.67367146991</v>
+        <v>46107.84033813658</v>
       </c>
       <c r="D50" s="5">
-        <v>46107.673672951394</v>
+        <v>46107.84033961805</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>174</v>
@@ -4834,13 +4834,13 @@
         <v>176</v>
       </c>
       <c r="B51" s="8">
-        <v>46078.48757837963</v>
+        <v>46078.654245046295</v>
       </c>
       <c r="C51" s="8">
-        <v>46105.616744212966</v>
+        <v>46105.78341087963</v>
       </c>
       <c r="D51" s="8">
-        <v>46105.61675715278</v>
+        <v>46105.78342381945</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>177</v>
@@ -4899,13 +4899,13 @@
         <v>181</v>
       </c>
       <c r="B52" s="5">
-        <v>46078.487632696764</v>
+        <v>46078.65429936342</v>
       </c>
       <c r="C52" s="5">
-        <v>46097.37018913194</v>
+        <v>46097.53685579861</v>
       </c>
       <c r="D52" s="5">
-        <v>46111.48887483796</v>
+        <v>46111.65554150463</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>182</v>
@@ -4960,13 +4960,13 @@
         <v>184</v>
       </c>
       <c r="B53" s="8">
-        <v>46078.488023275466</v>
+        <v>46078.65468994213</v>
       </c>
       <c r="C53" s="8">
-        <v>46105.61672585648</v>
+        <v>46105.78339252315</v>
       </c>
       <c r="D53" s="8">
-        <v>46105.616727395834</v>
+        <v>46105.7833940625</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>185</v>
@@ -5021,13 +5021,13 @@
         <v>188</v>
       </c>
       <c r="B54" s="5">
-        <v>46104.46379498843</v>
+        <v>46104.63046165509</v>
       </c>
       <c r="C54" s="5">
-        <v>46105.58714668981</v>
+        <v>46105.75381335648</v>
       </c>
       <c r="D54" s="5">
-        <v>46107.51235769676</v>
+        <v>46107.67902436343</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>189</v>
@@ -5076,13 +5076,13 @@
         <v>190</v>
       </c>
       <c r="B55" s="8">
-        <v>46104.46460832176</v>
+        <v>46104.631274988424</v>
       </c>
       <c r="C55" s="8">
-        <v>46104.48089810185</v>
+        <v>46104.647564768515</v>
       </c>
       <c r="D55" s="8">
-        <v>46107.512552361106</v>
+        <v>46107.67921902778</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>191</v>
@@ -5131,13 +5131,13 @@
         <v>192</v>
       </c>
       <c r="B56" s="5">
-        <v>46104.465005011574</v>
+        <v>46104.631671678246</v>
       </c>
       <c r="C56" s="5">
-        <v>46104.480031886575</v>
+        <v>46104.646698553246</v>
       </c>
       <c r="D56" s="5">
-        <v>46107.512663877314</v>
+        <v>46107.67933054398</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>193</v>
@@ -5186,13 +5186,13 @@
         <v>194</v>
       </c>
       <c r="B57" s="8">
-        <v>46104.46529033565</v>
+        <v>46104.63195700232</v>
       </c>
       <c r="C57" s="8">
-        <v>46104.47969530092</v>
+        <v>46104.64636196759</v>
       </c>
       <c r="D57" s="8">
-        <v>46107.51277224537</v>
+        <v>46107.67943891203</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>195</v>
@@ -5241,13 +5241,13 @@
         <v>196</v>
       </c>
       <c r="B58" s="5">
-        <v>46104.46541815972</v>
+        <v>46104.632084826386</v>
       </c>
       <c r="C58" s="5">
-        <v>46104.47900508102</v>
+        <v>46104.64567174768</v>
       </c>
       <c r="D58" s="5">
-        <v>46107.51318376158</v>
+        <v>46107.67985042824</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>197</v>
@@ -5296,13 +5296,13 @@
         <v>198</v>
       </c>
       <c r="B59" s="8">
-        <v>46104.46560704861</v>
+        <v>46104.63227371528</v>
       </c>
       <c r="C59" s="8">
-        <v>46104.478267708335</v>
+        <v>46104.644934375</v>
       </c>
       <c r="D59" s="8">
-        <v>46107.512891921295</v>
+        <v>46107.67955858796</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>199</v>
@@ -5351,13 +5351,13 @@
         <v>200</v>
       </c>
       <c r="B60" s="5">
-        <v>46077.65351149306</v>
+        <v>46077.82017815972</v>
       </c>
       <c r="C60" s="5">
-        <v>46114.60105153936</v>
+        <v>46114.767718206014</v>
       </c>
       <c r="D60" s="5">
-        <v>46114.682059224535</v>
+        <v>46114.84872589121</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>201</v>
@@ -5402,13 +5402,13 @@
         <v>203</v>
       </c>
       <c r="B61" s="8">
-        <v>46077.65351179398</v>
+        <v>46077.82017846065</v>
       </c>
       <c r="C61" s="8">
-        <v>46097.37042160879</v>
+        <v>46097.537088275465</v>
       </c>
       <c r="D61" s="8">
-        <v>46197.54047175926</v>
+        <v>46197.707138425925</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>204</v>
@@ -5467,13 +5467,13 @@
         <v>208</v>
       </c>
       <c r="B62" s="5">
-        <v>46077.65350959491</v>
+        <v>46077.82017626158</v>
       </c>
       <c r="C62" s="5">
-        <v>46097.3704739699</v>
+        <v>46097.537140636574</v>
       </c>
       <c r="D62" s="5">
-        <v>46197.54049266204</v>
+        <v>46197.707159328704</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>209</v>
@@ -5532,13 +5532,13 @@
         <v>212</v>
       </c>
       <c r="B63" s="8">
-        <v>46090.71305146991</v>
+        <v>46090.87971813657</v>
       </c>
       <c r="C63" s="8">
-        <v>46097.370544652775</v>
+        <v>46097.537211319446</v>
       </c>
       <c r="D63" s="8">
-        <v>46114.48416702547</v>
+        <v>46114.650833692125</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>213</v>
@@ -5595,13 +5595,13 @@
         <v>217</v>
       </c>
       <c r="B64" s="5">
-        <v>46090.71317484954</v>
+        <v>46090.8798415162</v>
       </c>
       <c r="C64" s="5">
-        <v>46114.601034293984</v>
+        <v>46114.76770096065</v>
       </c>
       <c r="D64" s="5">
-        <v>46119.61215399306</v>
+        <v>46119.77882065972</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>218</v>
@@ -5660,13 +5660,13 @@
         <v>222</v>
       </c>
       <c r="B65" s="8">
-        <v>46107.43952543981</v>
+        <v>46107.60619210648</v>
       </c>
       <c r="C65" s="8">
-        <v>46114.62188774305</v>
+        <v>46114.78855440972</v>
       </c>
       <c r="D65" s="8">
-        <v>46114.621889201386</v>
+        <v>46114.78855586806</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>223</v>
@@ -5713,13 +5713,13 @@
         <v>225</v>
       </c>
       <c r="B66" s="5">
-        <v>46107.439735775464</v>
+        <v>46107.60640244213</v>
       </c>
       <c r="C66" s="5">
-        <v>46114.62191454861</v>
+        <v>46114.78858121528</v>
       </c>
       <c r="D66" s="5">
-        <v>46114.62191614583</v>
+        <v>46114.7885828125</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>226</v>
@@ -5766,13 +5766,13 @@
         <v>227</v>
       </c>
       <c r="B67" s="8">
-        <v>46107.43976915509</v>
+        <v>46107.606435821755</v>
       </c>
       <c r="C67" s="8">
-        <v>46108.49240393519</v>
+        <v>46108.65907060185</v>
       </c>
       <c r="D67" s="8">
-        <v>46114.68165832176</v>
+        <v>46114.84832498843</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>228</v>
@@ -5819,13 +5819,13 @@
         <v>230</v>
       </c>
       <c r="B68" s="5">
-        <v>46107.439817199076</v>
+        <v>46107.60648386574</v>
       </c>
       <c r="C68" s="5">
-        <v>46108.49242011574</v>
+        <v>46108.65908678241</v>
       </c>
       <c r="D68" s="5">
-        <v>46114.6818049537</v>
+        <v>46114.84847162037</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>231</v>
@@ -5872,13 +5872,13 @@
         <v>232</v>
       </c>
       <c r="B69" s="8">
-        <v>46078.48723896991</v>
+        <v>46078.65390563657</v>
       </c>
       <c r="C69" s="8">
-        <v>46105.68957541666</v>
+        <v>46105.85624208333</v>
       </c>
       <c r="D69" s="8">
-        <v>46107.52070784722</v>
+        <v>46107.68737451389</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>233</v>
@@ -5925,13 +5925,13 @@
         <v>236</v>
       </c>
       <c r="B70" s="5">
-        <v>46078.53589244213</v>
+        <v>46078.702559108795</v>
       </c>
       <c r="C70" s="5">
-        <v>46105.68955804398</v>
+        <v>46105.856224710646</v>
       </c>
       <c r="D70" s="5">
-        <v>46107.67383010416</v>
+        <v>46107.840496770834</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>234</v>
@@ -5990,13 +5990,13 @@
         <v>241</v>
       </c>
       <c r="B71" s="8">
-        <v>46077.65351230324</v>
+        <v>46077.82017896991</v>
       </c>
       <c r="C71" s="8">
-        <v>46107.67721232639</v>
+        <v>46107.84387899305</v>
       </c>
       <c r="D71" s="8">
-        <v>46107.67722675926</v>
+        <v>46107.843893425925</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>242</v>
@@ -6043,13 +6043,13 @@
         <v>244</v>
       </c>
       <c r="B72" s="5">
-        <v>46077.65351263889</v>
+        <v>46077.820179305556</v>
       </c>
       <c r="C72" s="5">
-        <v>46107.67567266204</v>
+        <v>46107.84233932871</v>
       </c>
       <c r="D72" s="5">
-        <v>46107.67568759259</v>
+        <v>46107.842354259265</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>245</v>
@@ -6108,13 +6108,13 @@
         <v>249</v>
       </c>
       <c r="B73" s="8">
-        <v>46077.65351076389</v>
+        <v>46077.820177430556</v>
       </c>
       <c r="C73" s="8">
-        <v>46107.67719534722</v>
+        <v>46107.84386201389</v>
       </c>
       <c r="D73" s="8">
-        <v>46107.67721335648</v>
+        <v>46107.84388002315</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>57</v>
@@ -6173,13 +6173,13 @@
         <v>251</v>
       </c>
       <c r="B74" s="5">
-        <v>46077.65351128472</v>
+        <v>46077.82017795139</v>
       </c>
       <c r="C74" s="5">
-        <v>46107.67525778935</v>
+        <v>46107.84192445602</v>
       </c>
       <c r="D74" s="5">
-        <v>46107.67527457176</v>
+        <v>46107.841941238425</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>252</v>
@@ -6238,13 +6238,13 @@
         <v>254</v>
       </c>
       <c r="B75" s="8">
-        <v>46077.65351174769</v>
+        <v>46077.82017841435</v>
       </c>
       <c r="C75" s="8">
-        <v>46107.67515953704</v>
+        <v>46107.8418262037</v>
       </c>
       <c r="D75" s="8">
-        <v>46107.675177708334</v>
+        <v>46107.841844375</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>255</v>
@@ -6303,13 +6303,13 @@
         <v>256</v>
       </c>
       <c r="B76" s="5">
-        <v>46078.49225604167</v>
+        <v>46078.65892270833</v>
       </c>
       <c r="C76" s="5">
-        <v>46107.676195196764</v>
+        <v>46107.84286186342</v>
       </c>
       <c r="D76" s="5">
-        <v>46107.67621280093</v>
+        <v>46107.84287946759</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>257</v>
@@ -6368,13 +6368,13 @@
         <v>258</v>
       </c>
       <c r="B77" s="8">
-        <v>46078.49233570602</v>
+        <v>46078.65900237269</v>
       </c>
       <c r="C77" s="8">
-        <v>46107.675708993054</v>
+        <v>46107.84237565972</v>
       </c>
       <c r="D77" s="8">
-        <v>46107.67572636574</v>
+        <v>46107.842393032406</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>259</v>
@@ -6433,13 +6433,13 @@
         <v>260</v>
       </c>
       <c r="B78" s="5">
-        <v>46077.65351240741</v>
+        <v>46077.82017907407</v>
       </c>
       <c r="C78" s="5">
-        <v>46118.6844856713</v>
+        <v>46118.851152337964</v>
       </c>
       <c r="D78" s="5">
-        <v>46125.39512971065</v>
+        <v>46125.56179637731</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>261</v>
@@ -6484,13 +6484,13 @@
         <v>263</v>
       </c>
       <c r="B79" s="8">
-        <v>46077.65351276621</v>
+        <v>46077.82017943287</v>
       </c>
       <c r="C79" s="8">
-        <v>46113.39128444444</v>
+        <v>46113.557951111114</v>
       </c>
       <c r="D79" s="8">
-        <v>46114.68664321759</v>
+        <v>46114.85330988426</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>264</v>
@@ -6549,13 +6549,13 @@
         <v>266</v>
       </c>
       <c r="B80" s="5">
-        <v>46107.429962152775</v>
+        <v>46107.59662881945</v>
       </c>
       <c r="C80" s="5">
-        <v>46113.39093767361</v>
+        <v>46113.557604340276</v>
       </c>
       <c r="D80" s="5">
-        <v>46114.689403067125</v>
+        <v>46114.856069733796</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>224</v>
@@ -6604,13 +6604,13 @@
         <v>268</v>
       </c>
       <c r="B81" s="8">
-        <v>46107.431094583335</v>
+        <v>46107.59776125</v>
       </c>
       <c r="C81" s="8">
-        <v>46113.39095212963</v>
+        <v>46113.5576187963</v>
       </c>
       <c r="D81" s="8">
-        <v>46114.68945225695</v>
+        <v>46114.856118923606</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>224</v>
@@ -6659,13 +6659,13 @@
         <v>269</v>
       </c>
       <c r="B82" s="5">
-        <v>46107.43050732639</v>
+        <v>46107.597173993054</v>
       </c>
       <c r="C82" s="5">
-        <v>46107.67206599537</v>
+        <v>46107.838732662036</v>
       </c>
       <c r="D82" s="5">
-        <v>46107.672067673615</v>
+        <v>46107.83873434028</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>228</v>
@@ -6714,13 +6714,13 @@
         <v>271</v>
       </c>
       <c r="B83" s="8">
-        <v>46107.43079521991</v>
+        <v>46107.59746188657</v>
       </c>
       <c r="C83" s="8">
-        <v>46107.67207206019</v>
+        <v>46107.83873872685</v>
       </c>
       <c r="D83" s="8">
-        <v>46107.672073842594</v>
+        <v>46107.83874050926</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>231</v>
@@ -6769,13 +6769,13 @@
         <v>273</v>
       </c>
       <c r="B84" s="5">
-        <v>46077.653513136574</v>
+        <v>46077.82017980324</v>
       </c>
       <c r="C84" s="5">
-        <v>46113.39102497685</v>
+        <v>46113.557691643524</v>
       </c>
       <c r="D84" s="5">
-        <v>46125.395162615736</v>
+        <v>46125.56182928241</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>274</v>
@@ -6834,13 +6834,13 @@
         <v>277</v>
       </c>
       <c r="B85" s="8">
-        <v>46107.433116099535</v>
+        <v>46107.59978276621</v>
       </c>
       <c r="C85" s="8">
-        <v>46113.39158454861</v>
+        <v>46113.558251215276</v>
       </c>
       <c r="D85" s="8">
-        <v>46114.68904462963</v>
+        <v>46114.855711296295</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>224</v>
@@ -6889,13 +6889,13 @@
         <v>280</v>
       </c>
       <c r="B86" s="5">
-        <v>46107.433155763894</v>
+        <v>46107.59982243055</v>
       </c>
       <c r="C86" s="5">
-        <v>46113.3915975</v>
+        <v>46113.55826416667</v>
       </c>
       <c r="D86" s="5">
-        <v>46114.68909915509</v>
+        <v>46114.85576582176</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>224</v>
@@ -6944,13 +6944,13 @@
         <v>281</v>
       </c>
       <c r="B87" s="8">
-        <v>46107.43319819444</v>
+        <v>46107.59986486111</v>
       </c>
       <c r="C87" s="8">
-        <v>46107.68172623843</v>
+        <v>46107.84839290509</v>
       </c>
       <c r="D87" s="8">
-        <v>46107.68172790509</v>
+        <v>46107.84839457176</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>228</v>
@@ -6999,13 +6999,13 @@
         <v>284</v>
       </c>
       <c r="B88" s="5">
-        <v>46107.43324458333</v>
+        <v>46107.59991125</v>
       </c>
       <c r="C88" s="5">
-        <v>46107.68171991898</v>
+        <v>46107.84838658565</v>
       </c>
       <c r="D88" s="5">
-        <v>46107.68172150463</v>
+        <v>46107.8483881713</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>231</v>
@@ -7054,13 +7054,13 @@
         <v>287</v>
       </c>
       <c r="B89" s="8">
-        <v>46077.65351359954</v>
+        <v>46077.82018026621</v>
       </c>
       <c r="C89" s="8">
-        <v>46113.39107770834</v>
+        <v>46113.557744375</v>
       </c>
       <c r="D89" s="8">
-        <v>46125.395179432875</v>
+        <v>46125.56184609953</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>288</v>
@@ -7119,13 +7119,13 @@
         <v>290</v>
       </c>
       <c r="B90" s="5">
-        <v>46107.433287962966</v>
+        <v>46107.59995462963</v>
       </c>
       <c r="C90" s="5">
-        <v>46113.391681747686</v>
+        <v>46113.55834841436</v>
       </c>
       <c r="D90" s="5">
-        <v>46114.68927886574</v>
+        <v>46114.85594553241</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>291</v>
@@ -7174,13 +7174,13 @@
         <v>294</v>
       </c>
       <c r="B91" s="8">
-        <v>46107.433360069444</v>
+        <v>46107.60002673611</v>
       </c>
       <c r="C91" s="8">
-        <v>46113.39169880787</v>
+        <v>46113.55836547454</v>
       </c>
       <c r="D91" s="8">
-        <v>46114.689099490744</v>
+        <v>46114.85576615741</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>291</v>
@@ -7229,13 +7229,13 @@
         <v>296</v>
       </c>
       <c r="B92" s="5">
-        <v>46107.433403159725</v>
+        <v>46107.60006982639</v>
       </c>
       <c r="C92" s="5">
-        <v>46107.68177224537</v>
+        <v>46107.84843891204</v>
       </c>
       <c r="D92" s="5">
-        <v>46107.68177365741</v>
+        <v>46107.84844032407</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>228</v>
@@ -7284,13 +7284,13 @@
         <v>299</v>
       </c>
       <c r="B93" s="8">
-        <v>46107.43343826389</v>
+        <v>46107.600104930556</v>
       </c>
       <c r="C93" s="8">
-        <v>46107.68176678241</v>
+        <v>46107.84843344908</v>
       </c>
       <c r="D93" s="8">
-        <v>46107.681768587965</v>
+        <v>46107.84843525463</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>231</v>
@@ -7339,13 +7339,13 @@
         <v>302</v>
       </c>
       <c r="B94" s="5">
-        <v>46077.65351396991</v>
+        <v>46077.82018063657</v>
       </c>
       <c r="C94" s="5">
-        <v>46113.39114666666</v>
+        <v>46113.55781333333</v>
       </c>
       <c r="D94" s="5">
-        <v>46125.39520136574</v>
+        <v>46125.56186803241</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>303</v>
@@ -7404,13 +7404,13 @@
         <v>304</v>
       </c>
       <c r="B95" s="8">
-        <v>46107.434553125</v>
+        <v>46107.60121979167</v>
       </c>
       <c r="C95" s="8">
-        <v>46113.391739212966</v>
+        <v>46113.55840587963</v>
       </c>
       <c r="D95" s="8">
-        <v>46114.68386609954</v>
+        <v>46114.8505327662</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>224</v>
@@ -7459,13 +7459,13 @@
         <v>307</v>
       </c>
       <c r="B96" s="5">
-        <v>46107.43462958334</v>
+        <v>46107.601296249995</v>
       </c>
       <c r="C96" s="5">
-        <v>46113.3917533912</v>
+        <v>46113.558420057874</v>
       </c>
       <c r="D96" s="5">
-        <v>46114.68410795139</v>
+        <v>46114.850774618055</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>224</v>
@@ -7514,13 +7514,13 @@
         <v>309</v>
       </c>
       <c r="B97" s="8">
-        <v>46107.43467732639</v>
+        <v>46107.601343993054</v>
       </c>
       <c r="C97" s="8">
-        <v>46107.68184967592</v>
+        <v>46107.848516342594</v>
       </c>
       <c r="D97" s="8">
-        <v>46107.681851284724</v>
+        <v>46107.84851795139</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>228</v>
@@ -7569,13 +7569,13 @@
         <v>312</v>
       </c>
       <c r="B98" s="5">
-        <v>46107.434719675926</v>
+        <v>46107.60138634259</v>
       </c>
       <c r="C98" s="5">
-        <v>46107.68184467593</v>
+        <v>46107.84851134259</v>
       </c>
       <c r="D98" s="5">
-        <v>46107.68184670139</v>
+        <v>46107.84851336805</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>231</v>
@@ -7624,13 +7624,13 @@
         <v>315</v>
       </c>
       <c r="B99" s="8">
-        <v>46078.492548043985</v>
+        <v>46078.65921471065</v>
       </c>
       <c r="C99" s="8">
-        <v>46114.47800960648</v>
+        <v>46114.64467627315</v>
       </c>
       <c r="D99" s="8">
-        <v>46114.484171331016</v>
+        <v>46114.65083799769</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>316</v>
@@ -7689,13 +7689,13 @@
         <v>318</v>
       </c>
       <c r="B100" s="5">
-        <v>46107.43478660879</v>
+        <v>46107.60145327546</v>
       </c>
       <c r="C100" s="5">
-        <v>46114.47798848379</v>
+        <v>46114.64465515046</v>
       </c>
       <c r="D100" s="5">
-        <v>46114.683211145835</v>
+        <v>46114.8498778125</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>224</v>
@@ -7744,13 +7744,13 @@
         <v>320</v>
       </c>
       <c r="B101" s="8">
-        <v>46107.43485856481</v>
+        <v>46107.60152523148</v>
       </c>
       <c r="C101" s="8">
-        <v>46114.47799614583</v>
+        <v>46114.6446628125</v>
       </c>
       <c r="D101" s="8">
-        <v>46114.683343171295</v>
+        <v>46114.85000983796</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>224</v>
@@ -7799,13 +7799,13 @@
         <v>322</v>
       </c>
       <c r="B102" s="5">
-        <v>46107.43489554398</v>
+        <v>46107.60156221065</v>
       </c>
       <c r="C102" s="5">
-        <v>46107.68189892361</v>
+        <v>46107.84856559028</v>
       </c>
       <c r="D102" s="5">
-        <v>46107.68190063657</v>
+        <v>46107.84856730324</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>228</v>
@@ -7854,13 +7854,13 @@
         <v>324</v>
       </c>
       <c r="B103" s="8">
-        <v>46107.43494063657</v>
+        <v>46107.60160730324</v>
       </c>
       <c r="C103" s="8">
-        <v>46107.68189209491</v>
+        <v>46107.84855876157</v>
       </c>
       <c r="D103" s="8">
-        <v>46107.681893726854</v>
+        <v>46107.84856039352</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>231</v>
@@ -7909,13 +7909,13 @@
         <v>326</v>
       </c>
       <c r="B104" s="5">
-        <v>46077.653514363425</v>
+        <v>46077.820181030096</v>
       </c>
       <c r="C104" s="5">
-        <v>46114.47811685185</v>
+        <v>46114.64478351852</v>
       </c>
       <c r="D104" s="5">
-        <v>46125.395225775464</v>
+        <v>46125.56189244213</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>327</v>
@@ -7974,13 +7974,13 @@
         <v>330</v>
       </c>
       <c r="B105" s="8">
-        <v>46107.435016828706</v>
+        <v>46107.60168349537</v>
       </c>
       <c r="C105" s="8">
-        <v>46114.4780957176</v>
+        <v>46114.644762384254</v>
       </c>
       <c r="D105" s="8">
-        <v>46114.68904494213</v>
+        <v>46114.8557116088</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>224</v>
@@ -8027,13 +8027,13 @@
         <v>332</v>
       </c>
       <c r="B106" s="5">
-        <v>46107.43508928241</v>
+        <v>46107.60175594907</v>
       </c>
       <c r="C106" s="5">
-        <v>46114.47810065972</v>
+        <v>46114.64476732639</v>
       </c>
       <c r="D106" s="5">
-        <v>46114.68909969907</v>
+        <v>46114.85576636574</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>224</v>
@@ -8080,13 +8080,13 @@
         <v>333</v>
       </c>
       <c r="B107" s="8">
-        <v>46107.43512337963</v>
+        <v>46107.6017900463</v>
       </c>
       <c r="C107" s="8">
-        <v>46107.6819471412</v>
+        <v>46107.84861380787</v>
       </c>
       <c r="D107" s="8">
-        <v>46114.680651574075</v>
+        <v>46114.84731824074</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>228</v>
@@ -8135,13 +8135,13 @@
         <v>335</v>
       </c>
       <c r="B108" s="5">
-        <v>46107.43515822917</v>
+        <v>46107.60182489583</v>
       </c>
       <c r="C108" s="5">
-        <v>46107.68194172454</v>
+        <v>46107.8486083912</v>
       </c>
       <c r="D108" s="5">
-        <v>46114.68076538194</v>
+        <v>46114.84743204861</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>231</v>
@@ -8190,13 +8190,13 @@
         <v>337</v>
       </c>
       <c r="B109" s="8">
-        <v>46077.653514756945</v>
+        <v>46077.82018142361</v>
       </c>
       <c r="C109" s="8">
-        <v>46118.68446939815</v>
+        <v>46118.85113606481</v>
       </c>
       <c r="D109" s="8">
-        <v>46118.694731550924</v>
+        <v>46118.86139821759</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>338</v>
@@ -8255,13 +8255,13 @@
         <v>339</v>
       </c>
       <c r="B110" s="5">
-        <v>46107.43520423611</v>
+        <v>46107.60187090278</v>
       </c>
       <c r="C110" s="5">
-        <v>46114.685311967594</v>
+        <v>46114.85197863426</v>
       </c>
       <c r="D110" s="5">
-        <v>46114.68531369213</v>
+        <v>46114.8519803588</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>224</v>
@@ -8308,13 +8308,13 @@
         <v>341</v>
       </c>
       <c r="B111" s="8">
-        <v>46107.4352709838</v>
+        <v>46107.60193765046</v>
       </c>
       <c r="C111" s="8">
-        <v>46118.6843984838</v>
+        <v>46118.85106515046</v>
       </c>
       <c r="D111" s="8">
-        <v>46118.69489804398</v>
+        <v>46118.86156471065</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>224</v>
@@ -8361,13 +8361,13 @@
         <v>342</v>
       </c>
       <c r="B112" s="5">
-        <v>46107.43531439815</v>
+        <v>46107.601981064814</v>
       </c>
       <c r="C112" s="5">
-        <v>46108.49721596065</v>
+        <v>46108.66388262731</v>
       </c>
       <c r="D112" s="5">
-        <v>46114.68252231482</v>
+        <v>46114.84918898148</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>228</v>
@@ -8414,13 +8414,13 @@
         <v>344</v>
       </c>
       <c r="B113" s="8">
-        <v>46107.43534848379</v>
+        <v>46107.60201515046</v>
       </c>
       <c r="C113" s="8">
-        <v>46108.49722452546</v>
+        <v>46108.66389119213</v>
       </c>
       <c r="D113" s="8">
-        <v>46114.68260300926</v>
+        <v>46114.84926967593</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>231</v>
@@ -8469,13 +8469,13 @@
         <v>346</v>
       </c>
       <c r="B114" s="5">
-        <v>46077.65350886574</v>
+        <v>46077.82017553241</v>
       </c>
       <c r="C114" s="5">
-        <v>46125.39424491898</v>
+        <v>46125.56091158565</v>
       </c>
       <c r="D114" s="5">
-        <v>46125.39504523148</v>
+        <v>46125.561711898146</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>347</v>
@@ -8518,13 +8518,13 @@
         <v>349</v>
       </c>
       <c r="B115" s="8">
-        <v>46077.65350920139</v>
+        <v>46077.82017586805</v>
       </c>
       <c r="C115" s="8">
-        <v>46121.67337837963</v>
+        <v>46121.840045046294</v>
       </c>
       <c r="D115" s="8">
-        <v>46121.67339505787</v>
+        <v>46121.840061724535</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>350</v>
@@ -8583,13 +8583,13 @@
         <v>354</v>
       </c>
       <c r="B116" s="5">
-        <v>46107.435515474535</v>
+        <v>46107.6021821412</v>
       </c>
       <c r="C116" s="5">
-        <v>46121.67334778935</v>
+        <v>46121.840014456015</v>
       </c>
       <c r="D116" s="5">
-        <v>46121.673349930556</v>
+        <v>46121.84001659723</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>224</v>
@@ -8636,13 +8636,13 @@
         <v>356</v>
       </c>
       <c r="B117" s="8">
-        <v>46107.43555876157</v>
+        <v>46107.60222542824</v>
       </c>
       <c r="C117" s="8">
-        <v>46121.67335912037</v>
+        <v>46121.84002578704</v>
       </c>
       <c r="D117" s="8">
-        <v>46121.673360706016</v>
+        <v>46121.84002737269</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>224</v>
@@ -8689,13 +8689,13 @@
         <v>357</v>
       </c>
       <c r="B118" s="5">
-        <v>46107.43558870371</v>
+        <v>46107.602255370366</v>
       </c>
       <c r="C118" s="5">
-        <v>46108.49733738426</v>
+        <v>46108.66400405092</v>
       </c>
       <c r="D118" s="5">
-        <v>46114.69284753472</v>
+        <v>46114.85951420139</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>228</v>
@@ -8744,13 +8744,13 @@
         <v>359</v>
       </c>
       <c r="B119" s="8">
-        <v>46107.43562164352</v>
+        <v>46107.60228831018</v>
       </c>
       <c r="C119" s="8">
-        <v>46108.49736246528</v>
+        <v>46108.66402913195</v>
       </c>
       <c r="D119" s="8">
-        <v>46114.69290731481</v>
+        <v>46114.85957398148</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>231</v>
@@ -8797,13 +8797,13 @@
         <v>361</v>
       </c>
       <c r="B120" s="5">
-        <v>46107.46985704861</v>
+        <v>46107.63652371528</v>
       </c>
       <c r="C120" s="5">
-        <v>46109.56785152778</v>
+        <v>46109.73451819444</v>
       </c>
       <c r="D120" s="5">
-        <v>46109.56785303241</v>
+        <v>46109.73451969908</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>56</v>
@@ -8850,13 +8850,13 @@
         <v>363</v>
       </c>
       <c r="B121" s="8">
-        <v>46107.469900763885</v>
+        <v>46107.636567430556</v>
       </c>
       <c r="C121" s="8">
-        <v>46109.56543170139</v>
+        <v>46109.732098368055</v>
       </c>
       <c r="D121" s="8">
-        <v>46109.56543320602</v>
+        <v>46109.73209987269</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>60</v>
@@ -8903,13 +8903,13 @@
         <v>365</v>
       </c>
       <c r="B122" s="5">
-        <v>46107.46993355324</v>
+        <v>46107.63660021991</v>
       </c>
       <c r="C122" s="5">
-        <v>46109.56547548611</v>
+        <v>46109.732142152774</v>
       </c>
       <c r="D122" s="5">
-        <v>46109.56547681713</v>
+        <v>46109.732143483794</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>63</v>
@@ -8956,13 +8956,13 @@
         <v>367</v>
       </c>
       <c r="B123" s="8">
-        <v>46107.46997388889</v>
+        <v>46107.63664055556</v>
       </c>
       <c r="C123" s="8">
-        <v>46113.39993212963</v>
+        <v>46113.5665987963</v>
       </c>
       <c r="D123" s="8">
-        <v>46113.399933622684</v>
+        <v>46113.566600289356</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>66</v>
@@ -9009,13 +9009,13 @@
         <v>369</v>
       </c>
       <c r="B124" s="5">
-        <v>46107.470011550926</v>
+        <v>46107.63667821759</v>
       </c>
       <c r="C124" s="5">
-        <v>46113.39994310185</v>
+        <v>46113.56660976852</v>
       </c>
       <c r="D124" s="5">
-        <v>46113.39994459491</v>
+        <v>46113.56661126157</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>69</v>
@@ -9062,13 +9062,13 @@
         <v>371</v>
       </c>
       <c r="B125" s="8">
-        <v>46077.653509490745</v>
+        <v>46077.82017615741</v>
       </c>
       <c r="C125" s="8">
-        <v>46122.4457921875</v>
+        <v>46122.61245885417</v>
       </c>
       <c r="D125" s="8">
-        <v>46126.00348665509</v>
+        <v>46126.17015332176</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>372</v>
@@ -9127,13 +9127,13 @@
         <v>374</v>
       </c>
       <c r="B126" s="5">
-        <v>46107.435665509256</v>
+        <v>46107.60233217593</v>
       </c>
       <c r="C126" s="5">
-        <v>46122.44576736111</v>
+        <v>46122.612434027775</v>
       </c>
       <c r="D126" s="5">
-        <v>46122.44576905093</v>
+        <v>46122.612435717594</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>224</v>
@@ -9182,13 +9182,13 @@
         <v>376</v>
       </c>
       <c r="B127" s="8">
-        <v>46107.43573319445</v>
+        <v>46107.60239986111</v>
       </c>
       <c r="C127" s="8">
-        <v>46122.445778657406</v>
+        <v>46122.61244532408</v>
       </c>
       <c r="D127" s="8">
-        <v>46122.44578006944</v>
+        <v>46122.61244673611</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>224</v>
@@ -9237,13 +9237,13 @@
         <v>377</v>
       </c>
       <c r="B128" s="5">
-        <v>46107.43576706019</v>
+        <v>46107.60243372685</v>
       </c>
       <c r="C128" s="5">
-        <v>46108.49749129629</v>
+        <v>46108.664157962965</v>
       </c>
       <c r="D128" s="5">
-        <v>46114.69284715278</v>
+        <v>46114.85951381944</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>228</v>
@@ -9292,13 +9292,13 @@
         <v>379</v>
       </c>
       <c r="B129" s="8">
-        <v>46107.435805138884</v>
+        <v>46107.602471805556</v>
       </c>
       <c r="C129" s="8">
-        <v>46108.4974994213</v>
+        <v>46108.66416608796</v>
       </c>
       <c r="D129" s="8">
-        <v>46114.69290652778</v>
+        <v>46114.859573194444</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>231</v>
@@ -9347,13 +9347,13 @@
         <v>381</v>
       </c>
       <c r="B130" s="5">
-        <v>46107.47200091435</v>
+        <v>46107.63866758102</v>
       </c>
       <c r="C130" s="5">
-        <v>46109.567952638885</v>
+        <v>46109.73461930556</v>
       </c>
       <c r="D130" s="5">
-        <v>46109.56795405093</v>
+        <v>46109.734620717594</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>56</v>
@@ -9402,13 +9402,13 @@
         <v>383</v>
       </c>
       <c r="B131" s="8">
-        <v>46107.47204607639</v>
+        <v>46107.63871274306</v>
       </c>
       <c r="C131" s="8">
-        <v>46109.56796303241</v>
+        <v>46109.73462969907</v>
       </c>
       <c r="D131" s="8">
-        <v>46109.567964525464</v>
+        <v>46109.73463119213</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>60</v>
@@ -9457,13 +9457,13 @@
         <v>385</v>
       </c>
       <c r="B132" s="5">
-        <v>46107.47208232639</v>
+        <v>46107.63874899306</v>
       </c>
       <c r="C132" s="5">
-        <v>46109.567997465274</v>
+        <v>46109.734664131945</v>
       </c>
       <c r="D132" s="5">
-        <v>46109.56799877315</v>
+        <v>46109.73466543981</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>63</v>
@@ -9512,13 +9512,13 @@
         <v>387</v>
       </c>
       <c r="B133" s="8">
-        <v>46107.47212644676</v>
+        <v>46107.63879311342</v>
       </c>
       <c r="C133" s="8">
-        <v>46113.40002371528</v>
+        <v>46113.566690381944</v>
       </c>
       <c r="D133" s="8">
-        <v>46113.40002502315</v>
+        <v>46113.56669168982</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>66</v>
@@ -9567,13 +9567,13 @@
         <v>389</v>
       </c>
       <c r="B134" s="5">
-        <v>46107.472158449076</v>
+        <v>46107.63882511574</v>
       </c>
       <c r="C134" s="5">
-        <v>46113.40003310185</v>
+        <v>46113.56669976852</v>
       </c>
       <c r="D134" s="5">
-        <v>46113.40003446759</v>
+        <v>46113.56670113426</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>69</v>
@@ -9622,13 +9622,13 @@
         <v>391</v>
       </c>
       <c r="B135" s="8">
-        <v>46077.653509780095</v>
+        <v>46077.82017644676</v>
       </c>
       <c r="C135" s="8">
-        <v>46125.39418625</v>
+        <v>46125.560852916664</v>
       </c>
       <c r="D135" s="8">
-        <v>46127.018723113426</v>
+        <v>46127.18538978009</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>392</v>
@@ -9687,13 +9687,13 @@
         <v>395</v>
       </c>
       <c r="B136" s="5">
-        <v>46107.43598591435</v>
+        <v>46107.602652581016</v>
       </c>
       <c r="C136" s="5">
-        <v>46125.394441805554</v>
+        <v>46125.56110847222</v>
       </c>
       <c r="D136" s="5">
-        <v>46125.39444354166</v>
+        <v>46125.561110208335</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>224</v>
@@ -9740,13 +9740,13 @@
         <v>397</v>
       </c>
       <c r="B137" s="8">
-        <v>46107.436006585645</v>
+        <v>46107.60267325232</v>
       </c>
       <c r="C137" s="8">
-        <v>46125.39445302083</v>
+        <v>46125.561119687496</v>
       </c>
       <c r="D137" s="8">
-        <v>46125.394454548616</v>
+        <v>46125.56112121527</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>224</v>
@@ -9793,13 +9793,13 @@
         <v>398</v>
       </c>
       <c r="B138" s="5">
-        <v>46107.436163171296</v>
+        <v>46107.60282983797</v>
       </c>
       <c r="C138" s="5">
-        <v>46109.56209954861</v>
+        <v>46109.72876621528</v>
       </c>
       <c r="D138" s="5">
-        <v>46114.69138053241</v>
+        <v>46114.85804719907</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>228</v>
@@ -9846,13 +9846,13 @@
         <v>400</v>
       </c>
       <c r="B139" s="8">
-        <v>46107.4362052662</v>
+        <v>46107.602871932875</v>
       </c>
       <c r="C139" s="8">
-        <v>46109.56211155093</v>
+        <v>46109.72877821759</v>
       </c>
       <c r="D139" s="8">
-        <v>46114.69138138889</v>
+        <v>46114.858048055554</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>231</v>
@@ -9899,13 +9899,13 @@
         <v>402</v>
       </c>
       <c r="B140" s="5">
-        <v>46107.43795597222</v>
+        <v>46107.604622638886</v>
       </c>
       <c r="C140" s="5">
-        <v>46109.56809878472</v>
+        <v>46109.73476545139</v>
       </c>
       <c r="D140" s="5">
-        <v>46109.56810045139</v>
+        <v>46109.734767118054</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>56</v>
@@ -9952,13 +9952,13 @@
         <v>404</v>
       </c>
       <c r="B141" s="8">
-        <v>46107.43799892361</v>
+        <v>46107.604665590276</v>
       </c>
       <c r="C141" s="8">
-        <v>46109.568112395835</v>
+        <v>46109.7347790625</v>
       </c>
       <c r="D141" s="8">
-        <v>46109.56811394676</v>
+        <v>46109.73478061343</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>60</v>
@@ -10005,13 +10005,13 @@
         <v>406</v>
       </c>
       <c r="B142" s="5">
-        <v>46107.438038148146</v>
+        <v>46107.60470481482</v>
       </c>
       <c r="C142" s="5">
-        <v>46109.56814829861</v>
+        <v>46109.73481496528</v>
       </c>
       <c r="D142" s="5">
-        <v>46109.56814986111</v>
+        <v>46109.73481652778</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>63</v>
@@ -10058,13 +10058,13 @@
         <v>408</v>
       </c>
       <c r="B143" s="8">
-        <v>46107.438075405094</v>
+        <v>46107.60474207176</v>
       </c>
       <c r="C143" s="8">
-        <v>46113.400086435184</v>
+        <v>46113.566753101855</v>
       </c>
       <c r="D143" s="8">
-        <v>46113.40008774305</v>
+        <v>46113.56675440972</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>66</v>
@@ -10111,13 +10111,13 @@
         <v>410</v>
       </c>
       <c r="B144" s="5">
-        <v>46107.43810650463</v>
+        <v>46107.6047731713</v>
       </c>
       <c r="C144" s="5">
-        <v>46113.400100659725</v>
+        <v>46113.56676732639</v>
       </c>
       <c r="D144" s="5">
-        <v>46113.40010255787</v>
+        <v>46113.56676922453</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>69</v>
@@ -10164,13 +10164,13 @@
         <v>412</v>
       </c>
       <c r="B145" s="8">
-        <v>46077.65351005787</v>
+        <v>46077.820176724534</v>
       </c>
       <c r="C145" s="8">
-        <v>46125.39422983796</v>
+        <v>46125.56089650463</v>
       </c>
       <c r="D145" s="8">
-        <v>46128.030638738426</v>
+        <v>46128.19730540509</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>413</v>
@@ -10229,13 +10229,13 @@
         <v>416</v>
       </c>
       <c r="B146" s="5">
-        <v>46107.438723113424</v>
+        <v>46107.60538978009</v>
       </c>
       <c r="C146" s="5">
-        <v>46125.39450851852</v>
+        <v>46125.56117518518</v>
       </c>
       <c r="D146" s="5">
-        <v>46125.394510011574</v>
+        <v>46125.56117667824</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>224</v>
@@ -10282,13 +10282,13 @@
         <v>417</v>
       </c>
       <c r="B147" s="8">
-        <v>46107.43882452547</v>
+        <v>46107.60549119213</v>
       </c>
       <c r="C147" s="8">
-        <v>46125.39451719908</v>
+        <v>46125.56118386574</v>
       </c>
       <c r="D147" s="8">
-        <v>46125.39451866898</v>
+        <v>46125.56118533565</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>224</v>
@@ -10335,13 +10335,13 @@
         <v>418</v>
       </c>
       <c r="B148" s="5">
-        <v>46107.43886091435</v>
+        <v>46107.60552758102</v>
       </c>
       <c r="C148" s="5">
-        <v>46109.56822582176</v>
+        <v>46109.73489248843</v>
       </c>
       <c r="D148" s="5">
-        <v>46114.69214179398</v>
+        <v>46114.858808460645</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>228</v>
@@ -10388,13 +10388,13 @@
         <v>419</v>
       </c>
       <c r="B149" s="8">
-        <v>46107.43889311343</v>
+        <v>46107.60555978009</v>
       </c>
       <c r="C149" s="8">
-        <v>46109.5682419213</v>
+        <v>46109.73490858796</v>
       </c>
       <c r="D149" s="8">
-        <v>46114.69204347223</v>
+        <v>46114.858710138884</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>231</v>
@@ -10441,13 +10441,13 @@
         <v>420</v>
       </c>
       <c r="B150" s="5">
-        <v>46107.439016122684</v>
+        <v>46107.60568278935</v>
       </c>
       <c r="C150" s="5">
-        <v>46109.56874033565</v>
+        <v>46109.735407002314</v>
       </c>
       <c r="D150" s="5">
-        <v>46109.56874215278</v>
+        <v>46109.73540881944</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>421</v>
@@ -10494,13 +10494,13 @@
         <v>422</v>
       </c>
       <c r="B151" s="8">
-        <v>46107.43907828703</v>
+        <v>46107.605744953704</v>
       </c>
       <c r="C151" s="8">
-        <v>46109.56880127315</v>
+        <v>46109.73546793981</v>
       </c>
       <c r="D151" s="8">
-        <v>46109.56880287037</v>
+        <v>46109.73546953704</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>60</v>
@@ -10547,13 +10547,13 @@
         <v>423</v>
       </c>
       <c r="B152" s="5">
-        <v>46107.43916361111</v>
+        <v>46107.60583027778</v>
       </c>
       <c r="C152" s="5">
-        <v>46109.56885171296</v>
+        <v>46109.73551837963</v>
       </c>
       <c r="D152" s="5">
-        <v>46109.56885335648</v>
+        <v>46109.73552002315</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>63</v>
@@ -10600,13 +10600,13 @@
         <v>424</v>
       </c>
       <c r="B153" s="8">
-        <v>46107.43920138889</v>
+        <v>46107.60586805556</v>
       </c>
       <c r="C153" s="8">
-        <v>46113.4001645949</v>
+        <v>46113.566831261574</v>
       </c>
       <c r="D153" s="8">
-        <v>46113.40016614583</v>
+        <v>46113.5668328125</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>66</v>
@@ -10653,13 +10653,13 @@
         <v>425</v>
       </c>
       <c r="B154" s="5">
-        <v>46107.43923920139</v>
+        <v>46107.605905868055</v>
       </c>
       <c r="C154" s="5">
-        <v>46113.40017584491</v>
+        <v>46113.56684251157</v>
       </c>
       <c r="D154" s="5">
-        <v>46113.40017732639</v>
+        <v>46113.56684399306</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>69</v>
@@ -10706,11 +10706,11 @@
         <v>426</v>
       </c>
       <c r="B155" s="8">
-        <v>46077.65351034723</v>
+        <v>46077.820177013884</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46114.48416508102</v>
+        <v>46114.650831747684</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>427</v>
@@ -10753,11 +10753,11 @@
         <v>429</v>
       </c>
       <c r="B156" s="5">
-        <v>46077.65351063658</v>
+        <v>46077.82017730324</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46137.02136050926</v>
+        <v>46137.18802717593</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>430</v>
@@ -10816,11 +10816,11 @@
         <v>434</v>
       </c>
       <c r="B157" s="8">
-        <v>46077.653510902775</v>
+        <v>46077.82017756945</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46137.02136047454</v>
+        <v>46137.18802714121</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>435</v>
@@ -10879,11 +10879,11 @@
         <v>437</v>
       </c>
       <c r="B158" s="5">
-        <v>46090.71338690972</v>
+        <v>46090.88005357639</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46114.48434215278</v>
+        <v>46114.65100881945</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>438</v>
@@ -10926,11 +10926,11 @@
         <v>440</v>
       </c>
       <c r="B159" s="8">
-        <v>46090.713713668985</v>
+        <v>46090.88038033565</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46137.02136048611</v>
+        <v>46137.18802715278</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>441</v>
@@ -10989,11 +10989,11 @@
         <v>442</v>
       </c>
       <c r="B160" s="5">
-        <v>46090.71395774306</v>
+        <v>46090.88062440972</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46137.02136047454</v>
+        <v>46137.18802714121</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>443</v>

--- a/data/50001451 - ZITRON COLOMBIA.xlsx
+++ b/data/50001451 - ZITRON COLOMBIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1828" uniqueCount="443">
   <si>
     <t>50001451 - ZITRON COLOMBIA</t>
   </si>
@@ -317,9 +317,6 @@
   </si>
   <si>
     <t>propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC materiales</t>
@@ -3422,11 +3419,9 @@
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H28" s="6"/>
       <c r="I28" s="5">
         <v>45903</v>
       </c>
@@ -3449,7 +3444,7 @@
         <v>81</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q28" s="5">
         <v>45903</v>
@@ -3469,7 +3464,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B29" s="8">
         <v>46078.658673831014</v>
@@ -3481,7 +3476,7 @@
         <v>46104.62858377315</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3514,7 +3509,7 @@
         <v>81</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q29" s="8">
         <v>45903</v>
@@ -3534,7 +3529,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B30" s="5">
         <v>46078.65875901621</v>
@@ -3546,7 +3541,7 @@
         <v>46097.536774548615</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3579,7 +3574,7 @@
         <v>81</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q30" s="5">
         <v>45903</v>
@@ -3599,7 +3594,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B31" s="8">
         <v>46077.820175960645</v>
@@ -3611,7 +3606,7 @@
         <v>46112.798028969904</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>25</v>
@@ -3635,7 +3630,7 @@
         <v>26</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P31" s="9" t="s">
         <v>26</v>
@@ -3648,7 +3643,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B32" s="5">
         <v>46077.82017622685</v>
@@ -3660,16 +3655,16 @@
         <v>46097.535346944445</v>
       </c>
       <c r="E32" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="F32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G32" s="6" t="s">
+      <c r="H32" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="I32" s="5">
         <v>45912</v>
@@ -3687,13 +3682,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q32" s="5">
         <v>45912</v>
@@ -3713,7 +3708,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B33" s="8">
         <v>46077.820176504625</v>
@@ -3725,16 +3720,16 @@
         <v>46097.535276400464</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="H33" s="9" t="s">
         <v>115</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>116</v>
       </c>
       <c r="I33" s="8">
         <v>45912</v>
@@ -3752,13 +3747,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>92</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3766,15 +3761,15 @@
         <v>0</v>
       </c>
       <c r="T33" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="U33" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="U33" s="10" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B34" s="5">
         <v>46077.82017679398</v>
@@ -3786,16 +3781,16 @@
         <v>46097.53531515047</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="I34" s="5">
         <v>45916</v>
@@ -3813,13 +3808,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3827,15 +3822,15 @@
         <v>0</v>
       </c>
       <c r="T34" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="U34" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="U34" s="10" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B35" s="8">
         <v>46077.82017706019</v>
@@ -3847,16 +3842,16 @@
         <v>46097.539690150465</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="H35" s="9" t="s">
         <v>115</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>116</v>
       </c>
       <c r="I35" s="8">
         <v>45908</v>
@@ -3874,13 +3869,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q35" s="8">
         <v>45908</v>
@@ -3900,7 +3895,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B36" s="5">
         <v>46077.82017730324</v>
@@ -3912,16 +3907,16 @@
         <v>46097.53890119213</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="I36" s="5">
         <v>45908</v>
@@ -3939,13 +3934,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>95</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3953,15 +3948,15 @@
         <v>0</v>
       </c>
       <c r="T36" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="U36" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="U36" s="10" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B37" s="8">
         <v>46077.82017755787</v>
@@ -3973,16 +3968,16 @@
         <v>46097.53966494213</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="H37" s="9" t="s">
         <v>115</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>116</v>
       </c>
       <c r="I37" s="8">
         <v>45917</v>
@@ -4000,13 +3995,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -4014,15 +4009,15 @@
         <v>0</v>
       </c>
       <c r="T37" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="U37" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="U37" s="10" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B38" s="5">
         <v>46077.8201778125</v>
@@ -4034,16 +4029,16 @@
         <v>46097.53602381944</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="I38" s="5">
         <v>45912</v>
@@ -4061,13 +4056,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q38" s="5">
         <v>45912</v>
@@ -4087,7 +4082,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B39" s="8">
         <v>46077.820178055554</v>
@@ -4099,16 +4094,16 @@
         <v>46097.5359540625</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="H39" s="9" t="s">
         <v>115</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>116</v>
       </c>
       <c r="I39" s="8">
         <v>45912</v>
@@ -4126,13 +4121,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>98</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -4140,15 +4135,15 @@
         <v>0</v>
       </c>
       <c r="T39" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="U39" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="U39" s="10" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B40" s="5">
         <v>46077.82017554398</v>
@@ -4160,16 +4155,16 @@
         <v>46097.53599474537</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="I40" s="5">
         <v>45916</v>
@@ -4187,13 +4182,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4201,15 +4196,15 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="U40" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="U40" s="10" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B41" s="8">
         <v>46077.82017600695</v>
@@ -4221,16 +4216,16 @@
         <v>46097.5354607176</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>115</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>116</v>
       </c>
       <c r="I41" s="8">
         <v>45898</v>
@@ -4248,13 +4243,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q41" s="8">
         <v>45898</v>
@@ -4274,7 +4269,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B42" s="5">
         <v>46077.820176319445</v>
@@ -4286,16 +4281,16 @@
         <v>46182.693444861114</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="I42" s="5">
         <v>45898</v>
@@ -4313,13 +4308,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O42" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="P42" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="P42" s="6" t="s">
-        <v>150</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4327,15 +4322,15 @@
         <v>0</v>
       </c>
       <c r="T42" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="U42" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="U42" s="10" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B43" s="8">
         <v>46077.82017663194</v>
@@ -4347,16 +4342,16 @@
         <v>46097.5354075</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>115</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>116</v>
       </c>
       <c r="I43" s="8">
         <v>45922</v>
@@ -4374,13 +4369,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -4388,15 +4383,15 @@
         <v>0</v>
       </c>
       <c r="T43" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="U43" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="U43" s="10" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B44" s="5">
         <v>46077.82017693287</v>
@@ -4408,16 +4403,16 @@
         <v>46097.535433425925</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="I44" s="5">
         <v>45922</v>
@@ -4435,13 +4430,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4449,15 +4444,15 @@
         <v>0</v>
       </c>
       <c r="T44" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="U44" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="U44" s="10" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B45" s="8">
         <v>46077.82017723379</v>
@@ -4469,16 +4464,16 @@
         <v>46097.53669974537</v>
       </c>
       <c r="E45" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="F45" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="9" t="s">
+      <c r="H45" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>160</v>
       </c>
       <c r="I45" s="8">
         <v>45912</v>
@@ -4496,13 +4491,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q45" s="8">
         <v>45912</v>
@@ -4522,7 +4517,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B46" s="5">
         <v>46077.82017756945</v>
@@ -4534,16 +4529,16 @@
         <v>46097.53661077547</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I46" s="5">
         <v>45912</v>
@@ -4561,13 +4556,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>101</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4575,15 +4570,15 @@
         <v>0</v>
       </c>
       <c r="T46" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="U46" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="U46" s="10" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B47" s="8">
         <v>46077.820177870366</v>
@@ -4595,16 +4590,16 @@
         <v>46097.536673703704</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H47" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>160</v>
       </c>
       <c r="I47" s="8">
         <v>45932</v>
@@ -4622,13 +4617,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4636,15 +4631,15 @@
         <v>0</v>
       </c>
       <c r="T47" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="U47" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="U47" s="10" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B48" s="5">
         <v>46078.65559880787</v>
@@ -4656,16 +4651,16 @@
         <v>46107.84042637731</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I48" s="5">
         <v>45912</v>
@@ -4683,13 +4678,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q48" s="5">
         <v>45912</v>
@@ -4709,7 +4704,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B49" s="8">
         <v>46078.655658090276</v>
@@ -4721,16 +4716,16 @@
         <v>46107.84024543982</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>160</v>
       </c>
       <c r="I49" s="8">
         <v>45912</v>
@@ -4748,13 +4743,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q49" s="9"/>
       <c r="R49" s="9"/>
@@ -4762,15 +4757,15 @@
         <v>0</v>
       </c>
       <c r="T49" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="U49" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="U49" s="10" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B50" s="5">
         <v>46078.65577003472</v>
@@ -4782,16 +4777,16 @@
         <v>46107.84033961805</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I50" s="5">
         <v>45946</v>
@@ -4809,13 +4804,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4823,15 +4818,15 @@
         <v>0</v>
       </c>
       <c r="T50" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="U50" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="U50" s="10" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B51" s="8">
         <v>46078.654245046295</v>
@@ -4843,16 +4838,16 @@
         <v>46105.78342381945</v>
       </c>
       <c r="E51" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="F51" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="9" t="s">
+      <c r="H51" s="9" t="s">
         <v>178</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>179</v>
       </c>
       <c r="I51" s="8">
         <v>45912</v>
@@ -4870,13 +4865,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q51" s="8">
         <v>45912</v>
@@ -4896,7 +4891,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B52" s="5">
         <v>46078.65429936342</v>
@@ -4908,16 +4903,16 @@
         <v>46111.65554150463</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="I52" s="5">
         <v>45912</v>
@@ -4935,13 +4930,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4949,15 +4944,15 @@
         <v>0</v>
       </c>
       <c r="T52" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="U52" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="U52" s="10" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B53" s="8">
         <v>46078.65468994213</v>
@@ -4969,16 +4964,16 @@
         <v>46105.7833940625</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>178</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>179</v>
       </c>
       <c r="I53" s="8">
         <v>45968</v>
@@ -4996,13 +4991,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O53" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="P53" s="9" t="s">
         <v>186</v>
-      </c>
-      <c r="P53" s="9" t="s">
-        <v>187</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5010,15 +5005,15 @@
         <v>0</v>
       </c>
       <c r="T53" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="U53" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="U53" s="10" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B54" s="5">
         <v>46104.63046165509</v>
@@ -5030,16 +5025,16 @@
         <v>46107.67902436343</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="I54" s="5">
         <v>45912</v>
@@ -5057,10 +5052,10 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -5073,7 +5068,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B55" s="8">
         <v>46104.631274988424</v>
@@ -5085,16 +5080,16 @@
         <v>46107.67921902778</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>178</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>179</v>
       </c>
       <c r="I55" s="8">
         <v>45912</v>
@@ -5112,10 +5107,10 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5128,7 +5123,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B56" s="5">
         <v>46104.631671678246</v>
@@ -5140,16 +5135,16 @@
         <v>46107.67933054398</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="I56" s="5">
         <v>45912</v>
@@ -5167,10 +5162,10 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -5183,7 +5178,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B57" s="8">
         <v>46104.63195700232</v>
@@ -5195,16 +5190,16 @@
         <v>46107.67943891203</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>178</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>179</v>
       </c>
       <c r="I57" s="8">
         <v>45912</v>
@@ -5222,10 +5217,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -5238,7 +5233,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B58" s="5">
         <v>46104.632084826386</v>
@@ -5250,16 +5245,16 @@
         <v>46107.67985042824</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="I58" s="5">
         <v>45912</v>
@@ -5277,10 +5272,10 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5293,7 +5288,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B59" s="8">
         <v>46104.63227371528</v>
@@ -5305,16 +5300,16 @@
         <v>46107.67955858796</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>178</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>179</v>
       </c>
       <c r="I59" s="8">
         <v>45912</v>
@@ -5332,10 +5327,10 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>26</v>
@@ -5348,7 +5343,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B60" s="5">
         <v>46077.82017815972</v>
@@ -5360,7 +5355,7 @@
         <v>46114.84872589121</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5384,7 +5379,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5399,7 +5394,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B61" s="8">
         <v>46077.82017846065</v>
@@ -5411,16 +5406,16 @@
         <v>46197.707138425925</v>
       </c>
       <c r="E61" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="F61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="9" t="s">
+      <c r="H61" s="9" t="s">
         <v>205</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>206</v>
       </c>
       <c r="I61" s="8">
         <v>45903</v>
@@ -5438,13 +5433,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>81</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q61" s="8">
         <v>45903</v>
@@ -5464,7 +5459,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B62" s="5">
         <v>46077.82017626158</v>
@@ -5476,16 +5471,16 @@
         <v>46197.707159328704</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>205</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>206</v>
       </c>
       <c r="I62" s="5">
         <v>45960</v>
@@ -5503,13 +5498,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O62" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="Q62" s="5">
         <v>45960</v>
@@ -5529,7 +5524,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B63" s="8">
         <v>46090.87971813657</v>
@@ -5541,16 +5536,16 @@
         <v>46114.650833692125</v>
       </c>
       <c r="E63" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="F63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="9" t="s">
+      <c r="H63" s="9" t="s">
         <v>214</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>215</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="8">
@@ -5566,13 +5561,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q63" s="8">
         <v>45967</v>
@@ -5592,7 +5587,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B64" s="5">
         <v>46090.8798415162</v>
@@ -5604,16 +5599,16 @@
         <v>46119.77882065972</v>
       </c>
       <c r="E64" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G64" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="F64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G64" s="6" t="s">
+      <c r="H64" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I64" s="5">
         <v>46092</v>
@@ -5631,13 +5626,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q64" s="5">
         <v>46092</v>
@@ -5657,7 +5652,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B65" s="8">
         <v>46107.60619210648</v>
@@ -5669,16 +5664,16 @@
         <v>46114.78855586806</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="I65" s="9"/>
       <c r="J65" s="8">
@@ -5694,13 +5689,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5710,7 +5705,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B66" s="5">
         <v>46107.60640244213</v>
@@ -5722,16 +5717,16 @@
         <v>46114.7885828125</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5747,13 +5742,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5763,7 +5758,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B67" s="8">
         <v>46107.606435821755</v>
@@ -5775,16 +5770,16 @@
         <v>46114.84832498843</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>214</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>215</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="8">
@@ -5794,19 +5789,19 @@
         <v>26</v>
       </c>
       <c r="L67" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -5816,7 +5811,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B68" s="5">
         <v>46107.60648386574</v>
@@ -5828,16 +5823,16 @@
         <v>46114.84847162037</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>214</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>215</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5853,13 +5848,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5869,7 +5864,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B69" s="8">
         <v>46078.65390563657</v>
@@ -5881,7 +5876,7 @@
         <v>46107.68737451389</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5905,10 +5900,10 @@
         <v>26</v>
       </c>
       <c r="O69" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="P69" s="9" t="s">
         <v>234</v>
-      </c>
-      <c r="P69" s="9" t="s">
-        <v>235</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5922,7 +5917,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B70" s="5">
         <v>46078.702559108795</v>
@@ -5934,16 +5929,16 @@
         <v>46107.840496770834</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>238</v>
       </c>
       <c r="I70" s="5">
         <v>46057</v>
@@ -5961,13 +5956,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="O70" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="P70" s="6" t="s">
         <v>239</v>
-      </c>
-      <c r="P70" s="6" t="s">
-        <v>240</v>
       </c>
       <c r="Q70" s="5">
         <v>46057</v>
@@ -5987,7 +5982,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B71" s="8">
         <v>46077.82017896991</v>
@@ -5999,7 +5994,7 @@
         <v>46107.843893425925</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -6023,7 +6018,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6040,7 +6035,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B72" s="5">
         <v>46077.820179305556</v>
@@ -6052,16 +6047,16 @@
         <v>46107.842354259265</v>
       </c>
       <c r="E72" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G72" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="F72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G72" s="6" t="s">
+      <c r="H72" s="6" t="s">
         <v>246</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>247</v>
       </c>
       <c r="I72" s="5">
         <v>45971</v>
@@ -6079,13 +6074,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q72" s="5">
         <v>45971</v>
@@ -6105,7 +6100,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B73" s="8">
         <v>46077.820177430556</v>
@@ -6123,10 +6118,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>246</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>247</v>
       </c>
       <c r="I73" s="8">
         <v>46027</v>
@@ -6144,13 +6139,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q73" s="8">
         <v>46027</v>
@@ -6170,7 +6165,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B74" s="5">
         <v>46077.82017795139</v>
@@ -6182,16 +6177,16 @@
         <v>46107.841941238425</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>246</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>247</v>
       </c>
       <c r="I74" s="5">
         <v>46041</v>
@@ -6209,13 +6204,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q74" s="5">
         <v>46041</v>
@@ -6235,7 +6230,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B75" s="8">
         <v>46077.82017841435</v>
@@ -6247,16 +6242,16 @@
         <v>46107.841844375</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>246</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>247</v>
       </c>
       <c r="I75" s="8">
         <v>46056</v>
@@ -6274,13 +6269,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q75" s="8">
         <v>46056</v>
@@ -6300,7 +6295,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B76" s="5">
         <v>46078.65892270833</v>
@@ -6312,16 +6307,16 @@
         <v>46107.84287946759</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>246</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>247</v>
       </c>
       <c r="I76" s="5">
         <v>46057</v>
@@ -6339,13 +6334,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q76" s="5">
         <v>46034</v>
@@ -6365,7 +6360,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B77" s="8">
         <v>46078.65900237269</v>
@@ -6377,16 +6372,16 @@
         <v>46107.842393032406</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="H77" s="9" t="s">
         <v>246</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>247</v>
       </c>
       <c r="I77" s="8">
         <v>46034</v>
@@ -6404,13 +6399,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q77" s="8">
         <v>46034</v>
@@ -6430,7 +6425,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B78" s="5">
         <v>46077.82017907407</v>
@@ -6442,7 +6437,7 @@
         <v>46125.56179637731</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6466,7 +6461,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6481,7 +6476,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B79" s="8">
         <v>46077.82017943287</v>
@@ -6493,17 +6488,15 @@
         <v>46114.85330988426</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H79" s="9"/>
       <c r="I79" s="8">
         <v>46059</v>
       </c>
@@ -6520,13 +6513,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q79" s="8">
         <v>46059</v>
@@ -6546,7 +6539,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B80" s="5">
         <v>46107.59662881945</v>
@@ -6558,17 +6551,15 @@
         <v>46114.856069733796</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H80" s="6"/>
       <c r="I80" s="5">
         <v>46108</v>
       </c>
@@ -6585,13 +6576,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6601,7 +6592,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B81" s="8">
         <v>46107.59776125</v>
@@ -6613,17 +6604,15 @@
         <v>46114.856118923606</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H81" s="9"/>
       <c r="I81" s="8">
         <v>46108</v>
       </c>
@@ -6640,13 +6629,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6656,7 +6645,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B82" s="5">
         <v>46107.597173993054</v>
@@ -6668,17 +6657,15 @@
         <v>46107.83873434028</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H82" s="6"/>
       <c r="I82" s="5">
         <v>46059</v>
       </c>
@@ -6695,13 +6682,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6711,7 +6698,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B83" s="8">
         <v>46107.59746188657</v>
@@ -6723,17 +6710,15 @@
         <v>46107.83874050926</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H83" s="9"/>
       <c r="I83" s="8">
         <v>46059</v>
       </c>
@@ -6750,13 +6735,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6766,7 +6751,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B84" s="5">
         <v>46077.82017980324</v>
@@ -6778,17 +6763,15 @@
         <v>46125.56182928241</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H84" s="6"/>
       <c r="I84" s="5">
         <v>46079</v>
       </c>
@@ -6805,13 +6788,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O84" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="P84" s="6" t="s">
         <v>275</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>276</v>
       </c>
       <c r="Q84" s="5">
         <v>46079</v>
@@ -6831,7 +6814,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B85" s="8">
         <v>46107.59978276621</v>
@@ -6843,17 +6826,15 @@
         <v>46114.855711296295</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H85" s="9"/>
       <c r="I85" s="8">
         <v>46111</v>
       </c>
@@ -6870,13 +6851,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O85" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="P85" s="9" t="s">
         <v>278</v>
-      </c>
-      <c r="P85" s="9" t="s">
-        <v>279</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6886,7 +6867,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B86" s="5">
         <v>46107.59982243055</v>
@@ -6898,17 +6879,15 @@
         <v>46114.85576582176</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H86" s="6"/>
       <c r="I86" s="5">
         <v>46111</v>
       </c>
@@ -6925,13 +6904,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O86" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="P86" s="6" t="s">
         <v>278</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>279</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6941,7 +6920,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B87" s="8">
         <v>46107.59986486111</v>
@@ -6953,17 +6932,15 @@
         <v>46107.84839457176</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H87" s="9"/>
       <c r="I87" s="8">
         <v>46079</v>
       </c>
@@ -6980,13 +6957,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O87" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="P87" s="9" t="s">
         <v>282</v>
-      </c>
-      <c r="P87" s="9" t="s">
-        <v>283</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -6996,7 +6973,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B88" s="5">
         <v>46107.59991125</v>
@@ -7008,17 +6985,15 @@
         <v>46107.8483881713</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H88" s="6"/>
       <c r="I88" s="5">
         <v>46079</v>
       </c>
@@ -7035,13 +7010,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O88" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="P88" s="6" t="s">
         <v>285</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>286</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7051,7 +7026,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B89" s="8">
         <v>46077.82018026621</v>
@@ -7063,17 +7038,15 @@
         <v>46125.56184609953</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H89" s="9"/>
       <c r="I89" s="8">
         <v>46083</v>
       </c>
@@ -7090,13 +7063,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q89" s="8">
         <v>46083</v>
@@ -7116,7 +7089,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B90" s="5">
         <v>46107.59995462963</v>
@@ -7128,17 +7101,15 @@
         <v>46114.85594553241</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H90" s="6"/>
       <c r="I90" s="5">
         <v>46112</v>
       </c>
@@ -7155,13 +7126,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="O90" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="P90" s="6" t="s">
         <v>292</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>293</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7171,7 +7142,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B91" s="8">
         <v>46107.60002673611</v>
@@ -7183,17 +7154,15 @@
         <v>46114.85576615741</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H91" s="9"/>
       <c r="I91" s="8">
         <v>46112</v>
       </c>
@@ -7210,13 +7179,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -7226,7 +7195,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B92" s="5">
         <v>46107.60006982639</v>
@@ -7238,17 +7207,15 @@
         <v>46107.84844032407</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H92" s="6"/>
       <c r="I92" s="5">
         <v>46083</v>
       </c>
@@ -7265,13 +7232,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="O92" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="P92" s="6" t="s">
         <v>297</v>
-      </c>
-      <c r="P92" s="6" t="s">
-        <v>298</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7281,7 +7248,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B93" s="8">
         <v>46107.600104930556</v>
@@ -7293,17 +7260,15 @@
         <v>46107.84843525463</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H93" s="9"/>
       <c r="I93" s="8">
         <v>46083</v>
       </c>
@@ -7320,13 +7285,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="O93" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="P93" s="9" t="s">
         <v>300</v>
-      </c>
-      <c r="P93" s="9" t="s">
-        <v>301</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7336,7 +7301,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B94" s="5">
         <v>46077.82018063657</v>
@@ -7348,17 +7313,15 @@
         <v>46125.56186803241</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H94" s="6"/>
       <c r="I94" s="5">
         <v>46085</v>
       </c>
@@ -7375,13 +7338,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q94" s="5">
         <v>46085</v>
@@ -7401,7 +7364,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B95" s="8">
         <v>46107.60121979167</v>
@@ -7413,17 +7376,15 @@
         <v>46114.8505327662</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H95" s="9"/>
       <c r="I95" s="8">
         <v>46113</v>
       </c>
@@ -7440,13 +7401,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O95" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="P95" s="9" t="s">
         <v>305</v>
-      </c>
-      <c r="P95" s="9" t="s">
-        <v>306</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7456,7 +7417,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B96" s="5">
         <v>46107.601296249995</v>
@@ -7468,17 +7429,15 @@
         <v>46114.850774618055</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H96" s="6"/>
       <c r="I96" s="5">
         <v>46113</v>
       </c>
@@ -7495,13 +7454,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7511,7 +7470,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B97" s="8">
         <v>46107.601343993054</v>
@@ -7523,17 +7482,15 @@
         <v>46107.84851795139</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H97" s="9"/>
       <c r="I97" s="8">
         <v>46085</v>
       </c>
@@ -7550,13 +7507,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O97" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="P97" s="9" t="s">
         <v>310</v>
-      </c>
-      <c r="P97" s="9" t="s">
-        <v>311</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7566,7 +7523,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B98" s="5">
         <v>46107.60138634259</v>
@@ -7578,17 +7535,15 @@
         <v>46107.84851336805</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H98" s="6"/>
       <c r="I98" s="5">
         <v>46085</v>
       </c>
@@ -7605,13 +7560,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O98" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="P98" s="6" t="s">
         <v>313</v>
-      </c>
-      <c r="P98" s="6" t="s">
-        <v>314</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7621,7 +7576,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B99" s="8">
         <v>46078.65921471065</v>
@@ -7633,17 +7588,15 @@
         <v>46114.65083799769</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H99" s="9"/>
       <c r="I99" s="8">
         <v>46087</v>
       </c>
@@ -7660,13 +7613,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q99" s="8">
         <v>46087</v>
@@ -7686,7 +7639,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B100" s="5">
         <v>46107.60145327546</v>
@@ -7698,17 +7651,15 @@
         <v>46114.8498778125</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H100" s="6"/>
       <c r="I100" s="5">
         <v>46113</v>
       </c>
@@ -7725,13 +7676,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7741,7 +7692,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B101" s="8">
         <v>46107.60152523148</v>
@@ -7753,17 +7704,15 @@
         <v>46114.85000983796</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H101" s="9"/>
       <c r="I101" s="8">
         <v>46113</v>
       </c>
@@ -7780,13 +7729,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7796,7 +7745,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B102" s="5">
         <v>46107.60156221065</v>
@@ -7808,17 +7757,15 @@
         <v>46107.84856730324</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H102" s="6"/>
       <c r="I102" s="5">
         <v>46087</v>
       </c>
@@ -7835,13 +7782,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7851,7 +7798,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B103" s="8">
         <v>46107.60160730324</v>
@@ -7863,17 +7810,15 @@
         <v>46107.84856039352</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H103" s="9" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H103" s="9"/>
       <c r="I103" s="8">
         <v>46087</v>
       </c>
@@ -7890,13 +7835,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7906,7 +7851,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B104" s="5">
         <v>46077.820181030096</v>
@@ -7918,17 +7863,15 @@
         <v>46125.56189244213</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H104" s="6"/>
       <c r="I104" s="5">
         <v>46091</v>
       </c>
@@ -7945,13 +7888,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O104" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="P104" s="6" t="s">
         <v>328</v>
-      </c>
-      <c r="P104" s="6" t="s">
-        <v>329</v>
       </c>
       <c r="Q104" s="5">
         <v>46091</v>
@@ -7971,7 +7914,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B105" s="8">
         <v>46107.60168349537</v>
@@ -7983,17 +7926,15 @@
         <v>46114.8557116088</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H105" s="9" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H105" s="9"/>
       <c r="I105" s="9"/>
       <c r="J105" s="8">
         <v>46115</v>
@@ -8008,13 +7949,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8024,7 +7965,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B106" s="5">
         <v>46107.60175594907</v>
@@ -8036,17 +7977,15 @@
         <v>46114.85576636574</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H106" s="6"/>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
         <v>46115</v>
@@ -8061,13 +8000,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8077,7 +8016,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B107" s="8">
         <v>46107.6017900463</v>
@@ -8089,17 +8028,15 @@
         <v>46114.84731824074</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H107" s="9" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H107" s="9"/>
       <c r="I107" s="8">
         <v>46091</v>
       </c>
@@ -8116,13 +8053,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8132,7 +8069,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B108" s="5">
         <v>46107.60182489583</v>
@@ -8144,17 +8081,15 @@
         <v>46114.84743204861</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H108" s="6"/>
       <c r="I108" s="5">
         <v>46091</v>
       </c>
@@ -8171,13 +8106,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8187,7 +8122,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B109" s="8">
         <v>46077.82018142361</v>
@@ -8199,17 +8134,15 @@
         <v>46118.86139821759</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H109" s="9" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H109" s="9"/>
       <c r="I109" s="8">
         <v>46093</v>
       </c>
@@ -8226,13 +8159,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q109" s="8">
         <v>46119</v>
@@ -8252,7 +8185,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B110" s="5">
         <v>46107.60187090278</v>
@@ -8264,17 +8197,15 @@
         <v>46114.8519803588</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H110" s="6"/>
       <c r="I110" s="6"/>
       <c r="J110" s="5">
         <v>46119</v>
@@ -8289,13 +8220,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8305,7 +8236,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B111" s="8">
         <v>46107.60193765046</v>
@@ -8317,17 +8248,15 @@
         <v>46118.86156471065</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H111" s="9" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H111" s="9"/>
       <c r="I111" s="9"/>
       <c r="J111" s="8">
         <v>46119</v>
@@ -8342,13 +8271,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8358,7 +8287,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B112" s="5">
         <v>46107.601981064814</v>
@@ -8370,17 +8299,15 @@
         <v>46114.84918898148</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H112" s="6"/>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
         <v>46093</v>
@@ -8395,13 +8322,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8411,7 +8338,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B113" s="8">
         <v>46107.60201515046</v>
@@ -8423,17 +8350,15 @@
         <v>46114.84926967593</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H113" s="9" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H113" s="9"/>
       <c r="I113" s="8">
         <v>46093</v>
       </c>
@@ -8450,13 +8375,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8466,7 +8391,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B114" s="5">
         <v>46077.82017553241</v>
@@ -8478,7 +8403,7 @@
         <v>46125.561711898146</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>25</v>
@@ -8502,7 +8427,7 @@
         <v>26</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8515,7 +8440,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B115" s="8">
         <v>46077.82017586805</v>
@@ -8527,16 +8452,16 @@
         <v>46121.840061724535</v>
       </c>
       <c r="E115" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="F115" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G115" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="F115" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G115" s="9" t="s">
+      <c r="H115" s="9" t="s">
         <v>351</v>
-      </c>
-      <c r="H115" s="9" t="s">
-        <v>352</v>
       </c>
       <c r="I115" s="8">
         <v>46094</v>
@@ -8554,13 +8479,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q115" s="8">
         <v>46097</v>
@@ -8580,7 +8505,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B116" s="5">
         <v>46107.6021821412</v>
@@ -8592,16 +8517,16 @@
         <v>46121.84001659723</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="H116" s="6" t="s">
         <v>351</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>352</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8617,13 +8542,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8633,7 +8558,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B117" s="8">
         <v>46107.60222542824</v>
@@ -8645,16 +8570,16 @@
         <v>46121.84002737269</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="H117" s="9" t="s">
         <v>351</v>
-      </c>
-      <c r="H117" s="9" t="s">
-        <v>352</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8670,13 +8595,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8686,7 +8611,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B118" s="5">
         <v>46107.602255370366</v>
@@ -8698,16 +8623,16 @@
         <v>46114.85951420139</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="H118" s="6" t="s">
         <v>351</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>352</v>
       </c>
       <c r="I118" s="5">
         <v>46094</v>
@@ -8725,13 +8650,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8741,7 +8666,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B119" s="8">
         <v>46107.60228831018</v>
@@ -8753,16 +8678,16 @@
         <v>46114.85957398148</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="H119" s="9" t="s">
         <v>351</v>
-      </c>
-      <c r="H119" s="9" t="s">
-        <v>352</v>
       </c>
       <c r="I119" s="9"/>
       <c r="J119" s="8">
@@ -8778,13 +8703,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8794,7 +8719,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B120" s="5">
         <v>46107.63652371528</v>
@@ -8812,10 +8737,10 @@
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="H120" s="6" t="s">
         <v>351</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>352</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8831,13 +8756,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8847,7 +8772,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B121" s="8">
         <v>46107.636567430556</v>
@@ -8865,10 +8790,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="H121" s="9" t="s">
         <v>351</v>
-      </c>
-      <c r="H121" s="9" t="s">
-        <v>352</v>
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
@@ -8884,13 +8809,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O121" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8900,7 +8825,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B122" s="5">
         <v>46107.63660021991</v>
@@ -8918,10 +8843,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="H122" s="6" t="s">
         <v>351</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>352</v>
       </c>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
@@ -8937,13 +8862,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8953,7 +8878,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B123" s="8">
         <v>46107.63664055556</v>
@@ -8971,10 +8896,10 @@
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="H123" s="9" t="s">
         <v>351</v>
-      </c>
-      <c r="H123" s="9" t="s">
-        <v>352</v>
       </c>
       <c r="I123" s="9"/>
       <c r="J123" s="8">
@@ -8990,13 +8915,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O123" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -9006,7 +8931,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B124" s="5">
         <v>46107.63667821759</v>
@@ -9024,10 +8949,10 @@
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="H124" s="6" t="s">
         <v>351</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>352</v>
       </c>
       <c r="I124" s="6"/>
       <c r="J124" s="5">
@@ -9043,13 +8968,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9059,7 +8984,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B125" s="8">
         <v>46077.82017615741</v>
@@ -9071,17 +8996,15 @@
         <v>46126.17015332176</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H125" s="9" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H125" s="9"/>
       <c r="I125" s="8">
         <v>46097</v>
       </c>
@@ -9098,13 +9021,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q125" s="8">
         <v>46097</v>
@@ -9124,7 +9047,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B126" s="5">
         <v>46107.60233217593</v>
@@ -9136,17 +9059,15 @@
         <v>46122.612435717594</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H126" s="6"/>
       <c r="I126" s="5">
         <v>46121</v>
       </c>
@@ -9163,13 +9084,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9179,7 +9100,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B127" s="8">
         <v>46107.60239986111</v>
@@ -9191,17 +9112,15 @@
         <v>46122.61244673611</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H127" s="9" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H127" s="9"/>
       <c r="I127" s="8">
         <v>46121</v>
       </c>
@@ -9218,13 +9137,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9234,7 +9153,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B128" s="5">
         <v>46107.60243372685</v>
@@ -9246,17 +9165,15 @@
         <v>46114.85951381944</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H128" s="6"/>
       <c r="I128" s="5">
         <v>46097</v>
       </c>
@@ -9273,13 +9190,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9289,7 +9206,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B129" s="8">
         <v>46107.602471805556</v>
@@ -9301,17 +9218,15 @@
         <v>46114.859573194444</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H129" s="9" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H129" s="9"/>
       <c r="I129" s="8">
         <v>46097</v>
       </c>
@@ -9328,13 +9243,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9344,7 +9259,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B130" s="5">
         <v>46107.63866758102</v>
@@ -9362,11 +9277,9 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H130" s="6"/>
       <c r="I130" s="5">
         <v>46097</v>
       </c>
@@ -9383,13 +9296,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9399,7 +9312,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B131" s="8">
         <v>46107.63871274306</v>
@@ -9417,11 +9330,9 @@
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H131" s="9" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H131" s="9"/>
       <c r="I131" s="8">
         <v>46097</v>
       </c>
@@ -9438,13 +9349,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O131" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9454,7 +9365,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B132" s="5">
         <v>46107.63874899306</v>
@@ -9472,11 +9383,9 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H132" s="6"/>
       <c r="I132" s="5">
         <v>46097</v>
       </c>
@@ -9493,13 +9402,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9509,7 +9418,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B133" s="8">
         <v>46107.63879311342</v>
@@ -9527,11 +9436,9 @@
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H133" s="9" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H133" s="9"/>
       <c r="I133" s="8">
         <v>46097</v>
       </c>
@@ -9548,13 +9455,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O133" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9564,7 +9471,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B134" s="5">
         <v>46107.63882511574</v>
@@ -9582,11 +9489,9 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>102</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H134" s="6"/>
       <c r="I134" s="5">
         <v>46097</v>
       </c>
@@ -9603,13 +9508,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9619,7 +9524,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B135" s="8">
         <v>46077.82017644676</v>
@@ -9631,16 +9536,16 @@
         <v>46127.18538978009</v>
       </c>
       <c r="E135" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="F135" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G135" s="9" t="s">
         <v>392</v>
       </c>
-      <c r="F135" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G135" s="9" t="s">
+      <c r="H135" s="9" t="s">
         <v>393</v>
-      </c>
-      <c r="H135" s="9" t="s">
-        <v>394</v>
       </c>
       <c r="I135" s="8">
         <v>46100</v>
@@ -9658,13 +9563,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q135" s="8">
         <v>46100</v>
@@ -9684,7 +9589,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B136" s="5">
         <v>46107.602652581016</v>
@@ -9696,16 +9601,16 @@
         <v>46125.561110208335</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="H136" s="6" t="s">
         <v>393</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>394</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9721,13 +9626,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9737,7 +9642,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B137" s="8">
         <v>46107.60267325232</v>
@@ -9749,16 +9654,16 @@
         <v>46125.56112121527</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="H137" s="9" t="s">
         <v>393</v>
-      </c>
-      <c r="H137" s="9" t="s">
-        <v>394</v>
       </c>
       <c r="I137" s="9"/>
       <c r="J137" s="8">
@@ -9774,13 +9679,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9790,7 +9695,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B138" s="5">
         <v>46107.60282983797</v>
@@ -9802,16 +9707,16 @@
         <v>46114.85804719907</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="H138" s="6" t="s">
         <v>393</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>394</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9827,13 +9732,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9843,7 +9748,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B139" s="8">
         <v>46107.602871932875</v>
@@ -9855,16 +9760,16 @@
         <v>46114.858048055554</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="H139" s="9" t="s">
         <v>393</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>394</v>
       </c>
       <c r="I139" s="9"/>
       <c r="J139" s="8">
@@ -9880,13 +9785,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9896,7 +9801,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B140" s="5">
         <v>46107.604622638886</v>
@@ -9914,10 +9819,10 @@
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="H140" s="6" t="s">
         <v>393</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>394</v>
       </c>
       <c r="I140" s="6"/>
       <c r="J140" s="5">
@@ -9933,13 +9838,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="O140" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9949,7 +9854,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B141" s="8">
         <v>46107.604665590276</v>
@@ -9967,10 +9872,10 @@
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="H141" s="9" t="s">
         <v>393</v>
-      </c>
-      <c r="H141" s="9" t="s">
-        <v>394</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="8">
@@ -9986,13 +9891,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="O141" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -10002,7 +9907,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B142" s="5">
         <v>46107.60470481482</v>
@@ -10020,10 +9925,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="H142" s="6" t="s">
         <v>393</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>394</v>
       </c>
       <c r="I142" s="6"/>
       <c r="J142" s="5">
@@ -10039,13 +9944,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10055,7 +9960,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B143" s="8">
         <v>46107.60474207176</v>
@@ -10073,10 +9978,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="H143" s="9" t="s">
         <v>393</v>
-      </c>
-      <c r="H143" s="9" t="s">
-        <v>394</v>
       </c>
       <c r="I143" s="9"/>
       <c r="J143" s="8">
@@ -10092,13 +9997,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="O143" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10108,7 +10013,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B144" s="5">
         <v>46107.6047731713</v>
@@ -10126,10 +10031,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="H144" s="6" t="s">
         <v>393</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>394</v>
       </c>
       <c r="I144" s="6"/>
       <c r="J144" s="5">
@@ -10145,13 +10050,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10161,7 +10066,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B145" s="8">
         <v>46077.820176724534</v>
@@ -10173,16 +10078,16 @@
         <v>46128.19730540509</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="H145" s="9" t="s">
         <v>393</v>
-      </c>
-      <c r="H145" s="9" t="s">
-        <v>394</v>
       </c>
       <c r="I145" s="8">
         <v>46101</v>
@@ -10200,13 +10105,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="O145" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="P145" s="9" t="s">
         <v>414</v>
-      </c>
-      <c r="P145" s="9" t="s">
-        <v>415</v>
       </c>
       <c r="Q145" s="8">
         <v>46101</v>
@@ -10226,7 +10131,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B146" s="5">
         <v>46107.60538978009</v>
@@ -10238,16 +10143,16 @@
         <v>46125.56117667824</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="H146" s="6" t="s">
         <v>393</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>394</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10263,13 +10168,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10279,7 +10184,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B147" s="8">
         <v>46107.60549119213</v>
@@ -10291,16 +10196,16 @@
         <v>46125.56118533565</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="H147" s="9" t="s">
         <v>393</v>
-      </c>
-      <c r="H147" s="9" t="s">
-        <v>394</v>
       </c>
       <c r="I147" s="9"/>
       <c r="J147" s="8">
@@ -10316,13 +10221,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
@@ -10332,7 +10237,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B148" s="5">
         <v>46107.60552758102</v>
@@ -10344,16 +10249,16 @@
         <v>46114.858808460645</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="H148" s="6" t="s">
         <v>393</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>394</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">
@@ -10369,13 +10274,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10385,7 +10290,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B149" s="8">
         <v>46107.60555978009</v>
@@ -10397,16 +10302,16 @@
         <v>46114.858710138884</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="H149" s="9" t="s">
         <v>393</v>
-      </c>
-      <c r="H149" s="9" t="s">
-        <v>394</v>
       </c>
       <c r="I149" s="9"/>
       <c r="J149" s="8">
@@ -10422,13 +10327,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10438,7 +10343,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B150" s="5">
         <v>46107.60568278935</v>
@@ -10450,16 +10355,16 @@
         <v>46109.73540881944</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="H150" s="6" t="s">
         <v>393</v>
-      </c>
-      <c r="H150" s="6" t="s">
-        <v>394</v>
       </c>
       <c r="I150" s="6"/>
       <c r="J150" s="5">
@@ -10475,13 +10380,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="O150" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10491,7 +10396,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B151" s="8">
         <v>46107.605744953704</v>
@@ -10509,10 +10414,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="H151" s="9" t="s">
         <v>393</v>
-      </c>
-      <c r="H151" s="9" t="s">
-        <v>394</v>
       </c>
       <c r="I151" s="9"/>
       <c r="J151" s="8">
@@ -10528,13 +10433,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="O151" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10544,7 +10449,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B152" s="5">
         <v>46107.60583027778</v>
@@ -10562,10 +10467,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="H152" s="6" t="s">
         <v>393</v>
-      </c>
-      <c r="H152" s="6" t="s">
-        <v>394</v>
       </c>
       <c r="I152" s="6"/>
       <c r="J152" s="5">
@@ -10581,13 +10486,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="O152" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10597,7 +10502,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B153" s="8">
         <v>46107.60586805556</v>
@@ -10615,10 +10520,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="H153" s="9" t="s">
         <v>393</v>
-      </c>
-      <c r="H153" s="9" t="s">
-        <v>394</v>
       </c>
       <c r="I153" s="9"/>
       <c r="J153" s="8">
@@ -10634,13 +10539,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="O153" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P153" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
@@ -10650,7 +10555,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B154" s="5">
         <v>46107.605905868055</v>
@@ -10668,10 +10573,10 @@
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="H154" s="6" t="s">
         <v>393</v>
-      </c>
-      <c r="H154" s="6" t="s">
-        <v>394</v>
       </c>
       <c r="I154" s="6"/>
       <c r="J154" s="5">
@@ -10687,13 +10592,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="O154" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10703,7 +10608,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B155" s="8">
         <v>46077.820177013884</v>
@@ -10713,7 +10618,7 @@
         <v>46114.650831747684</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>25</v>
@@ -10737,7 +10642,7 @@
         <v>26</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P155" s="9" t="s">
         <v>26</v>
@@ -10750,7 +10655,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B156" s="5">
         <v>46077.82017730324</v>
@@ -10760,16 +10665,16 @@
         <v>46137.18802717593</v>
       </c>
       <c r="E156" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G156" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="F156" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G156" s="6" t="s">
+      <c r="H156" s="6" t="s">
         <v>431</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>432</v>
       </c>
       <c r="I156" s="5">
         <v>46128</v>
@@ -10787,13 +10692,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Q156" s="5">
         <v>46128</v>
@@ -10808,12 +10713,12 @@
         <v>31</v>
       </c>
       <c r="U156" s="12" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B157" s="8">
         <v>46077.82017756945</v>
@@ -10823,16 +10728,16 @@
         <v>46137.18802714121</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="H157" s="9" t="s">
         <v>431</v>
-      </c>
-      <c r="H157" s="9" t="s">
-        <v>432</v>
       </c>
       <c r="I157" s="8">
         <v>46128</v>
@@ -10850,13 +10755,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P157" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Q157" s="8">
         <v>46128</v>
@@ -10871,12 +10776,12 @@
         <v>31</v>
       </c>
       <c r="U157" s="12" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B158" s="5">
         <v>46090.88005357639</v>
@@ -10886,7 +10791,7 @@
         <v>46114.65100881945</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>25</v>
@@ -10910,7 +10815,7 @@
         <v>26</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>26</v>
@@ -10923,7 +10828,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B159" s="8">
         <v>46090.88038033565</v>
@@ -10933,7 +10838,7 @@
         <v>46137.18802715278</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
@@ -10960,13 +10865,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="P159" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q159" s="8">
         <v>46128</v>
@@ -10981,12 +10886,12 @@
         <v>31</v>
       </c>
       <c r="U159" s="12" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B160" s="5">
         <v>46090.88062440972</v>
@@ -10996,7 +10901,7 @@
         <v>46137.18802714121</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -11023,13 +10928,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q160" s="5">
         <v>46128</v>
@@ -11044,7 +10949,7 @@
         <v>31</v>
       </c>
       <c r="U160" s="12" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001451 - ZITRON COLOMBIA.xlsx
+++ b/data/50001451 - ZITRON COLOMBIA.xlsx
@@ -4648,7 +4648,7 @@
         <v>46107.840353321764</v>
       </c>
       <c r="D48" s="5">
-        <v>46107.84042637731</v>
+        <v>46220.94303859954</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>167</v>
@@ -5352,7 +5352,7 @@
         <v>46114.767718206014</v>
       </c>
       <c r="D60" s="5">
-        <v>46114.84872589121</v>
+        <v>46221.07565987269</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>200</v>
@@ -5661,7 +5661,7 @@
         <v>46114.78855440972</v>
       </c>
       <c r="D65" s="8">
-        <v>46114.78855586806</v>
+        <v>46221.38854112268</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>222</v>
@@ -5714,7 +5714,7 @@
         <v>46114.78858121528</v>
       </c>
       <c r="D66" s="5">
-        <v>46114.7885828125</v>
+        <v>46221.38859300926</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>225</v>

--- a/data/50001451 - ZITRON COLOMBIA.xlsx
+++ b/data/50001451 - ZITRON COLOMBIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1828" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="444">
   <si>
     <t>50001451 - ZITRON COLOMBIA</t>
   </si>
@@ -317,6 +317,9 @@
   </si>
   <si>
     <t>propuesta compras a codigo // aprovisionamiento</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC materiales</t>
@@ -3410,7 +3413,7 @@
         <v>46097.53652079861</v>
       </c>
       <c r="D28" s="5">
-        <v>46097.53654111111</v>
+        <v>46223.81360527778</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>101</v>
@@ -3419,9 +3422,11 @@
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I28" s="5">
         <v>45903</v>
       </c>
@@ -3444,7 +3449,7 @@
         <v>81</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q28" s="5">
         <v>45903</v>
@@ -3464,7 +3469,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B29" s="8">
         <v>46078.658673831014</v>
@@ -3476,7 +3481,7 @@
         <v>46104.62858377315</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3509,7 +3514,7 @@
         <v>81</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q29" s="8">
         <v>45903</v>
@@ -3529,7 +3534,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B30" s="5">
         <v>46078.65875901621</v>
@@ -3541,7 +3546,7 @@
         <v>46097.536774548615</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3574,7 +3579,7 @@
         <v>81</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q30" s="5">
         <v>45903</v>
@@ -3594,7 +3599,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B31" s="8">
         <v>46077.820175960645</v>
@@ -3606,7 +3611,7 @@
         <v>46112.798028969904</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>25</v>
@@ -3630,7 +3635,7 @@
         <v>26</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P31" s="9" t="s">
         <v>26</v>
@@ -3643,7 +3648,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B32" s="5">
         <v>46077.82017622685</v>
@@ -3655,16 +3660,16 @@
         <v>46097.535346944445</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I32" s="5">
         <v>45912</v>
@@ -3682,13 +3687,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q32" s="5">
         <v>45912</v>
@@ -3708,7 +3713,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B33" s="8">
         <v>46077.820176504625</v>
@@ -3720,16 +3725,16 @@
         <v>46097.535276400464</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I33" s="8">
         <v>45912</v>
@@ -3747,13 +3752,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>92</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3761,15 +3766,15 @@
         <v>0</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B34" s="5">
         <v>46077.82017679398</v>
@@ -3781,16 +3786,16 @@
         <v>46097.53531515047</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I34" s="5">
         <v>45916</v>
@@ -3808,13 +3813,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3822,15 +3827,15 @@
         <v>0</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B35" s="8">
         <v>46077.82017706019</v>
@@ -3842,16 +3847,16 @@
         <v>46097.539690150465</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I35" s="8">
         <v>45908</v>
@@ -3869,13 +3874,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q35" s="8">
         <v>45908</v>
@@ -3895,7 +3900,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B36" s="5">
         <v>46077.82017730324</v>
@@ -3907,16 +3912,16 @@
         <v>46097.53890119213</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I36" s="5">
         <v>45908</v>
@@ -3934,13 +3939,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>95</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3948,15 +3953,15 @@
         <v>0</v>
       </c>
       <c r="T36" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B37" s="8">
         <v>46077.82017755787</v>
@@ -3968,16 +3973,16 @@
         <v>46097.53966494213</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I37" s="8">
         <v>45917</v>
@@ -3995,13 +4000,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -4009,15 +4014,15 @@
         <v>0</v>
       </c>
       <c r="T37" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B38" s="5">
         <v>46077.8201778125</v>
@@ -4029,16 +4034,16 @@
         <v>46097.53602381944</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I38" s="5">
         <v>45912</v>
@@ -4056,13 +4061,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q38" s="5">
         <v>45912</v>
@@ -4082,7 +4087,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B39" s="8">
         <v>46077.820178055554</v>
@@ -4094,16 +4099,16 @@
         <v>46097.5359540625</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I39" s="8">
         <v>45912</v>
@@ -4121,13 +4126,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>98</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -4135,15 +4140,15 @@
         <v>0</v>
       </c>
       <c r="T39" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="U39" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B40" s="5">
         <v>46077.82017554398</v>
@@ -4155,16 +4160,16 @@
         <v>46097.53599474537</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I40" s="5">
         <v>45916</v>
@@ -4182,13 +4187,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4196,15 +4201,15 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B41" s="8">
         <v>46077.82017600695</v>
@@ -4216,16 +4221,16 @@
         <v>46097.5354607176</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I41" s="8">
         <v>45898</v>
@@ -4243,13 +4248,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q41" s="8">
         <v>45898</v>
@@ -4269,7 +4274,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B42" s="5">
         <v>46077.820176319445</v>
@@ -4281,16 +4286,16 @@
         <v>46182.693444861114</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I42" s="5">
         <v>45898</v>
@@ -4308,13 +4313,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4322,15 +4327,15 @@
         <v>0</v>
       </c>
       <c r="T42" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="U42" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B43" s="8">
         <v>46077.82017663194</v>
@@ -4342,16 +4347,16 @@
         <v>46097.5354075</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I43" s="8">
         <v>45922</v>
@@ -4369,13 +4374,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -4383,15 +4388,15 @@
         <v>0</v>
       </c>
       <c r="T43" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B44" s="5">
         <v>46077.82017693287</v>
@@ -4403,16 +4408,16 @@
         <v>46097.535433425925</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I44" s="5">
         <v>45922</v>
@@ -4430,13 +4435,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4444,15 +4449,15 @@
         <v>0</v>
       </c>
       <c r="T44" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="U44" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B45" s="8">
         <v>46077.82017723379</v>
@@ -4464,16 +4469,16 @@
         <v>46097.53669974537</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I45" s="8">
         <v>45912</v>
@@ -4491,13 +4496,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q45" s="8">
         <v>45912</v>
@@ -4517,7 +4522,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B46" s="5">
         <v>46077.82017756945</v>
@@ -4529,16 +4534,16 @@
         <v>46097.53661077547</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I46" s="5">
         <v>45912</v>
@@ -4556,13 +4561,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>101</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4570,15 +4575,15 @@
         <v>0</v>
       </c>
       <c r="T46" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="U46" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B47" s="8">
         <v>46077.820177870366</v>
@@ -4590,16 +4595,16 @@
         <v>46097.536673703704</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I47" s="8">
         <v>45932</v>
@@ -4617,13 +4622,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4631,15 +4636,15 @@
         <v>0</v>
       </c>
       <c r="T47" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="U47" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B48" s="5">
         <v>46078.65559880787</v>
@@ -4651,16 +4656,16 @@
         <v>46220.94303859954</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I48" s="5">
         <v>45912</v>
@@ -4678,13 +4683,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q48" s="5">
         <v>45912</v>
@@ -4704,7 +4709,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B49" s="8">
         <v>46078.655658090276</v>
@@ -4716,16 +4721,16 @@
         <v>46107.84024543982</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I49" s="8">
         <v>45912</v>
@@ -4743,13 +4748,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q49" s="9"/>
       <c r="R49" s="9"/>
@@ -4757,15 +4762,15 @@
         <v>0</v>
       </c>
       <c r="T49" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="U49" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B50" s="5">
         <v>46078.65577003472</v>
@@ -4777,16 +4782,16 @@
         <v>46107.84033961805</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I50" s="5">
         <v>45946</v>
@@ -4804,13 +4809,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4818,15 +4823,15 @@
         <v>0</v>
       </c>
       <c r="T50" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="U50" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B51" s="8">
         <v>46078.654245046295</v>
@@ -4838,16 +4843,16 @@
         <v>46105.78342381945</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I51" s="8">
         <v>45912</v>
@@ -4865,13 +4870,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q51" s="8">
         <v>45912</v>
@@ -4891,7 +4896,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B52" s="5">
         <v>46078.65429936342</v>
@@ -4903,16 +4908,16 @@
         <v>46111.65554150463</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I52" s="5">
         <v>45912</v>
@@ -4930,13 +4935,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4944,15 +4949,15 @@
         <v>0</v>
       </c>
       <c r="T52" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B53" s="8">
         <v>46078.65468994213</v>
@@ -4964,16 +4969,16 @@
         <v>46105.7833940625</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I53" s="8">
         <v>45968</v>
@@ -4991,13 +4996,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5005,15 +5010,15 @@
         <v>0</v>
       </c>
       <c r="T53" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="U53" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B54" s="5">
         <v>46104.63046165509</v>
@@ -5025,16 +5030,16 @@
         <v>46107.67902436343</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I54" s="5">
         <v>45912</v>
@@ -5052,10 +5057,10 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -5068,7 +5073,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B55" s="8">
         <v>46104.631274988424</v>
@@ -5080,16 +5085,16 @@
         <v>46107.67921902778</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I55" s="8">
         <v>45912</v>
@@ -5107,10 +5112,10 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5123,7 +5128,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B56" s="5">
         <v>46104.631671678246</v>
@@ -5135,16 +5140,16 @@
         <v>46107.67933054398</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I56" s="5">
         <v>45912</v>
@@ -5162,10 +5167,10 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -5178,7 +5183,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B57" s="8">
         <v>46104.63195700232</v>
@@ -5190,16 +5195,16 @@
         <v>46107.67943891203</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I57" s="8">
         <v>45912</v>
@@ -5217,10 +5222,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -5233,7 +5238,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B58" s="5">
         <v>46104.632084826386</v>
@@ -5245,16 +5250,16 @@
         <v>46107.67985042824</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I58" s="5">
         <v>45912</v>
@@ -5272,10 +5277,10 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5288,7 +5293,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B59" s="8">
         <v>46104.63227371528</v>
@@ -5300,16 +5305,16 @@
         <v>46107.67955858796</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I59" s="8">
         <v>45912</v>
@@ -5327,10 +5332,10 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>26</v>
@@ -5343,7 +5348,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B60" s="5">
         <v>46077.82017815972</v>
@@ -5355,7 +5360,7 @@
         <v>46221.07565987269</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5379,7 +5384,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5394,7 +5399,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B61" s="8">
         <v>46077.82017846065</v>
@@ -5406,16 +5411,16 @@
         <v>46197.707138425925</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I61" s="8">
         <v>45903</v>
@@ -5433,13 +5438,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>81</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q61" s="8">
         <v>45903</v>
@@ -5459,7 +5464,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B62" s="5">
         <v>46077.82017626158</v>
@@ -5471,16 +5476,16 @@
         <v>46197.707159328704</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I62" s="5">
         <v>45960</v>
@@ -5498,13 +5503,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q62" s="5">
         <v>45960</v>
@@ -5524,7 +5529,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B63" s="8">
         <v>46090.87971813657</v>
@@ -5536,16 +5541,16 @@
         <v>46114.650833692125</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="8">
@@ -5561,13 +5566,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q63" s="8">
         <v>45967</v>
@@ -5587,7 +5592,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B64" s="5">
         <v>46090.8798415162</v>
@@ -5599,16 +5604,16 @@
         <v>46119.77882065972</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I64" s="5">
         <v>46092</v>
@@ -5626,13 +5631,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q64" s="5">
         <v>46092</v>
@@ -5652,7 +5657,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B65" s="8">
         <v>46107.60619210648</v>
@@ -5664,16 +5669,16 @@
         <v>46221.38854112268</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I65" s="9"/>
       <c r="J65" s="8">
@@ -5689,13 +5694,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5705,7 +5710,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B66" s="5">
         <v>46107.60640244213</v>
@@ -5717,16 +5722,16 @@
         <v>46221.38859300926</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5742,13 +5747,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5758,7 +5763,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B67" s="8">
         <v>46107.606435821755</v>
@@ -5770,16 +5775,16 @@
         <v>46114.84832498843</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="8">
@@ -5789,19 +5794,19 @@
         <v>26</v>
       </c>
       <c r="L67" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="M67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N67" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="O67" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="M67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N67" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="O67" s="9" t="s">
-        <v>227</v>
-      </c>
       <c r="P67" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -5811,7 +5816,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B68" s="5">
         <v>46107.60648386574</v>
@@ -5823,16 +5828,16 @@
         <v>46114.84847162037</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5848,13 +5853,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5864,7 +5869,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B69" s="8">
         <v>46078.65390563657</v>
@@ -5876,7 +5881,7 @@
         <v>46107.68737451389</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5900,10 +5905,10 @@
         <v>26</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5917,7 +5922,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
         <v>46078.702559108795</v>
@@ -5929,16 +5934,16 @@
         <v>46107.840496770834</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I70" s="5">
         <v>46057</v>
@@ -5956,13 +5961,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q70" s="5">
         <v>46057</v>
@@ -5982,7 +5987,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B71" s="8">
         <v>46077.82017896991</v>
@@ -5994,7 +5999,7 @@
         <v>46107.843893425925</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -6018,7 +6023,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6035,7 +6040,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B72" s="5">
         <v>46077.820179305556</v>
@@ -6047,16 +6052,16 @@
         <v>46107.842354259265</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I72" s="5">
         <v>45971</v>
@@ -6074,13 +6079,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q72" s="5">
         <v>45971</v>
@@ -6100,7 +6105,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B73" s="8">
         <v>46077.820177430556</v>
@@ -6118,10 +6123,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I73" s="8">
         <v>46027</v>
@@ -6139,13 +6144,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q73" s="8">
         <v>46027</v>
@@ -6165,7 +6170,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B74" s="5">
         <v>46077.82017795139</v>
@@ -6177,16 +6182,16 @@
         <v>46107.841941238425</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I74" s="5">
         <v>46041</v>
@@ -6204,13 +6209,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q74" s="5">
         <v>46041</v>
@@ -6230,7 +6235,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B75" s="8">
         <v>46077.82017841435</v>
@@ -6242,16 +6247,16 @@
         <v>46107.841844375</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I75" s="8">
         <v>46056</v>
@@ -6269,13 +6274,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q75" s="8">
         <v>46056</v>
@@ -6295,7 +6300,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B76" s="5">
         <v>46078.65892270833</v>
@@ -6307,16 +6312,16 @@
         <v>46107.84287946759</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I76" s="5">
         <v>46057</v>
@@ -6334,13 +6339,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q76" s="5">
         <v>46034</v>
@@ -6360,7 +6365,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B77" s="8">
         <v>46078.65900237269</v>
@@ -6372,16 +6377,16 @@
         <v>46107.842393032406</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I77" s="8">
         <v>46034</v>
@@ -6399,13 +6404,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q77" s="8">
         <v>46034</v>
@@ -6425,7 +6430,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B78" s="5">
         <v>46077.82017907407</v>
@@ -6437,7 +6442,7 @@
         <v>46125.56179637731</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6461,7 +6466,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6476,7 +6481,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B79" s="8">
         <v>46077.82017943287</v>
@@ -6485,18 +6490,20 @@
         <v>46113.557951111114</v>
       </c>
       <c r="D79" s="8">
-        <v>46114.85330988426</v>
+        <v>46223.81375739584</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H79" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I79" s="8">
         <v>46059</v>
       </c>
@@ -6513,13 +6520,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q79" s="8">
         <v>46059</v>
@@ -6539,7 +6546,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B80" s="5">
         <v>46107.59662881945</v>
@@ -6548,18 +6555,20 @@
         <v>46113.557604340276</v>
       </c>
       <c r="D80" s="5">
-        <v>46114.856069733796</v>
+        <v>46223.813830740735</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H80" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I80" s="5">
         <v>46108</v>
       </c>
@@ -6576,13 +6585,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6592,7 +6601,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B81" s="8">
         <v>46107.59776125</v>
@@ -6601,18 +6610,20 @@
         <v>46113.5576187963</v>
       </c>
       <c r="D81" s="8">
-        <v>46114.856118923606</v>
+        <v>46223.81382685185</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H81" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I81" s="8">
         <v>46108</v>
       </c>
@@ -6629,13 +6640,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6645,7 +6656,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B82" s="5">
         <v>46107.597173993054</v>
@@ -6654,18 +6665,20 @@
         <v>46107.838732662036</v>
       </c>
       <c r="D82" s="5">
-        <v>46107.83873434028</v>
+        <v>46223.813822881944</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H82" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I82" s="5">
         <v>46059</v>
       </c>
@@ -6682,13 +6695,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6698,7 +6711,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B83" s="8">
         <v>46107.59746188657</v>
@@ -6707,18 +6720,20 @@
         <v>46107.83873872685</v>
       </c>
       <c r="D83" s="8">
-        <v>46107.83874050926</v>
+        <v>46223.81381796296</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H83" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I83" s="8">
         <v>46059</v>
       </c>
@@ -6735,13 +6750,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6751,7 +6766,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B84" s="5">
         <v>46077.82017980324</v>
@@ -6760,18 +6775,20 @@
         <v>46113.557691643524</v>
       </c>
       <c r="D84" s="5">
-        <v>46125.56182928241</v>
+        <v>46223.81375368056</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H84" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I84" s="5">
         <v>46079</v>
       </c>
@@ -6788,13 +6805,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q84" s="5">
         <v>46079</v>
@@ -6814,7 +6831,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B85" s="8">
         <v>46107.59978276621</v>
@@ -6823,18 +6840,20 @@
         <v>46113.558251215276</v>
       </c>
       <c r="D85" s="8">
-        <v>46114.855711296295</v>
+        <v>46223.81391319445</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H85" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I85" s="8">
         <v>46111</v>
       </c>
@@ -6851,13 +6870,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6867,7 +6886,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B86" s="5">
         <v>46107.59982243055</v>
@@ -6876,18 +6895,20 @@
         <v>46113.55826416667</v>
       </c>
       <c r="D86" s="5">
-        <v>46114.85576582176</v>
+        <v>46223.81390922454</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H86" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I86" s="5">
         <v>46111</v>
       </c>
@@ -6904,13 +6925,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6920,7 +6941,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B87" s="8">
         <v>46107.59986486111</v>
@@ -6929,18 +6950,20 @@
         <v>46107.84839290509</v>
       </c>
       <c r="D87" s="8">
-        <v>46107.84839457176</v>
+        <v>46223.81390537037</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H87" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I87" s="8">
         <v>46079</v>
       </c>
@@ -6957,13 +6980,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -6973,7 +6996,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B88" s="5">
         <v>46107.59991125</v>
@@ -6982,18 +7005,20 @@
         <v>46107.84838658565</v>
       </c>
       <c r="D88" s="5">
-        <v>46107.8483881713</v>
+        <v>46223.81390003472</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H88" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I88" s="5">
         <v>46079</v>
       </c>
@@ -7010,13 +7035,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7026,7 +7051,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B89" s="8">
         <v>46077.82018026621</v>
@@ -7035,18 +7060,20 @@
         <v>46113.557744375</v>
       </c>
       <c r="D89" s="8">
-        <v>46125.56184609953</v>
+        <v>46223.81374972222</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H89" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I89" s="8">
         <v>46083</v>
       </c>
@@ -7063,13 +7090,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q89" s="8">
         <v>46083</v>
@@ -7089,7 +7116,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B90" s="5">
         <v>46107.59995462963</v>
@@ -7098,18 +7125,20 @@
         <v>46113.55834841436</v>
       </c>
       <c r="D90" s="5">
-        <v>46114.85594553241</v>
+        <v>46223.8139969676</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H90" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I90" s="5">
         <v>46112</v>
       </c>
@@ -7126,13 +7155,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7142,7 +7171,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B91" s="8">
         <v>46107.60002673611</v>
@@ -7151,18 +7180,20 @@
         <v>46113.55836547454</v>
       </c>
       <c r="D91" s="8">
-        <v>46114.85576615741</v>
+        <v>46223.81399342592</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H91" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I91" s="8">
         <v>46112</v>
       </c>
@@ -7179,13 +7210,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -7195,7 +7226,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B92" s="5">
         <v>46107.60006982639</v>
@@ -7204,18 +7235,20 @@
         <v>46107.84843891204</v>
       </c>
       <c r="D92" s="5">
-        <v>46107.84844032407</v>
+        <v>46223.81398994213</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H92" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I92" s="5">
         <v>46083</v>
       </c>
@@ -7232,13 +7265,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7248,7 +7281,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B93" s="8">
         <v>46107.600104930556</v>
@@ -7257,18 +7290,20 @@
         <v>46107.84843344908</v>
       </c>
       <c r="D93" s="8">
-        <v>46107.84843525463</v>
+        <v>46223.81398546296</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H93" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I93" s="8">
         <v>46083</v>
       </c>
@@ -7285,13 +7320,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7301,7 +7336,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B94" s="5">
         <v>46077.82018063657</v>
@@ -7310,18 +7345,20 @@
         <v>46113.55781333333</v>
       </c>
       <c r="D94" s="5">
-        <v>46125.56186803241</v>
+        <v>46223.813744756946</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H94" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I94" s="5">
         <v>46085</v>
       </c>
@@ -7338,13 +7375,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q94" s="5">
         <v>46085</v>
@@ -7364,7 +7401,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B95" s="8">
         <v>46107.60121979167</v>
@@ -7373,18 +7410,20 @@
         <v>46113.55840587963</v>
       </c>
       <c r="D95" s="8">
-        <v>46114.8505327662</v>
+        <v>46223.814080104166</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H95" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="H95" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I95" s="8">
         <v>46113</v>
       </c>
@@ -7401,13 +7440,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7417,7 +7456,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B96" s="5">
         <v>46107.601296249995</v>
@@ -7426,18 +7465,20 @@
         <v>46113.558420057874</v>
       </c>
       <c r="D96" s="5">
-        <v>46114.850774618055</v>
+        <v>46223.81407638889</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H96" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I96" s="5">
         <v>46113</v>
       </c>
@@ -7454,13 +7495,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7470,7 +7511,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B97" s="8">
         <v>46107.601343993054</v>
@@ -7479,18 +7520,20 @@
         <v>46107.848516342594</v>
       </c>
       <c r="D97" s="8">
-        <v>46107.84851795139</v>
+        <v>46223.81407283565</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H97" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I97" s="8">
         <v>46085</v>
       </c>
@@ -7507,13 +7550,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7523,7 +7566,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B98" s="5">
         <v>46107.60138634259</v>
@@ -7532,18 +7575,20 @@
         <v>46107.84851134259</v>
       </c>
       <c r="D98" s="5">
-        <v>46107.84851336805</v>
+        <v>46223.81406783564</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H98" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I98" s="5">
         <v>46085</v>
       </c>
@@ -7560,13 +7605,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7576,7 +7621,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B99" s="8">
         <v>46078.65921471065</v>
@@ -7585,18 +7630,20 @@
         <v>46114.64467627315</v>
       </c>
       <c r="D99" s="8">
-        <v>46114.65083799769</v>
+        <v>46223.813740428246</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H99" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I99" s="8">
         <v>46087</v>
       </c>
@@ -7613,13 +7660,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q99" s="8">
         <v>46087</v>
@@ -7639,7 +7686,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B100" s="5">
         <v>46107.60145327546</v>
@@ -7648,18 +7695,20 @@
         <v>46114.64465515046</v>
       </c>
       <c r="D100" s="5">
-        <v>46114.8498778125</v>
+        <v>46223.81416679398</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H100" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I100" s="5">
         <v>46113</v>
       </c>
@@ -7676,13 +7725,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7692,7 +7741,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B101" s="8">
         <v>46107.60152523148</v>
@@ -7701,18 +7750,20 @@
         <v>46114.6446628125</v>
       </c>
       <c r="D101" s="8">
-        <v>46114.85000983796</v>
+        <v>46223.814163229166</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H101" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I101" s="8">
         <v>46113</v>
       </c>
@@ -7729,13 +7780,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7745,7 +7796,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B102" s="5">
         <v>46107.60156221065</v>
@@ -7754,18 +7805,20 @@
         <v>46107.84856559028</v>
       </c>
       <c r="D102" s="5">
-        <v>46107.84856730324</v>
+        <v>46223.814158113426</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H102" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I102" s="5">
         <v>46087</v>
       </c>
@@ -7782,13 +7835,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7798,7 +7851,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B103" s="8">
         <v>46107.60160730324</v>
@@ -7807,18 +7860,20 @@
         <v>46107.84855876157</v>
       </c>
       <c r="D103" s="8">
-        <v>46107.84856039352</v>
+        <v>46223.81415733796</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H103" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="H103" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I103" s="8">
         <v>46087</v>
       </c>
@@ -7835,13 +7890,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7851,7 +7906,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B104" s="5">
         <v>46077.820181030096</v>
@@ -7860,18 +7915,20 @@
         <v>46114.64478351852</v>
       </c>
       <c r="D104" s="5">
-        <v>46125.56189244213</v>
+        <v>46223.81373618056</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H104" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I104" s="5">
         <v>46091</v>
       </c>
@@ -7888,13 +7945,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q104" s="5">
         <v>46091</v>
@@ -7914,7 +7971,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B105" s="8">
         <v>46107.60168349537</v>
@@ -7923,18 +7980,20 @@
         <v>46114.644762384254</v>
       </c>
       <c r="D105" s="8">
-        <v>46114.8557116088</v>
+        <v>46223.81425516204</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H105" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="H105" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I105" s="9"/>
       <c r="J105" s="8">
         <v>46115</v>
@@ -7949,13 +8008,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7965,7 +8024,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B106" s="5">
         <v>46107.60175594907</v>
@@ -7974,18 +8033,20 @@
         <v>46114.64476732639</v>
       </c>
       <c r="D106" s="5">
-        <v>46114.85576636574</v>
+        <v>46223.8142515625</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H106" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
         <v>46115</v>
@@ -8000,13 +8061,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8016,7 +8077,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B107" s="8">
         <v>46107.6017900463</v>
@@ -8025,18 +8086,20 @@
         <v>46107.84861380787</v>
       </c>
       <c r="D107" s="8">
-        <v>46114.84731824074</v>
+        <v>46223.814248090275</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H107" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="H107" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I107" s="8">
         <v>46091</v>
       </c>
@@ -8053,13 +8116,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8069,7 +8132,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B108" s="5">
         <v>46107.60182489583</v>
@@ -8078,18 +8141,20 @@
         <v>46107.8486083912</v>
       </c>
       <c r="D108" s="5">
-        <v>46114.84743204861</v>
+        <v>46223.81424232639</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H108" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I108" s="5">
         <v>46091</v>
       </c>
@@ -8106,13 +8171,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8122,7 +8187,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B109" s="8">
         <v>46077.82018142361</v>
@@ -8131,18 +8196,20 @@
         <v>46118.85113606481</v>
       </c>
       <c r="D109" s="8">
-        <v>46118.86139821759</v>
+        <v>46223.81429516204</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H109" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="H109" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I109" s="8">
         <v>46093</v>
       </c>
@@ -8159,13 +8226,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q109" s="8">
         <v>46119</v>
@@ -8185,27 +8252,29 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B110" s="5">
         <v>46107.60187090278</v>
       </c>
       <c r="C110" s="5">
-        <v>46114.85197863426</v>
+        <v>46223.814289814814</v>
       </c>
       <c r="D110" s="5">
-        <v>46114.8519803588</v>
+        <v>46223.814366446764</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H110" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I110" s="6"/>
       <c r="J110" s="5">
         <v>46119</v>
@@ -8220,13 +8289,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8236,7 +8305,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B111" s="8">
         <v>46107.60193765046</v>
@@ -8245,18 +8314,20 @@
         <v>46118.85106515046</v>
       </c>
       <c r="D111" s="8">
-        <v>46118.86156471065</v>
+        <v>46223.814362777775</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H111" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="H111" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I111" s="9"/>
       <c r="J111" s="8">
         <v>46119</v>
@@ -8271,13 +8342,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8287,7 +8358,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B112" s="5">
         <v>46107.601981064814</v>
@@ -8296,18 +8367,20 @@
         <v>46108.66388262731</v>
       </c>
       <c r="D112" s="5">
-        <v>46114.84918898148</v>
+        <v>46223.81435921296</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H112" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
         <v>46093</v>
@@ -8322,13 +8395,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8338,7 +8411,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B113" s="8">
         <v>46107.60201515046</v>
@@ -8347,18 +8420,20 @@
         <v>46108.66389119213</v>
       </c>
       <c r="D113" s="8">
-        <v>46114.84926967593</v>
+        <v>46223.8143546875</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H113" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="H113" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I113" s="8">
         <v>46093</v>
       </c>
@@ -8375,13 +8450,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8391,7 +8466,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B114" s="5">
         <v>46077.82017553241</v>
@@ -8403,7 +8478,7 @@
         <v>46125.561711898146</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>25</v>
@@ -8427,7 +8502,7 @@
         <v>26</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8440,7 +8515,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B115" s="8">
         <v>46077.82017586805</v>
@@ -8452,16 +8527,16 @@
         <v>46121.840061724535</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I115" s="8">
         <v>46094</v>
@@ -8479,13 +8554,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q115" s="8">
         <v>46097</v>
@@ -8505,7 +8580,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B116" s="5">
         <v>46107.6021821412</v>
@@ -8514,19 +8589,19 @@
         <v>46121.840014456015</v>
       </c>
       <c r="D116" s="5">
-        <v>46121.84001659723</v>
+        <v>46223.81429664352</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8542,13 +8617,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8558,7 +8633,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B117" s="8">
         <v>46107.60222542824</v>
@@ -8570,16 +8645,16 @@
         <v>46121.84002737269</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8595,13 +8670,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8611,7 +8686,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B118" s="5">
         <v>46107.602255370366</v>
@@ -8623,16 +8698,16 @@
         <v>46114.85951420139</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I118" s="5">
         <v>46094</v>
@@ -8650,13 +8725,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8666,7 +8741,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B119" s="8">
         <v>46107.60228831018</v>
@@ -8678,16 +8753,16 @@
         <v>46114.85957398148</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I119" s="9"/>
       <c r="J119" s="8">
@@ -8703,13 +8778,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8719,7 +8794,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B120" s="5">
         <v>46107.63652371528</v>
@@ -8737,10 +8812,10 @@
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8756,13 +8831,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8772,7 +8847,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B121" s="8">
         <v>46107.636567430556</v>
@@ -8790,10 +8865,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
@@ -8809,13 +8884,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O121" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8825,7 +8900,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B122" s="5">
         <v>46107.63660021991</v>
@@ -8843,10 +8918,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
@@ -8862,13 +8937,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8878,7 +8953,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B123" s="8">
         <v>46107.63664055556</v>
@@ -8896,10 +8971,10 @@
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I123" s="9"/>
       <c r="J123" s="8">
@@ -8915,13 +8990,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O123" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8931,7 +9006,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B124" s="5">
         <v>46107.63667821759</v>
@@ -8949,10 +9024,10 @@
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I124" s="6"/>
       <c r="J124" s="5">
@@ -8968,13 +9043,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8984,7 +9059,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B125" s="8">
         <v>46077.82017615741</v>
@@ -8993,18 +9068,20 @@
         <v>46122.61245885417</v>
       </c>
       <c r="D125" s="8">
-        <v>46126.17015332176</v>
+        <v>46223.81452300926</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H125" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="H125" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I125" s="8">
         <v>46097</v>
       </c>
@@ -9021,13 +9098,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q125" s="8">
         <v>46097</v>
@@ -9047,7 +9124,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B126" s="5">
         <v>46107.60233217593</v>
@@ -9056,18 +9133,20 @@
         <v>46122.612434027775</v>
       </c>
       <c r="D126" s="5">
-        <v>46122.612435717594</v>
+        <v>46223.81465353009</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H126" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="H126" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I126" s="5">
         <v>46121</v>
       </c>
@@ -9084,13 +9163,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9100,7 +9179,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B127" s="8">
         <v>46107.60239986111</v>
@@ -9109,18 +9188,20 @@
         <v>46122.61244532408</v>
       </c>
       <c r="D127" s="8">
-        <v>46122.61244673611</v>
+        <v>46223.81464974537</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H127" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="H127" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I127" s="8">
         <v>46121</v>
       </c>
@@ -9137,13 +9218,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9153,7 +9234,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B128" s="5">
         <v>46107.60243372685</v>
@@ -9162,18 +9243,20 @@
         <v>46108.664157962965</v>
       </c>
       <c r="D128" s="5">
-        <v>46114.85951381944</v>
+        <v>46223.81464652778</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H128" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="H128" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I128" s="5">
         <v>46097</v>
       </c>
@@ -9190,13 +9273,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9206,7 +9289,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B129" s="8">
         <v>46107.602471805556</v>
@@ -9215,18 +9298,20 @@
         <v>46108.66416608796</v>
       </c>
       <c r="D129" s="8">
-        <v>46114.859573194444</v>
+        <v>46223.81464329861</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H129" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="H129" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I129" s="8">
         <v>46097</v>
       </c>
@@ -9243,13 +9328,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9259,16 +9344,16 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B130" s="5">
         <v>46107.63866758102</v>
       </c>
       <c r="C130" s="5">
-        <v>46109.73461930556</v>
+        <v>46223.81451494213</v>
       </c>
       <c r="D130" s="5">
-        <v>46109.734620717594</v>
+        <v>46223.81463959491</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>56</v>
@@ -9277,9 +9362,11 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H130" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="H130" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I130" s="5">
         <v>46097</v>
       </c>
@@ -9296,13 +9383,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9312,7 +9399,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B131" s="8">
         <v>46107.63871274306</v>
@@ -9321,7 +9408,7 @@
         <v>46109.73462969907</v>
       </c>
       <c r="D131" s="8">
-        <v>46109.73463119213</v>
+        <v>46223.81463597222</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>60</v>
@@ -9330,9 +9417,11 @@
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H131" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="H131" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I131" s="8">
         <v>46097</v>
       </c>
@@ -9349,13 +9438,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O131" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9365,7 +9454,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B132" s="5">
         <v>46107.63874899306</v>
@@ -9374,7 +9463,7 @@
         <v>46109.734664131945</v>
       </c>
       <c r="D132" s="5">
-        <v>46109.73466543981</v>
+        <v>46223.81463277778</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>63</v>
@@ -9383,9 +9472,11 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H132" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="H132" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I132" s="5">
         <v>46097</v>
       </c>
@@ -9402,13 +9493,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9418,7 +9509,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B133" s="8">
         <v>46107.63879311342</v>
@@ -9427,7 +9518,7 @@
         <v>46113.566690381944</v>
       </c>
       <c r="D133" s="8">
-        <v>46113.56669168982</v>
+        <v>46223.814625127314</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>66</v>
@@ -9436,9 +9527,11 @@
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H133" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="H133" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I133" s="8">
         <v>46097</v>
       </c>
@@ -9455,13 +9548,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O133" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9471,7 +9564,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B134" s="5">
         <v>46107.63882511574</v>
@@ -9480,7 +9573,7 @@
         <v>46113.56669976852</v>
       </c>
       <c r="D134" s="5">
-        <v>46113.56670113426</v>
+        <v>46223.814624502316</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>69</v>
@@ -9489,9 +9582,11 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H134" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="H134" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I134" s="5">
         <v>46097</v>
       </c>
@@ -9508,13 +9603,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9524,7 +9619,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B135" s="8">
         <v>46077.82017644676</v>
@@ -9536,16 +9631,16 @@
         <v>46127.18538978009</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I135" s="8">
         <v>46100</v>
@@ -9563,13 +9658,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q135" s="8">
         <v>46100</v>
@@ -9589,7 +9684,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B136" s="5">
         <v>46107.602652581016</v>
@@ -9601,16 +9696,16 @@
         <v>46125.561110208335</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9626,13 +9721,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9642,7 +9737,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B137" s="8">
         <v>46107.60267325232</v>
@@ -9654,16 +9749,16 @@
         <v>46125.56112121527</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I137" s="9"/>
       <c r="J137" s="8">
@@ -9679,13 +9774,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9695,7 +9790,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B138" s="5">
         <v>46107.60282983797</v>
@@ -9707,16 +9802,16 @@
         <v>46114.85804719907</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9732,13 +9827,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9748,7 +9843,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B139" s="8">
         <v>46107.602871932875</v>
@@ -9760,16 +9855,16 @@
         <v>46114.858048055554</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I139" s="9"/>
       <c r="J139" s="8">
@@ -9785,13 +9880,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9801,7 +9896,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B140" s="5">
         <v>46107.604622638886</v>
@@ -9810,7 +9905,7 @@
         <v>46109.73476545139</v>
       </c>
       <c r="D140" s="5">
-        <v>46109.734767118054</v>
+        <v>46223.814522256944</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>56</v>
@@ -9819,10 +9914,10 @@
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I140" s="6"/>
       <c r="J140" s="5">
@@ -9838,13 +9933,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O140" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9854,7 +9949,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B141" s="8">
         <v>46107.604665590276</v>
@@ -9872,10 +9967,10 @@
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="8">
@@ -9891,13 +9986,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O141" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -9907,7 +10002,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B142" s="5">
         <v>46107.60470481482</v>
@@ -9925,10 +10020,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I142" s="6"/>
       <c r="J142" s="5">
@@ -9944,13 +10039,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9960,7 +10055,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B143" s="8">
         <v>46107.60474207176</v>
@@ -9978,10 +10073,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I143" s="9"/>
       <c r="J143" s="8">
@@ -9997,13 +10092,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O143" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10013,7 +10108,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B144" s="5">
         <v>46107.6047731713</v>
@@ -10031,10 +10126,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I144" s="6"/>
       <c r="J144" s="5">
@@ -10050,13 +10145,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10066,7 +10161,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B145" s="8">
         <v>46077.820176724534</v>
@@ -10078,16 +10173,16 @@
         <v>46128.19730540509</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I145" s="8">
         <v>46101</v>
@@ -10105,13 +10200,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q145" s="8">
         <v>46101</v>
@@ -10131,7 +10226,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B146" s="5">
         <v>46107.60538978009</v>
@@ -10143,16 +10238,16 @@
         <v>46125.56117667824</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10168,13 +10263,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10184,7 +10279,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B147" s="8">
         <v>46107.60549119213</v>
@@ -10196,16 +10291,16 @@
         <v>46125.56118533565</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I147" s="9"/>
       <c r="J147" s="8">
@@ -10221,13 +10316,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
@@ -10237,7 +10332,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B148" s="5">
         <v>46107.60552758102</v>
@@ -10249,16 +10344,16 @@
         <v>46114.858808460645</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">
@@ -10274,13 +10369,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10290,7 +10385,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B149" s="8">
         <v>46107.60555978009</v>
@@ -10302,16 +10397,16 @@
         <v>46114.858710138884</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I149" s="9"/>
       <c r="J149" s="8">
@@ -10327,13 +10422,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10343,7 +10438,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B150" s="5">
         <v>46107.60568278935</v>
@@ -10355,16 +10450,16 @@
         <v>46109.73540881944</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I150" s="6"/>
       <c r="J150" s="5">
@@ -10380,13 +10475,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O150" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10396,7 +10491,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B151" s="8">
         <v>46107.605744953704</v>
@@ -10414,10 +10509,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I151" s="9"/>
       <c r="J151" s="8">
@@ -10433,13 +10528,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O151" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10449,7 +10544,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B152" s="5">
         <v>46107.60583027778</v>
@@ -10467,10 +10562,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I152" s="6"/>
       <c r="J152" s="5">
@@ -10486,13 +10581,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O152" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10502,7 +10597,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B153" s="8">
         <v>46107.60586805556</v>
@@ -10520,10 +10615,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H153" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I153" s="9"/>
       <c r="J153" s="8">
@@ -10539,13 +10634,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O153" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P153" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
@@ -10555,7 +10650,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B154" s="5">
         <v>46107.605905868055</v>
@@ -10573,10 +10668,10 @@
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I154" s="6"/>
       <c r="J154" s="5">
@@ -10592,13 +10687,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O154" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10608,7 +10703,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B155" s="8">
         <v>46077.820177013884</v>
@@ -10618,7 +10713,7 @@
         <v>46114.650831747684</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>25</v>
@@ -10642,7 +10737,7 @@
         <v>26</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P155" s="9" t="s">
         <v>26</v>
@@ -10655,7 +10750,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B156" s="5">
         <v>46077.82017730324</v>
@@ -10665,16 +10760,16 @@
         <v>46137.18802717593</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="I156" s="5">
         <v>46128</v>
@@ -10692,13 +10787,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q156" s="5">
         <v>46128</v>
@@ -10713,12 +10808,12 @@
         <v>31</v>
       </c>
       <c r="U156" s="12" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B157" s="8">
         <v>46077.82017756945</v>
@@ -10728,16 +10823,16 @@
         <v>46137.18802714121</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H157" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="I157" s="8">
         <v>46128</v>
@@ -10755,13 +10850,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P157" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q157" s="8">
         <v>46128</v>
@@ -10776,12 +10871,12 @@
         <v>31</v>
       </c>
       <c r="U157" s="12" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B158" s="5">
         <v>46090.88005357639</v>
@@ -10791,7 +10886,7 @@
         <v>46114.65100881945</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>25</v>
@@ -10815,7 +10910,7 @@
         <v>26</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>26</v>
@@ -10828,7 +10923,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B159" s="8">
         <v>46090.88038033565</v>
@@ -10838,7 +10933,7 @@
         <v>46137.18802715278</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
@@ -10865,13 +10960,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P159" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q159" s="8">
         <v>46128</v>
@@ -10886,12 +10981,12 @@
         <v>31</v>
       </c>
       <c r="U159" s="12" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B160" s="5">
         <v>46090.88062440972</v>
@@ -10901,7 +10996,7 @@
         <v>46137.18802714121</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -10928,13 +11023,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q160" s="5">
         <v>46128</v>
@@ -10949,7 +11044,7 @@
         <v>31</v>
       </c>
       <c r="U160" s="12" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001451 - ZITRON COLOMBIA.xlsx
+++ b/data/50001451 - ZITRON COLOMBIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="445">
   <si>
     <t>50001451 - ZITRON COLOMBIA</t>
   </si>
@@ -317,6 +317,9 @@
   </si>
   <si>
     <t>propuesta compras a codigo // aprovisionamiento</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
   </si>
   <si>
     <t>nespinoza@zitron.com</t>
@@ -3425,7 +3428,7 @@
         <v>102</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I28" s="5">
         <v>45903</v>
@@ -3449,7 +3452,7 @@
         <v>81</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q28" s="5">
         <v>45903</v>
@@ -3469,7 +3472,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B29" s="8">
         <v>46078.658673831014</v>
@@ -3481,7 +3484,7 @@
         <v>46104.62858377315</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3514,7 +3517,7 @@
         <v>81</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q29" s="8">
         <v>45903</v>
@@ -3534,7 +3537,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B30" s="5">
         <v>46078.65875901621</v>
@@ -3546,7 +3549,7 @@
         <v>46097.536774548615</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3579,7 +3582,7 @@
         <v>81</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q30" s="5">
         <v>45903</v>
@@ -3599,7 +3602,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B31" s="8">
         <v>46077.820175960645</v>
@@ -3611,7 +3614,7 @@
         <v>46112.798028969904</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>25</v>
@@ -3635,7 +3638,7 @@
         <v>26</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P31" s="9" t="s">
         <v>26</v>
@@ -3648,7 +3651,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B32" s="5">
         <v>46077.82017622685</v>
@@ -3660,16 +3663,16 @@
         <v>46097.535346944445</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I32" s="5">
         <v>45912</v>
@@ -3687,13 +3690,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q32" s="5">
         <v>45912</v>
@@ -3713,7 +3716,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B33" s="8">
         <v>46077.820176504625</v>
@@ -3725,16 +3728,16 @@
         <v>46097.535276400464</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I33" s="8">
         <v>45912</v>
@@ -3752,13 +3755,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>92</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3766,15 +3769,15 @@
         <v>0</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B34" s="5">
         <v>46077.82017679398</v>
@@ -3786,16 +3789,16 @@
         <v>46097.53531515047</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I34" s="5">
         <v>45916</v>
@@ -3813,13 +3816,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3827,15 +3830,15 @@
         <v>0</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B35" s="8">
         <v>46077.82017706019</v>
@@ -3847,16 +3850,16 @@
         <v>46097.539690150465</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I35" s="8">
         <v>45908</v>
@@ -3874,13 +3877,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q35" s="8">
         <v>45908</v>
@@ -3900,7 +3903,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B36" s="5">
         <v>46077.82017730324</v>
@@ -3912,16 +3915,16 @@
         <v>46097.53890119213</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I36" s="5">
         <v>45908</v>
@@ -3939,13 +3942,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>95</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3953,15 +3956,15 @@
         <v>0</v>
       </c>
       <c r="T36" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B37" s="8">
         <v>46077.82017755787</v>
@@ -3973,16 +3976,16 @@
         <v>46097.53966494213</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I37" s="8">
         <v>45917</v>
@@ -4000,13 +4003,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -4014,15 +4017,15 @@
         <v>0</v>
       </c>
       <c r="T37" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B38" s="5">
         <v>46077.8201778125</v>
@@ -4034,16 +4037,16 @@
         <v>46097.53602381944</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I38" s="5">
         <v>45912</v>
@@ -4061,13 +4064,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q38" s="5">
         <v>45912</v>
@@ -4087,7 +4090,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B39" s="8">
         <v>46077.820178055554</v>
@@ -4099,16 +4102,16 @@
         <v>46097.5359540625</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I39" s="8">
         <v>45912</v>
@@ -4126,13 +4129,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>98</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -4140,15 +4143,15 @@
         <v>0</v>
       </c>
       <c r="T39" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="U39" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B40" s="5">
         <v>46077.82017554398</v>
@@ -4160,16 +4163,16 @@
         <v>46097.53599474537</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I40" s="5">
         <v>45916</v>
@@ -4187,13 +4190,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4201,15 +4204,15 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B41" s="8">
         <v>46077.82017600695</v>
@@ -4221,16 +4224,16 @@
         <v>46097.5354607176</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I41" s="8">
         <v>45898</v>
@@ -4248,13 +4251,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q41" s="8">
         <v>45898</v>
@@ -4274,7 +4277,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B42" s="5">
         <v>46077.820176319445</v>
@@ -4286,16 +4289,16 @@
         <v>46182.693444861114</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I42" s="5">
         <v>45898</v>
@@ -4313,13 +4316,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4327,15 +4330,15 @@
         <v>0</v>
       </c>
       <c r="T42" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="U42" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B43" s="8">
         <v>46077.82017663194</v>
@@ -4347,16 +4350,16 @@
         <v>46097.5354075</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I43" s="8">
         <v>45922</v>
@@ -4374,13 +4377,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -4388,15 +4391,15 @@
         <v>0</v>
       </c>
       <c r="T43" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B44" s="5">
         <v>46077.82017693287</v>
@@ -4408,16 +4411,16 @@
         <v>46097.535433425925</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I44" s="5">
         <v>45922</v>
@@ -4435,13 +4438,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4449,15 +4452,15 @@
         <v>0</v>
       </c>
       <c r="T44" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="U44" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B45" s="8">
         <v>46077.82017723379</v>
@@ -4469,16 +4472,16 @@
         <v>46097.53669974537</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I45" s="8">
         <v>45912</v>
@@ -4496,13 +4499,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q45" s="8">
         <v>45912</v>
@@ -4522,7 +4525,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B46" s="5">
         <v>46077.82017756945</v>
@@ -4534,16 +4537,16 @@
         <v>46097.53661077547</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I46" s="5">
         <v>45912</v>
@@ -4561,13 +4564,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>101</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4575,15 +4578,15 @@
         <v>0</v>
       </c>
       <c r="T46" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="U46" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B47" s="8">
         <v>46077.820177870366</v>
@@ -4595,16 +4598,16 @@
         <v>46097.536673703704</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I47" s="8">
         <v>45932</v>
@@ -4622,13 +4625,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4636,15 +4639,15 @@
         <v>0</v>
       </c>
       <c r="T47" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="U47" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B48" s="5">
         <v>46078.65559880787</v>
@@ -4656,16 +4659,16 @@
         <v>46220.94303859954</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I48" s="5">
         <v>45912</v>
@@ -4683,13 +4686,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q48" s="5">
         <v>45912</v>
@@ -4709,7 +4712,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B49" s="8">
         <v>46078.655658090276</v>
@@ -4721,16 +4724,16 @@
         <v>46107.84024543982</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I49" s="8">
         <v>45912</v>
@@ -4748,13 +4751,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q49" s="9"/>
       <c r="R49" s="9"/>
@@ -4762,15 +4765,15 @@
         <v>0</v>
       </c>
       <c r="T49" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="U49" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B50" s="5">
         <v>46078.65577003472</v>
@@ -4782,16 +4785,16 @@
         <v>46107.84033961805</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I50" s="5">
         <v>45946</v>
@@ -4809,13 +4812,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4823,15 +4826,15 @@
         <v>0</v>
       </c>
       <c r="T50" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="U50" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B51" s="8">
         <v>46078.654245046295</v>
@@ -4843,16 +4846,16 @@
         <v>46105.78342381945</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I51" s="8">
         <v>45912</v>
@@ -4870,13 +4873,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q51" s="8">
         <v>45912</v>
@@ -4896,7 +4899,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B52" s="5">
         <v>46078.65429936342</v>
@@ -4908,16 +4911,16 @@
         <v>46111.65554150463</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I52" s="5">
         <v>45912</v>
@@ -4935,13 +4938,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4949,15 +4952,15 @@
         <v>0</v>
       </c>
       <c r="T52" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B53" s="8">
         <v>46078.65468994213</v>
@@ -4969,16 +4972,16 @@
         <v>46105.7833940625</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I53" s="8">
         <v>45968</v>
@@ -4996,13 +4999,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5010,15 +5013,15 @@
         <v>0</v>
       </c>
       <c r="T53" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="U53" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B54" s="5">
         <v>46104.63046165509</v>
@@ -5030,16 +5033,16 @@
         <v>46107.67902436343</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I54" s="5">
         <v>45912</v>
@@ -5057,10 +5060,10 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -5073,7 +5076,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B55" s="8">
         <v>46104.631274988424</v>
@@ -5085,16 +5088,16 @@
         <v>46107.67921902778</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I55" s="8">
         <v>45912</v>
@@ -5112,10 +5115,10 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5128,7 +5131,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B56" s="5">
         <v>46104.631671678246</v>
@@ -5140,16 +5143,16 @@
         <v>46107.67933054398</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I56" s="5">
         <v>45912</v>
@@ -5167,10 +5170,10 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -5183,7 +5186,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B57" s="8">
         <v>46104.63195700232</v>
@@ -5195,16 +5198,16 @@
         <v>46107.67943891203</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I57" s="8">
         <v>45912</v>
@@ -5222,10 +5225,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -5238,7 +5241,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B58" s="5">
         <v>46104.632084826386</v>
@@ -5250,16 +5253,16 @@
         <v>46107.67985042824</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I58" s="5">
         <v>45912</v>
@@ -5277,10 +5280,10 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5293,7 +5296,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B59" s="8">
         <v>46104.63227371528</v>
@@ -5305,16 +5308,16 @@
         <v>46107.67955858796</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I59" s="8">
         <v>45912</v>
@@ -5332,10 +5335,10 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>26</v>
@@ -5348,7 +5351,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B60" s="5">
         <v>46077.82017815972</v>
@@ -5360,7 +5363,7 @@
         <v>46221.07565987269</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5384,7 +5387,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5399,7 +5402,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B61" s="8">
         <v>46077.82017846065</v>
@@ -5411,16 +5414,16 @@
         <v>46197.707138425925</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I61" s="8">
         <v>45903</v>
@@ -5438,13 +5441,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>81</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q61" s="8">
         <v>45903</v>
@@ -5464,7 +5467,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B62" s="5">
         <v>46077.82017626158</v>
@@ -5476,16 +5479,16 @@
         <v>46197.707159328704</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I62" s="5">
         <v>45960</v>
@@ -5503,13 +5506,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q62" s="5">
         <v>45960</v>
@@ -5529,7 +5532,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B63" s="8">
         <v>46090.87971813657</v>
@@ -5541,16 +5544,16 @@
         <v>46114.650833692125</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="8">
@@ -5566,13 +5569,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q63" s="8">
         <v>45967</v>
@@ -5592,7 +5595,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B64" s="5">
         <v>46090.8798415162</v>
@@ -5604,16 +5607,16 @@
         <v>46119.77882065972</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I64" s="5">
         <v>46092</v>
@@ -5631,13 +5634,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q64" s="5">
         <v>46092</v>
@@ -5657,7 +5660,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B65" s="8">
         <v>46107.60619210648</v>
@@ -5669,16 +5672,16 @@
         <v>46221.38854112268</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I65" s="9"/>
       <c r="J65" s="8">
@@ -5694,13 +5697,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5710,7 +5713,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B66" s="5">
         <v>46107.60640244213</v>
@@ -5722,16 +5725,16 @@
         <v>46221.38859300926</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5747,13 +5750,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5763,7 +5766,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B67" s="8">
         <v>46107.606435821755</v>
@@ -5775,16 +5778,16 @@
         <v>46114.84832498843</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="8">
@@ -5794,19 +5797,19 @@
         <v>26</v>
       </c>
       <c r="L67" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="M67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N67" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="O67" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="M67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N67" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="O67" s="9" t="s">
-        <v>228</v>
-      </c>
       <c r="P67" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -5816,7 +5819,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B68" s="5">
         <v>46107.60648386574</v>
@@ -5828,16 +5831,16 @@
         <v>46114.84847162037</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5853,13 +5856,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5869,7 +5872,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B69" s="8">
         <v>46078.65390563657</v>
@@ -5881,7 +5884,7 @@
         <v>46107.68737451389</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5905,10 +5908,10 @@
         <v>26</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5922,7 +5925,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B70" s="5">
         <v>46078.702559108795</v>
@@ -5934,16 +5937,16 @@
         <v>46107.840496770834</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I70" s="5">
         <v>46057</v>
@@ -5961,13 +5964,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q70" s="5">
         <v>46057</v>
@@ -5987,7 +5990,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B71" s="8">
         <v>46077.82017896991</v>
@@ -5999,7 +6002,7 @@
         <v>46107.843893425925</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -6023,7 +6026,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6040,7 +6043,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B72" s="5">
         <v>46077.820179305556</v>
@@ -6052,16 +6055,16 @@
         <v>46107.842354259265</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I72" s="5">
         <v>45971</v>
@@ -6079,13 +6082,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q72" s="5">
         <v>45971</v>
@@ -6105,7 +6108,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B73" s="8">
         <v>46077.820177430556</v>
@@ -6123,10 +6126,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I73" s="8">
         <v>46027</v>
@@ -6144,13 +6147,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q73" s="8">
         <v>46027</v>
@@ -6170,7 +6173,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B74" s="5">
         <v>46077.82017795139</v>
@@ -6182,16 +6185,16 @@
         <v>46107.841941238425</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I74" s="5">
         <v>46041</v>
@@ -6209,13 +6212,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q74" s="5">
         <v>46041</v>
@@ -6235,7 +6238,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B75" s="8">
         <v>46077.82017841435</v>
@@ -6247,16 +6250,16 @@
         <v>46107.841844375</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I75" s="8">
         <v>46056</v>
@@ -6274,13 +6277,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q75" s="8">
         <v>46056</v>
@@ -6300,7 +6303,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B76" s="5">
         <v>46078.65892270833</v>
@@ -6312,16 +6315,16 @@
         <v>46107.84287946759</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I76" s="5">
         <v>46057</v>
@@ -6339,13 +6342,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q76" s="5">
         <v>46034</v>
@@ -6365,7 +6368,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B77" s="8">
         <v>46078.65900237269</v>
@@ -6377,16 +6380,16 @@
         <v>46107.842393032406</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I77" s="8">
         <v>46034</v>
@@ -6404,13 +6407,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q77" s="8">
         <v>46034</v>
@@ -6430,7 +6433,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B78" s="5">
         <v>46077.82017907407</v>
@@ -6442,7 +6445,7 @@
         <v>46125.56179637731</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6466,7 +6469,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6481,7 +6484,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B79" s="8">
         <v>46077.82017943287</v>
@@ -6493,7 +6496,7 @@
         <v>46223.81375739584</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6502,7 +6505,7 @@
         <v>102</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I79" s="8">
         <v>46059</v>
@@ -6520,13 +6523,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q79" s="8">
         <v>46059</v>
@@ -6546,7 +6549,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B80" s="5">
         <v>46107.59662881945</v>
@@ -6558,7 +6561,7 @@
         <v>46223.813830740735</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6567,7 +6570,7 @@
         <v>102</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I80" s="5">
         <v>46108</v>
@@ -6585,13 +6588,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6601,7 +6604,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B81" s="8">
         <v>46107.59776125</v>
@@ -6613,7 +6616,7 @@
         <v>46223.81382685185</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6622,7 +6625,7 @@
         <v>102</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I81" s="8">
         <v>46108</v>
@@ -6640,13 +6643,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6656,7 +6659,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B82" s="5">
         <v>46107.597173993054</v>
@@ -6668,7 +6671,7 @@
         <v>46223.813822881944</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6677,7 +6680,7 @@
         <v>102</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I82" s="5">
         <v>46059</v>
@@ -6695,13 +6698,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6711,7 +6714,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B83" s="8">
         <v>46107.59746188657</v>
@@ -6723,7 +6726,7 @@
         <v>46223.81381796296</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6732,7 +6735,7 @@
         <v>102</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I83" s="8">
         <v>46059</v>
@@ -6750,13 +6753,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6766,7 +6769,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B84" s="5">
         <v>46077.82017980324</v>
@@ -6778,7 +6781,7 @@
         <v>46223.81375368056</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6787,7 +6790,7 @@
         <v>102</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I84" s="5">
         <v>46079</v>
@@ -6805,13 +6808,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q84" s="5">
         <v>46079</v>
@@ -6831,7 +6834,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B85" s="8">
         <v>46107.59978276621</v>
@@ -6843,7 +6846,7 @@
         <v>46223.81391319445</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6852,7 +6855,7 @@
         <v>102</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I85" s="8">
         <v>46111</v>
@@ -6870,13 +6873,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6886,7 +6889,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B86" s="5">
         <v>46107.59982243055</v>
@@ -6898,7 +6901,7 @@
         <v>46223.81390922454</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6907,7 +6910,7 @@
         <v>102</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I86" s="5">
         <v>46111</v>
@@ -6925,13 +6928,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6941,7 +6944,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B87" s="8">
         <v>46107.59986486111</v>
@@ -6953,7 +6956,7 @@
         <v>46223.81390537037</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
@@ -6962,7 +6965,7 @@
         <v>102</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I87" s="8">
         <v>46079</v>
@@ -6980,13 +6983,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -6996,7 +6999,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B88" s="5">
         <v>46107.59991125</v>
@@ -7008,7 +7011,7 @@
         <v>46223.81390003472</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -7017,7 +7020,7 @@
         <v>102</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I88" s="5">
         <v>46079</v>
@@ -7035,13 +7038,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7051,7 +7054,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B89" s="8">
         <v>46077.82018026621</v>
@@ -7063,7 +7066,7 @@
         <v>46223.81374972222</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -7072,7 +7075,7 @@
         <v>102</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I89" s="8">
         <v>46083</v>
@@ -7090,13 +7093,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q89" s="8">
         <v>46083</v>
@@ -7116,7 +7119,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B90" s="5">
         <v>46107.59995462963</v>
@@ -7128,7 +7131,7 @@
         <v>46223.8139969676</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7137,7 +7140,7 @@
         <v>102</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I90" s="5">
         <v>46112</v>
@@ -7155,13 +7158,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7171,7 +7174,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B91" s="8">
         <v>46107.60002673611</v>
@@ -7183,7 +7186,7 @@
         <v>46223.81399342592</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -7192,7 +7195,7 @@
         <v>102</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I91" s="8">
         <v>46112</v>
@@ -7210,13 +7213,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -7226,7 +7229,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B92" s="5">
         <v>46107.60006982639</v>
@@ -7238,7 +7241,7 @@
         <v>46223.81398994213</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7247,7 +7250,7 @@
         <v>102</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I92" s="5">
         <v>46083</v>
@@ -7265,13 +7268,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7281,7 +7284,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B93" s="8">
         <v>46107.600104930556</v>
@@ -7293,7 +7296,7 @@
         <v>46223.81398546296</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7302,7 +7305,7 @@
         <v>102</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I93" s="8">
         <v>46083</v>
@@ -7320,13 +7323,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7336,7 +7339,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B94" s="5">
         <v>46077.82018063657</v>
@@ -7348,7 +7351,7 @@
         <v>46223.813744756946</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7357,7 +7360,7 @@
         <v>102</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I94" s="5">
         <v>46085</v>
@@ -7375,13 +7378,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q94" s="5">
         <v>46085</v>
@@ -7401,7 +7404,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B95" s="8">
         <v>46107.60121979167</v>
@@ -7413,7 +7416,7 @@
         <v>46223.814080104166</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7422,7 +7425,7 @@
         <v>102</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I95" s="8">
         <v>46113</v>
@@ -7440,13 +7443,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7456,7 +7459,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B96" s="5">
         <v>46107.601296249995</v>
@@ -7468,7 +7471,7 @@
         <v>46223.81407638889</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7477,7 +7480,7 @@
         <v>102</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I96" s="5">
         <v>46113</v>
@@ -7495,13 +7498,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7511,7 +7514,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B97" s="8">
         <v>46107.601343993054</v>
@@ -7523,7 +7526,7 @@
         <v>46223.81407283565</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7532,7 +7535,7 @@
         <v>102</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I97" s="8">
         <v>46085</v>
@@ -7550,13 +7553,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7566,7 +7569,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B98" s="5">
         <v>46107.60138634259</v>
@@ -7578,7 +7581,7 @@
         <v>46223.81406783564</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7587,7 +7590,7 @@
         <v>102</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I98" s="5">
         <v>46085</v>
@@ -7605,13 +7608,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7621,7 +7624,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B99" s="8">
         <v>46078.65921471065</v>
@@ -7633,7 +7636,7 @@
         <v>46223.813740428246</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7642,7 +7645,7 @@
         <v>102</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I99" s="8">
         <v>46087</v>
@@ -7660,13 +7663,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q99" s="8">
         <v>46087</v>
@@ -7686,7 +7689,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B100" s="5">
         <v>46107.60145327546</v>
@@ -7698,7 +7701,7 @@
         <v>46223.81416679398</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7707,7 +7710,7 @@
         <v>102</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I100" s="5">
         <v>46113</v>
@@ -7725,13 +7728,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7741,7 +7744,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B101" s="8">
         <v>46107.60152523148</v>
@@ -7753,7 +7756,7 @@
         <v>46223.814163229166</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7762,7 +7765,7 @@
         <v>102</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I101" s="8">
         <v>46113</v>
@@ -7780,13 +7783,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7796,7 +7799,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B102" s="5">
         <v>46107.60156221065</v>
@@ -7808,7 +7811,7 @@
         <v>46223.814158113426</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7817,7 +7820,7 @@
         <v>102</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I102" s="5">
         <v>46087</v>
@@ -7835,13 +7838,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7851,7 +7854,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B103" s="8">
         <v>46107.60160730324</v>
@@ -7863,7 +7866,7 @@
         <v>46223.81415733796</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7872,7 +7875,7 @@
         <v>102</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I103" s="8">
         <v>46087</v>
@@ -7890,13 +7893,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7906,7 +7909,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B104" s="5">
         <v>46077.820181030096</v>
@@ -7918,7 +7921,7 @@
         <v>46223.81373618056</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7927,7 +7930,7 @@
         <v>102</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I104" s="5">
         <v>46091</v>
@@ -7945,13 +7948,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q104" s="5">
         <v>46091</v>
@@ -7971,7 +7974,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B105" s="8">
         <v>46107.60168349537</v>
@@ -7983,7 +7986,7 @@
         <v>46223.81425516204</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7992,7 +7995,7 @@
         <v>102</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I105" s="9"/>
       <c r="J105" s="8">
@@ -8008,13 +8011,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8024,7 +8027,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B106" s="5">
         <v>46107.60175594907</v>
@@ -8036,7 +8039,7 @@
         <v>46223.8142515625</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8045,7 +8048,7 @@
         <v>102</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
@@ -8061,13 +8064,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8077,7 +8080,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B107" s="8">
         <v>46107.6017900463</v>
@@ -8089,7 +8092,7 @@
         <v>46223.814248090275</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -8098,7 +8101,7 @@
         <v>102</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I107" s="8">
         <v>46091</v>
@@ -8116,13 +8119,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8132,7 +8135,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B108" s="5">
         <v>46107.60182489583</v>
@@ -8144,7 +8147,7 @@
         <v>46223.81424232639</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8153,7 +8156,7 @@
         <v>102</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I108" s="5">
         <v>46091</v>
@@ -8171,13 +8174,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8187,7 +8190,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B109" s="8">
         <v>46077.82018142361</v>
@@ -8199,7 +8202,7 @@
         <v>46223.81429516204</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8208,7 +8211,7 @@
         <v>102</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I109" s="8">
         <v>46093</v>
@@ -8226,13 +8229,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q109" s="8">
         <v>46119</v>
@@ -8252,7 +8255,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B110" s="5">
         <v>46107.60187090278</v>
@@ -8264,7 +8267,7 @@
         <v>46223.814366446764</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8273,7 +8276,7 @@
         <v>102</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I110" s="6"/>
       <c r="J110" s="5">
@@ -8289,13 +8292,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8305,7 +8308,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B111" s="8">
         <v>46107.60193765046</v>
@@ -8317,7 +8320,7 @@
         <v>46223.814362777775</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8326,7 +8329,7 @@
         <v>102</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I111" s="9"/>
       <c r="J111" s="8">
@@ -8342,13 +8345,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8358,7 +8361,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B112" s="5">
         <v>46107.601981064814</v>
@@ -8370,7 +8373,7 @@
         <v>46223.81435921296</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8379,7 +8382,7 @@
         <v>102</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8395,13 +8398,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8411,7 +8414,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B113" s="8">
         <v>46107.60201515046</v>
@@ -8423,7 +8426,7 @@
         <v>46223.8143546875</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8432,7 +8435,7 @@
         <v>102</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I113" s="8">
         <v>46093</v>
@@ -8450,13 +8453,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8466,7 +8469,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B114" s="5">
         <v>46077.82017553241</v>
@@ -8478,7 +8481,7 @@
         <v>46125.561711898146</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>25</v>
@@ -8502,7 +8505,7 @@
         <v>26</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8515,7 +8518,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B115" s="8">
         <v>46077.82017586805</v>
@@ -8524,19 +8527,19 @@
         <v>46121.840045046294</v>
       </c>
       <c r="D115" s="8">
-        <v>46121.840061724535</v>
+        <v>46225.80624795139</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I115" s="8">
         <v>46094</v>
@@ -8554,13 +8557,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q115" s="8">
         <v>46097</v>
@@ -8580,28 +8583,26 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B116" s="5">
         <v>46107.6021821412</v>
       </c>
-      <c r="C116" s="5">
-        <v>46121.840014456015</v>
-      </c>
+      <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46223.81429664352</v>
+        <v>46225.80624259259</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8617,13 +8618,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8633,7 +8634,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B117" s="8">
         <v>46107.60222542824</v>
@@ -8645,16 +8646,16 @@
         <v>46121.84002737269</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8670,13 +8671,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8686,7 +8687,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B118" s="5">
         <v>46107.602255370366</v>
@@ -8698,16 +8699,16 @@
         <v>46114.85951420139</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I118" s="5">
         <v>46094</v>
@@ -8725,13 +8726,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8741,7 +8742,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B119" s="8">
         <v>46107.60228831018</v>
@@ -8753,16 +8754,16 @@
         <v>46114.85957398148</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I119" s="9"/>
       <c r="J119" s="8">
@@ -8778,13 +8779,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8794,7 +8795,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B120" s="5">
         <v>46107.63652371528</v>
@@ -8812,10 +8813,10 @@
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8831,13 +8832,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8847,7 +8848,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B121" s="8">
         <v>46107.636567430556</v>
@@ -8865,10 +8866,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
@@ -8884,13 +8885,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O121" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8900,7 +8901,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B122" s="5">
         <v>46107.63660021991</v>
@@ -8918,10 +8919,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
@@ -8937,13 +8938,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8953,7 +8954,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B123" s="8">
         <v>46107.63664055556</v>
@@ -8971,10 +8972,10 @@
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I123" s="9"/>
       <c r="J123" s="8">
@@ -8990,13 +8991,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O123" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -9006,7 +9007,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B124" s="5">
         <v>46107.63667821759</v>
@@ -9024,10 +9025,10 @@
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I124" s="6"/>
       <c r="J124" s="5">
@@ -9043,13 +9044,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9059,7 +9060,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B125" s="8">
         <v>46077.82017615741</v>
@@ -9071,7 +9072,7 @@
         <v>46223.81452300926</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9080,7 +9081,7 @@
         <v>102</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I125" s="8">
         <v>46097</v>
@@ -9098,13 +9099,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q125" s="8">
         <v>46097</v>
@@ -9124,7 +9125,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B126" s="5">
         <v>46107.60233217593</v>
@@ -9133,10 +9134,10 @@
         <v>46122.612434027775</v>
       </c>
       <c r="D126" s="5">
-        <v>46223.81465353009</v>
+        <v>46225.80624855324</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9145,7 +9146,7 @@
         <v>102</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I126" s="5">
         <v>46121</v>
@@ -9163,13 +9164,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9179,7 +9180,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B127" s="8">
         <v>46107.60239986111</v>
@@ -9191,7 +9192,7 @@
         <v>46223.81464974537</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -9200,7 +9201,7 @@
         <v>102</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I127" s="8">
         <v>46121</v>
@@ -9218,13 +9219,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9234,7 +9235,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B128" s="5">
         <v>46107.60243372685</v>
@@ -9246,7 +9247,7 @@
         <v>46223.81464652778</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9255,7 +9256,7 @@
         <v>102</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I128" s="5">
         <v>46097</v>
@@ -9273,13 +9274,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9289,7 +9290,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B129" s="8">
         <v>46107.602471805556</v>
@@ -9301,7 +9302,7 @@
         <v>46223.81464329861</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -9310,7 +9311,7 @@
         <v>102</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I129" s="8">
         <v>46097</v>
@@ -9328,13 +9329,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9344,7 +9345,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B130" s="5">
         <v>46107.63866758102</v>
@@ -9365,7 +9366,7 @@
         <v>102</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I130" s="5">
         <v>46097</v>
@@ -9383,13 +9384,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9399,7 +9400,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B131" s="8">
         <v>46107.63871274306</v>
@@ -9420,7 +9421,7 @@
         <v>102</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I131" s="8">
         <v>46097</v>
@@ -9438,13 +9439,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O131" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9454,7 +9455,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B132" s="5">
         <v>46107.63874899306</v>
@@ -9475,7 +9476,7 @@
         <v>102</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I132" s="5">
         <v>46097</v>
@@ -9493,13 +9494,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9509,7 +9510,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B133" s="8">
         <v>46107.63879311342</v>
@@ -9530,7 +9531,7 @@
         <v>102</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I133" s="8">
         <v>46097</v>
@@ -9548,13 +9549,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O133" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9564,7 +9565,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B134" s="5">
         <v>46107.63882511574</v>
@@ -9585,7 +9586,7 @@
         <v>102</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I134" s="5">
         <v>46097</v>
@@ -9603,13 +9604,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9619,7 +9620,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B135" s="8">
         <v>46077.82017644676</v>
@@ -9631,16 +9632,16 @@
         <v>46127.18538978009</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I135" s="8">
         <v>46100</v>
@@ -9658,13 +9659,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q135" s="8">
         <v>46100</v>
@@ -9684,7 +9685,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B136" s="5">
         <v>46107.602652581016</v>
@@ -9696,16 +9697,16 @@
         <v>46125.561110208335</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9721,13 +9722,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9737,7 +9738,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B137" s="8">
         <v>46107.60267325232</v>
@@ -9749,16 +9750,16 @@
         <v>46125.56112121527</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I137" s="9"/>
       <c r="J137" s="8">
@@ -9774,13 +9775,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9790,7 +9791,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B138" s="5">
         <v>46107.60282983797</v>
@@ -9802,16 +9803,16 @@
         <v>46114.85804719907</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9827,13 +9828,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9843,7 +9844,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B139" s="8">
         <v>46107.602871932875</v>
@@ -9855,16 +9856,16 @@
         <v>46114.858048055554</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I139" s="9"/>
       <c r="J139" s="8">
@@ -9880,13 +9881,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9896,7 +9897,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B140" s="5">
         <v>46107.604622638886</v>
@@ -9914,10 +9915,10 @@
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I140" s="6"/>
       <c r="J140" s="5">
@@ -9933,13 +9934,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O140" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9949,7 +9950,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B141" s="8">
         <v>46107.604665590276</v>
@@ -9967,10 +9968,10 @@
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="8">
@@ -9986,13 +9987,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O141" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -10002,7 +10003,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B142" s="5">
         <v>46107.60470481482</v>
@@ -10020,10 +10021,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I142" s="6"/>
       <c r="J142" s="5">
@@ -10039,13 +10040,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10055,7 +10056,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B143" s="8">
         <v>46107.60474207176</v>
@@ -10073,10 +10074,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I143" s="9"/>
       <c r="J143" s="8">
@@ -10092,13 +10093,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O143" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10108,7 +10109,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B144" s="5">
         <v>46107.6047731713</v>
@@ -10126,10 +10127,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I144" s="6"/>
       <c r="J144" s="5">
@@ -10145,13 +10146,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10161,7 +10162,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B145" s="8">
         <v>46077.820176724534</v>
@@ -10173,16 +10174,16 @@
         <v>46128.19730540509</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I145" s="8">
         <v>46101</v>
@@ -10200,13 +10201,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q145" s="8">
         <v>46101</v>
@@ -10226,7 +10227,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B146" s="5">
         <v>46107.60538978009</v>
@@ -10238,16 +10239,16 @@
         <v>46125.56117667824</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10263,13 +10264,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10279,7 +10280,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B147" s="8">
         <v>46107.60549119213</v>
@@ -10291,16 +10292,16 @@
         <v>46125.56118533565</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I147" s="9"/>
       <c r="J147" s="8">
@@ -10316,13 +10317,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
@@ -10332,7 +10333,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B148" s="5">
         <v>46107.60552758102</v>
@@ -10344,16 +10345,16 @@
         <v>46114.858808460645</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">
@@ -10369,13 +10370,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10385,7 +10386,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B149" s="8">
         <v>46107.60555978009</v>
@@ -10397,16 +10398,16 @@
         <v>46114.858710138884</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I149" s="9"/>
       <c r="J149" s="8">
@@ -10422,13 +10423,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10438,7 +10439,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B150" s="5">
         <v>46107.60568278935</v>
@@ -10450,16 +10451,16 @@
         <v>46109.73540881944</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I150" s="6"/>
       <c r="J150" s="5">
@@ -10475,13 +10476,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O150" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10491,7 +10492,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B151" s="8">
         <v>46107.605744953704</v>
@@ -10509,10 +10510,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I151" s="9"/>
       <c r="J151" s="8">
@@ -10528,13 +10529,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O151" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10544,7 +10545,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B152" s="5">
         <v>46107.60583027778</v>
@@ -10562,10 +10563,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I152" s="6"/>
       <c r="J152" s="5">
@@ -10581,13 +10582,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O152" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10597,7 +10598,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B153" s="8">
         <v>46107.60586805556</v>
@@ -10615,10 +10616,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H153" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I153" s="9"/>
       <c r="J153" s="8">
@@ -10634,13 +10635,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O153" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P153" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
@@ -10650,7 +10651,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B154" s="5">
         <v>46107.605905868055</v>
@@ -10668,10 +10669,10 @@
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I154" s="6"/>
       <c r="J154" s="5">
@@ -10687,13 +10688,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O154" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10703,7 +10704,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B155" s="8">
         <v>46077.820177013884</v>
@@ -10713,7 +10714,7 @@
         <v>46114.650831747684</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>25</v>
@@ -10737,7 +10738,7 @@
         <v>26</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P155" s="9" t="s">
         <v>26</v>
@@ -10750,7 +10751,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B156" s="5">
         <v>46077.82017730324</v>
@@ -10760,16 +10761,16 @@
         <v>46137.18802717593</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I156" s="5">
         <v>46128</v>
@@ -10787,13 +10788,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q156" s="5">
         <v>46128</v>
@@ -10808,12 +10809,12 @@
         <v>31</v>
       </c>
       <c r="U156" s="12" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B157" s="8">
         <v>46077.82017756945</v>
@@ -10823,16 +10824,16 @@
         <v>46137.18802714121</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H157" s="9" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I157" s="8">
         <v>46128</v>
@@ -10850,13 +10851,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P157" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q157" s="8">
         <v>46128</v>
@@ -10871,12 +10872,12 @@
         <v>31</v>
       </c>
       <c r="U157" s="12" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B158" s="5">
         <v>46090.88005357639</v>
@@ -10886,7 +10887,7 @@
         <v>46114.65100881945</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>25</v>
@@ -10910,7 +10911,7 @@
         <v>26</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>26</v>
@@ -10923,7 +10924,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B159" s="8">
         <v>46090.88038033565</v>
@@ -10933,7 +10934,7 @@
         <v>46137.18802715278</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
@@ -10960,13 +10961,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P159" s="9" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q159" s="8">
         <v>46128</v>
@@ -10981,12 +10982,12 @@
         <v>31</v>
       </c>
       <c r="U159" s="12" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B160" s="5">
         <v>46090.88062440972</v>
@@ -10996,7 +10997,7 @@
         <v>46137.18802714121</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -11023,13 +11024,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q160" s="5">
         <v>46128</v>
@@ -11044,7 +11045,7 @@
         <v>31</v>
       </c>
       <c r="U160" s="12" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001451 - ZITRON COLOMBIA.xlsx
+++ b/data/50001451 - ZITRON COLOMBIA.xlsx
@@ -10711,7 +10711,7 @@
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46114.650831747684</v>
+        <v>46232.710285810186</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>428</v>
@@ -10756,9 +10756,11 @@
       <c r="B156" s="5">
         <v>46077.82017730324</v>
       </c>
-      <c r="C156" s="6"/>
+      <c r="C156" s="5">
+        <v>46232.710263773144</v>
+      </c>
       <c r="D156" s="5">
-        <v>46137.18802717593</v>
+        <v>46232.71026662037</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>431</v>
@@ -10819,9 +10821,11 @@
       <c r="B157" s="8">
         <v>46077.82017756945</v>
       </c>
-      <c r="C157" s="9"/>
+      <c r="C157" s="8">
+        <v>46232.71028025463</v>
+      </c>
       <c r="D157" s="8">
-        <v>46137.18802714121</v>
+        <v>46232.71028196759</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>436</v>

--- a/data/50001451 - ZITRON COLOMBIA.xlsx
+++ b/data/50001451 - ZITRON COLOMBIA.xlsx
@@ -10709,9 +10709,11 @@
       <c r="B155" s="8">
         <v>46077.820177013884</v>
       </c>
-      <c r="C155" s="9"/>
+      <c r="C155" s="8">
+        <v>46237.55265341435</v>
+      </c>
       <c r="D155" s="8">
-        <v>46232.710285810186</v>
+        <v>46237.552655625</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>428</v>

--- a/data/50001451 - ZITRON COLOMBIA.xlsx
+++ b/data/50001451 - ZITRON COLOMBIA.xlsx
@@ -8527,7 +8527,7 @@
         <v>46121.840045046294</v>
       </c>
       <c r="D115" s="8">
-        <v>46225.80624795139</v>
+        <v>46237.56487802083</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>351</v>
@@ -8588,9 +8588,11 @@
       <c r="B116" s="5">
         <v>46107.6021821412</v>
       </c>
-      <c r="C116" s="6"/>
+      <c r="C116" s="5">
+        <v>46237.56487096065</v>
+      </c>
       <c r="D116" s="5">
-        <v>46225.80624259259</v>
+        <v>46237.56487265046</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>225</v>
@@ -9134,7 +9136,7 @@
         <v>46122.612434027775</v>
       </c>
       <c r="D126" s="5">
-        <v>46225.80624855324</v>
+        <v>46237.564880034726</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>225</v>

--- a/data/50001451 - ZITRON COLOMBIA.xlsx
+++ b/data/50001451 - ZITRON COLOMBIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="438">
   <si>
     <t>50001451 - ZITRON COLOMBIA</t>
   </si>
@@ -1261,7 +1261,7 @@
     <t>OT 4094 - ZVN 1-25-630/6,OT 4094 - ZVN 1-25-630/6,OT 4095 - ZVN 1-20-220/6,OT 4096 - ZVN 1-20-200/6,OT 4097- VDF 640 KW,OT 4098 - VDF 220KW,OT 4099 VDF 200KW,OT 4100- PLC 2XFN,OT 4101- PLC 1XFAN</t>
   </si>
   <si>
-    <t>Logistica:,Gestion,Costos,Instalación componentes,Pruebas de instalación Componentes,Instalación Componentes</t>
+    <t>Logistica:,Gestion,Costos,Instalación Componentes</t>
   </si>
   <si>
     <t>1213819468744590</t>
@@ -1325,27 +1325,6 @@
   </si>
   <si>
     <t>Despacho,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>1213576320894717</t>
-  </si>
-  <si>
-    <t>Puesta en Marcha Servicios</t>
-  </si>
-  <si>
-    <t>Instalación componentes,Pruebas de instalación Componentes</t>
-  </si>
-  <si>
-    <t>1213576320894719</t>
-  </si>
-  <si>
-    <t>Instalación componentes</t>
-  </si>
-  <si>
-    <t>1213576320894723</t>
-  </si>
-  <si>
-    <t>Pruebas de instalación Componentes</t>
   </si>
 </sst>
 </file>
@@ -1869,7 +1848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U160"/>
+  <dimension ref="A1:U157"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -10173,7 +10152,7 @@
         <v>46125.56089650463</v>
       </c>
       <c r="D145" s="8">
-        <v>46128.19730540509</v>
+        <v>46240.72264099537</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>414</v>
@@ -10880,179 +10859,6 @@
         <v>31</v>
       </c>
       <c r="U157" s="12" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="158" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A158" s="4" t="s">
-        <v>438</v>
-      </c>
-      <c r="B158" s="5">
-        <v>46090.88005357639</v>
-      </c>
-      <c r="C158" s="6"/>
-      <c r="D158" s="5">
-        <v>46114.65100881945</v>
-      </c>
-      <c r="E158" s="6" t="s">
-        <v>439</v>
-      </c>
-      <c r="F158" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G158" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H158" s="6"/>
-      <c r="I158" s="6"/>
-      <c r="J158" s="6"/>
-      <c r="K158" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L158" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M158" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N158" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O158" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="P158" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="6"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-    </row>
-    <row r="159" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A159" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="B159" s="8">
-        <v>46090.88038033565</v>
-      </c>
-      <c r="C159" s="9"/>
-      <c r="D159" s="8">
-        <v>46137.18802715278</v>
-      </c>
-      <c r="E159" s="9" t="s">
-        <v>442</v>
-      </c>
-      <c r="F159" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G159" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="H159" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="I159" s="8">
-        <v>46128</v>
-      </c>
-      <c r="J159" s="8">
-        <v>46136</v>
-      </c>
-      <c r="K159" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L159" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M159" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N159" s="9" t="s">
-        <v>439</v>
-      </c>
-      <c r="O159" s="9" t="s">
-        <v>414</v>
-      </c>
-      <c r="P159" s="9" t="s">
-        <v>439</v>
-      </c>
-      <c r="Q159" s="8">
-        <v>46128</v>
-      </c>
-      <c r="R159" s="8">
-        <v>46136</v>
-      </c>
-      <c r="S159" s="9">
-        <v>0</v>
-      </c>
-      <c r="T159" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U159" s="12" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="160" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A160" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="B160" s="5">
-        <v>46090.88062440972</v>
-      </c>
-      <c r="C160" s="6"/>
-      <c r="D160" s="5">
-        <v>46137.18802714121</v>
-      </c>
-      <c r="E160" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="F160" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G160" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H160" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I160" s="5">
-        <v>46128</v>
-      </c>
-      <c r="J160" s="5">
-        <v>46136</v>
-      </c>
-      <c r="K160" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L160" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M160" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N160" s="6" t="s">
-        <v>439</v>
-      </c>
-      <c r="O160" s="6" t="s">
-        <v>414</v>
-      </c>
-      <c r="P160" s="6" t="s">
-        <v>439</v>
-      </c>
-      <c r="Q160" s="5">
-        <v>46128</v>
-      </c>
-      <c r="R160" s="5">
-        <v>46136</v>
-      </c>
-      <c r="S160" s="6">
-        <v>0</v>
-      </c>
-      <c r="T160" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U160" s="12" t="s">
         <v>434</v>
       </c>
     </row>
